--- a/enlaces_equipos.xlsx
+++ b/enlaces_equipos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose-\Trabajo\statsFutbol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF14C381-3CDA-4C4A-80E3-1C2351578325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53AC76EC-A780-41A2-81F3-76B242781F97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" xr2:uid="{474EBA83-D6A0-4565-BEB0-BC6B2AA992C1}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="626">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="629">
   <si>
     <t>EQUIPO</t>
   </si>
@@ -768,9 +768,6 @@
     <t>europe/france/as-monaco-fc</t>
   </si>
   <si>
-    <t>europe/france/fc-nantes</t>
-  </si>
-  <si>
     <t>europe/france/ogc-nice</t>
   </si>
   <si>
@@ -867,9 +864,6 @@
     <t>europe/italy/udinese-calcio</t>
   </si>
   <si>
-    <t>europe/italy/hellas-verona-fc</t>
-  </si>
-  <si>
     <t>n-s-america/mexico/atletico-san-luis</t>
   </si>
   <si>
@@ -1470,21 +1464,12 @@
     <t>europe/germany/hamburger-sv</t>
   </si>
   <si>
-    <t>europe/italy/us-cremonese</t>
-  </si>
-  <si>
-    <t>europe/italy/ac-pisa-1909</t>
-  </si>
-  <si>
     <t>europe/italy/us-sassuolo-calcio</t>
   </si>
   <si>
     <t>europe/france/fc-lorient</t>
   </si>
   <si>
-    <t>europe/france/fc-metz</t>
-  </si>
-  <si>
     <t>europe/france/paris-fc</t>
   </si>
   <si>
@@ -1500,9 +1485,6 @@
     <t>europe/greece/aek-athens-fc</t>
   </si>
   <si>
-    <t>europe/greece/ael-fc</t>
-  </si>
-  <si>
     <t>europe/greece/aris-thessaloniki-fc</t>
   </si>
   <si>
@@ -1530,9 +1512,6 @@
     <t>europe/greece/panetolikos-fc</t>
   </si>
   <si>
-    <t>europe/greece/panserraikos-fc</t>
-  </si>
-  <si>
     <t>europe/greece/paok-fc</t>
   </si>
   <si>
@@ -1936,6 +1915,36 @@
   </si>
   <si>
     <t>europe/spain/cd-tenerife</t>
+  </si>
+  <si>
+    <t>europe/france/le-mans-fc</t>
+  </si>
+  <si>
+    <t>europe/france/troyes-ac</t>
+  </si>
+  <si>
+    <t>europe/germany/sv-elversberg</t>
+  </si>
+  <si>
+    <t>europe/germany/sc-paderborn</t>
+  </si>
+  <si>
+    <t>europe/germany/schalke-04</t>
+  </si>
+  <si>
+    <t>europe/greece/iraklis-fc</t>
+  </si>
+  <si>
+    <t>europe/greece/kalamata-fc</t>
+  </si>
+  <si>
+    <t>europe/italy/frosinone-calcio</t>
+  </si>
+  <si>
+    <t>europe/italy/ac-monza</t>
+  </si>
+  <si>
+    <t>europe/italy/venezia-fc</t>
   </si>
 </sst>
 </file>
@@ -2443,10 +2452,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>584</v>
+        <v>577</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>531</v>
+        <v>524</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -2481,7 +2490,7 @@
         <v>46227</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -2547,7 +2556,7 @@
         <v>46237</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
@@ -2581,7 +2590,7 @@
         <v>46241</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
@@ -2615,7 +2624,7 @@
         <v>46050</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -2649,7 +2658,7 @@
         <v>46224</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
@@ -2683,7 +2692,7 @@
         <v>46052</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
@@ -2717,7 +2726,7 @@
         <v>46230</v>
       </c>
       <c r="K9" s="9" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
@@ -2751,7 +2760,7 @@
         <v>46235</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
@@ -2785,7 +2794,7 @@
         <v>46231</v>
       </c>
       <c r="K11" s="9" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
@@ -2819,7 +2828,7 @@
         <v>46230</v>
       </c>
       <c r="K12" s="9" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -2828,7 +2837,7 @@
         <v>estudiantes-de-rio-cuarto</v>
       </c>
       <c r="B13" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="C13" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -2853,7 +2862,7 @@
         <v>46220</v>
       </c>
       <c r="K13" s="9" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -2887,7 +2896,7 @@
         <v>46252</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
@@ -2896,7 +2905,7 @@
         <v>club-gimnasia-de-mendoza</v>
       </c>
       <c r="B15" t="s">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="C15" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -2921,7 +2930,7 @@
         <v>46116</v>
       </c>
       <c r="K15" s="9" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
@@ -2949,12 +2958,14 @@
       </c>
       <c r="I16" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>X</v>
       </c>
       <c r="J16" s="10">
         <v>46258</v>
       </c>
-      <c r="K16" s="9"/>
+      <c r="K16" s="9" t="s">
+        <v>525</v>
+      </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="str">
@@ -2986,7 +2997,9 @@
       <c r="J17" s="10">
         <v>46244</v>
       </c>
-      <c r="K17" s="9"/>
+      <c r="K17" s="9" t="s">
+        <v>525</v>
+      </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="str">
@@ -3013,12 +3026,14 @@
       </c>
       <c r="I18" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>X</v>
       </c>
       <c r="J18" s="10">
         <v>46257</v>
       </c>
-      <c r="K18" s="9"/>
+      <c r="K18" s="9" t="s">
+        <v>525</v>
+      </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="str">
@@ -3045,12 +3060,14 @@
       </c>
       <c r="I19" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>X</v>
       </c>
       <c r="J19" s="10">
         <v>46259</v>
       </c>
-      <c r="K19" s="9"/>
+      <c r="K19" s="9" t="s">
+        <v>525</v>
+      </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="str">
@@ -3083,7 +3100,7 @@
         <v>46220</v>
       </c>
       <c r="K20" s="9" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
@@ -3117,7 +3134,7 @@
         <v>46244</v>
       </c>
       <c r="K21" s="9" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
@@ -3151,7 +3168,7 @@
         <v>46095</v>
       </c>
       <c r="K22" s="9" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
@@ -3185,7 +3202,7 @@
         <v>46223</v>
       </c>
       <c r="K23" s="9" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
@@ -3219,7 +3236,7 @@
         <v>46231</v>
       </c>
       <c r="K24" s="9" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
@@ -3253,7 +3270,7 @@
         <v>46243</v>
       </c>
       <c r="K25" s="9" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
@@ -3287,7 +3304,7 @@
         <v>46224</v>
       </c>
       <c r="K26" s="9" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
@@ -3321,7 +3338,7 @@
         <v>46242</v>
       </c>
       <c r="K27" s="9" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
@@ -3355,7 +3372,7 @@
         <v>46238</v>
       </c>
       <c r="K28" s="9" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
@@ -3389,7 +3406,7 @@
         <v>46252</v>
       </c>
       <c r="K29" s="9" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
@@ -3423,7 +3440,7 @@
         <v>46229</v>
       </c>
       <c r="K30" s="9" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
@@ -3457,7 +3474,7 @@
         <v>46230</v>
       </c>
       <c r="K31" s="9" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
@@ -3466,7 +3483,7 @@
         <v>adelaide-united-fc</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="C32" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3491,7 +3508,7 @@
         <v>46074</v>
       </c>
       <c r="K32" s="9" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
@@ -3500,7 +3517,7 @@
         <v>auckland-fc</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="C33" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3525,7 +3542,7 @@
         <v>46121</v>
       </c>
       <c r="K33" s="9" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
@@ -3534,7 +3551,7 @@
         <v>brisbane-roar-fc</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="C34" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3559,7 +3576,7 @@
         <v>46121</v>
       </c>
       <c r="K34" s="9" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
@@ -3568,7 +3585,7 @@
         <v>central-coast-mariners-fc</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="C35" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3593,7 +3610,7 @@
         <v>macarthur-fc</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="C36" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3614,7 +3631,7 @@
         <v>melbourne-city-fc</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="C37" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3635,7 +3652,7 @@
         <v>melbourne-victory-fc</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="C38" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3656,7 +3673,7 @@
         <v>newcastle-jets-fc</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="C39" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3677,7 +3694,7 @@
         <v>perth-glory-fc</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="C40" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3698,7 +3715,7 @@
         <v>sydney-fc</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="C41" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3719,7 +3736,7 @@
         <v>wellington-phoenix-fc</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="C42" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3740,7 +3757,7 @@
         <v>western-sydney-wanderers-fc</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="C43" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3761,7 +3778,7 @@
         <v>sc-austria-lustenau</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>587</v>
+        <v>580</v>
       </c>
       <c r="C44" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4055,7 +4072,7 @@
         <v>sk-beveren</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="C58" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4181,7 +4198,7 @@
         <v>kv-kortrijk</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>611</v>
+        <v>604</v>
       </c>
       <c r="C64" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4244,7 +4261,7 @@
         <v>lommel-sk</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>612</v>
+        <v>605</v>
       </c>
       <c r="C67" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4349,7 +4366,7 @@
         <v>club-athletico-paranaense</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="C72" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4454,7 +4471,7 @@
         <v>associacao-chapecoense-de-futebol</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="C77" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4496,7 +4513,7 @@
         <v>coritiba-football-club</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>538</v>
+        <v>531</v>
       </c>
       <c r="C79" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4664,7 +4681,7 @@
         <v>clube-do-remo</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="C87" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4895,7 +4912,7 @@
         <v>fc-dunav-ruse</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="C98" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5147,7 +5164,7 @@
         <v>deportes-concepcion</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="C110" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5378,7 +5395,7 @@
         <v>cd-universidad-de-concepcion</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="C121" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5525,7 +5542,7 @@
         <v>cucuta-deportivo-fc</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="C128" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5609,7 +5626,7 @@
         <v>internacional-de-bogota</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="C132" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5630,7 +5647,7 @@
         <v>jaguares-de-cordoba</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="C133" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5966,7 +5983,7 @@
         <v>nk-rudes</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="C149" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6029,7 +6046,7 @@
         <v>sk-artis-brno</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="C152" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6071,7 +6088,7 @@
         <v>fc-zbrojovka-brno</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="C154" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6428,7 +6445,7 @@
         <v>ac-horsens</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="C171" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6449,7 +6466,7 @@
         <v>lyngby-bk</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="C172" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6617,7 +6634,7 @@
         <v>sd-aucas</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="C180" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6638,7 +6655,7 @@
         <v>barcelona-sc</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="C181" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6659,7 +6676,7 @@
         <v>delfin-sc</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="C182" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6680,7 +6697,7 @@
         <v>cd-cuenca</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="C183" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6701,7 +6718,7 @@
         <v>cs-emelec</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="C184" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6722,7 +6739,7 @@
         <v>guayaquil-city-fc</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="C185" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6743,7 +6760,7 @@
         <v>csd-independiente-del-valle</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C186" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6764,7 +6781,7 @@
         <v>ldu-quito</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="C187" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6785,7 +6802,7 @@
         <v>leones-fc</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="C188" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6806,7 +6823,7 @@
         <v>libertad-fc</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="C189" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6827,7 +6844,7 @@
         <v>csd-macara</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="C190" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6848,7 +6865,7 @@
         <v>manta-fc</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="C191" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6869,7 +6886,7 @@
         <v>mushuc-runa-sc</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="C192" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6890,7 +6907,7 @@
         <v>orense-sc</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="C193" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6911,7 +6928,7 @@
         <v>tecnico-universitario</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="C194" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6932,7 +6949,7 @@
         <v>cd-universidad-catolica</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="C195" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7380,7 +7397,7 @@
         <v>england</v>
       </c>
       <c r="D216" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="E216" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -7400,7 +7417,7 @@
         <v>england</v>
       </c>
       <c r="D217" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="E217" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -7413,14 +7430,14 @@
         <v>bolton-wanderers-fc</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>613</v>
+        <v>606</v>
       </c>
       <c r="C218" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>england</v>
       </c>
       <c r="D218" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="E218" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -7440,7 +7457,7 @@
         <v>england</v>
       </c>
       <c r="D219" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="E219" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -7460,7 +7477,7 @@
         <v>england</v>
       </c>
       <c r="D220" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="E220" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -7473,14 +7490,14 @@
         <v>cardiff-city-fc</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>614</v>
+        <v>607</v>
       </c>
       <c r="C221" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>england</v>
       </c>
       <c r="D221" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="E221" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -7500,7 +7517,7 @@
         <v>england</v>
       </c>
       <c r="D222" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="E222" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -7520,7 +7537,7 @@
         <v>england</v>
       </c>
       <c r="D223" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="E223" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -7533,14 +7550,14 @@
         <v>lincoln-city-fc</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>615</v>
+        <v>608</v>
       </c>
       <c r="C224" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>england</v>
       </c>
       <c r="D224" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="E224" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -7560,7 +7577,7 @@
         <v>england</v>
       </c>
       <c r="D225" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="E225" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -7580,7 +7597,7 @@
         <v>england</v>
       </c>
       <c r="D226" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="E226" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -7600,7 +7617,7 @@
         <v>england</v>
       </c>
       <c r="D227" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="E227" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -7620,7 +7637,7 @@
         <v>england</v>
       </c>
       <c r="D228" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="E228" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -7640,7 +7657,7 @@
         <v>england</v>
       </c>
       <c r="D229" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="E229" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -7660,7 +7677,7 @@
         <v>england</v>
       </c>
       <c r="D230" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="E230" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -7680,7 +7697,7 @@
         <v>england</v>
       </c>
       <c r="D231" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="E231" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -7700,7 +7717,7 @@
         <v>england</v>
       </c>
       <c r="D232" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="E232" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -7720,7 +7737,7 @@
         <v>england</v>
       </c>
       <c r="D233" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="E233" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -7740,7 +7757,7 @@
         <v>england</v>
       </c>
       <c r="D234" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="E234" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -7760,7 +7777,7 @@
         <v>england</v>
       </c>
       <c r="D235" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="E235" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -7780,7 +7797,7 @@
         <v>england</v>
       </c>
       <c r="D236" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="E236" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -7800,7 +7817,7 @@
         <v>england</v>
       </c>
       <c r="D237" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="E237" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -7820,7 +7837,7 @@
         <v>england</v>
       </c>
       <c r="D238" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="E238" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -7840,7 +7857,7 @@
         <v>england</v>
       </c>
       <c r="D239" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="E239" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -7853,7 +7870,7 @@
         <v>if-gnistan</v>
       </c>
       <c r="B240" s="5" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="C240" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7874,7 +7891,7 @@
         <v>hjk-helsinki</v>
       </c>
       <c r="B241" s="5" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="C241" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7895,7 +7912,7 @@
         <v>fc-ilves</v>
       </c>
       <c r="B242" s="5" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="C242" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7916,7 +7933,7 @@
         <v>fc-inter-turku</v>
       </c>
       <c r="B243" s="5" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="C243" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7937,7 +7954,7 @@
         <v>ff-jaro</v>
       </c>
       <c r="B244" s="5" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="C244" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7958,7 +7975,7 @@
         <v>kuopion-palloseura</v>
       </c>
       <c r="B245" s="5" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="C245" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7979,7 +7996,7 @@
         <v>fc-lahti</v>
       </c>
       <c r="B246" s="5" t="s">
-        <v>582</v>
+        <v>575</v>
       </c>
       <c r="C246" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8000,7 +8017,7 @@
         <v>ifk-mariehamn</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="C247" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8021,7 +8038,7 @@
         <v>ac-oulu</v>
       </c>
       <c r="B248" s="5" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="C248" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8042,7 +8059,7 @@
         <v>sjk</v>
       </c>
       <c r="B249" s="5" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="C249" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8063,7 +8080,7 @@
         <v>tps-turku</v>
       </c>
       <c r="B250" s="5" t="s">
-        <v>583</v>
+        <v>576</v>
       </c>
       <c r="C250" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8084,7 +8101,7 @@
         <v>vaasan-palloseura</v>
       </c>
       <c r="B251" s="5" t="s">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="C251" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8117,7 +8134,7 @@
       </c>
       <c r="E252" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.3">
@@ -8138,7 +8155,7 @@
       </c>
       <c r="E253" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.3">
@@ -8159,7 +8176,7 @@
       </c>
       <c r="E254" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.3">
@@ -8180,16 +8197,16 @@
       </c>
       <c r="E255" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A256" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>rc-lens</v>
+        <v>le-mans-fc</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>231</v>
+        <v>619</v>
       </c>
       <c r="C256" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8201,16 +8218,16 @@
       </c>
       <c r="E256" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A257" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>lille-osc</v>
+        <v>rc-lens</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C257" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8222,16 +8239,16 @@
       </c>
       <c r="E257" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A258" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-lorient</v>
+        <v>lille-osc</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>473</v>
+        <v>232</v>
       </c>
       <c r="C258" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8243,16 +8260,16 @@
       </c>
       <c r="E258" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A259" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>olympique-lyonnais</v>
+        <v>fc-lorient</v>
       </c>
       <c r="B259" s="5" t="s">
-        <v>233</v>
+        <v>469</v>
       </c>
       <c r="C259" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8264,16 +8281,16 @@
       </c>
       <c r="E259" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A260" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>olympique-de-marseille</v>
+        <v>olympique-lyonnais</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C260" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8285,16 +8302,16 @@
       </c>
       <c r="E260" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A261" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-metz</v>
+        <v>olympique-de-marseille</v>
       </c>
       <c r="B261" s="5" t="s">
-        <v>474</v>
+        <v>234</v>
       </c>
       <c r="C261" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8306,7 +8323,7 @@
       </c>
       <c r="E261" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.3">
@@ -8327,13 +8344,13 @@
       </c>
       <c r="E262" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A263" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-nantes</v>
+        <v>ogc-nice</v>
       </c>
       <c r="B263" s="5" t="s">
         <v>236</v>
@@ -8348,16 +8365,16 @@
       </c>
       <c r="E263" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A264" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ogc-nice</v>
+        <v>paris-fc</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>237</v>
+        <v>470</v>
       </c>
       <c r="C264" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8369,16 +8386,16 @@
       </c>
       <c r="E264" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A265" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>paris-fc</v>
+        <v>paris-saint-germain-fc</v>
       </c>
       <c r="B265" s="5" t="s">
-        <v>475</v>
+        <v>237</v>
       </c>
       <c r="C265" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8390,13 +8407,13 @@
       </c>
       <c r="E265" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A266" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>paris-saint-germain-fc</v>
+        <v>stade-rennais-fc</v>
       </c>
       <c r="B266" s="2" t="s">
         <v>238</v>
@@ -8411,13 +8428,13 @@
       </c>
       <c r="E266" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A267" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>stade-rennais-fc</v>
+        <v>rc-strasbourg-alsace</v>
       </c>
       <c r="B267" s="5" t="s">
         <v>239</v>
@@ -8432,13 +8449,13 @@
       </c>
       <c r="E267" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A268" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>rc-strasbourg-alsace</v>
+        <v>toulouse-fc</v>
       </c>
       <c r="B268" s="2" t="s">
         <v>240</v>
@@ -8453,16 +8470,16 @@
       </c>
       <c r="E268" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A269" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>toulouse-fc</v>
+        <v>troyes-ac</v>
       </c>
       <c r="B269" s="5" t="s">
-        <v>241</v>
+        <v>620</v>
       </c>
       <c r="C269" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8474,7 +8491,7 @@
       </c>
       <c r="E269" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.3">
@@ -8564,10 +8581,10 @@
     <row r="274" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A274" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-koln</v>
+        <v>sv-elversberg</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>468</v>
+        <v>621</v>
       </c>
       <c r="C274" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8585,10 +8602,10 @@
     <row r="275" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A275" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>eintracht-frankfurt</v>
+        <v>fc-koln</v>
       </c>
       <c r="B275" s="5" t="s">
-        <v>65</v>
+        <v>466</v>
       </c>
       <c r="C275" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8606,10 +8623,10 @@
     <row r="276" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A276" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>sc-freiburg</v>
+        <v>eintracht-frankfurt</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C276" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8627,10 +8644,10 @@
     <row r="277" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A277" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>hamburger-sv</v>
+        <v>sc-freiburg</v>
       </c>
       <c r="B277" s="5" t="s">
-        <v>469</v>
+        <v>66</v>
       </c>
       <c r="C277" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8648,10 +8665,10 @@
     <row r="278" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A278" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-heidenheim</v>
+        <v>hamburger-sv</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>67</v>
+        <v>467</v>
       </c>
       <c r="C278" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8753,10 +8770,10 @@
     <row r="283" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A283" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>rb-leipzig</v>
+        <v>sc-paderborn</v>
       </c>
       <c r="B283" s="5" t="s">
-        <v>73</v>
+        <v>622</v>
       </c>
       <c r="C283" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8774,10 +8791,10 @@
     <row r="284" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A284" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-st-pauli</v>
+        <v>rb-leipzig</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C284" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8795,10 +8812,10 @@
     <row r="285" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A285" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>vfb-stuttgart</v>
+        <v>schalke-04</v>
       </c>
       <c r="B285" s="5" t="s">
-        <v>75</v>
+        <v>623</v>
       </c>
       <c r="C285" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8816,10 +8833,10 @@
     <row r="286" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A286" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>union-berlin</v>
+        <v>vfb-stuttgart</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C286" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8837,10 +8854,10 @@
     <row r="287" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A287" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>vfl-wolfsburg</v>
+        <v>union-berlin</v>
       </c>
       <c r="B287" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C287" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8861,7 +8878,7 @@
         <v>arminia-bielefeld</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C288" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8903,7 +8920,7 @@
         <v>eintracht-braunschweig</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C290" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8924,7 +8941,7 @@
         <v>fc-energie-cottbus</v>
       </c>
       <c r="B291" s="5" t="s">
-        <v>602</v>
+        <v>595</v>
       </c>
       <c r="C291" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8945,7 +8962,7 @@
         <v>darmstadt-98</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C292" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8966,7 +8983,7 @@
         <v>dynamo-dresden</v>
       </c>
       <c r="B293" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C293" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8987,7 +9004,7 @@
         <v>greuther-furth</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C294" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9008,7 +9025,7 @@
         <v>hannover-96</v>
       </c>
       <c r="B295" s="5" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C295" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9050,7 +9067,7 @@
         <v>hertha-berlin</v>
       </c>
       <c r="B297" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C297" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9071,7 +9088,7 @@
         <v>fc-kaiserslautern</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C298" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9092,7 +9109,7 @@
         <v>karlsruher-sc</v>
       </c>
       <c r="B299" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C299" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9134,7 +9151,7 @@
         <v>fc-magdeburg</v>
       </c>
       <c r="B301" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C301" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9155,7 +9172,7 @@
         <v>fc-nurnberg</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C302" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9176,7 +9193,7 @@
         <v>vfl-osnabruck</v>
       </c>
       <c r="B303" s="5" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="C303" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9239,7 +9256,7 @@
         <v>aek-athens-fc</v>
       </c>
       <c r="B306" s="5" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="C306" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9251,16 +9268,16 @@
       </c>
       <c r="E306" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A307" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ael-fc</v>
+        <v>aris-thessaloniki-fc</v>
       </c>
       <c r="B307" s="5" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="C307" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9272,16 +9289,16 @@
       </c>
       <c r="E307" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A308" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>aris-thessaloniki-fc</v>
+        <v>asteras-tripolis-fc</v>
       </c>
       <c r="B308" s="5" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="C308" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9293,16 +9310,16 @@
       </c>
       <c r="E308" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A309" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>asteras-tripolis-fc</v>
+        <v>atromitos-fc</v>
       </c>
       <c r="B309" s="5" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="C309" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9314,16 +9331,16 @@
       </c>
       <c r="E309" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A310" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>atromitos-fc</v>
+        <v>iraklis-fc</v>
       </c>
       <c r="B310" s="5" t="s">
-        <v>483</v>
+        <v>624</v>
       </c>
       <c r="C310" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9335,16 +9352,16 @@
       </c>
       <c r="E310" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A311" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ae-kifisia-fc</v>
+        <v>kalamata-fc</v>
       </c>
       <c r="B311" s="5" t="s">
-        <v>484</v>
+        <v>625</v>
       </c>
       <c r="C311" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9356,16 +9373,16 @@
       </c>
       <c r="E311" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A312" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>levadiakos-fc</v>
+        <v>ae-kifisia-fc</v>
       </c>
       <c r="B312" s="5" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="C312" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9377,16 +9394,16 @@
       </c>
       <c r="E312" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A313" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ofi-crete-fc</v>
+        <v>levadiakos-fc</v>
       </c>
       <c r="B313" s="5" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="C313" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9398,16 +9415,16 @@
       </c>
       <c r="E313" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A314" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>olympiacos-fc</v>
+        <v>ofi-crete-fc</v>
       </c>
       <c r="B314" s="5" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="C314" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9419,16 +9436,16 @@
       </c>
       <c r="E314" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A315" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>panathinaikos-fc</v>
+        <v>olympiacos-fc</v>
       </c>
       <c r="B315" s="5" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="C315" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9440,16 +9457,16 @@
       </c>
       <c r="E315" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A316" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>panetolikos-fc</v>
+        <v>panathinaikos-fc</v>
       </c>
       <c r="B316" s="5" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="C316" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9461,16 +9478,16 @@
       </c>
       <c r="E316" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A317" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>panserraikos-fc</v>
+        <v>panetolikos-fc</v>
       </c>
       <c r="B317" s="5" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C317" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9482,7 +9499,7 @@
       </c>
       <c r="E317" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.3">
@@ -9491,7 +9508,7 @@
         <v>paok-fc</v>
       </c>
       <c r="B318" s="5" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="C318" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9503,7 +9520,7 @@
       </c>
       <c r="E318" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.3">
@@ -9512,7 +9529,7 @@
         <v>volos-fc</v>
       </c>
       <c r="B319" s="5" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="C319" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9524,7 +9541,7 @@
       </c>
       <c r="E319" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.3">
@@ -9533,7 +9550,7 @@
         <v>ac-milan</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C320" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9545,7 +9562,7 @@
       </c>
       <c r="E320" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.3">
@@ -9554,7 +9571,7 @@
         <v>as-roma</v>
       </c>
       <c r="B321" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C321" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9566,7 +9583,7 @@
       </c>
       <c r="E321" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.3">
@@ -9575,7 +9592,7 @@
         <v>atalanta-bc</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C322" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9587,7 +9604,7 @@
       </c>
       <c r="E322" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.3">
@@ -9596,7 +9613,7 @@
         <v>bologna-fc-1909</v>
       </c>
       <c r="B323" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C323" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9608,7 +9625,7 @@
       </c>
       <c r="E323" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.3">
@@ -9617,7 +9634,7 @@
         <v>cagliari-calcio</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C324" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9629,7 +9646,7 @@
       </c>
       <c r="E324" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.3">
@@ -9638,7 +9655,7 @@
         <v>como-1907</v>
       </c>
       <c r="B325" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C325" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9650,16 +9667,16 @@
       </c>
       <c r="E325" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A326" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>us-cremonese</v>
+        <v>acf-fiorentina</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>470</v>
+        <v>258</v>
       </c>
       <c r="C326" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9671,16 +9688,16 @@
       </c>
       <c r="E326" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A327" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>acf-fiorentina</v>
+        <v>frosinone-calcio</v>
       </c>
       <c r="B327" s="5" t="s">
-        <v>259</v>
+        <v>626</v>
       </c>
       <c r="C327" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9692,7 +9709,7 @@
       </c>
       <c r="E327" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.3">
@@ -9701,7 +9718,7 @@
         <v>genoa-cfc</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C328" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9713,7 +9730,7 @@
       </c>
       <c r="E328" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.3">
@@ -9722,7 +9739,7 @@
         <v>inter-milan</v>
       </c>
       <c r="B329" s="5" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C329" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9734,7 +9751,7 @@
       </c>
       <c r="E329" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.3">
@@ -9743,7 +9760,7 @@
         <v>juventus-fc</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C330" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9755,7 +9772,7 @@
       </c>
       <c r="E330" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.3">
@@ -9764,7 +9781,7 @@
         <v>ss-lazio</v>
       </c>
       <c r="B331" s="5" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C331" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9776,7 +9793,7 @@
       </c>
       <c r="E331" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.3">
@@ -9785,7 +9802,7 @@
         <v>us-lecce</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C332" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9797,16 +9814,16 @@
       </c>
       <c r="E332" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A333" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ssc-napoli</v>
+        <v>ac-monza</v>
       </c>
       <c r="B333" s="5" t="s">
-        <v>265</v>
+        <v>627</v>
       </c>
       <c r="C333" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9818,16 +9835,16 @@
       </c>
       <c r="E333" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A334" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>parma-calcio-1913</v>
+        <v>ssc-napoli</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C334" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9839,16 +9856,16 @@
       </c>
       <c r="E334" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A335" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ac-pisa-1909</v>
+        <v>parma-calcio-1913</v>
       </c>
       <c r="B335" s="5" t="s">
-        <v>471</v>
+        <v>265</v>
       </c>
       <c r="C335" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9860,7 +9877,7 @@
       </c>
       <c r="E335" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.3">
@@ -9869,7 +9886,7 @@
         <v>us-sassuolo-calcio</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="C336" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9881,7 +9898,7 @@
       </c>
       <c r="E336" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.3">
@@ -9890,7 +9907,7 @@
         <v>torino-fc</v>
       </c>
       <c r="B337" s="5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C337" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9902,7 +9919,7 @@
       </c>
       <c r="E337" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.3">
@@ -9911,7 +9928,7 @@
         <v>udinese-calcio</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C338" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9923,16 +9940,16 @@
       </c>
       <c r="E338" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A339" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>hellas-verona-fc</v>
+        <v>venezia-fc</v>
       </c>
       <c r="B339" s="5" t="s">
-        <v>269</v>
+        <v>628</v>
       </c>
       <c r="C339" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9944,7 +9961,7 @@
       </c>
       <c r="E339" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.3">
@@ -9953,7 +9970,7 @@
         <v>atletico-san-luis</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C340" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9974,7 +9991,7 @@
         <v>atlas-fc</v>
       </c>
       <c r="B341" s="5" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C341" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9995,7 +10012,7 @@
         <v>club-america</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C342" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10016,7 +10033,7 @@
         <v>cruz-azul</v>
       </c>
       <c r="B343" s="5" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C343" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10037,7 +10054,7 @@
         <v>cd-guadalajara</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C344" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10058,7 +10075,7 @@
         <v>fc-juarez</v>
       </c>
       <c r="B345" s="5" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C345" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10079,7 +10096,7 @@
         <v>club-leon</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C346" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10100,7 +10117,7 @@
         <v>mazatlan-fc</v>
       </c>
       <c r="B347" s="5" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C347" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10121,7 +10138,7 @@
         <v>cf-monterrey</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C348" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10142,7 +10159,7 @@
         <v>club-necaxa</v>
       </c>
       <c r="B349" s="5" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C349" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10163,7 +10180,7 @@
         <v>cf-pachuca</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C350" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10184,7 +10201,7 @@
         <v>club-puebla</v>
       </c>
       <c r="B351" s="5" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C351" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10205,7 +10222,7 @@
         <v>queretaro-fc</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C352" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10226,7 +10243,7 @@
         <v>santos-laguna</v>
       </c>
       <c r="B353" s="5" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C353" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10247,7 +10264,7 @@
         <v>tigres-uanl</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C354" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10268,7 +10285,7 @@
         <v>club-tijuana</v>
       </c>
       <c r="B355" s="5" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C355" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10289,7 +10306,7 @@
         <v>deportivo-toluca-fc</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C356" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10310,7 +10327,7 @@
         <v>unam</v>
       </c>
       <c r="B357" s="5" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C357" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10331,7 +10348,7 @@
         <v>afc-ajax</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C358" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10352,7 +10369,7 @@
         <v>az-alkmaar</v>
       </c>
       <c r="B359" s="5" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C359" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10373,7 +10390,7 @@
         <v>sc-cambuur</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>604</v>
+        <v>597</v>
       </c>
       <c r="C360" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10394,7 +10411,7 @@
         <v>ado-den-haag</v>
       </c>
       <c r="B361" s="5" t="s">
-        <v>605</v>
+        <v>598</v>
       </c>
       <c r="C361" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10415,7 +10432,7 @@
         <v>sbv-excelsior</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C362" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10436,7 +10453,7 @@
         <v>feyenoord-rotterdam</v>
       </c>
       <c r="B363" s="5" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C363" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10457,7 +10474,7 @@
         <v>go-ahead-eagles</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C364" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10478,7 +10495,7 @@
         <v>fc-groningen</v>
       </c>
       <c r="B365" s="5" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C365" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10499,7 +10516,7 @@
         <v>sc-heerenveen</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C366" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10520,7 +10537,7 @@
         <v>nec-nijmegen</v>
       </c>
       <c r="B367" s="5" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C367" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10541,7 +10558,7 @@
         <v>psv-eindhoven</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C368" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10562,7 +10579,7 @@
         <v>fortuna-sittard</v>
       </c>
       <c r="B369" s="5" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C369" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10583,7 +10600,7 @@
         <v>sparta-rotterdam</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C370" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10604,7 +10621,7 @@
         <v>sc-telstar</v>
       </c>
       <c r="B371" s="5" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C371" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10625,7 +10642,7 @@
         <v>fc-twente</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C372" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10646,7 +10663,7 @@
         <v>fc-utrecht</v>
       </c>
       <c r="B373" s="5" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C373" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10667,7 +10684,7 @@
         <v>willem-ii</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>606</v>
+        <v>599</v>
       </c>
       <c r="C374" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10688,7 +10705,7 @@
         <v>pec-zwolle</v>
       </c>
       <c r="B375" s="5" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C375" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10709,7 +10726,7 @@
         <v>aalesunds-fk</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="C376" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10730,7 +10747,7 @@
         <v>fk-bodo-glimt</v>
       </c>
       <c r="B377" s="5" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C377" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10751,7 +10768,7 @@
         <v>sk-brann</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C378" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10772,7 +10789,7 @@
         <v>fredrikstad-fk</v>
       </c>
       <c r="B379" s="5" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C379" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10793,7 +10810,7 @@
         <v>ham-kam</v>
       </c>
       <c r="B380" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C380" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10814,7 +10831,7 @@
         <v>kfum-kameratene-oslo</v>
       </c>
       <c r="B381" s="5" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C381" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10835,7 +10852,7 @@
         <v>kristiansund-bk</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C382" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10856,7 +10873,7 @@
         <v>lillestrom-sk</v>
       </c>
       <c r="B383" s="5" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="C383" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10877,7 +10894,7 @@
         <v>molde-fk</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C384" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10898,7 +10915,7 @@
         <v>rosenborg-bk</v>
       </c>
       <c r="B385" s="5" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C385" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10919,7 +10936,7 @@
         <v>sandefjord-fotball</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C386" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10940,7 +10957,7 @@
         <v>sarpsborg-08-ff</v>
       </c>
       <c r="B387" s="5" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C387" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10961,7 +10978,7 @@
         <v>ik-start</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>618</v>
+        <v>611</v>
       </c>
       <c r="C388" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10982,7 +10999,7 @@
         <v>tromso-il</v>
       </c>
       <c r="B389" s="5" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C389" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11003,7 +11020,7 @@
         <v>valerenga-fotball</v>
       </c>
       <c r="B390" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C390" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11024,7 +11041,7 @@
         <v>viking-fk</v>
       </c>
       <c r="B391" s="5" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C391" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11045,7 +11062,7 @@
         <v>alianza-lima</v>
       </c>
       <c r="B392" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C392" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11066,7 +11083,7 @@
         <v>asociacion-deportiva-tarma</v>
       </c>
       <c r="B393" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C393" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11087,7 +11104,7 @@
         <v>alianza-atletico</v>
       </c>
       <c r="B394" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C394" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11108,7 +11125,7 @@
         <v>universidad-tecnica-de-cajamarca</v>
       </c>
       <c r="B395" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C395" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11129,7 +11146,7 @@
         <v>club-sportivo-cienciano</v>
       </c>
       <c r="B396" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C396" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11150,7 +11167,7 @@
         <v>comerciantes-unidos</v>
       </c>
       <c r="B397" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C397" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11171,7 +11188,7 @@
         <v>cusco-fc</v>
       </c>
       <c r="B398" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C398" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11192,7 +11209,7 @@
         <v>deportivo-garcilaso</v>
       </c>
       <c r="B399" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C399" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11213,7 +11230,7 @@
         <v>fc-cajamarca</v>
       </c>
       <c r="B400" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="C400" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11234,7 +11251,7 @@
         <v>atletico-grau</v>
       </c>
       <c r="B401" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C401" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11255,7 +11272,7 @@
         <v>sport-huancayo</v>
       </c>
       <c r="B402" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C402" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11276,7 +11293,7 @@
         <v>adc-juan-pablo-ii-college</v>
       </c>
       <c r="B403" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C403" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11297,7 +11314,7 @@
         <v>los-chankas-cyc</v>
       </c>
       <c r="B404" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C404" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11318,7 +11335,7 @@
         <v>fbc-melgar</v>
       </c>
       <c r="B405" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C405" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11339,7 +11356,7 @@
         <v>club-deportivo-moquegua</v>
       </c>
       <c r="B406" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="C406" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11360,7 +11377,7 @@
         <v>sport-boys</v>
       </c>
       <c r="B407" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C407" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11381,7 +11398,7 @@
         <v>sporting-cristal</v>
       </c>
       <c r="B408" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C408" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11402,7 +11419,7 @@
         <v>club-universitario-de-deportes</v>
       </c>
       <c r="B409" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C409" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11423,7 +11440,7 @@
         <v>cracovia</v>
       </c>
       <c r="B410" s="5" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C410" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11444,7 +11461,7 @@
         <v>gornik-zabrze</v>
       </c>
       <c r="B411" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C411" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11465,7 +11482,7 @@
         <v>jagiellona-bialystok</v>
       </c>
       <c r="B412" s="5" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C412" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11486,7 +11503,7 @@
         <v>gks-katowice</v>
       </c>
       <c r="B413" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C413" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11507,7 +11524,7 @@
         <v>korona-kielce</v>
       </c>
       <c r="B414" s="5" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C414" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11528,7 +11545,7 @@
         <v>lech-poznan</v>
       </c>
       <c r="B415" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C415" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11549,7 +11566,7 @@
         <v>legia-warsaw</v>
       </c>
       <c r="B416" s="5" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C416" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11570,7 +11587,7 @@
         <v>motor-lublin</v>
       </c>
       <c r="B417" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C417" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11591,7 +11608,7 @@
         <v>piast-gliwice</v>
       </c>
       <c r="B418" s="5" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C418" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11612,7 +11629,7 @@
         <v>mks-pogon-szczecin</v>
       </c>
       <c r="B419" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C419" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11633,7 +11650,7 @@
         <v>radomiak-radom</v>
       </c>
       <c r="B420" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C420" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11654,7 +11671,7 @@
         <v>rakow-czestochowa</v>
       </c>
       <c r="B421" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C421" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11675,7 +11692,7 @@
         <v>slask-wroclaw</v>
       </c>
       <c r="B422" s="5" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="C422" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11696,7 +11713,7 @@
         <v>rts-widzew-lodz</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C423" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11717,7 +11734,7 @@
         <v>ks-wieczysta-krokow</v>
       </c>
       <c r="B424" s="5" t="s">
-        <v>595</v>
+        <v>588</v>
       </c>
       <c r="C424" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11738,7 +11755,7 @@
         <v>wisla-krakow</v>
       </c>
       <c r="B425" s="2" t="s">
-        <v>596</v>
+        <v>589</v>
       </c>
       <c r="C425" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11759,7 +11776,7 @@
         <v>wisla-plock</v>
       </c>
       <c r="B426" s="5" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C426" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11780,7 +11797,7 @@
         <v>zaglebie-lubin</v>
       </c>
       <c r="B427" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C427" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11801,7 +11818,7 @@
         <v>academico-de-viseu-fc</v>
       </c>
       <c r="B428" s="5" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
       <c r="C428" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11822,7 +11839,7 @@
         <v>fc-alverca</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C429" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11843,7 +11860,7 @@
         <v>fc-arouca</v>
       </c>
       <c r="B430" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C430" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11864,7 +11881,7 @@
         <v>benfica</v>
       </c>
       <c r="B431" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C431" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11885,7 +11902,7 @@
         <v>braga</v>
       </c>
       <c r="B432" s="5" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C432" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11906,7 +11923,7 @@
         <v>casa-pia-ac</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C433" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11927,7 +11944,7 @@
         <v>gd-estoril-praia</v>
       </c>
       <c r="B434" s="5" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C434" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11948,7 +11965,7 @@
         <v>cf-estrela-da-amadora</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C435" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11969,7 +11986,7 @@
         <v>famalicao</v>
       </c>
       <c r="B436" s="5" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C436" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11990,7 +12007,7 @@
         <v>fc-porto</v>
       </c>
       <c r="B437" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C437" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12011,7 +12028,7 @@
         <v>gil-vicente</v>
       </c>
       <c r="B438" s="5" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C438" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12032,7 +12049,7 @@
         <v>vitoria-de-guimaraes</v>
       </c>
       <c r="B439" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C439" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12053,7 +12070,7 @@
         <v>maritimo</v>
       </c>
       <c r="B440" s="5" t="s">
-        <v>620</v>
+        <v>613</v>
       </c>
       <c r="C440" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12074,7 +12091,7 @@
         <v>moreirense-fc</v>
       </c>
       <c r="B441" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C441" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12095,7 +12112,7 @@
         <v>cd-nacional</v>
       </c>
       <c r="B442" s="5" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C442" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12116,7 +12133,7 @@
         <v>rio-ave-fc</v>
       </c>
       <c r="B443" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C443" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12137,7 +12154,7 @@
         <v>santa-clara</v>
       </c>
       <c r="B444" s="5" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C444" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12158,7 +12175,7 @@
         <v>sporting-cp</v>
       </c>
       <c r="B445" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C445" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12179,7 +12196,7 @@
         <v>fc-botosani</v>
       </c>
       <c r="B446" s="5" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C446" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12200,7 +12217,7 @@
         <v>cfr-cluj</v>
       </c>
       <c r="B447" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C447" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12221,7 +12238,7 @@
         <v>corvinul-hunedoara</v>
       </c>
       <c r="B448" s="5" t="s">
-        <v>597</v>
+        <v>590</v>
       </c>
       <c r="C448" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12242,7 +12259,7 @@
         <v>fk-miercurea-ciuc</v>
       </c>
       <c r="B449" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C449" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12263,7 +12280,7 @@
         <v>fc-dinamo-bucuresti</v>
       </c>
       <c r="B450" s="5" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C450" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12284,7 +12301,7 @@
         <v>fc-farul-constanta</v>
       </c>
       <c r="B451" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C451" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12305,7 +12322,7 @@
         <v>fc-arges-pitesti</v>
       </c>
       <c r="B452" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C452" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12326,7 +12343,7 @@
         <v>fc-rapid-bucuresti</v>
       </c>
       <c r="B453" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C453" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12347,7 +12364,7 @@
         <v>fc-voluntari</v>
       </c>
       <c r="B454" s="5" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="C454" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12368,7 +12385,7 @@
         <v>fcsb</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C455" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12389,7 +12406,7 @@
         <v>asc-otelul-galati</v>
       </c>
       <c r="B456" s="5" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C456" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12410,7 +12427,7 @@
         <v>fc-petrolul-ploiesti</v>
       </c>
       <c r="B457" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C457" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12431,7 +12448,7 @@
         <v>sepsi-osk-sftantu-gheorghe</v>
       </c>
       <c r="B458" s="5" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="C458" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12452,7 +12469,7 @@
         <v>fc-universitatea-cluj</v>
       </c>
       <c r="B459" s="2" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C459" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12473,7 +12490,7 @@
         <v>cs-universitatea-craiova</v>
       </c>
       <c r="B460" s="5" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C460" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12494,7 +12511,7 @@
         <v>fc-uta-arad</v>
       </c>
       <c r="B461" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C461" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12515,7 +12532,7 @@
         <v>abha-club</v>
       </c>
       <c r="B462" s="5" t="s">
-        <v>607</v>
+        <v>600</v>
       </c>
       <c r="C462" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12536,7 +12553,7 @@
         <v>diriyah-club</v>
       </c>
       <c r="B463" s="2" t="s">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="C463" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12557,7 +12574,7 @@
         <v>al-fateh-sc</v>
       </c>
       <c r="B464" s="5" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C464" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12578,7 +12595,7 @@
         <v>al-fayha-fc</v>
       </c>
       <c r="B465" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C465" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12599,7 +12616,7 @@
         <v>al-hazem-fc</v>
       </c>
       <c r="B466" s="5" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="C466" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12620,7 +12637,7 @@
         <v>khaleej-fc</v>
       </c>
       <c r="B467" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C467" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12641,7 +12658,7 @@
         <v>al-kholood-club</v>
       </c>
       <c r="B468" s="5" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C468" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12662,7 +12679,7 @@
         <v>al-qadsiah-fc</v>
       </c>
       <c r="B469" s="2" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C469" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12683,7 +12700,7 @@
         <v>al-riyadh-sc</v>
       </c>
       <c r="B470" s="5" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C470" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12704,7 +12721,7 @@
         <v>al-ahli-saudi-fc</v>
       </c>
       <c r="B471" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C471" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12725,7 +12742,7 @@
         <v>al-ettifaq-fc</v>
       </c>
       <c r="B472" s="5" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C472" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12746,7 +12763,7 @@
         <v>al-faisaly-fc</v>
       </c>
       <c r="B473" s="2" t="s">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="C473" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12767,7 +12784,7 @@
         <v>al-hilal-fc</v>
       </c>
       <c r="B474" s="5" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C474" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12788,7 +12805,7 @@
         <v>al-ittihad-fc</v>
       </c>
       <c r="B475" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C475" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12809,7 +12826,7 @@
         <v>al-nassr-fc</v>
       </c>
       <c r="B476" s="5" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C476" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12830,7 +12847,7 @@
         <v>al-shabab-fc</v>
       </c>
       <c r="B477" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C477" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12851,7 +12868,7 @@
         <v>al-taawoun-fc</v>
       </c>
       <c r="B478" s="5" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C478" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12872,7 +12889,7 @@
         <v>neom-sc</v>
       </c>
       <c r="B479" s="2" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="C479" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12893,7 +12910,7 @@
         <v>aberdeen-fc</v>
       </c>
       <c r="B480" s="5" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C480" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12914,7 +12931,7 @@
         <v>celtic-fc</v>
       </c>
       <c r="B481" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C481" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12935,7 +12952,7 @@
         <v>dundee-fc</v>
       </c>
       <c r="B482" s="5" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C482" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12956,7 +12973,7 @@
         <v>dundee-united-fc</v>
       </c>
       <c r="B483" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C483" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12977,7 +12994,7 @@
         <v>falkirk-fc</v>
       </c>
       <c r="B484" s="5" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C484" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12998,7 +13015,7 @@
         <v>heart-of-midlothian-fc</v>
       </c>
       <c r="B485" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C485" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13019,7 +13036,7 @@
         <v>hibernian-fc</v>
       </c>
       <c r="B486" s="5" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C486" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13040,7 +13057,7 @@
         <v>kilmarnock-fc</v>
       </c>
       <c r="B487" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C487" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13061,7 +13078,7 @@
         <v>motherwell-fc</v>
       </c>
       <c r="B488" s="5" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C488" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13082,7 +13099,7 @@
         <v>rangers-fc</v>
       </c>
       <c r="B489" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C489" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13103,7 +13120,7 @@
         <v>st-johnstone-fc</v>
       </c>
       <c r="B490" s="5" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="C490" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13124,7 +13141,7 @@
         <v>st-mirren-fc</v>
       </c>
       <c r="B491" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C491" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13145,7 +13162,7 @@
         <v>deportivo-de-a-coruna</v>
       </c>
       <c r="B492" s="5" t="s">
-        <v>621</v>
+        <v>614</v>
       </c>
       <c r="C492" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13292,7 +13309,7 @@
         <v>elche-cf</v>
       </c>
       <c r="B499" s="2" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="C499" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13355,7 +13372,7 @@
         <v>levante-ud</v>
       </c>
       <c r="B502" s="5" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="C502" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13376,7 +13393,7 @@
         <v>malaga-cf</v>
       </c>
       <c r="B503" s="2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C503" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13418,7 +13435,7 @@
         <v>racing-de-santander</v>
       </c>
       <c r="B505" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C505" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13565,14 +13582,14 @@
         <v>albacete-balompie</v>
       </c>
       <c r="B512" s="5" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C512" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D512" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="E512" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -13585,14 +13602,14 @@
         <v>ud-almeria</v>
       </c>
       <c r="B513" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C513" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D513" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="E513" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -13605,14 +13622,14 @@
         <v>fc-andorra</v>
       </c>
       <c r="B514" s="5" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C514" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D514" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="E514" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -13625,14 +13642,14 @@
         <v>burgos-cf</v>
       </c>
       <c r="B515" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C515" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D515" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="E515" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -13645,14 +13662,14 @@
         <v>cadiz-cf</v>
       </c>
       <c r="B516" s="5" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C516" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D516" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="E516" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -13665,14 +13682,14 @@
         <v>cd-castellon</v>
       </c>
       <c r="B517" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C517" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D517" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="E517" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -13685,14 +13702,14 @@
         <v>celta-de-vigo-b</v>
       </c>
       <c r="B518" s="5" t="s">
-        <v>622</v>
+        <v>615</v>
       </c>
       <c r="C518" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D518" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="E518" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -13705,14 +13722,14 @@
         <v>ad-ceuta-fc</v>
       </c>
       <c r="B519" s="2" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C519" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D519" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="E519" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -13725,14 +13742,14 @@
         <v>cordoba-cf</v>
       </c>
       <c r="B520" s="5" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C520" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D520" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="E520" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -13745,14 +13762,14 @@
         <v>sd-eibar</v>
       </c>
       <c r="B521" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C521" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D521" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="E521" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -13765,14 +13782,14 @@
         <v>cd-eldense</v>
       </c>
       <c r="B522" s="5" t="s">
-        <v>623</v>
+        <v>616</v>
       </c>
       <c r="C522" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D522" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="E522" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -13785,14 +13802,14 @@
         <v>sporting-de-gijon</v>
       </c>
       <c r="B523" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C523" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D523" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="E523" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -13812,7 +13829,7 @@
         <v>spain</v>
       </c>
       <c r="D524" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="E524" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -13825,14 +13842,14 @@
         <v>granada-cf</v>
       </c>
       <c r="B525" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C525" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D525" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="E525" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -13852,7 +13869,7 @@
         <v>spain</v>
       </c>
       <c r="D526" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="E526" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -13872,7 +13889,7 @@
         <v>spain</v>
       </c>
       <c r="D527" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="E527" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -13892,7 +13909,7 @@
         <v>spain</v>
       </c>
       <c r="D528" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="E528" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -13905,14 +13922,14 @@
         <v>real-oviedo</v>
       </c>
       <c r="B529" s="2" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="C529" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D529" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="E529" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -13925,14 +13942,14 @@
         <v>real-sociedad-b</v>
       </c>
       <c r="B530" s="5" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C530" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D530" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="E530" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -13945,14 +13962,14 @@
         <v>ce-sabadell-fc</v>
       </c>
       <c r="B531" s="2" t="s">
-        <v>624</v>
+        <v>617</v>
       </c>
       <c r="C531" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D531" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="E531" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -13965,14 +13982,14 @@
         <v>cd-tenerife</v>
       </c>
       <c r="B532" s="5" t="s">
-        <v>625</v>
+        <v>618</v>
       </c>
       <c r="C532" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D532" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="E532" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -13992,7 +14009,7 @@
         <v>spain</v>
       </c>
       <c r="D533" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="E533" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -14005,7 +14022,7 @@
         <v>aik</v>
       </c>
       <c r="B534" s="5" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C534" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14026,7 +14043,7 @@
         <v>if-brommapojkarna</v>
       </c>
       <c r="B535" s="2" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C535" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14047,7 +14064,7 @@
         <v>degerfors-if</v>
       </c>
       <c r="B536" s="5" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C536" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14068,7 +14085,7 @@
         <v>djurgardens-if</v>
       </c>
       <c r="B537" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C537" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14089,7 +14106,7 @@
         <v>if-elfsborg</v>
       </c>
       <c r="B538" s="5" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C538" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14110,7 +14127,7 @@
         <v>gais</v>
       </c>
       <c r="B539" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C539" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14131,7 +14148,7 @@
         <v>ifk-goteborg</v>
       </c>
       <c r="B540" s="5" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C540" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14152,7 +14169,7 @@
         <v>bk-hacken</v>
       </c>
       <c r="B541" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C541" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14173,7 +14190,7 @@
         <v>halmstads-bk</v>
       </c>
       <c r="B542" s="5" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C542" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14194,7 +14211,7 @@
         <v>hammarby-if</v>
       </c>
       <c r="B543" s="2" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C543" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14215,7 +14232,7 @@
         <v>kalmar-ff</v>
       </c>
       <c r="B544" s="5" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="C544" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14236,7 +14253,7 @@
         <v>malmo-ff</v>
       </c>
       <c r="B545" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C545" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14257,7 +14274,7 @@
         <v>mjallby-aif</v>
       </c>
       <c r="B546" s="5" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C546" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14278,7 +14295,7 @@
         <v>orgryte-is</v>
       </c>
       <c r="B547" s="2" t="s">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="C547" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14299,7 +14316,7 @@
         <v>ik-sirius</v>
       </c>
       <c r="B548" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C548" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14320,7 +14337,7 @@
         <v>vasteras-sk</v>
       </c>
       <c r="B549" s="2" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="C549" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14341,7 +14358,7 @@
         <v>fc-basel</v>
       </c>
       <c r="B550" s="5" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C550" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14362,7 +14379,7 @@
         <v>grasshopper-club-zurich</v>
       </c>
       <c r="B551" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C551" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14383,7 +14400,7 @@
         <v>fc-lausanne-sport</v>
       </c>
       <c r="B552" s="5" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C552" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14404,7 +14421,7 @@
         <v>fc-lugano</v>
       </c>
       <c r="B553" s="2" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C553" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14425,7 +14442,7 @@
         <v>fc-luzern</v>
       </c>
       <c r="B554" s="5" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C554" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14446,7 +14463,7 @@
         <v>servette-fc</v>
       </c>
       <c r="B555" s="6" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C555" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14467,7 +14484,7 @@
         <v>fc-sion</v>
       </c>
       <c r="B556" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C556" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14488,7 +14505,7 @@
         <v>fc-st-gallen</v>
       </c>
       <c r="B557" s="7" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C557" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14509,7 +14526,7 @@
         <v>fc-thun</v>
       </c>
       <c r="B558" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C558" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14530,7 +14547,7 @@
         <v>fc-vaduz</v>
       </c>
       <c r="B559" s="7" t="s">
-        <v>601</v>
+        <v>594</v>
       </c>
       <c r="C559" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14551,7 +14568,7 @@
         <v>bsc-young-boys</v>
       </c>
       <c r="B560" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C560" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14572,7 +14589,7 @@
         <v>fc-zurich</v>
       </c>
       <c r="B561" s="7" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C561" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14593,7 +14610,7 @@
         <v>atlanta-united-fc</v>
       </c>
       <c r="B562" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C562" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14614,7 +14631,7 @@
         <v>austin-fc</v>
       </c>
       <c r="B563" s="7" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C563" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14635,7 +14652,7 @@
         <v>club-de-foot-montreal</v>
       </c>
       <c r="B564" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C564" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14656,7 +14673,7 @@
         <v>charlotte-fc</v>
       </c>
       <c r="B565" s="7" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C565" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14677,7 +14694,7 @@
         <v>chicago-fire-fc</v>
       </c>
       <c r="B566" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C566" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14698,7 +14715,7 @@
         <v>fc-cincinnati</v>
       </c>
       <c r="B567" s="7" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C567" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14719,7 +14736,7 @@
         <v>colorado-rapids</v>
       </c>
       <c r="B568" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C568" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14740,7 +14757,7 @@
         <v>columbus-crew-sc</v>
       </c>
       <c r="B569" s="7" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C569" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14761,7 +14778,7 @@
         <v>dc-united</v>
       </c>
       <c r="B570" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C570" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14782,7 +14799,7 @@
         <v>fc-dallas</v>
       </c>
       <c r="B571" s="7" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C571" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14803,7 +14820,7 @@
         <v>houston-dynamo</v>
       </c>
       <c r="B572" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C572" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14824,7 +14841,7 @@
         <v>inter-miami-cf</v>
       </c>
       <c r="B573" s="7" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C573" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14845,7 +14862,7 @@
         <v>los-angeles-fc</v>
       </c>
       <c r="B574" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C574" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14866,7 +14883,7 @@
         <v>los-angeles-galaxy</v>
       </c>
       <c r="B575" s="7" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C575" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14887,7 +14904,7 @@
         <v>minnesota-united-fc</v>
       </c>
       <c r="B576" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C576" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14908,7 +14925,7 @@
         <v>nashville-sc</v>
       </c>
       <c r="B577" s="7" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C577" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14929,7 +14946,7 @@
         <v>new-england-revolution</v>
       </c>
       <c r="B578" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C578" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14950,7 +14967,7 @@
         <v>new-york-city-fc</v>
       </c>
       <c r="B579" s="7" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C579" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14971,7 +14988,7 @@
         <v>new-york-red-bulls</v>
       </c>
       <c r="B580" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C580" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14992,7 +15009,7 @@
         <v>orlando-city-sc</v>
       </c>
       <c r="B581" s="7" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C581" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15013,7 +15030,7 @@
         <v>philadelphia-union</v>
       </c>
       <c r="B582" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C582" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15034,7 +15051,7 @@
         <v>portland-timbers</v>
       </c>
       <c r="B583" s="7" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C583" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15055,7 +15072,7 @@
         <v>real-salt-lake</v>
       </c>
       <c r="B584" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C584" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15076,7 +15093,7 @@
         <v>san-diego-fc</v>
       </c>
       <c r="B585" s="7" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C585" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15097,7 +15114,7 @@
         <v>san-jose-earthquakes</v>
       </c>
       <c r="B586" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C586" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15118,7 +15135,7 @@
         <v>seattle-sounders-fc</v>
       </c>
       <c r="B587" s="7" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C587" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15139,7 +15156,7 @@
         <v>sporting-kansas-city</v>
       </c>
       <c r="B588" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C588" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15160,7 +15177,7 @@
         <v>st-louis-city-sc</v>
       </c>
       <c r="B589" s="7" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C589" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15181,7 +15198,7 @@
         <v>toronto-fc</v>
       </c>
       <c r="B590" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C590" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15202,7 +15219,7 @@
         <v>vancouver-whitecaps-fc</v>
       </c>
       <c r="B591" s="7" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C591" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15223,7 +15240,7 @@
         <v>bohemians-fc</v>
       </c>
       <c r="B592" t="s">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="C592" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15235,7 +15252,7 @@
       </c>
       <c r="E592" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="593" spans="1:5" x14ac:dyDescent="0.3">
@@ -15244,7 +15261,7 @@
         <v>derry-city-fc</v>
       </c>
       <c r="B593" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="C593" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15256,7 +15273,7 @@
       </c>
       <c r="E593" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="594" spans="1:5" x14ac:dyDescent="0.3">
@@ -15265,7 +15282,7 @@
         <v>drogheda-united-fc</v>
       </c>
       <c r="B594" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="C594" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15277,7 +15294,7 @@
       </c>
       <c r="E594" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="595" spans="1:5" x14ac:dyDescent="0.3">
@@ -15286,7 +15303,7 @@
         <v>dundalk-fc</v>
       </c>
       <c r="B595" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="C595" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15298,7 +15315,7 @@
       </c>
       <c r="E595" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="596" spans="1:5" x14ac:dyDescent="0.3">
@@ -15307,7 +15324,7 @@
         <v>galway-united-fc</v>
       </c>
       <c r="B596" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="C596" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15319,7 +15336,7 @@
       </c>
       <c r="E596" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="597" spans="1:5" x14ac:dyDescent="0.3">
@@ -15328,7 +15345,7 @@
         <v>shamrock-rovers-fc</v>
       </c>
       <c r="B597" t="s">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="C597" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15340,7 +15357,7 @@
       </c>
       <c r="E597" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="598" spans="1:5" x14ac:dyDescent="0.3">
@@ -15349,7 +15366,7 @@
         <v>shelbourne-fc</v>
       </c>
       <c r="B598" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="C598" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15361,7 +15378,7 @@
       </c>
       <c r="E598" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="599" spans="1:5" x14ac:dyDescent="0.3">
@@ -15370,7 +15387,7 @@
         <v>sligo-rovers-fc</v>
       </c>
       <c r="B599" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="C599" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15382,7 +15399,7 @@
       </c>
       <c r="E599" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="600" spans="1:5" x14ac:dyDescent="0.3">
@@ -15391,7 +15408,7 @@
         <v>st-patricks-athletic-fc</v>
       </c>
       <c r="B600" t="s">
-        <v>559</v>
+        <v>552</v>
       </c>
       <c r="C600" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15403,7 +15420,7 @@
       </c>
       <c r="E600" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="601" spans="1:5" x14ac:dyDescent="0.3">
@@ -15412,7 +15429,7 @@
         <v>waterford-fc</v>
       </c>
       <c r="B601" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="C601" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15424,7 +15441,7 @@
       </c>
       <c r="E601" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="602" spans="1:5" x14ac:dyDescent="0.3">
@@ -15433,7 +15450,7 @@
         <v>al-ahly-sc</v>
       </c>
       <c r="B602" t="s">
-        <v>561</v>
+        <v>554</v>
       </c>
       <c r="C602" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15454,7 +15471,7 @@
         <v>al-ittihad-ac</v>
       </c>
       <c r="B603" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="C603" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15475,7 +15492,7 @@
         <v>al-masry-sc</v>
       </c>
       <c r="B604" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="C604" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15496,7 +15513,7 @@
         <v>arab-contractors-sc</v>
       </c>
       <c r="B605" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="C605" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15517,7 +15534,7 @@
         <v>ceramica-cleopatra-fc</v>
       </c>
       <c r="B606" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="C606" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15538,7 +15555,7 @@
         <v>talaea-el-gaish-sc</v>
       </c>
       <c r="B607" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="C607" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15559,7 +15576,7 @@
         <v>el-gouna-fc</v>
       </c>
       <c r="B608" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="C608" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15580,7 +15597,7 @@
         <v>enppi-sc</v>
       </c>
       <c r="B609" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="C609" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15601,7 +15618,7 @@
         <v>ghazi-el-mahalla-sc</v>
       </c>
       <c r="B610" t="s">
-        <v>569</v>
+        <v>562</v>
       </c>
       <c r="C610" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15622,7 +15639,7 @@
         <v>haras-el-hodoud-sc</v>
       </c>
       <c r="B611" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
       <c r="C611" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15643,7 +15660,7 @@
         <v>ismaily-sc</v>
       </c>
       <c r="B612" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
       <c r="C612" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15664,7 +15681,7 @@
         <v>kahrabaa-ismailia-sc</v>
       </c>
       <c r="B613" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="C613" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15685,7 +15702,7 @@
         <v>modern-sport-fc</v>
       </c>
       <c r="B614" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="C614" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15706,7 +15723,7 @@
         <v>national-bank-of-egypt-sc</v>
       </c>
       <c r="B615" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
       <c r="C615" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15727,7 +15744,7 @@
         <v>petrojet-sc</v>
       </c>
       <c r="B616" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="C616" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15748,7 +15765,7 @@
         <v>pharco-fc</v>
       </c>
       <c r="B617" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="C617" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15769,7 +15786,7 @@
         <v>pyramids-fc</v>
       </c>
       <c r="B618" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
       <c r="C618" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15790,7 +15807,7 @@
         <v>smouha-sc</v>
       </c>
       <c r="B619" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
       <c r="C619" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15811,7 +15828,7 @@
         <v>wadi-degla-sc</v>
       </c>
       <c r="B620" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="C620" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15832,7 +15849,7 @@
         <v>zamalek-sc</v>
       </c>
       <c r="B621" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="C621" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15853,7 +15870,7 @@
         <v>zed-fc</v>
       </c>
       <c r="B622" t="s">
-        <v>581</v>
+        <v>574</v>
       </c>
       <c r="C622" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>

--- a/enlaces_equipos.xlsx
+++ b/enlaces_equipos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose-\Trabajo\statsFutbol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53AC76EC-A780-41A2-81F3-76B242781F97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D318A235-5B65-4F10-AA8C-198C8AB8BCA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" xr2:uid="{474EBA83-D6A0-4565-BEB0-BC6B2AA992C1}"/>
   </bookViews>
@@ -2064,7 +2064,21 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="8">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2108,23 +2122,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1329FF03-B366-468C-915B-7B9006981626}" name="Tabla1" displayName="Tabla1" ref="A1:E622" totalsRowShown="0" headerRowDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1329FF03-B366-468C-915B-7B9006981626}" name="Tabla1" displayName="Tabla1" ref="A1:E622" totalsRowShown="0" headerRowDxfId="7">
   <autoFilter ref="A1:E622" xr:uid="{1329FF03-B366-468C-915B-7B9006981626}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C591">
     <sortCondition ref="C1:C591"/>
   </sortState>
   <tableColumns count="5">
-    <tableColumn id="2" xr3:uid="{94084D0E-9EB8-4AA2-8B8F-47973A2CEB88}" name="EQUIPO" dataDxfId="4">
+    <tableColumn id="2" xr3:uid="{94084D0E-9EB8-4AA2-8B8F-47973A2CEB88}" name="EQUIPO" dataDxfId="6">
       <calculatedColumnFormula>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="1" xr3:uid="{B01E1C82-362B-4BF7-BCB9-D64E8D4F9629}" name="ENLACE"/>
-    <tableColumn id="3" xr3:uid="{E3AB90A5-DEAD-4B94-A136-1E8126059E3B}" name="PAIS" dataDxfId="3">
+    <tableColumn id="3" xr3:uid="{E3AB90A5-DEAD-4B94-A136-1E8126059E3B}" name="PAIS" dataDxfId="5">
       <calculatedColumnFormula>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{F2E44DAA-70E6-4294-A083-84669D9B9C01}" name="DIVISION" dataDxfId="2">
+    <tableColumn id="5" xr3:uid="{F2E44DAA-70E6-4294-A083-84669D9B9C01}" name="DIVISION" dataDxfId="4">
       <calculatedColumnFormula>Tabla1[[#This Row],[PAIS]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{864CABB9-1E94-4601-B818-3F8256A83250}" name="ANALIZAR" dataDxfId="1">
+    <tableColumn id="4" xr3:uid="{864CABB9-1E94-4601-B818-3F8256A83250}" name="ANALIZAR" dataDxfId="3">
       <calculatedColumnFormula>IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2483,7 +2497,7 @@
         <v>argentina</v>
       </c>
       <c r="I2" s="9" t="str">
-        <f ca="1">IF(J2&gt;TODAY(),"","X")</f>
+        <f t="shared" ref="I2:I29" ca="1" si="0">IF(J2&gt;TODAY(),"","X")</f>
         <v>X</v>
       </c>
       <c r="J2" s="10">
@@ -2517,7 +2531,7 @@
         <v>australia</v>
       </c>
       <c r="I3" s="9" t="str">
-        <f ca="1">IF(J3&gt;TODAY(),"","X")</f>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
       <c r="J3" s="10">
@@ -2549,7 +2563,7 @@
         <v>austria</v>
       </c>
       <c r="I4" s="9" t="str">
-        <f t="shared" ref="I4:I34" ca="1" si="0">IF(J4&gt;TODAY(),"","X")</f>
+        <f t="shared" ca="1" si="0"/>
         <v>X</v>
       </c>
       <c r="J4" s="10">
@@ -3433,7 +3447,7 @@
         <v>sweden</v>
       </c>
       <c r="I30" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" ref="I30:I34" ca="1" si="1">IF(J30&gt;TODAY(),"","X")</f>
         <v>X</v>
       </c>
       <c r="J30" s="10">
@@ -3467,7 +3481,7 @@
         <v>switzerland</v>
       </c>
       <c r="I31" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" ca="1" si="1"/>
         <v>X</v>
       </c>
       <c r="J31" s="10">
@@ -3501,7 +3515,7 @@
         <v>usa</v>
       </c>
       <c r="I32" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" ca="1" si="1"/>
         <v>X</v>
       </c>
       <c r="J32" s="10">
@@ -3535,7 +3549,7 @@
         <v>ireland</v>
       </c>
       <c r="I33" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" ca="1" si="1"/>
         <v>X</v>
       </c>
       <c r="J33" s="10">
@@ -3569,7 +3583,7 @@
         <v>egypt</v>
       </c>
       <c r="I34" s="9" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" ca="1" si="1"/>
         <v>X</v>
       </c>
       <c r="J34" s="10">
@@ -15886,7 +15900,12 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="K2:K35">
+  <conditionalFormatting sqref="K30:K35">
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="act">
+      <formula>NOT(ISERROR(SEARCH("act",K30)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K29">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="act">
       <formula>NOT(ISERROR(SEARCH("act",K2)))</formula>
     </cfRule>

--- a/enlaces_equipos.xlsx
+++ b/enlaces_equipos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose-\Trabajo\statsFutbol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D318A235-5B65-4F10-AA8C-198C8AB8BCA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB4BAD73-4AFD-43D7-8990-79661ED218B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" xr2:uid="{474EBA83-D6A0-4565-BEB0-BC6B2AA992C1}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="629">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="671">
   <si>
     <t>EQUIPO</t>
   </si>
@@ -1945,6 +1945,132 @@
   </si>
   <si>
     <t>europe/italy/venezia-fc</t>
+  </si>
+  <si>
+    <t>europe/cyprus/aek-larnaca-fc</t>
+  </si>
+  <si>
+    <t>europe/cyprus/ael-limassol</t>
+  </si>
+  <si>
+    <t>europe/cyprus/anorthosis-famagusta-fc</t>
+  </si>
+  <si>
+    <t>europe/cyprus/apoel-fc</t>
+  </si>
+  <si>
+    <t>europe/cyprus/apollon-limassol</t>
+  </si>
+  <si>
+    <t>europe/cyprus/aris-limassol-fc</t>
+  </si>
+  <si>
+    <t>europe/cyprus/karmiotissa-fc</t>
+  </si>
+  <si>
+    <t>europe/cyprus/krasava-eny-ypsonas-fc</t>
+  </si>
+  <si>
+    <t>europe/cyprus/nea-salamis-famagusta-fc</t>
+  </si>
+  <si>
+    <t>europe/cyprus/olympiakos-nicosia</t>
+  </si>
+  <si>
+    <t>europe/cyprus/ac-omonia</t>
+  </si>
+  <si>
+    <t>europe/cyprus/pac-omonia-29m</t>
+  </si>
+  <si>
+    <t>europe/cyprus/omonia-aradippou</t>
+  </si>
+  <si>
+    <t>europe/cyprus/pafos-fc</t>
+  </si>
+  <si>
+    <t>europe/hungary/debrecen</t>
+  </si>
+  <si>
+    <t>europe/hungary/ferencvaros</t>
+  </si>
+  <si>
+    <t>europe/hungary/gyori-eto-fc</t>
+  </si>
+  <si>
+    <t>europe/hungary/budapest-honved-fc</t>
+  </si>
+  <si>
+    <t>europe/hungary/kisvarda-fc</t>
+  </si>
+  <si>
+    <t>europe/hungary/mtk-budapest-fc</t>
+  </si>
+  <si>
+    <t>europe/hungary/nyiregyhaza-spartacus-fc</t>
+  </si>
+  <si>
+    <t>europe/hungary/paksi-fc</t>
+  </si>
+  <si>
+    <t>europe/hungary/puskas-akademia-fc</t>
+  </si>
+  <si>
+    <t>europe/hungary/ujpest-fc</t>
+  </si>
+  <si>
+    <t>europe/hungary/vasas-sc</t>
+  </si>
+  <si>
+    <t>europe/hungary/zalaegerszeg-te</t>
+  </si>
+  <si>
+    <t>n-s-america/uruguay/albion-fc</t>
+  </si>
+  <si>
+    <t>n-s-america/uruguay/boston-river</t>
+  </si>
+  <si>
+    <t>n-s-america/uruguay/central-espanol</t>
+  </si>
+  <si>
+    <t>n-s-america/uruguay/club-atletico-cerro</t>
+  </si>
+  <si>
+    <t>n-s-america/uruguay/cerro-largo-fc</t>
+  </si>
+  <si>
+    <t>n-s-america/uruguay/danubio-fc</t>
+  </si>
+  <si>
+    <t>n-s-america/uruguay/defensor-sporting</t>
+  </si>
+  <si>
+    <t>n-s-america/uruguay/juventud-de-las-piedras</t>
+  </si>
+  <si>
+    <t>n-s-america/uruguay/liverpool-fc-montevideo</t>
+  </si>
+  <si>
+    <t>n-s-america/uruguay/deportivo-maldonado</t>
+  </si>
+  <si>
+    <t>n-s-america/uruguay/montevideo-city-torque</t>
+  </si>
+  <si>
+    <t>n-s-america/uruguay/club-nacional-de-football</t>
+  </si>
+  <si>
+    <t>n-s-america/uruguay/penarol</t>
+  </si>
+  <si>
+    <t>n-s-america/uruguay/club-atletico-progreso</t>
+  </si>
+  <si>
+    <t>n-s-america/uruguay/racing-club-de-montevideo</t>
+  </si>
+  <si>
+    <t>n-s-america/uruguay/montevideo-wanderers-fc</t>
   </si>
 </sst>
 </file>
@@ -2040,7 +2166,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2060,32 +2186,15 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="6">
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2108,6 +2217,13 @@
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2122,23 +2238,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1329FF03-B366-468C-915B-7B9006981626}" name="Tabla1" displayName="Tabla1" ref="A1:E622" totalsRowShown="0" headerRowDxfId="7">
-  <autoFilter ref="A1:E622" xr:uid="{1329FF03-B366-468C-915B-7B9006981626}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1329FF03-B366-468C-915B-7B9006981626}" name="Tabla1" displayName="Tabla1" ref="A1:E664" totalsRowShown="0" headerRowDxfId="4">
+  <autoFilter ref="A1:E664" xr:uid="{1329FF03-B366-468C-915B-7B9006981626}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C591">
     <sortCondition ref="C1:C591"/>
   </sortState>
   <tableColumns count="5">
-    <tableColumn id="2" xr3:uid="{94084D0E-9EB8-4AA2-8B8F-47973A2CEB88}" name="EQUIPO" dataDxfId="6">
+    <tableColumn id="2" xr3:uid="{94084D0E-9EB8-4AA2-8B8F-47973A2CEB88}" name="EQUIPO" dataDxfId="3">
       <calculatedColumnFormula>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="1" xr3:uid="{B01E1C82-362B-4BF7-BCB9-D64E8D4F9629}" name="ENLACE"/>
-    <tableColumn id="3" xr3:uid="{E3AB90A5-DEAD-4B94-A136-1E8126059E3B}" name="PAIS" dataDxfId="5">
+    <tableColumn id="3" xr3:uid="{E3AB90A5-DEAD-4B94-A136-1E8126059E3B}" name="PAIS" dataDxfId="2">
       <calculatedColumnFormula>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{F2E44DAA-70E6-4294-A083-84669D9B9C01}" name="DIVISION" dataDxfId="4">
+    <tableColumn id="5" xr3:uid="{F2E44DAA-70E6-4294-A083-84669D9B9C01}" name="DIVISION" dataDxfId="1">
       <calculatedColumnFormula>Tabla1[[#This Row],[PAIS]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{864CABB9-1E94-4601-B818-3F8256A83250}" name="ANALIZAR" dataDxfId="3">
+    <tableColumn id="4" xr3:uid="{864CABB9-1E94-4601-B818-3F8256A83250}" name="ANALIZAR" dataDxfId="0">
       <calculatedColumnFormula>IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2443,7 +2559,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EC3E121-4DD2-4C5A-A60B-ED62DD98B116}">
-  <dimension ref="A1:K622"/>
+  <dimension ref="A1:K664"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.33203125" bestFit="1" customWidth="1"/>
@@ -2493,7 +2609,7 @@
         <v>SI</v>
       </c>
       <c r="H2" s="9" t="str" cm="1">
-        <f t="array" ref="H2:H34">_xlfn.UNIQUE(Tabla1[PAIS])</f>
+        <f t="array" ref="H2:H37">_xlfn.UNIQUE(Tabla1[PAIS])</f>
         <v>argentina</v>
       </c>
       <c r="I2" s="9" t="str">
@@ -3447,7 +3563,7 @@
         <v>sweden</v>
       </c>
       <c r="I30" s="9" t="str">
-        <f t="shared" ref="I30:I34" ca="1" si="1">IF(J30&gt;TODAY(),"","X")</f>
+        <f t="shared" ref="I30:I37" ca="1" si="1">IF(J30&gt;TODAY(),"","X")</f>
         <v>X</v>
       </c>
       <c r="J30" s="10">
@@ -3613,10 +3729,19 @@
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>NO</v>
       </c>
-      <c r="H35" s="9"/>
-      <c r="I35" s="9"/>
-      <c r="J35" s="10"/>
-      <c r="K35" s="9"/>
+      <c r="H35" s="9" t="str">
+        <v>cyprus</v>
+      </c>
+      <c r="I35" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>X</v>
+      </c>
+      <c r="J35" s="10">
+        <v>46284</v>
+      </c>
+      <c r="K35" s="9" t="s">
+        <v>525</v>
+      </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="str">
@@ -3638,6 +3763,19 @@
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>NO</v>
       </c>
+      <c r="H36" s="9" t="str">
+        <v>hungary</v>
+      </c>
+      <c r="I36" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>X</v>
+      </c>
+      <c r="J36" s="10">
+        <v>46284</v>
+      </c>
+      <c r="K36" s="9" t="s">
+        <v>525</v>
+      </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="str">
@@ -3659,6 +3797,19 @@
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>NO</v>
       </c>
+      <c r="H37" s="9" t="str">
+        <v>uruguay</v>
+      </c>
+      <c r="I37" s="9" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v>X</v>
+      </c>
+      <c r="J37" s="10">
+        <v>46284</v>
+      </c>
+      <c r="K37" s="9" t="s">
+        <v>525</v>
+      </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="str">
@@ -15899,14 +16050,891 @@
         <v>SI</v>
       </c>
     </row>
+    <row r="623" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A623" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>aek-larnaca-fc</v>
+      </c>
+      <c r="B623" t="s">
+        <v>629</v>
+      </c>
+      <c r="C623" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>cyprus</v>
+      </c>
+      <c r="D623" s="11" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>cyprus</v>
+      </c>
+      <c r="E623" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="624" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A624" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>ael-limassol</v>
+      </c>
+      <c r="B624" t="s">
+        <v>630</v>
+      </c>
+      <c r="C624" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>cyprus</v>
+      </c>
+      <c r="D624" s="11" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>cyprus</v>
+      </c>
+      <c r="E624" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="625" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A625" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>anorthosis-famagusta-fc</v>
+      </c>
+      <c r="B625" t="s">
+        <v>631</v>
+      </c>
+      <c r="C625" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>cyprus</v>
+      </c>
+      <c r="D625" s="11" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>cyprus</v>
+      </c>
+      <c r="E625" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="626" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A626" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>apoel-fc</v>
+      </c>
+      <c r="B626" t="s">
+        <v>632</v>
+      </c>
+      <c r="C626" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>cyprus</v>
+      </c>
+      <c r="D626" s="11" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>cyprus</v>
+      </c>
+      <c r="E626" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="627" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A627" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>apollon-limassol</v>
+      </c>
+      <c r="B627" t="s">
+        <v>633</v>
+      </c>
+      <c r="C627" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>cyprus</v>
+      </c>
+      <c r="D627" s="11" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>cyprus</v>
+      </c>
+      <c r="E627" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="628" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A628" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>aris-limassol-fc</v>
+      </c>
+      <c r="B628" t="s">
+        <v>634</v>
+      </c>
+      <c r="C628" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>cyprus</v>
+      </c>
+      <c r="D628" s="11" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>cyprus</v>
+      </c>
+      <c r="E628" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="629" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A629" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>karmiotissa-fc</v>
+      </c>
+      <c r="B629" t="s">
+        <v>635</v>
+      </c>
+      <c r="C629" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>cyprus</v>
+      </c>
+      <c r="D629" s="11" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>cyprus</v>
+      </c>
+      <c r="E629" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="630" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A630" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>krasava-eny-ypsonas-fc</v>
+      </c>
+      <c r="B630" t="s">
+        <v>636</v>
+      </c>
+      <c r="C630" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>cyprus</v>
+      </c>
+      <c r="D630" s="11" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>cyprus</v>
+      </c>
+      <c r="E630" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="631" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A631" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>nea-salamis-famagusta-fc</v>
+      </c>
+      <c r="B631" t="s">
+        <v>637</v>
+      </c>
+      <c r="C631" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>cyprus</v>
+      </c>
+      <c r="D631" s="11" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>cyprus</v>
+      </c>
+      <c r="E631" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="632" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A632" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>olympiakos-nicosia</v>
+      </c>
+      <c r="B632" t="s">
+        <v>638</v>
+      </c>
+      <c r="C632" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>cyprus</v>
+      </c>
+      <c r="D632" s="11" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>cyprus</v>
+      </c>
+      <c r="E632" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="633" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A633" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>ac-omonia</v>
+      </c>
+      <c r="B633" t="s">
+        <v>639</v>
+      </c>
+      <c r="C633" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>cyprus</v>
+      </c>
+      <c r="D633" s="11" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>cyprus</v>
+      </c>
+      <c r="E633" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="634" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A634" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>pac-omonia-29m</v>
+      </c>
+      <c r="B634" t="s">
+        <v>640</v>
+      </c>
+      <c r="C634" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>cyprus</v>
+      </c>
+      <c r="D634" s="11" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>cyprus</v>
+      </c>
+      <c r="E634" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="635" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A635" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>omonia-aradippou</v>
+      </c>
+      <c r="B635" t="s">
+        <v>641</v>
+      </c>
+      <c r="C635" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>cyprus</v>
+      </c>
+      <c r="D635" s="11" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>cyprus</v>
+      </c>
+      <c r="E635" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="636" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A636" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>pafos-fc</v>
+      </c>
+      <c r="B636" t="s">
+        <v>642</v>
+      </c>
+      <c r="C636" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>cyprus</v>
+      </c>
+      <c r="D636" s="11" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>cyprus</v>
+      </c>
+      <c r="E636" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="637" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A637" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>debrecen</v>
+      </c>
+      <c r="B637" t="s">
+        <v>643</v>
+      </c>
+      <c r="C637" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>hungary</v>
+      </c>
+      <c r="D637" s="11" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>hungary</v>
+      </c>
+      <c r="E637" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="638" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A638" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>ferencvaros</v>
+      </c>
+      <c r="B638" t="s">
+        <v>644</v>
+      </c>
+      <c r="C638" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>hungary</v>
+      </c>
+      <c r="D638" s="11" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>hungary</v>
+      </c>
+      <c r="E638" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="639" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A639" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>gyori-eto-fc</v>
+      </c>
+      <c r="B639" t="s">
+        <v>645</v>
+      </c>
+      <c r="C639" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>hungary</v>
+      </c>
+      <c r="D639" s="11" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>hungary</v>
+      </c>
+      <c r="E639" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="640" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A640" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>budapest-honved-fc</v>
+      </c>
+      <c r="B640" t="s">
+        <v>646</v>
+      </c>
+      <c r="C640" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>hungary</v>
+      </c>
+      <c r="D640" s="11" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>hungary</v>
+      </c>
+      <c r="E640" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="641" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A641" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>kisvarda-fc</v>
+      </c>
+      <c r="B641" t="s">
+        <v>647</v>
+      </c>
+      <c r="C641" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>hungary</v>
+      </c>
+      <c r="D641" s="11" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>hungary</v>
+      </c>
+      <c r="E641" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="642" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A642" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>mtk-budapest-fc</v>
+      </c>
+      <c r="B642" t="s">
+        <v>648</v>
+      </c>
+      <c r="C642" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>hungary</v>
+      </c>
+      <c r="D642" s="11" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>hungary</v>
+      </c>
+      <c r="E642" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="643" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A643" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>nyiregyhaza-spartacus-fc</v>
+      </c>
+      <c r="B643" t="s">
+        <v>649</v>
+      </c>
+      <c r="C643" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>hungary</v>
+      </c>
+      <c r="D643" s="11" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>hungary</v>
+      </c>
+      <c r="E643" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="644" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A644" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>paksi-fc</v>
+      </c>
+      <c r="B644" t="s">
+        <v>650</v>
+      </c>
+      <c r="C644" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>hungary</v>
+      </c>
+      <c r="D644" s="11" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>hungary</v>
+      </c>
+      <c r="E644" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="645" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A645" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>puskas-akademia-fc</v>
+      </c>
+      <c r="B645" t="s">
+        <v>651</v>
+      </c>
+      <c r="C645" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>hungary</v>
+      </c>
+      <c r="D645" s="11" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>hungary</v>
+      </c>
+      <c r="E645" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="646" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A646" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>ujpest-fc</v>
+      </c>
+      <c r="B646" t="s">
+        <v>652</v>
+      </c>
+      <c r="C646" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>hungary</v>
+      </c>
+      <c r="D646" s="11" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>hungary</v>
+      </c>
+      <c r="E646" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="647" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A647" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>vasas-sc</v>
+      </c>
+      <c r="B647" t="s">
+        <v>653</v>
+      </c>
+      <c r="C647" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>hungary</v>
+      </c>
+      <c r="D647" s="11" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>hungary</v>
+      </c>
+      <c r="E647" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="648" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A648" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>zalaegerszeg-te</v>
+      </c>
+      <c r="B648" t="s">
+        <v>654</v>
+      </c>
+      <c r="C648" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>hungary</v>
+      </c>
+      <c r="D648" s="11" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>hungary</v>
+      </c>
+      <c r="E648" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="649" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A649" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>albion-fc</v>
+      </c>
+      <c r="B649" t="s">
+        <v>655</v>
+      </c>
+      <c r="C649" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>uruguay</v>
+      </c>
+      <c r="D649" s="11" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>uruguay</v>
+      </c>
+      <c r="E649" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="650" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A650" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>boston-river</v>
+      </c>
+      <c r="B650" t="s">
+        <v>656</v>
+      </c>
+      <c r="C650" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>uruguay</v>
+      </c>
+      <c r="D650" s="11" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>uruguay</v>
+      </c>
+      <c r="E650" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="651" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A651" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>central-espanol</v>
+      </c>
+      <c r="B651" t="s">
+        <v>657</v>
+      </c>
+      <c r="C651" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>uruguay</v>
+      </c>
+      <c r="D651" s="11" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>uruguay</v>
+      </c>
+      <c r="E651" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="652" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A652" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>club-atletico-cerro</v>
+      </c>
+      <c r="B652" t="s">
+        <v>658</v>
+      </c>
+      <c r="C652" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>uruguay</v>
+      </c>
+      <c r="D652" s="11" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>uruguay</v>
+      </c>
+      <c r="E652" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="653" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A653" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>cerro-largo-fc</v>
+      </c>
+      <c r="B653" t="s">
+        <v>659</v>
+      </c>
+      <c r="C653" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>uruguay</v>
+      </c>
+      <c r="D653" s="11" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>uruguay</v>
+      </c>
+      <c r="E653" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="654" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A654" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>danubio-fc</v>
+      </c>
+      <c r="B654" t="s">
+        <v>660</v>
+      </c>
+      <c r="C654" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>uruguay</v>
+      </c>
+      <c r="D654" s="11" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>uruguay</v>
+      </c>
+      <c r="E654" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="655" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A655" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>defensor-sporting</v>
+      </c>
+      <c r="B655" t="s">
+        <v>661</v>
+      </c>
+      <c r="C655" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>uruguay</v>
+      </c>
+      <c r="D655" s="11" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>uruguay</v>
+      </c>
+      <c r="E655" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="656" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A656" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>juventud-de-las-piedras</v>
+      </c>
+      <c r="B656" t="s">
+        <v>662</v>
+      </c>
+      <c r="C656" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>uruguay</v>
+      </c>
+      <c r="D656" s="11" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>uruguay</v>
+      </c>
+      <c r="E656" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="657" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A657" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>liverpool-fc-montevideo</v>
+      </c>
+      <c r="B657" t="s">
+        <v>663</v>
+      </c>
+      <c r="C657" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>uruguay</v>
+      </c>
+      <c r="D657" s="11" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>uruguay</v>
+      </c>
+      <c r="E657" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="658" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A658" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>deportivo-maldonado</v>
+      </c>
+      <c r="B658" t="s">
+        <v>664</v>
+      </c>
+      <c r="C658" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>uruguay</v>
+      </c>
+      <c r="D658" s="11" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>uruguay</v>
+      </c>
+      <c r="E658" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="659" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A659" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>montevideo-city-torque</v>
+      </c>
+      <c r="B659" t="s">
+        <v>665</v>
+      </c>
+      <c r="C659" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>uruguay</v>
+      </c>
+      <c r="D659" s="11" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>uruguay</v>
+      </c>
+      <c r="E659" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="660" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A660" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>club-nacional-de-football</v>
+      </c>
+      <c r="B660" t="s">
+        <v>666</v>
+      </c>
+      <c r="C660" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>uruguay</v>
+      </c>
+      <c r="D660" s="11" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>uruguay</v>
+      </c>
+      <c r="E660" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="661" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A661" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>penarol</v>
+      </c>
+      <c r="B661" t="s">
+        <v>667</v>
+      </c>
+      <c r="C661" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>uruguay</v>
+      </c>
+      <c r="D661" s="11" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>uruguay</v>
+      </c>
+      <c r="E661" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="662" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A662" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>club-atletico-progreso</v>
+      </c>
+      <c r="B662" t="s">
+        <v>668</v>
+      </c>
+      <c r="C662" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>uruguay</v>
+      </c>
+      <c r="D662" s="11" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>uruguay</v>
+      </c>
+      <c r="E662" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="663" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A663" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>racing-club-de-montevideo</v>
+      </c>
+      <c r="B663" t="s">
+        <v>669</v>
+      </c>
+      <c r="C663" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>uruguay</v>
+      </c>
+      <c r="D663" s="11" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>uruguay</v>
+      </c>
+      <c r="E663" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="664" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A664" s="11" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>montevideo-wanderers-fc</v>
+      </c>
+      <c r="B664" t="s">
+        <v>670</v>
+      </c>
+      <c r="C664" s="11" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>uruguay</v>
+      </c>
+      <c r="D664" s="11" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>uruguay</v>
+      </c>
+      <c r="E664" s="12" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="K30:K35">
-    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="act">
-      <formula>NOT(ISERROR(SEARCH("act",K30)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K29">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="act">
+  <conditionalFormatting sqref="K2:K37">
+    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="act">
       <formula>NOT(ISERROR(SEARCH("act",K2)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/enlaces_equipos.xlsx
+++ b/enlaces_equipos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose-\Trabajo\statsFutbol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB4BAD73-4AFD-43D7-8990-79661ED218B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E7ED5CF-1E35-4409-88C4-9D7D7B9659F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" xr2:uid="{474EBA83-D6A0-4565-BEB0-BC6B2AA992C1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{474EBA83-D6A0-4565-BEB0-BC6B2AA992C1}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="671">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="735">
   <si>
     <t>EQUIPO</t>
   </si>
@@ -2071,6 +2071,198 @@
   </si>
   <si>
     <t>n-s-america/uruguay/montevideo-wanderers-fc</t>
+  </si>
+  <si>
+    <t>europe/ukraine/fsc-bukovyna-chernivtsi</t>
+  </si>
+  <si>
+    <t>europe/ukraine/fc-chornomorets-odessa</t>
+  </si>
+  <si>
+    <t>europe/ukraine/fc-dynamo-kyiv</t>
+  </si>
+  <si>
+    <t>europe/ukraine/fc-epitsentr-kamianets-podilskyi</t>
+  </si>
+  <si>
+    <t>europe/ukraine/fc-kharkiv</t>
+  </si>
+  <si>
+    <t>europe/ukraine/fc-karpaty-lviv</t>
+  </si>
+  <si>
+    <t>europe/ukraine/fc-kolos-kovalivka</t>
+  </si>
+  <si>
+    <t>europe/ukraine/fc-kryvbas-kryvyi-rih</t>
+  </si>
+  <si>
+    <t>europe/ukraine/fc-kudrivka</t>
+  </si>
+  <si>
+    <t>europe/ukraine/fc-livyi-bereh-kyiv</t>
+  </si>
+  <si>
+    <t>europe/ukraine/fc-lnz-cherkasy</t>
+  </si>
+  <si>
+    <t>europe/ukraine/fc-obolon-kyiv</t>
+  </si>
+  <si>
+    <t>europe/ukraine/fc-polissya-zhytomyr</t>
+  </si>
+  <si>
+    <t>europe/ukraine/fc-shakhtar-donetsk</t>
+  </si>
+  <si>
+    <t>europe/ukraine/nk-veres-rivne</t>
+  </si>
+  <si>
+    <t>europe/ukraine/fc-zorya-luhansk</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/japan/avispa-fukuoka</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/japan/cerezo-osaka</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/japan/fagiano-okayama</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/japan/gamba-osaka</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/japan/sanfreece-hiroshima</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/japan/jef-united-chiba</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/japan/kashima-antlers</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/japan/kashiwa-reysol</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/japan/kawasaki-frontale</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/japan/vissel-kobe</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/japan/kyoto-sanga-fc</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/japan/fc-machida-zelvia</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/japan/mito-hollyhock</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/japan/nagoya-grampus</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/japan/shimizu-s-pulse</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/japan/fc-tokyo</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/japan/tokyo-verdy</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/japan/urawa-red-diamonds</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/japan/v-varen-nagasaki</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/japan/yokohama-f-marinos</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/south-korea/fc-anyang</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/south-korea/bucheon-fc-1995</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/south-korea/daejeon-hana-citizen</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/south-korea/gangwon-fc</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/south-korea/gimcheon-sangmu-fc</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/south-korea/gwangju-fc</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/south-korea/incheon-united</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/south-korea/jeju-sk-fc</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/south-korea/jeonbuk-hyundai-motors</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/south-korea/pohang-steelers</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/south-korea/fc-seoul</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/south-korea/ulsan-hd-fc</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/china/beijing-guoan-fc</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/china/chengdu-rongcheng-fc</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/china/chongqing-tonglianglong-fc</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/china/dalian-yingbo-fc</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/china/henan-fc</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/china/liaoning-tieren-fc</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/china/qingdao-hainiu-fc</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/china/qingdao-west-coast-fc</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/china/shandong-taishan-fc</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/china/shanghai-port-fc</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/china/shanghai-shenhua-fc</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/china/shenzhen-peng-city-fc</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/china/tianjin-jinmen-tiger-fc</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/china/wuhan-three-towns-fc</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/china/yunnan-yukun-fc</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/china/zhejiang-professional-fc</t>
   </si>
 </sst>
 </file>
@@ -2166,7 +2358,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2186,15 +2378,21 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="6">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2217,13 +2415,6 @@
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2238,23 +2429,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1329FF03-B366-468C-915B-7B9006981626}" name="Tabla1" displayName="Tabla1" ref="A1:E664" totalsRowShown="0" headerRowDxfId="4">
-  <autoFilter ref="A1:E664" xr:uid="{1329FF03-B366-468C-915B-7B9006981626}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1329FF03-B366-468C-915B-7B9006981626}" name="Tabla1" displayName="Tabla1" ref="A1:E728" totalsRowShown="0" headerRowDxfId="5">
+  <autoFilter ref="A1:E728" xr:uid="{1329FF03-B366-468C-915B-7B9006981626}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C591">
     <sortCondition ref="C1:C591"/>
   </sortState>
   <tableColumns count="5">
-    <tableColumn id="2" xr3:uid="{94084D0E-9EB8-4AA2-8B8F-47973A2CEB88}" name="EQUIPO" dataDxfId="3">
+    <tableColumn id="2" xr3:uid="{94084D0E-9EB8-4AA2-8B8F-47973A2CEB88}" name="EQUIPO" dataDxfId="4">
       <calculatedColumnFormula>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="1" xr3:uid="{B01E1C82-362B-4BF7-BCB9-D64E8D4F9629}" name="ENLACE"/>
-    <tableColumn id="3" xr3:uid="{E3AB90A5-DEAD-4B94-A136-1E8126059E3B}" name="PAIS" dataDxfId="2">
+    <tableColumn id="3" xr3:uid="{E3AB90A5-DEAD-4B94-A136-1E8126059E3B}" name="PAIS" dataDxfId="3">
       <calculatedColumnFormula>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{F2E44DAA-70E6-4294-A083-84669D9B9C01}" name="DIVISION" dataDxfId="1">
+    <tableColumn id="5" xr3:uid="{F2E44DAA-70E6-4294-A083-84669D9B9C01}" name="DIVISION" dataDxfId="2">
       <calculatedColumnFormula>Tabla1[[#This Row],[PAIS]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{864CABB9-1E94-4601-B818-3F8256A83250}" name="ANALIZAR" dataDxfId="0">
+    <tableColumn id="4" xr3:uid="{864CABB9-1E94-4601-B818-3F8256A83250}" name="ANALIZAR" dataDxfId="1">
       <calculatedColumnFormula>IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2559,7 +2750,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EC3E121-4DD2-4C5A-A60B-ED62DD98B116}">
-  <dimension ref="A1:K664"/>
+  <dimension ref="A1:K728"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.33203125" bestFit="1" customWidth="1"/>
@@ -2609,11 +2800,11 @@
         <v>SI</v>
       </c>
       <c r="H2" s="9" t="str" cm="1">
-        <f t="array" ref="H2:H37">_xlfn.UNIQUE(Tabla1[PAIS])</f>
+        <f t="array" ref="H2:H41">_xlfn.UNIQUE(Tabla1[PAIS])</f>
         <v>argentina</v>
       </c>
       <c r="I2" s="9" t="str">
-        <f t="shared" ref="I2:I29" ca="1" si="0">IF(J2&gt;TODAY(),"","X")</f>
+        <f t="shared" ref="I2:I37" ca="1" si="0">IF(J2&gt;TODAY(),"","X")</f>
         <v>X</v>
       </c>
       <c r="J2" s="10">
@@ -3563,7 +3754,7 @@
         <v>sweden</v>
       </c>
       <c r="I30" s="9" t="str">
-        <f t="shared" ref="I30:I37" ca="1" si="1">IF(J30&gt;TODAY(),"","X")</f>
+        <f t="shared" ca="1" si="0"/>
         <v>X</v>
       </c>
       <c r="J30" s="10">
@@ -3597,302 +3788,354 @@
         <v>switzerland</v>
       </c>
       <c r="I31" s="9" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>X</v>
+      </c>
+      <c r="J31" s="10">
+        <v>46230</v>
+      </c>
+      <c r="K31" s="9" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>adelaide-united-fc</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="C32" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>australia</v>
+      </c>
+      <c r="D32" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>australia</v>
+      </c>
+      <c r="E32" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="H32" s="9" t="str">
+        <v>usa</v>
+      </c>
+      <c r="I32" s="9" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>X</v>
+      </c>
+      <c r="J32" s="10">
+        <v>46074</v>
+      </c>
+      <c r="K32" s="9" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A33" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>auckland-fc</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="C33" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>australia</v>
+      </c>
+      <c r="D33" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>australia</v>
+      </c>
+      <c r="E33" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="H33" s="9" t="str">
+        <v>ireland</v>
+      </c>
+      <c r="I33" s="9" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>X</v>
+      </c>
+      <c r="J33" s="10">
+        <v>46121</v>
+      </c>
+      <c r="K33" s="9" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A34" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>brisbane-roar-fc</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="C34" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>australia</v>
+      </c>
+      <c r="D34" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>australia</v>
+      </c>
+      <c r="E34" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="H34" s="9" t="str">
+        <v>egypt</v>
+      </c>
+      <c r="I34" s="9" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>X</v>
+      </c>
+      <c r="J34" s="10">
+        <v>46121</v>
+      </c>
+      <c r="K34" s="9" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A35" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>central-coast-mariners-fc</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="C35" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>australia</v>
+      </c>
+      <c r="D35" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>australia</v>
+      </c>
+      <c r="E35" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="H35" s="9" t="str">
+        <v>cyprus</v>
+      </c>
+      <c r="I35" s="9" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>X</v>
+      </c>
+      <c r="J35" s="10">
+        <v>46284</v>
+      </c>
+      <c r="K35" s="9" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A36" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>macarthur-fc</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="C36" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>australia</v>
+      </c>
+      <c r="D36" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>australia</v>
+      </c>
+      <c r="E36" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="H36" s="9" t="str">
+        <v>hungary</v>
+      </c>
+      <c r="I36" s="9" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>X</v>
+      </c>
+      <c r="J36" s="10">
+        <v>46284</v>
+      </c>
+      <c r="K36" s="9" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A37" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>melbourne-city-fc</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="C37" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>australia</v>
+      </c>
+      <c r="D37" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>australia</v>
+      </c>
+      <c r="E37" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="H37" s="9" t="str">
+        <v>uruguay</v>
+      </c>
+      <c r="I37" s="9" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>X</v>
+      </c>
+      <c r="J37" s="10">
+        <v>46284</v>
+      </c>
+      <c r="K37" s="9" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A38" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>melbourne-victory-fc</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="C38" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>australia</v>
+      </c>
+      <c r="D38" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>australia</v>
+      </c>
+      <c r="E38" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="H38" s="9" t="str">
+        <v>ukraine</v>
+      </c>
+      <c r="I38" s="9" t="str">
+        <f t="shared" ref="I38:I41" ca="1" si="1">IF(J38&gt;TODAY(),"","X")</f>
+        <v>X</v>
+      </c>
+      <c r="J38" s="11">
+        <v>46299</v>
+      </c>
+      <c r="K38" s="9" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A39" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>newcastle-jets-fc</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="C39" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>australia</v>
+      </c>
+      <c r="D39" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>australia</v>
+      </c>
+      <c r="E39" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="H39" s="9" t="str">
+        <v>japan</v>
+      </c>
+      <c r="I39" s="9" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>X</v>
       </c>
-      <c r="J31" s="10">
-        <v>46230</v>
-      </c>
-      <c r="K31" s="9" t="s">
+      <c r="J39" s="11">
+        <v>46299</v>
+      </c>
+      <c r="K39" s="9" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A32" t="str">
-        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>adelaide-united-fc</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="C32" t="str">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A40" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>perth-glory-fc</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="C40" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>australia</v>
       </c>
-      <c r="D32" t="str">
+      <c r="D40" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
         <v>australia</v>
       </c>
-      <c r="E32" s="8" t="str">
+      <c r="E40" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>NO</v>
       </c>
-      <c r="H32" s="9" t="str">
-        <v>usa</v>
-      </c>
-      <c r="I32" s="9" t="str">
+      <c r="H40" s="9" t="str">
+        <v>south-korea</v>
+      </c>
+      <c r="I40" s="9" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>X</v>
       </c>
-      <c r="J32" s="10">
-        <v>46074</v>
-      </c>
-      <c r="K32" s="9" t="s">
+      <c r="J40" s="11">
+        <v>46299</v>
+      </c>
+      <c r="K40" s="9" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A33" t="str">
-        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>auckland-fc</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>503</v>
-      </c>
-      <c r="C33" t="str">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A41" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>sydney-fc</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="C41" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>australia</v>
       </c>
-      <c r="D33" t="str">
+      <c r="D41" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
         <v>australia</v>
       </c>
-      <c r="E33" s="8" t="str">
+      <c r="E41" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>NO</v>
       </c>
-      <c r="H33" s="9" t="str">
-        <v>ireland</v>
-      </c>
-      <c r="I33" s="9" t="str">
+      <c r="H41" s="9" t="str">
+        <v>china</v>
+      </c>
+      <c r="I41" s="9" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>X</v>
       </c>
-      <c r="J33" s="10">
-        <v>46121</v>
-      </c>
-      <c r="K33" s="9" t="s">
+      <c r="J41" s="11">
+        <v>46299</v>
+      </c>
+      <c r="K41" s="9" t="s">
         <v>525</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A34" t="str">
-        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>brisbane-roar-fc</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>504</v>
-      </c>
-      <c r="C34" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>australia</v>
-      </c>
-      <c r="D34" t="str">
-        <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>australia</v>
-      </c>
-      <c r="E34" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
-      </c>
-      <c r="H34" s="9" t="str">
-        <v>egypt</v>
-      </c>
-      <c r="I34" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>X</v>
-      </c>
-      <c r="J34" s="10">
-        <v>46121</v>
-      </c>
-      <c r="K34" s="9" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" t="str">
-        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>central-coast-mariners-fc</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>505</v>
-      </c>
-      <c r="C35" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>australia</v>
-      </c>
-      <c r="D35" t="str">
-        <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>australia</v>
-      </c>
-      <c r="E35" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
-      </c>
-      <c r="H35" s="9" t="str">
-        <v>cyprus</v>
-      </c>
-      <c r="I35" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>X</v>
-      </c>
-      <c r="J35" s="10">
-        <v>46284</v>
-      </c>
-      <c r="K35" s="9" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A36" t="str">
-        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>macarthur-fc</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="C36" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>australia</v>
-      </c>
-      <c r="D36" t="str">
-        <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>australia</v>
-      </c>
-      <c r="E36" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
-      </c>
-      <c r="H36" s="9" t="str">
-        <v>hungary</v>
-      </c>
-      <c r="I36" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>X</v>
-      </c>
-      <c r="J36" s="10">
-        <v>46284</v>
-      </c>
-      <c r="K36" s="9" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A37" t="str">
-        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>melbourne-city-fc</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>507</v>
-      </c>
-      <c r="C37" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>australia</v>
-      </c>
-      <c r="D37" t="str">
-        <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>australia</v>
-      </c>
-      <c r="E37" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
-      </c>
-      <c r="H37" s="9" t="str">
-        <v>uruguay</v>
-      </c>
-      <c r="I37" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>X</v>
-      </c>
-      <c r="J37" s="10">
-        <v>46284</v>
-      </c>
-      <c r="K37" s="9" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A38" t="str">
-        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>melbourne-victory-fc</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>508</v>
-      </c>
-      <c r="C38" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>australia</v>
-      </c>
-      <c r="D38" t="str">
-        <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>australia</v>
-      </c>
-      <c r="E38" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A39" t="str">
-        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>newcastle-jets-fc</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>509</v>
-      </c>
-      <c r="C39" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>australia</v>
-      </c>
-      <c r="D39" t="str">
-        <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>australia</v>
-      </c>
-      <c r="E39" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A40" t="str">
-        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>perth-glory-fc</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>510</v>
-      </c>
-      <c r="C40" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>australia</v>
-      </c>
-      <c r="D40" t="str">
-        <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>australia</v>
-      </c>
-      <c r="E40" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A41" t="str">
-        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>sydney-fc</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>511</v>
-      </c>
-      <c r="C41" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>australia</v>
-      </c>
-      <c r="D41" t="str">
-        <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>australia</v>
-      </c>
-      <c r="E41" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
@@ -16051,890 +16294,2234 @@
       </c>
     </row>
     <row r="623" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A623" s="11" t="str">
+      <c r="A623" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
         <v>aek-larnaca-fc</v>
       </c>
       <c r="B623" t="s">
         <v>629</v>
       </c>
-      <c r="C623" s="11" t="str">
+      <c r="C623" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>cyprus</v>
       </c>
-      <c r="D623" s="11" t="str">
+      <c r="D623" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
         <v>cyprus</v>
       </c>
-      <c r="E623" s="12" t="str">
+      <c r="E623" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="624" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A624" s="11" t="str">
+      <c r="A624" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
         <v>ael-limassol</v>
       </c>
       <c r="B624" t="s">
         <v>630</v>
       </c>
-      <c r="C624" s="11" t="str">
+      <c r="C624" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>cyprus</v>
       </c>
-      <c r="D624" s="11" t="str">
+      <c r="D624" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
         <v>cyprus</v>
       </c>
-      <c r="E624" s="12" t="str">
+      <c r="E624" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="625" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A625" s="11" t="str">
+      <c r="A625" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
         <v>anorthosis-famagusta-fc</v>
       </c>
       <c r="B625" t="s">
         <v>631</v>
       </c>
-      <c r="C625" s="11" t="str">
+      <c r="C625" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>cyprus</v>
       </c>
-      <c r="D625" s="11" t="str">
+      <c r="D625" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
         <v>cyprus</v>
       </c>
-      <c r="E625" s="12" t="str">
+      <c r="E625" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="626" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A626" s="11" t="str">
+      <c r="A626" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
         <v>apoel-fc</v>
       </c>
       <c r="B626" t="s">
         <v>632</v>
       </c>
-      <c r="C626" s="11" t="str">
+      <c r="C626" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>cyprus</v>
       </c>
-      <c r="D626" s="11" t="str">
+      <c r="D626" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
         <v>cyprus</v>
       </c>
-      <c r="E626" s="12" t="str">
+      <c r="E626" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="627" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A627" s="11" t="str">
+      <c r="A627" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
         <v>apollon-limassol</v>
       </c>
       <c r="B627" t="s">
         <v>633</v>
       </c>
-      <c r="C627" s="11" t="str">
+      <c r="C627" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>cyprus</v>
       </c>
-      <c r="D627" s="11" t="str">
+      <c r="D627" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
         <v>cyprus</v>
       </c>
-      <c r="E627" s="12" t="str">
+      <c r="E627" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="628" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A628" s="11" t="str">
+      <c r="A628" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
         <v>aris-limassol-fc</v>
       </c>
       <c r="B628" t="s">
         <v>634</v>
       </c>
-      <c r="C628" s="11" t="str">
+      <c r="C628" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>cyprus</v>
       </c>
-      <c r="D628" s="11" t="str">
+      <c r="D628" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
         <v>cyprus</v>
       </c>
-      <c r="E628" s="12" t="str">
+      <c r="E628" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="629" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A629" s="11" t="str">
+      <c r="A629" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
         <v>karmiotissa-fc</v>
       </c>
       <c r="B629" t="s">
         <v>635</v>
       </c>
-      <c r="C629" s="11" t="str">
+      <c r="C629" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>cyprus</v>
       </c>
-      <c r="D629" s="11" t="str">
+      <c r="D629" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
         <v>cyprus</v>
       </c>
-      <c r="E629" s="12" t="str">
+      <c r="E629" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="630" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A630" s="11" t="str">
+      <c r="A630" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
         <v>krasava-eny-ypsonas-fc</v>
       </c>
       <c r="B630" t="s">
         <v>636</v>
       </c>
-      <c r="C630" s="11" t="str">
+      <c r="C630" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>cyprus</v>
       </c>
-      <c r="D630" s="11" t="str">
+      <c r="D630" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
         <v>cyprus</v>
       </c>
-      <c r="E630" s="12" t="str">
+      <c r="E630" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="631" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A631" s="11" t="str">
+      <c r="A631" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
         <v>nea-salamis-famagusta-fc</v>
       </c>
       <c r="B631" t="s">
         <v>637</v>
       </c>
-      <c r="C631" s="11" t="str">
+      <c r="C631" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>cyprus</v>
       </c>
-      <c r="D631" s="11" t="str">
+      <c r="D631" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
         <v>cyprus</v>
       </c>
-      <c r="E631" s="12" t="str">
+      <c r="E631" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="632" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A632" s="11" t="str">
+      <c r="A632" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
         <v>olympiakos-nicosia</v>
       </c>
       <c r="B632" t="s">
         <v>638</v>
       </c>
-      <c r="C632" s="11" t="str">
+      <c r="C632" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>cyprus</v>
       </c>
-      <c r="D632" s="11" t="str">
+      <c r="D632" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
         <v>cyprus</v>
       </c>
-      <c r="E632" s="12" t="str">
+      <c r="E632" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="633" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A633" s="11" t="str">
+      <c r="A633" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
         <v>ac-omonia</v>
       </c>
       <c r="B633" t="s">
         <v>639</v>
       </c>
-      <c r="C633" s="11" t="str">
+      <c r="C633" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>cyprus</v>
       </c>
-      <c r="D633" s="11" t="str">
+      <c r="D633" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
         <v>cyprus</v>
       </c>
-      <c r="E633" s="12" t="str">
+      <c r="E633" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="634" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A634" s="11" t="str">
+      <c r="A634" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
         <v>pac-omonia-29m</v>
       </c>
       <c r="B634" t="s">
         <v>640</v>
       </c>
-      <c r="C634" s="11" t="str">
+      <c r="C634" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>cyprus</v>
       </c>
-      <c r="D634" s="11" t="str">
+      <c r="D634" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
         <v>cyprus</v>
       </c>
-      <c r="E634" s="12" t="str">
+      <c r="E634" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="635" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A635" s="11" t="str">
+      <c r="A635" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
         <v>omonia-aradippou</v>
       </c>
       <c r="B635" t="s">
         <v>641</v>
       </c>
-      <c r="C635" s="11" t="str">
+      <c r="C635" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>cyprus</v>
       </c>
-      <c r="D635" s="11" t="str">
+      <c r="D635" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
         <v>cyprus</v>
       </c>
-      <c r="E635" s="12" t="str">
+      <c r="E635" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="636" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A636" s="11" t="str">
+      <c r="A636" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
         <v>pafos-fc</v>
       </c>
       <c r="B636" t="s">
         <v>642</v>
       </c>
-      <c r="C636" s="11" t="str">
+      <c r="C636" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>cyprus</v>
       </c>
-      <c r="D636" s="11" t="str">
+      <c r="D636" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
         <v>cyprus</v>
       </c>
-      <c r="E636" s="12" t="str">
+      <c r="E636" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="637" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A637" s="11" t="str">
+      <c r="A637" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
         <v>debrecen</v>
       </c>
       <c r="B637" t="s">
         <v>643</v>
       </c>
-      <c r="C637" s="11" t="str">
+      <c r="C637" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>hungary</v>
       </c>
-      <c r="D637" s="11" t="str">
+      <c r="D637" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
         <v>hungary</v>
       </c>
-      <c r="E637" s="12" t="str">
+      <c r="E637" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="638" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A638" s="11" t="str">
+      <c r="A638" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
         <v>ferencvaros</v>
       </c>
       <c r="B638" t="s">
         <v>644</v>
       </c>
-      <c r="C638" s="11" t="str">
+      <c r="C638" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>hungary</v>
       </c>
-      <c r="D638" s="11" t="str">
+      <c r="D638" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
         <v>hungary</v>
       </c>
-      <c r="E638" s="12" t="str">
+      <c r="E638" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="639" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A639" s="11" t="str">
+      <c r="A639" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
         <v>gyori-eto-fc</v>
       </c>
       <c r="B639" t="s">
         <v>645</v>
       </c>
-      <c r="C639" s="11" t="str">
+      <c r="C639" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>hungary</v>
       </c>
-      <c r="D639" s="11" t="str">
+      <c r="D639" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
         <v>hungary</v>
       </c>
-      <c r="E639" s="12" t="str">
+      <c r="E639" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="640" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A640" s="11" t="str">
+      <c r="A640" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
         <v>budapest-honved-fc</v>
       </c>
       <c r="B640" t="s">
         <v>646</v>
       </c>
-      <c r="C640" s="11" t="str">
+      <c r="C640" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>hungary</v>
       </c>
-      <c r="D640" s="11" t="str">
+      <c r="D640" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
         <v>hungary</v>
       </c>
-      <c r="E640" s="12" t="str">
+      <c r="E640" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="641" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A641" s="11" t="str">
+      <c r="A641" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
         <v>kisvarda-fc</v>
       </c>
       <c r="B641" t="s">
         <v>647</v>
       </c>
-      <c r="C641" s="11" t="str">
+      <c r="C641" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>hungary</v>
       </c>
-      <c r="D641" s="11" t="str">
+      <c r="D641" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
         <v>hungary</v>
       </c>
-      <c r="E641" s="12" t="str">
+      <c r="E641" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="642" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A642" s="11" t="str">
+      <c r="A642" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
         <v>mtk-budapest-fc</v>
       </c>
       <c r="B642" t="s">
         <v>648</v>
       </c>
-      <c r="C642" s="11" t="str">
+      <c r="C642" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>hungary</v>
       </c>
-      <c r="D642" s="11" t="str">
+      <c r="D642" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
         <v>hungary</v>
       </c>
-      <c r="E642" s="12" t="str">
+      <c r="E642" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="643" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A643" s="11" t="str">
+      <c r="A643" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
         <v>nyiregyhaza-spartacus-fc</v>
       </c>
       <c r="B643" t="s">
         <v>649</v>
       </c>
-      <c r="C643" s="11" t="str">
+      <c r="C643" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>hungary</v>
       </c>
-      <c r="D643" s="11" t="str">
+      <c r="D643" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
         <v>hungary</v>
       </c>
-      <c r="E643" s="12" t="str">
+      <c r="E643" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="644" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A644" s="11" t="str">
+      <c r="A644" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
         <v>paksi-fc</v>
       </c>
       <c r="B644" t="s">
         <v>650</v>
       </c>
-      <c r="C644" s="11" t="str">
+      <c r="C644" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>hungary</v>
       </c>
-      <c r="D644" s="11" t="str">
+      <c r="D644" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
         <v>hungary</v>
       </c>
-      <c r="E644" s="12" t="str">
+      <c r="E644" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="645" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A645" s="11" t="str">
+      <c r="A645" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
         <v>puskas-akademia-fc</v>
       </c>
       <c r="B645" t="s">
         <v>651</v>
       </c>
-      <c r="C645" s="11" t="str">
+      <c r="C645" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>hungary</v>
       </c>
-      <c r="D645" s="11" t="str">
+      <c r="D645" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
         <v>hungary</v>
       </c>
-      <c r="E645" s="12" t="str">
+      <c r="E645" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="646" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A646" s="11" t="str">
+      <c r="A646" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
         <v>ujpest-fc</v>
       </c>
       <c r="B646" t="s">
         <v>652</v>
       </c>
-      <c r="C646" s="11" t="str">
+      <c r="C646" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>hungary</v>
       </c>
-      <c r="D646" s="11" t="str">
+      <c r="D646" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
         <v>hungary</v>
       </c>
-      <c r="E646" s="12" t="str">
+      <c r="E646" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="647" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A647" s="11" t="str">
+      <c r="A647" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
         <v>vasas-sc</v>
       </c>
       <c r="B647" t="s">
         <v>653</v>
       </c>
-      <c r="C647" s="11" t="str">
+      <c r="C647" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>hungary</v>
       </c>
-      <c r="D647" s="11" t="str">
+      <c r="D647" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
         <v>hungary</v>
       </c>
-      <c r="E647" s="12" t="str">
+      <c r="E647" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="648" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A648" s="11" t="str">
+      <c r="A648" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
         <v>zalaegerszeg-te</v>
       </c>
       <c r="B648" t="s">
         <v>654</v>
       </c>
-      <c r="C648" s="11" t="str">
+      <c r="C648" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>hungary</v>
       </c>
-      <c r="D648" s="11" t="str">
+      <c r="D648" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
         <v>hungary</v>
       </c>
-      <c r="E648" s="12" t="str">
+      <c r="E648" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="649" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A649" s="11" t="str">
+      <c r="A649" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
         <v>albion-fc</v>
       </c>
       <c r="B649" t="s">
         <v>655</v>
       </c>
-      <c r="C649" s="11" t="str">
+      <c r="C649" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>uruguay</v>
       </c>
-      <c r="D649" s="11" t="str">
+      <c r="D649" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
         <v>uruguay</v>
       </c>
-      <c r="E649" s="12" t="str">
+      <c r="E649" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="650" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A650" s="11" t="str">
+      <c r="A650" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
         <v>boston-river</v>
       </c>
       <c r="B650" t="s">
         <v>656</v>
       </c>
-      <c r="C650" s="11" t="str">
+      <c r="C650" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>uruguay</v>
       </c>
-      <c r="D650" s="11" t="str">
+      <c r="D650" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
         <v>uruguay</v>
       </c>
-      <c r="E650" s="12" t="str">
+      <c r="E650" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="651" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A651" s="11" t="str">
+      <c r="A651" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
         <v>central-espanol</v>
       </c>
       <c r="B651" t="s">
         <v>657</v>
       </c>
-      <c r="C651" s="11" t="str">
+      <c r="C651" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>uruguay</v>
       </c>
-      <c r="D651" s="11" t="str">
+      <c r="D651" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
         <v>uruguay</v>
       </c>
-      <c r="E651" s="12" t="str">
+      <c r="E651" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="652" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A652" s="11" t="str">
+      <c r="A652" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
         <v>club-atletico-cerro</v>
       </c>
       <c r="B652" t="s">
         <v>658</v>
       </c>
-      <c r="C652" s="11" t="str">
+      <c r="C652" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>uruguay</v>
       </c>
-      <c r="D652" s="11" t="str">
+      <c r="D652" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
         <v>uruguay</v>
       </c>
-      <c r="E652" s="12" t="str">
+      <c r="E652" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="653" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A653" s="11" t="str">
+      <c r="A653" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
         <v>cerro-largo-fc</v>
       </c>
       <c r="B653" t="s">
         <v>659</v>
       </c>
-      <c r="C653" s="11" t="str">
+      <c r="C653" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>uruguay</v>
       </c>
-      <c r="D653" s="11" t="str">
+      <c r="D653" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
         <v>uruguay</v>
       </c>
-      <c r="E653" s="12" t="str">
+      <c r="E653" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="654" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A654" s="11" t="str">
+      <c r="A654" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
         <v>danubio-fc</v>
       </c>
       <c r="B654" t="s">
         <v>660</v>
       </c>
-      <c r="C654" s="11" t="str">
+      <c r="C654" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>uruguay</v>
       </c>
-      <c r="D654" s="11" t="str">
+      <c r="D654" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
         <v>uruguay</v>
       </c>
-      <c r="E654" s="12" t="str">
+      <c r="E654" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="655" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A655" s="11" t="str">
+      <c r="A655" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
         <v>defensor-sporting</v>
       </c>
       <c r="B655" t="s">
         <v>661</v>
       </c>
-      <c r="C655" s="11" t="str">
+      <c r="C655" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>uruguay</v>
       </c>
-      <c r="D655" s="11" t="str">
+      <c r="D655" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
         <v>uruguay</v>
       </c>
-      <c r="E655" s="12" t="str">
+      <c r="E655" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="656" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A656" s="11" t="str">
+      <c r="A656" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
         <v>juventud-de-las-piedras</v>
       </c>
       <c r="B656" t="s">
         <v>662</v>
       </c>
-      <c r="C656" s="11" t="str">
+      <c r="C656" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>uruguay</v>
       </c>
-      <c r="D656" s="11" t="str">
+      <c r="D656" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
         <v>uruguay</v>
       </c>
-      <c r="E656" s="12" t="str">
+      <c r="E656" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="657" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A657" s="11" t="str">
+      <c r="A657" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
         <v>liverpool-fc-montevideo</v>
       </c>
       <c r="B657" t="s">
         <v>663</v>
       </c>
-      <c r="C657" s="11" t="str">
+      <c r="C657" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>uruguay</v>
       </c>
-      <c r="D657" s="11" t="str">
+      <c r="D657" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
         <v>uruguay</v>
       </c>
-      <c r="E657" s="12" t="str">
+      <c r="E657" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="658" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A658" s="11" t="str">
+      <c r="A658" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
         <v>deportivo-maldonado</v>
       </c>
       <c r="B658" t="s">
         <v>664</v>
       </c>
-      <c r="C658" s="11" t="str">
+      <c r="C658" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>uruguay</v>
       </c>
-      <c r="D658" s="11" t="str">
+      <c r="D658" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
         <v>uruguay</v>
       </c>
-      <c r="E658" s="12" t="str">
+      <c r="E658" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="659" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A659" s="11" t="str">
+      <c r="A659" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
         <v>montevideo-city-torque</v>
       </c>
       <c r="B659" t="s">
         <v>665</v>
       </c>
-      <c r="C659" s="11" t="str">
+      <c r="C659" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>uruguay</v>
       </c>
-      <c r="D659" s="11" t="str">
+      <c r="D659" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
         <v>uruguay</v>
       </c>
-      <c r="E659" s="12" t="str">
+      <c r="E659" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="660" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A660" s="11" t="str">
+      <c r="A660" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
         <v>club-nacional-de-football</v>
       </c>
       <c r="B660" t="s">
         <v>666</v>
       </c>
-      <c r="C660" s="11" t="str">
+      <c r="C660" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>uruguay</v>
       </c>
-      <c r="D660" s="11" t="str">
+      <c r="D660" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
         <v>uruguay</v>
       </c>
-      <c r="E660" s="12" t="str">
+      <c r="E660" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="661" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A661" s="11" t="str">
+      <c r="A661" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
         <v>penarol</v>
       </c>
       <c r="B661" t="s">
         <v>667</v>
       </c>
-      <c r="C661" s="11" t="str">
+      <c r="C661" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>uruguay</v>
       </c>
-      <c r="D661" s="11" t="str">
+      <c r="D661" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
         <v>uruguay</v>
       </c>
-      <c r="E661" s="12" t="str">
+      <c r="E661" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="662" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A662" s="11" t="str">
+      <c r="A662" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
         <v>club-atletico-progreso</v>
       </c>
       <c r="B662" t="s">
         <v>668</v>
       </c>
-      <c r="C662" s="11" t="str">
+      <c r="C662" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>uruguay</v>
       </c>
-      <c r="D662" s="11" t="str">
+      <c r="D662" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
         <v>uruguay</v>
       </c>
-      <c r="E662" s="12" t="str">
+      <c r="E662" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="663" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A663" s="11" t="str">
+      <c r="A663" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
         <v>racing-club-de-montevideo</v>
       </c>
       <c r="B663" t="s">
         <v>669</v>
       </c>
-      <c r="C663" s="11" t="str">
+      <c r="C663" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>uruguay</v>
       </c>
-      <c r="D663" s="11" t="str">
+      <c r="D663" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
         <v>uruguay</v>
       </c>
-      <c r="E663" s="12" t="str">
+      <c r="E663" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="664" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A664" s="11" t="str">
+      <c r="A664" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
         <v>montevideo-wanderers-fc</v>
       </c>
       <c r="B664" t="s">
         <v>670</v>
       </c>
-      <c r="C664" s="11" t="str">
+      <c r="C664" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>uruguay</v>
       </c>
-      <c r="D664" s="11" t="str">
+      <c r="D664" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
         <v>uruguay</v>
       </c>
-      <c r="E664" s="12" t="str">
+      <c r="E664" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="665" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A665" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>fsc-bukovyna-chernivtsi</v>
+      </c>
+      <c r="B665" t="s">
+        <v>671</v>
+      </c>
+      <c r="C665" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>ukraine</v>
+      </c>
+      <c r="D665" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>ukraine</v>
+      </c>
+      <c r="E665" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="666" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A666" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>fc-chornomorets-odessa</v>
+      </c>
+      <c r="B666" t="s">
+        <v>672</v>
+      </c>
+      <c r="C666" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>ukraine</v>
+      </c>
+      <c r="D666" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>ukraine</v>
+      </c>
+      <c r="E666" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="667" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A667" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>fc-dynamo-kyiv</v>
+      </c>
+      <c r="B667" t="s">
+        <v>673</v>
+      </c>
+      <c r="C667" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>ukraine</v>
+      </c>
+      <c r="D667" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>ukraine</v>
+      </c>
+      <c r="E667" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="668" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A668" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>fc-epitsentr-kamianets-podilskyi</v>
+      </c>
+      <c r="B668" t="s">
+        <v>674</v>
+      </c>
+      <c r="C668" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>ukraine</v>
+      </c>
+      <c r="D668" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>ukraine</v>
+      </c>
+      <c r="E668" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="669" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A669" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>fc-kharkiv</v>
+      </c>
+      <c r="B669" t="s">
+        <v>675</v>
+      </c>
+      <c r="C669" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>ukraine</v>
+      </c>
+      <c r="D669" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>ukraine</v>
+      </c>
+      <c r="E669" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="670" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A670" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>fc-karpaty-lviv</v>
+      </c>
+      <c r="B670" t="s">
+        <v>676</v>
+      </c>
+      <c r="C670" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>ukraine</v>
+      </c>
+      <c r="D670" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>ukraine</v>
+      </c>
+      <c r="E670" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="671" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A671" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>fc-kolos-kovalivka</v>
+      </c>
+      <c r="B671" t="s">
+        <v>677</v>
+      </c>
+      <c r="C671" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>ukraine</v>
+      </c>
+      <c r="D671" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>ukraine</v>
+      </c>
+      <c r="E671" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="672" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A672" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>fc-kryvbas-kryvyi-rih</v>
+      </c>
+      <c r="B672" t="s">
+        <v>678</v>
+      </c>
+      <c r="C672" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>ukraine</v>
+      </c>
+      <c r="D672" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>ukraine</v>
+      </c>
+      <c r="E672" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="673" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A673" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>fc-kudrivka</v>
+      </c>
+      <c r="B673" t="s">
+        <v>679</v>
+      </c>
+      <c r="C673" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>ukraine</v>
+      </c>
+      <c r="D673" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>ukraine</v>
+      </c>
+      <c r="E673" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="674" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A674" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>fc-livyi-bereh-kyiv</v>
+      </c>
+      <c r="B674" t="s">
+        <v>680</v>
+      </c>
+      <c r="C674" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>ukraine</v>
+      </c>
+      <c r="D674" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>ukraine</v>
+      </c>
+      <c r="E674" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="675" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A675" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>fc-lnz-cherkasy</v>
+      </c>
+      <c r="B675" t="s">
+        <v>681</v>
+      </c>
+      <c r="C675" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>ukraine</v>
+      </c>
+      <c r="D675" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>ukraine</v>
+      </c>
+      <c r="E675" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="676" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A676" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>fc-obolon-kyiv</v>
+      </c>
+      <c r="B676" t="s">
+        <v>682</v>
+      </c>
+      <c r="C676" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>ukraine</v>
+      </c>
+      <c r="D676" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>ukraine</v>
+      </c>
+      <c r="E676" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="677" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A677" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>fc-polissya-zhytomyr</v>
+      </c>
+      <c r="B677" t="s">
+        <v>683</v>
+      </c>
+      <c r="C677" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>ukraine</v>
+      </c>
+      <c r="D677" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>ukraine</v>
+      </c>
+      <c r="E677" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="678" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A678" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>fc-shakhtar-donetsk</v>
+      </c>
+      <c r="B678" t="s">
+        <v>684</v>
+      </c>
+      <c r="C678" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>ukraine</v>
+      </c>
+      <c r="D678" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>ukraine</v>
+      </c>
+      <c r="E678" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="679" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A679" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>nk-veres-rivne</v>
+      </c>
+      <c r="B679" t="s">
+        <v>685</v>
+      </c>
+      <c r="C679" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>ukraine</v>
+      </c>
+      <c r="D679" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>ukraine</v>
+      </c>
+      <c r="E679" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="680" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A680" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>fc-zorya-luhansk</v>
+      </c>
+      <c r="B680" t="s">
+        <v>686</v>
+      </c>
+      <c r="C680" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>ukraine</v>
+      </c>
+      <c r="D680" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>ukraine</v>
+      </c>
+      <c r="E680" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="681" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A681" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>avispa-fukuoka</v>
+      </c>
+      <c r="B681" t="s">
+        <v>687</v>
+      </c>
+      <c r="C681" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>japan</v>
+      </c>
+      <c r="D681" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>japan</v>
+      </c>
+      <c r="E681" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="682" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A682" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>cerezo-osaka</v>
+      </c>
+      <c r="B682" t="s">
+        <v>688</v>
+      </c>
+      <c r="C682" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>japan</v>
+      </c>
+      <c r="D682" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>japan</v>
+      </c>
+      <c r="E682" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="683" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A683" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>fagiano-okayama</v>
+      </c>
+      <c r="B683" t="s">
+        <v>689</v>
+      </c>
+      <c r="C683" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>japan</v>
+      </c>
+      <c r="D683" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>japan</v>
+      </c>
+      <c r="E683" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="684" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A684" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>gamba-osaka</v>
+      </c>
+      <c r="B684" t="s">
+        <v>690</v>
+      </c>
+      <c r="C684" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>japan</v>
+      </c>
+      <c r="D684" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>japan</v>
+      </c>
+      <c r="E684" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="685" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A685" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>sanfreece-hiroshima</v>
+      </c>
+      <c r="B685" t="s">
+        <v>691</v>
+      </c>
+      <c r="C685" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>japan</v>
+      </c>
+      <c r="D685" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>japan</v>
+      </c>
+      <c r="E685" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="686" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A686" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>jef-united-chiba</v>
+      </c>
+      <c r="B686" t="s">
+        <v>692</v>
+      </c>
+      <c r="C686" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>japan</v>
+      </c>
+      <c r="D686" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>japan</v>
+      </c>
+      <c r="E686" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="687" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A687" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>kashima-antlers</v>
+      </c>
+      <c r="B687" t="s">
+        <v>693</v>
+      </c>
+      <c r="C687" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>japan</v>
+      </c>
+      <c r="D687" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>japan</v>
+      </c>
+      <c r="E687" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="688" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A688" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>kashiwa-reysol</v>
+      </c>
+      <c r="B688" t="s">
+        <v>694</v>
+      </c>
+      <c r="C688" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>japan</v>
+      </c>
+      <c r="D688" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>japan</v>
+      </c>
+      <c r="E688" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="689" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A689" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>kawasaki-frontale</v>
+      </c>
+      <c r="B689" t="s">
+        <v>695</v>
+      </c>
+      <c r="C689" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>japan</v>
+      </c>
+      <c r="D689" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>japan</v>
+      </c>
+      <c r="E689" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="690" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A690" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>vissel-kobe</v>
+      </c>
+      <c r="B690" t="s">
+        <v>696</v>
+      </c>
+      <c r="C690" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>japan</v>
+      </c>
+      <c r="D690" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>japan</v>
+      </c>
+      <c r="E690" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="691" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A691" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>kyoto-sanga-fc</v>
+      </c>
+      <c r="B691" t="s">
+        <v>697</v>
+      </c>
+      <c r="C691" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>japan</v>
+      </c>
+      <c r="D691" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>japan</v>
+      </c>
+      <c r="E691" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="692" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A692" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>fc-machida-zelvia</v>
+      </c>
+      <c r="B692" t="s">
+        <v>698</v>
+      </c>
+      <c r="C692" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>japan</v>
+      </c>
+      <c r="D692" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>japan</v>
+      </c>
+      <c r="E692" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="693" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A693" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>mito-hollyhock</v>
+      </c>
+      <c r="B693" t="s">
+        <v>699</v>
+      </c>
+      <c r="C693" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>japan</v>
+      </c>
+      <c r="D693" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>japan</v>
+      </c>
+      <c r="E693" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="694" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A694" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>nagoya-grampus</v>
+      </c>
+      <c r="B694" t="s">
+        <v>700</v>
+      </c>
+      <c r="C694" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>japan</v>
+      </c>
+      <c r="D694" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>japan</v>
+      </c>
+      <c r="E694" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="695" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A695" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>shimizu-s-pulse</v>
+      </c>
+      <c r="B695" t="s">
+        <v>701</v>
+      </c>
+      <c r="C695" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>japan</v>
+      </c>
+      <c r="D695" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>japan</v>
+      </c>
+      <c r="E695" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="696" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A696" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>fc-tokyo</v>
+      </c>
+      <c r="B696" t="s">
+        <v>702</v>
+      </c>
+      <c r="C696" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>japan</v>
+      </c>
+      <c r="D696" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>japan</v>
+      </c>
+      <c r="E696" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="697" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A697" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>tokyo-verdy</v>
+      </c>
+      <c r="B697" t="s">
+        <v>703</v>
+      </c>
+      <c r="C697" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>japan</v>
+      </c>
+      <c r="D697" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>japan</v>
+      </c>
+      <c r="E697" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="698" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A698" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>urawa-red-diamonds</v>
+      </c>
+      <c r="B698" t="s">
+        <v>704</v>
+      </c>
+      <c r="C698" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>japan</v>
+      </c>
+      <c r="D698" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>japan</v>
+      </c>
+      <c r="E698" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="699" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A699" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>v-varen-nagasaki</v>
+      </c>
+      <c r="B699" t="s">
+        <v>705</v>
+      </c>
+      <c r="C699" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>japan</v>
+      </c>
+      <c r="D699" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>japan</v>
+      </c>
+      <c r="E699" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="700" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A700" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>yokohama-f-marinos</v>
+      </c>
+      <c r="B700" t="s">
+        <v>706</v>
+      </c>
+      <c r="C700" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>japan</v>
+      </c>
+      <c r="D700" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>japan</v>
+      </c>
+      <c r="E700" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="701" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A701" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>fc-anyang</v>
+      </c>
+      <c r="B701" t="s">
+        <v>707</v>
+      </c>
+      <c r="C701" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>south-korea</v>
+      </c>
+      <c r="D701" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>south-korea</v>
+      </c>
+      <c r="E701" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="702" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A702" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>bucheon-fc-1995</v>
+      </c>
+      <c r="B702" t="s">
+        <v>708</v>
+      </c>
+      <c r="C702" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>south-korea</v>
+      </c>
+      <c r="D702" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>south-korea</v>
+      </c>
+      <c r="E702" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="703" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A703" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>daejeon-hana-citizen</v>
+      </c>
+      <c r="B703" t="s">
+        <v>709</v>
+      </c>
+      <c r="C703" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>south-korea</v>
+      </c>
+      <c r="D703" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>south-korea</v>
+      </c>
+      <c r="E703" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="704" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A704" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>gangwon-fc</v>
+      </c>
+      <c r="B704" t="s">
+        <v>710</v>
+      </c>
+      <c r="C704" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>south-korea</v>
+      </c>
+      <c r="D704" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>south-korea</v>
+      </c>
+      <c r="E704" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="705" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A705" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>gimcheon-sangmu-fc</v>
+      </c>
+      <c r="B705" t="s">
+        <v>711</v>
+      </c>
+      <c r="C705" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>south-korea</v>
+      </c>
+      <c r="D705" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>south-korea</v>
+      </c>
+      <c r="E705" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="706" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A706" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>gwangju-fc</v>
+      </c>
+      <c r="B706" t="s">
+        <v>712</v>
+      </c>
+      <c r="C706" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>south-korea</v>
+      </c>
+      <c r="D706" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>south-korea</v>
+      </c>
+      <c r="E706" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="707" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A707" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>incheon-united</v>
+      </c>
+      <c r="B707" t="s">
+        <v>713</v>
+      </c>
+      <c r="C707" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>south-korea</v>
+      </c>
+      <c r="D707" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>south-korea</v>
+      </c>
+      <c r="E707" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="708" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A708" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>jeju-sk-fc</v>
+      </c>
+      <c r="B708" t="s">
+        <v>714</v>
+      </c>
+      <c r="C708" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>south-korea</v>
+      </c>
+      <c r="D708" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>south-korea</v>
+      </c>
+      <c r="E708" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="709" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A709" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>jeonbuk-hyundai-motors</v>
+      </c>
+      <c r="B709" t="s">
+        <v>715</v>
+      </c>
+      <c r="C709" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>south-korea</v>
+      </c>
+      <c r="D709" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>south-korea</v>
+      </c>
+      <c r="E709" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="710" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A710" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>pohang-steelers</v>
+      </c>
+      <c r="B710" t="s">
+        <v>716</v>
+      </c>
+      <c r="C710" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>south-korea</v>
+      </c>
+      <c r="D710" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>south-korea</v>
+      </c>
+      <c r="E710" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="711" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A711" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>fc-seoul</v>
+      </c>
+      <c r="B711" t="s">
+        <v>717</v>
+      </c>
+      <c r="C711" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>south-korea</v>
+      </c>
+      <c r="D711" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>south-korea</v>
+      </c>
+      <c r="E711" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="712" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A712" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>ulsan-hd-fc</v>
+      </c>
+      <c r="B712" t="s">
+        <v>718</v>
+      </c>
+      <c r="C712" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>south-korea</v>
+      </c>
+      <c r="D712" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>south-korea</v>
+      </c>
+      <c r="E712" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="713" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A713" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>beijing-guoan-fc</v>
+      </c>
+      <c r="B713" t="s">
+        <v>719</v>
+      </c>
+      <c r="C713" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>china</v>
+      </c>
+      <c r="D713" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>china</v>
+      </c>
+      <c r="E713" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="714" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A714" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>chengdu-rongcheng-fc</v>
+      </c>
+      <c r="B714" t="s">
+        <v>720</v>
+      </c>
+      <c r="C714" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>china</v>
+      </c>
+      <c r="D714" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>china</v>
+      </c>
+      <c r="E714" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="715" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A715" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>chongqing-tonglianglong-fc</v>
+      </c>
+      <c r="B715" t="s">
+        <v>721</v>
+      </c>
+      <c r="C715" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>china</v>
+      </c>
+      <c r="D715" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>china</v>
+      </c>
+      <c r="E715" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="716" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A716" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>dalian-yingbo-fc</v>
+      </c>
+      <c r="B716" t="s">
+        <v>722</v>
+      </c>
+      <c r="C716" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>china</v>
+      </c>
+      <c r="D716" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>china</v>
+      </c>
+      <c r="E716" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="717" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A717" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>henan-fc</v>
+      </c>
+      <c r="B717" t="s">
+        <v>723</v>
+      </c>
+      <c r="C717" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>china</v>
+      </c>
+      <c r="D717" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>china</v>
+      </c>
+      <c r="E717" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="718" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A718" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>liaoning-tieren-fc</v>
+      </c>
+      <c r="B718" t="s">
+        <v>724</v>
+      </c>
+      <c r="C718" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>china</v>
+      </c>
+      <c r="D718" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>china</v>
+      </c>
+      <c r="E718" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="719" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A719" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>qingdao-hainiu-fc</v>
+      </c>
+      <c r="B719" t="s">
+        <v>725</v>
+      </c>
+      <c r="C719" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>china</v>
+      </c>
+      <c r="D719" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>china</v>
+      </c>
+      <c r="E719" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="720" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A720" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>qingdao-west-coast-fc</v>
+      </c>
+      <c r="B720" t="s">
+        <v>726</v>
+      </c>
+      <c r="C720" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>china</v>
+      </c>
+      <c r="D720" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>china</v>
+      </c>
+      <c r="E720" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="721" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A721" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>shandong-taishan-fc</v>
+      </c>
+      <c r="B721" t="s">
+        <v>727</v>
+      </c>
+      <c r="C721" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>china</v>
+      </c>
+      <c r="D721" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>china</v>
+      </c>
+      <c r="E721" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="722" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A722" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>shanghai-port-fc</v>
+      </c>
+      <c r="B722" t="s">
+        <v>728</v>
+      </c>
+      <c r="C722" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>china</v>
+      </c>
+      <c r="D722" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>china</v>
+      </c>
+      <c r="E722" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="723" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A723" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>shanghai-shenhua-fc</v>
+      </c>
+      <c r="B723" t="s">
+        <v>729</v>
+      </c>
+      <c r="C723" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>china</v>
+      </c>
+      <c r="D723" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>china</v>
+      </c>
+      <c r="E723" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="724" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A724" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>shenzhen-peng-city-fc</v>
+      </c>
+      <c r="B724" t="s">
+        <v>730</v>
+      </c>
+      <c r="C724" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>china</v>
+      </c>
+      <c r="D724" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>china</v>
+      </c>
+      <c r="E724" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="725" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A725" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>tianjin-jinmen-tiger-fc</v>
+      </c>
+      <c r="B725" t="s">
+        <v>731</v>
+      </c>
+      <c r="C725" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>china</v>
+      </c>
+      <c r="D725" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>china</v>
+      </c>
+      <c r="E725" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="726" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A726" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>wuhan-three-towns-fc</v>
+      </c>
+      <c r="B726" t="s">
+        <v>732</v>
+      </c>
+      <c r="C726" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>china</v>
+      </c>
+      <c r="D726" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>china</v>
+      </c>
+      <c r="E726" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="727" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A727" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>yunnan-yukun-fc</v>
+      </c>
+      <c r="B727" t="s">
+        <v>733</v>
+      </c>
+      <c r="C727" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>china</v>
+      </c>
+      <c r="D727" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>china</v>
+      </c>
+      <c r="E727" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="728" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A728" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>zhejiang-professional-fc</v>
+      </c>
+      <c r="B728" t="s">
+        <v>734</v>
+      </c>
+      <c r="C728" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>china</v>
+      </c>
+      <c r="D728" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>china</v>
+      </c>
+      <c r="E728" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="K2:K37">
-    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="act">
+  <conditionalFormatting sqref="K2:K41">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="act">
       <formula>NOT(ISERROR(SEARCH("act",K2)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/enlaces_equipos.xlsx
+++ b/enlaces_equipos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose-\Trabajo\statsFutbol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E7ED5CF-1E35-4409-88C4-9D7D7B9659F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3483EA1-0B06-4099-B87E-78E02DAE3106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{474EBA83-D6A0-4565-BEB0-BC6B2AA992C1}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="735">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="736">
   <si>
     <t>EQUIPO</t>
   </si>
@@ -2263,6 +2263,9 @@
   </si>
   <si>
     <t>rest-of-the-world/china/zhejiang-professional-fc</t>
+  </si>
+  <si>
+    <t>germany_b</t>
   </si>
 </sst>
 </file>
@@ -9292,9 +9295,8 @@
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>germany</v>
       </c>
-      <c r="D288" t="str">
-        <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>germany</v>
+      <c r="D288" t="s">
+        <v>735</v>
       </c>
       <c r="E288" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -9313,9 +9315,8 @@
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>germany</v>
       </c>
-      <c r="D289" t="str">
-        <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>germany</v>
+      <c r="D289" t="s">
+        <v>735</v>
       </c>
       <c r="E289" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -9334,9 +9335,8 @@
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>germany</v>
       </c>
-      <c r="D290" t="str">
-        <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>germany</v>
+      <c r="D290" t="s">
+        <v>735</v>
       </c>
       <c r="E290" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -9355,9 +9355,8 @@
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>germany</v>
       </c>
-      <c r="D291" t="str">
-        <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>germany</v>
+      <c r="D291" t="s">
+        <v>735</v>
       </c>
       <c r="E291" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -9376,9 +9375,8 @@
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>germany</v>
       </c>
-      <c r="D292" t="str">
-        <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>germany</v>
+      <c r="D292" t="s">
+        <v>735</v>
       </c>
       <c r="E292" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -9397,9 +9395,8 @@
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>germany</v>
       </c>
-      <c r="D293" t="str">
-        <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>germany</v>
+      <c r="D293" t="s">
+        <v>735</v>
       </c>
       <c r="E293" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -9418,9 +9415,8 @@
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>germany</v>
       </c>
-      <c r="D294" t="str">
-        <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>germany</v>
+      <c r="D294" t="s">
+        <v>735</v>
       </c>
       <c r="E294" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -9439,9 +9435,8 @@
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>germany</v>
       </c>
-      <c r="D295" t="str">
-        <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>germany</v>
+      <c r="D295" t="s">
+        <v>735</v>
       </c>
       <c r="E295" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -9460,9 +9455,8 @@
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>germany</v>
       </c>
-      <c r="D296" t="str">
-        <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>germany</v>
+      <c r="D296" t="s">
+        <v>735</v>
       </c>
       <c r="E296" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -9481,9 +9475,8 @@
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>germany</v>
       </c>
-      <c r="D297" t="str">
-        <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>germany</v>
+      <c r="D297" t="s">
+        <v>735</v>
       </c>
       <c r="E297" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -9502,9 +9495,8 @@
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>germany</v>
       </c>
-      <c r="D298" t="str">
-        <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>germany</v>
+      <c r="D298" t="s">
+        <v>735</v>
       </c>
       <c r="E298" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -9523,9 +9515,8 @@
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>germany</v>
       </c>
-      <c r="D299" t="str">
-        <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>germany</v>
+      <c r="D299" t="s">
+        <v>735</v>
       </c>
       <c r="E299" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -9544,9 +9535,8 @@
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>germany</v>
       </c>
-      <c r="D300" t="str">
-        <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>germany</v>
+      <c r="D300" t="s">
+        <v>735</v>
       </c>
       <c r="E300" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -9565,9 +9555,8 @@
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>germany</v>
       </c>
-      <c r="D301" t="str">
-        <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>germany</v>
+      <c r="D301" t="s">
+        <v>735</v>
       </c>
       <c r="E301" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -9586,9 +9575,8 @@
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>germany</v>
       </c>
-      <c r="D302" t="str">
-        <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>germany</v>
+      <c r="D302" t="s">
+        <v>735</v>
       </c>
       <c r="E302" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -9607,9 +9595,8 @@
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>germany</v>
       </c>
-      <c r="D303" t="str">
-        <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>germany</v>
+      <c r="D303" t="s">
+        <v>735</v>
       </c>
       <c r="E303" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -9628,9 +9615,8 @@
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>germany</v>
       </c>
-      <c r="D304" t="str">
-        <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>germany</v>
+      <c r="D304" t="s">
+        <v>735</v>
       </c>
       <c r="E304" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -9649,9 +9635,8 @@
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>germany</v>
       </c>
-      <c r="D305" t="str">
-        <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>germany</v>
+      <c r="D305" t="s">
+        <v>735</v>
       </c>
       <c r="E305" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -18528,7 +18513,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="D216:D239 D512:D533" calculatedColumn="1"/>
+    <ignoredError sqref="D216:D239 D512:D533 D288:D305" calculatedColumn="1"/>
   </ignoredErrors>
   <tableParts count="1">
     <tablePart r:id="rId2"/>

--- a/enlaces_equipos.xlsx
+++ b/enlaces_equipos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose-\Trabajo\statsFutbol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3483EA1-0B06-4099-B87E-78E02DAE3106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE335276-0F42-4080-9B9E-E7075569CE42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{474EBA83-D6A0-4565-BEB0-BC6B2AA992C1}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="736">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="738">
   <si>
     <t>EQUIPO</t>
   </si>
@@ -2266,6 +2266,12 @@
   </si>
   <si>
     <t>germany_b</t>
+  </si>
+  <si>
+    <t>europe/belgium/sv-zulte-waregem</t>
+  </si>
+  <si>
+    <t>europe/belgium/kvc-westerlo</t>
   </si>
 </sst>
 </file>
@@ -2361,7 +2367,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2383,6 +2389,10 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2432,10 +2442,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1329FF03-B366-468C-915B-7B9006981626}" name="Tabla1" displayName="Tabla1" ref="A1:E728" totalsRowShown="0" headerRowDxfId="5">
-  <autoFilter ref="A1:E728" xr:uid="{1329FF03-B366-468C-915B-7B9006981626}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C591">
-    <sortCondition ref="C1:C591"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1329FF03-B366-468C-915B-7B9006981626}" name="Tabla1" displayName="Tabla1" ref="A1:E730" totalsRowShown="0" headerRowDxfId="5">
+  <autoFilter ref="A1:E730" xr:uid="{1329FF03-B366-468C-915B-7B9006981626}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C593">
+    <sortCondition ref="C1:C593"/>
   </sortState>
   <tableColumns count="5">
     <tableColumn id="2" xr3:uid="{94084D0E-9EB8-4AA2-8B8F-47973A2CEB88}" name="EQUIPO" dataDxfId="4">
@@ -2753,7 +2763,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EC3E121-4DD2-4C5A-A60B-ED62DD98B116}">
-  <dimension ref="A1:K728"/>
+  <dimension ref="A1:K730"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.33203125" bestFit="1" customWidth="1"/>
@@ -2847,7 +2857,9 @@
       <c r="J3" s="10">
         <v>46313</v>
       </c>
-      <c r="K3" s="9"/>
+      <c r="K3" s="9" t="s">
+        <v>525</v>
+      </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="str">
@@ -4772,43 +4784,43 @@
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A72" t="str">
-        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>club-athletico-paranaense</v>
-      </c>
-      <c r="B72" s="4" t="s">
-        <v>529</v>
-      </c>
-      <c r="C72" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>brazil</v>
-      </c>
-      <c r="D72" t="str">
-        <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>brazil</v>
-      </c>
-      <c r="E72" s="8" t="str">
+      <c r="A72" s="12" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>sv-zulte-waregem</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>736</v>
+      </c>
+      <c r="C72" s="12" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>belgium</v>
+      </c>
+      <c r="D72" s="12" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>belgium</v>
+      </c>
+      <c r="E72" s="13" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A73" t="str">
-        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>clube-atletico-mineiro</v>
+      <c r="A73" s="12" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>kvc-westerlo</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C73" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>brazil</v>
-      </c>
-      <c r="D73" t="str">
-        <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>brazil</v>
-      </c>
-      <c r="E73" s="8" t="str">
+        <v>737</v>
+      </c>
+      <c r="C73" s="12" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>belgium</v>
+      </c>
+      <c r="D73" s="12" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>belgium</v>
+      </c>
+      <c r="E73" s="13" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
@@ -4816,10 +4828,10 @@
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>esporte-clube-bahia</v>
+        <v>club-athletico-paranaense</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>103</v>
+        <v>529</v>
       </c>
       <c r="C74" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4837,10 +4849,10 @@
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>botafogo-de-futebol-e-regatas</v>
+        <v>clube-atletico-mineiro</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C75" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4858,10 +4870,10 @@
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>red-bull-bragantino</v>
+        <v>esporte-clube-bahia</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C76" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4879,10 +4891,10 @@
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>associacao-chapecoense-de-futebol</v>
+        <v>botafogo-de-futebol-e-regatas</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>530</v>
+        <v>104</v>
       </c>
       <c r="C77" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4900,10 +4912,10 @@
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>sport-club-corinthians-paulista</v>
+        <v>red-bull-bragantino</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C78" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4921,10 +4933,10 @@
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>coritiba-football-club</v>
+        <v>associacao-chapecoense-de-futebol</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C79" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4942,10 +4954,10 @@
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>cruzeiro-esporte-clube</v>
+        <v>sport-club-corinthians-paulista</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C80" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4963,10 +4975,10 @@
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>clube-de-regatas-do-flamengo</v>
+        <v>coritiba-football-club</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>108</v>
+        <v>531</v>
       </c>
       <c r="C81" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4984,10 +4996,10 @@
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fluminense-fc</v>
+        <v>cruzeiro-esporte-clube</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C82" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5005,10 +5017,10 @@
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>gremio-football-porto-alagrense</v>
+        <v>clube-de-regatas-do-flamengo</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C83" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5026,10 +5038,10 @@
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>sport-club-internacional</v>
+        <v>fluminense-fc</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C84" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5047,10 +5059,10 @@
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>mirassol-fc</v>
+        <v>gremio-football-porto-alagrense</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C85" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5068,10 +5080,10 @@
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>sociedade-esportiva-palmeiras</v>
+        <v>sport-club-internacional</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C86" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5089,10 +5101,10 @@
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>clube-do-remo</v>
+        <v>mirassol-fc</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>532</v>
+        <v>112</v>
       </c>
       <c r="C87" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5110,10 +5122,10 @@
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>santos-fc</v>
+        <v>sociedade-esportiva-palmeiras</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C88" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5131,10 +5143,10 @@
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>sao-paulo-fc</v>
+        <v>clube-do-remo</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>115</v>
+        <v>532</v>
       </c>
       <c r="C89" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5152,10 +5164,10 @@
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>cr-vasco-da-gama</v>
+        <v>santos-fc</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C90" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5173,10 +5185,10 @@
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>esporte-clube-vitoria</v>
+        <v>sao-paulo-fc</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C91" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5194,18 +5206,18 @@
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>arda-kardzhali</v>
+        <v>cr-vasco-da-gama</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C92" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>bulgaria</v>
+        <v>brazil</v>
       </c>
       <c r="D92" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>bulgaria</v>
+        <v>brazil</v>
       </c>
       <c r="E92" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -5215,18 +5227,18 @@
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>botev-plovdiv</v>
+        <v>esporte-clube-vitoria</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C93" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>bulgaria</v>
+        <v>brazil</v>
       </c>
       <c r="D93" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>bulgaria</v>
+        <v>brazil</v>
       </c>
       <c r="E93" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -5236,10 +5248,10 @@
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>botev-vratsa</v>
+        <v>arda-kardzhali</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C94" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5257,10 +5269,10 @@
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>cherno-more</v>
+        <v>botev-plovdiv</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C95" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5278,10 +5290,10 @@
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-cska-1948-sofia</v>
+        <v>botev-vratsa</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C96" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5299,10 +5311,10 @@
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>cska-sofia</v>
+        <v>cherno-more</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C97" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5320,10 +5332,10 @@
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-dunav-ruse</v>
+        <v>fc-cska-1948-sofia</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>581</v>
+        <v>122</v>
       </c>
       <c r="C98" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5341,10 +5353,10 @@
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>levski-sofia</v>
+        <v>cska-sofia</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C99" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5362,10 +5374,10 @@
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>lokomotiv-plovdiv</v>
+        <v>fc-dunav-ruse</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>125</v>
+        <v>581</v>
       </c>
       <c r="C100" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5383,10 +5395,10 @@
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-lokomotiv-1929-sofia</v>
+        <v>levski-sofia</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C101" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5404,10 +5416,10 @@
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ludogorets</v>
+        <v>lokomotiv-plovdiv</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C102" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5425,10 +5437,10 @@
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>pfc-septemvri-sofia</v>
+        <v>fc-lokomotiv-1929-sofia</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C103" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5446,10 +5458,10 @@
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>slavia-sofia</v>
+        <v>ludogorets</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C104" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5467,10 +5479,10 @@
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-spartak-varna</v>
+        <v>pfc-septemvri-sofia</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C105" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5488,18 +5500,18 @@
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>audax-italiano</v>
+        <v>slavia-sofia</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>168</v>
+        <v>129</v>
       </c>
       <c r="C106" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>chile</v>
+        <v>bulgaria</v>
       </c>
       <c r="D106" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>chile</v>
+        <v>bulgaria</v>
       </c>
       <c r="E106" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -5509,18 +5521,18 @@
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>cd-cobresal</v>
+        <v>fc-spartak-varna</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>169</v>
+        <v>130</v>
       </c>
       <c r="C107" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>chile</v>
+        <v>bulgaria</v>
       </c>
       <c r="D107" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>chile</v>
+        <v>bulgaria</v>
       </c>
       <c r="E107" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -5530,10 +5542,10 @@
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>colo-colo</v>
+        <v>audax-italiano</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C108" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5551,10 +5563,10 @@
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>coquimbo-unido</v>
+        <v>cd-cobresal</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C109" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5572,10 +5584,10 @@
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>deportes-concepcion</v>
+        <v>colo-colo</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>533</v>
+        <v>170</v>
       </c>
       <c r="C110" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5593,10 +5605,10 @@
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>everton-de-vina-del-mar</v>
+        <v>coquimbo-unido</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C111" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5614,10 +5626,10 @@
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>cd-huachipato</v>
+        <v>deportes-concepcion</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>173</v>
+        <v>533</v>
       </c>
       <c r="C112" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5635,10 +5647,10 @@
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>deportes-la-serena</v>
+        <v>everton-de-vina-del-mar</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C113" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5656,10 +5668,10 @@
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>deportes-limache</v>
+        <v>cd-huachipato</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C114" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5677,10 +5689,10 @@
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>deportivo-nublense</v>
+        <v>deportes-la-serena</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C115" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5698,10 +5710,10 @@
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>o-higgins-fc</v>
+        <v>deportes-limache</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C116" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5719,10 +5731,10 @@
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>cd-palestino</v>
+        <v>deportivo-nublense</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C117" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5740,10 +5752,10 @@
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>union-la-calera</v>
+        <v>o-higgins-fc</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C118" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5761,10 +5773,10 @@
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>cd-universidad-catolica</v>
+        <v>cd-palestino</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C119" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5782,10 +5794,10 @@
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>club-universidad-de-chile</v>
+        <v>union-la-calera</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C120" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5803,10 +5815,10 @@
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>cd-universidad-de-concepcion</v>
+        <v>cd-universidad-catolica</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>534</v>
+        <v>180</v>
       </c>
       <c r="C121" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5824,18 +5836,18 @@
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>rionegro-aguilas</v>
-      </c>
-      <c r="B122" s="3" t="s">
-        <v>3</v>
+        <v>club-universidad-de-chile</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>181</v>
       </c>
       <c r="C122" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>colombia</v>
+        <v>chile</v>
       </c>
       <c r="D122" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>colombia</v>
+        <v>chile</v>
       </c>
       <c r="E122" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -5845,18 +5857,18 @@
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>alianza-fc</v>
+        <v>cd-universidad-de-concepcion</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>4</v>
+        <v>534</v>
       </c>
       <c r="C123" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>colombia</v>
+        <v>chile</v>
       </c>
       <c r="D123" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>colombia</v>
+        <v>chile</v>
       </c>
       <c r="E123" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -5866,10 +5878,10 @@
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>america-de-cali</v>
+        <v>rionegro-aguilas</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C124" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5887,10 +5899,10 @@
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>atletico-nacional</v>
+        <v>alianza-fc</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C125" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5908,10 +5920,10 @@
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>atletico-bucaramanga</v>
+        <v>america-de-cali</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C126" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5929,10 +5941,10 @@
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>boyaca-chico-fc</v>
+        <v>atletico-nacional</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C127" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5950,10 +5962,10 @@
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>cucuta-deportivo-fc</v>
+        <v>atletico-bucaramanga</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>526</v>
+        <v>7</v>
       </c>
       <c r="C128" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5971,10 +5983,10 @@
     <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>deportivo-cali</v>
+        <v>boyaca-chico-fc</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C129" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5992,10 +6004,10 @@
     <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fortaleza-ceif</v>
+        <v>cucuta-deportivo-fc</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>10</v>
+        <v>526</v>
       </c>
       <c r="C130" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6013,10 +6025,10 @@
     <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>deportivo-independiente-medellin</v>
+        <v>deportivo-cali</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C131" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6034,10 +6046,10 @@
     <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>internacional-de-bogota</v>
+        <v>fortaleza-ceif</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>527</v>
+        <v>10</v>
       </c>
       <c r="C132" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6055,10 +6067,10 @@
     <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>jaguares-de-cordoba</v>
+        <v>deportivo-independiente-medellin</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>528</v>
+        <v>11</v>
       </c>
       <c r="C133" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6076,10 +6088,10 @@
     <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>atletico-junior</v>
+        <v>internacional-de-bogota</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>12</v>
+        <v>527</v>
       </c>
       <c r="C134" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6097,10 +6109,10 @@
     <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>llaneros-fc</v>
+        <v>jaguares-de-cordoba</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>13</v>
+        <v>528</v>
       </c>
       <c r="C135" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6118,10 +6130,10 @@
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>millonarios-fc</v>
+        <v>atletico-junior</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C136" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6139,10 +6151,10 @@
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>once-caldas</v>
+        <v>llaneros-fc</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C137" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6160,10 +6172,10 @@
     <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>deportivo-pasto</v>
+        <v>millonarios-fc</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C138" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6181,10 +6193,10 @@
     <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>deportivo-pereira</v>
+        <v>once-caldas</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C139" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6202,10 +6214,10 @@
     <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>independiente-santa-fe</v>
+        <v>deportivo-pasto</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C140" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6223,10 +6235,10 @@
     <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>deportes-tolima</v>
+        <v>deportivo-pereira</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C141" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6244,18 +6256,18 @@
     <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>dinamo-zagreb</v>
-      </c>
-      <c r="B142" s="4" t="s">
-        <v>159</v>
+        <v>independiente-santa-fe</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="C142" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>croatia</v>
+        <v>colombia</v>
       </c>
       <c r="D142" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>croatia</v>
+        <v>colombia</v>
       </c>
       <c r="E142" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -6265,18 +6277,18 @@
     <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>gorica</v>
+        <v>deportes-tolima</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>160</v>
+        <v>19</v>
       </c>
       <c r="C143" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>croatia</v>
+        <v>colombia</v>
       </c>
       <c r="D143" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>croatia</v>
+        <v>colombia</v>
       </c>
       <c r="E143" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -6286,10 +6298,10 @@
     <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>hajduk-split</v>
+        <v>dinamo-zagreb</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C144" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6307,10 +6319,10 @@
     <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>istra-1961</v>
+        <v>gorica</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C145" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6328,10 +6340,10 @@
     <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>lokomotiva-zagreb</v>
+        <v>hajduk-split</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C146" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6349,10 +6361,10 @@
     <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>osijek</v>
+        <v>istra-1961</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C147" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6370,10 +6382,10 @@
     <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>rijeka</v>
+        <v>lokomotiva-zagreb</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C148" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6391,10 +6403,10 @@
     <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>nk-rudes</v>
+        <v>osijek</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>582</v>
+        <v>164</v>
       </c>
       <c r="C149" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6412,10 +6424,10 @@
     <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>slaven-belupo</v>
+        <v>rijeka</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C150" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6433,10 +6445,10 @@
     <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>varazdin</v>
+        <v>nk-rudes</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>167</v>
+        <v>582</v>
       </c>
       <c r="C151" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6454,18 +6466,18 @@
     <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>sk-artis-brno</v>
+        <v>slaven-belupo</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>583</v>
+        <v>166</v>
       </c>
       <c r="C152" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>czech-republic</v>
+        <v>croatia</v>
       </c>
       <c r="D152" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>czech-republic</v>
+        <v>croatia</v>
       </c>
       <c r="E152" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -6475,18 +6487,18 @@
     <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>bohemians-1905</v>
+        <v>varazdin</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="C153" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>czech-republic</v>
+        <v>croatia</v>
       </c>
       <c r="D153" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>czech-republic</v>
+        <v>croatia</v>
       </c>
       <c r="E153" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -6496,10 +6508,10 @@
     <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-zbrojovka-brno</v>
-      </c>
-      <c r="B154" s="2" t="s">
-        <v>584</v>
+        <v>sk-artis-brno</v>
+      </c>
+      <c r="B154" s="4" t="s">
+        <v>583</v>
       </c>
       <c r="C154" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6517,10 +6529,10 @@
     <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-hradec-kralove</v>
-      </c>
-      <c r="B155" s="5" t="s">
-        <v>183</v>
+        <v>bohemians-1905</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>182</v>
       </c>
       <c r="C155" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6538,10 +6550,10 @@
     <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fk-jablonec</v>
+        <v>fc-zbrojovka-brno</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>184</v>
+        <v>584</v>
       </c>
       <c r="C156" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6559,10 +6571,10 @@
     <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-slovan-liberec</v>
+        <v>fc-hradec-kralove</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C157" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6580,10 +6592,10 @@
     <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fk-mlada-boleslav</v>
+        <v>fk-jablonec</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C158" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6601,10 +6613,10 @@
     <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-banik-ostrava</v>
+        <v>fc-slovan-liberec</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C159" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6622,10 +6634,10 @@
     <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fk-pardubice</v>
+        <v>fk-mlada-boleslav</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C160" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6643,10 +6655,10 @@
     <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-viktoria-plzen</v>
+        <v>fc-banik-ostrava</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C161" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6664,10 +6676,10 @@
     <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>sk-sigma-olomouc</v>
+        <v>fk-pardubice</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C162" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6685,10 +6697,10 @@
     <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A163" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>slavia-prague</v>
+        <v>fc-viktoria-plzen</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C163" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6706,10 +6718,10 @@
     <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-slovacko</v>
+        <v>sk-sigma-olomouc</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C164" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6727,10 +6739,10 @@
     <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A165" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>sparta-prague</v>
+        <v>slavia-prague</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C165" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6748,10 +6760,10 @@
     <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fk-teplice</v>
+        <v>fc-slovacko</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C166" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6769,10 +6781,10 @@
     <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-fastav-zlin</v>
+        <v>sparta-prague</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C167" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6790,18 +6802,18 @@
     <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A168" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>aarhus</v>
+        <v>fk-teplice</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C168" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>denmark</v>
+        <v>czech-republic</v>
       </c>
       <c r="D168" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>denmark</v>
+        <v>czech-republic</v>
       </c>
       <c r="E168" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -6811,18 +6823,18 @@
     <row r="169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A169" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>brondby</v>
+        <v>fc-fastav-zlin</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C169" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>denmark</v>
+        <v>czech-republic</v>
       </c>
       <c r="D169" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>denmark</v>
+        <v>czech-republic</v>
       </c>
       <c r="E169" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -6832,10 +6844,10 @@
     <row r="170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A170" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-copenhagen</v>
+        <v>aarhus</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C170" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6853,10 +6865,10 @@
     <row r="171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A171" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ac-horsens</v>
+        <v>brondby</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>585</v>
+        <v>197</v>
       </c>
       <c r="C171" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6874,10 +6886,10 @@
     <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>lyngby-bk</v>
+        <v>fc-copenhagen</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>586</v>
+        <v>198</v>
       </c>
       <c r="C172" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6895,10 +6907,10 @@
     <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A173" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-midtjylland</v>
+        <v>ac-horsens</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>199</v>
+        <v>585</v>
       </c>
       <c r="C173" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6916,10 +6928,10 @@
     <row r="174" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A174" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-nordsjaelland</v>
+        <v>lyngby-bk</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>200</v>
+        <v>586</v>
       </c>
       <c r="C174" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6937,10 +6949,10 @@
     <row r="175" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A175" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>odense-boldklub</v>
+        <v>fc-midtjylland</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C175" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6958,10 +6970,10 @@
     <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A176" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>randers-fc</v>
+        <v>fc-nordsjaelland</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C176" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6979,10 +6991,10 @@
     <row r="177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A177" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>silkeborg-if</v>
+        <v>odense-boldklub</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C177" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7000,10 +7012,10 @@
     <row r="178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A178" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>sonderjyske</v>
+        <v>randers-fc</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C178" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7021,10 +7033,10 @@
     <row r="179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A179" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>viborg-ff</v>
+        <v>silkeborg-if</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C179" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7042,18 +7054,18 @@
     <row r="180" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A180" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>sd-aucas</v>
-      </c>
-      <c r="B180" s="5" t="s">
-        <v>486</v>
+        <v>sonderjyske</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>204</v>
       </c>
       <c r="C180" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>ecuador</v>
+        <v>denmark</v>
       </c>
       <c r="D180" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>ecuador</v>
+        <v>denmark</v>
       </c>
       <c r="E180" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -7063,18 +7075,18 @@
     <row r="181" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A181" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>barcelona-sc</v>
+        <v>viborg-ff</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>487</v>
+        <v>205</v>
       </c>
       <c r="C181" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>ecuador</v>
+        <v>denmark</v>
       </c>
       <c r="D181" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>ecuador</v>
+        <v>denmark</v>
       </c>
       <c r="E181" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -7084,10 +7096,10 @@
     <row r="182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A182" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>delfin-sc</v>
+        <v>sd-aucas</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C182" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7105,10 +7117,10 @@
     <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>cd-cuenca</v>
+        <v>barcelona-sc</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C183" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7126,10 +7138,10 @@
     <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>cs-emelec</v>
+        <v>delfin-sc</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C184" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7147,10 +7159,10 @@
     <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>guayaquil-city-fc</v>
+        <v>cd-cuenca</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>537</v>
+        <v>489</v>
       </c>
       <c r="C185" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7168,10 +7180,10 @@
     <row r="186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A186" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>csd-independiente-del-valle</v>
+        <v>cs-emelec</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C186" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7189,10 +7201,10 @@
     <row r="187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A187" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ldu-quito</v>
+        <v>guayaquil-city-fc</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>492</v>
+        <v>537</v>
       </c>
       <c r="C187" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7210,10 +7222,10 @@
     <row r="188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A188" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>leones-fc</v>
+        <v>csd-independiente-del-valle</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>538</v>
+        <v>491</v>
       </c>
       <c r="C188" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7231,10 +7243,10 @@
     <row r="189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A189" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>libertad-fc</v>
+        <v>ldu-quito</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C189" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7252,10 +7264,10 @@
     <row r="190" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A190" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>csd-macara</v>
+        <v>leones-fc</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>494</v>
+        <v>538</v>
       </c>
       <c r="C190" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7273,10 +7285,10 @@
     <row r="191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A191" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>manta-fc</v>
+        <v>libertad-fc</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C191" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7294,10 +7306,10 @@
     <row r="192" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A192" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>mushuc-runa-sc</v>
+        <v>csd-macara</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C192" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7315,10 +7327,10 @@
     <row r="193" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A193" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>orense-sc</v>
+        <v>manta-fc</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C193" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7336,10 +7348,10 @@
     <row r="194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A194" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>tecnico-universitario</v>
+        <v>mushuc-runa-sc</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C194" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7357,10 +7369,10 @@
     <row r="195" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A195" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>cd-universidad-catolica</v>
+        <v>orense-sc</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C195" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7378,18 +7390,18 @@
     <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A196" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>arsenal-fc</v>
-      </c>
-      <c r="B196" s="2" t="s">
-        <v>20</v>
+        <v>tecnico-universitario</v>
+      </c>
+      <c r="B196" s="5" t="s">
+        <v>498</v>
       </c>
       <c r="C196" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>england</v>
+        <v>ecuador</v>
       </c>
       <c r="D196" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>england</v>
+        <v>ecuador</v>
       </c>
       <c r="E196" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -7399,18 +7411,18 @@
     <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>aston-villa-fc</v>
+        <v>cd-universidad-catolica</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>21</v>
+        <v>499</v>
       </c>
       <c r="C197" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>england</v>
+        <v>ecuador</v>
       </c>
       <c r="D197" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>england</v>
+        <v>ecuador</v>
       </c>
       <c r="E197" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -7420,10 +7432,10 @@
     <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>afc-bournemouth</v>
+        <v>arsenal-fc</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C198" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7441,10 +7453,10 @@
     <row r="199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A199" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>brentford-fc</v>
+        <v>aston-villa-fc</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C199" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7462,10 +7474,10 @@
     <row r="200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A200" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>brighton-hove-albion-fc</v>
+        <v>afc-bournemouth</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C200" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7483,10 +7495,10 @@
     <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>chelsea-fc</v>
+        <v>brentford-fc</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C201" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7504,10 +7516,10 @@
     <row r="202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A202" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>coventry-city-fc</v>
+        <v>brighton-hove-albion-fc</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>210</v>
+        <v>24</v>
       </c>
       <c r="C202" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7525,10 +7537,10 @@
     <row r="203" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A203" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>crystal-palace-fc</v>
+        <v>chelsea-fc</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C203" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7546,10 +7558,10 @@
     <row r="204" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A204" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>everton-fc</v>
+        <v>coventry-city-fc</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>28</v>
+        <v>210</v>
       </c>
       <c r="C204" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7567,10 +7579,10 @@
     <row r="205" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A205" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fulham-fc</v>
+        <v>crystal-palace-fc</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C205" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7588,10 +7600,10 @@
     <row r="206" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A206" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>hull-city-fc</v>
+        <v>everton-fc</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>212</v>
+        <v>28</v>
       </c>
       <c r="C206" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7609,10 +7621,10 @@
     <row r="207" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A207" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ipswich-town-fc</v>
+        <v>fulham-fc</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>213</v>
+        <v>29</v>
       </c>
       <c r="C207" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7630,10 +7642,10 @@
     <row r="208" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A208" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>leeds-united-fc</v>
+        <v>hull-city-fc</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>30</v>
+        <v>212</v>
       </c>
       <c r="C208" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7651,10 +7663,10 @@
     <row r="209" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A209" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>liverpool-fc</v>
+        <v>ipswich-town-fc</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>31</v>
+        <v>213</v>
       </c>
       <c r="C209" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7672,10 +7684,10 @@
     <row r="210" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A210" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>manchester-city-fc</v>
+        <v>leeds-united-fc</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C210" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7693,10 +7705,10 @@
     <row r="211" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A211" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>manchester-united-fc</v>
+        <v>liverpool-fc</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C211" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7714,10 +7726,10 @@
     <row r="212" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A212" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>newcastle-united-fc</v>
+        <v>manchester-city-fc</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C212" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7735,10 +7747,10 @@
     <row r="213" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A213" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>nottingham-forest-fc</v>
+        <v>manchester-united-fc</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C213" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7756,10 +7768,10 @@
     <row r="214" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A214" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>sunderland-afc</v>
+        <v>newcastle-united-fc</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C214" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7777,10 +7789,10 @@
     <row r="215" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A215" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>tottenham-hotspur-fc</v>
+        <v>nottingham-forest-fc</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C215" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7798,17 +7810,18 @@
     <row r="216" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A216" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>birmingham-city-fc</v>
+        <v>sunderland-afc</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>206</v>
+        <v>36</v>
       </c>
       <c r="C216" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>england</v>
       </c>
-      <c r="D216" t="s">
-        <v>578</v>
+      <c r="D216" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>england</v>
       </c>
       <c r="E216" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -7818,17 +7831,18 @@
     <row r="217" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A217" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>blackburn-rovers-fc</v>
+        <v>tottenham-hotspur-fc</v>
       </c>
       <c r="B217" s="5" t="s">
-        <v>207</v>
+        <v>37</v>
       </c>
       <c r="C217" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>england</v>
       </c>
-      <c r="D217" t="s">
-        <v>578</v>
+      <c r="D217" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>england</v>
       </c>
       <c r="E217" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -7838,10 +7852,10 @@
     <row r="218" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A218" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>bolton-wanderers-fc</v>
+        <v>birmingham-city-fc</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>606</v>
+        <v>206</v>
       </c>
       <c r="C218" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7858,10 +7872,10 @@
     <row r="219" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A219" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>bristol-city-fc</v>
+        <v>blackburn-rovers-fc</v>
       </c>
       <c r="B219" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C219" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7878,10 +7892,10 @@
     <row r="220" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A220" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>burnley-fc</v>
+        <v>bolton-wanderers-fc</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>25</v>
+        <v>606</v>
       </c>
       <c r="C220" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7898,10 +7912,10 @@
     <row r="221" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A221" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>cardiff-city-fc</v>
+        <v>bristol-city-fc</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>607</v>
+        <v>208</v>
       </c>
       <c r="C221" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7918,10 +7932,10 @@
     <row r="222" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A222" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>charlton-athletic-fc</v>
+        <v>burnley-fc</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>209</v>
+        <v>25</v>
       </c>
       <c r="C222" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7938,10 +7952,10 @@
     <row r="223" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A223" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>derby-county-fc</v>
+        <v>cardiff-city-fc</v>
       </c>
       <c r="B223" s="5" t="s">
-        <v>211</v>
+        <v>607</v>
       </c>
       <c r="C223" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7958,10 +7972,10 @@
     <row r="224" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A224" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>lincoln-city-fc</v>
+        <v>charlton-athletic-fc</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>608</v>
+        <v>209</v>
       </c>
       <c r="C224" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7978,10 +7992,10 @@
     <row r="225" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A225" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>middlesbrough-fc</v>
+        <v>derby-county-fc</v>
       </c>
       <c r="B225" s="5" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C225" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7998,10 +8012,10 @@
     <row r="226" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A226" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>millwall-fc</v>
+        <v>lincoln-city-fc</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>215</v>
+        <v>608</v>
       </c>
       <c r="C226" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8018,10 +8032,10 @@
     <row r="227" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A227" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>norwich-city-fc</v>
+        <v>middlesbrough-fc</v>
       </c>
       <c r="B227" s="5" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C227" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8038,10 +8052,10 @@
     <row r="228" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A228" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>portsmouth-fc</v>
+        <v>millwall-fc</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C228" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8058,10 +8072,10 @@
     <row r="229" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A229" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>preston-north-end-fc</v>
+        <v>norwich-city-fc</v>
       </c>
       <c r="B229" s="5" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C229" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8078,10 +8092,10 @@
     <row r="230" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A230" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>queens-park-rangers-fc</v>
+        <v>portsmouth-fc</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C230" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8098,10 +8112,10 @@
     <row r="231" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A231" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>sheffield-united-fc</v>
+        <v>preston-north-end-fc</v>
       </c>
       <c r="B231" s="5" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C231" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8118,10 +8132,10 @@
     <row r="232" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A232" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>southampton-fc</v>
+        <v>queens-park-rangers-fc</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C232" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8138,10 +8152,10 @@
     <row r="233" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A233" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>stoke-city-fc</v>
+        <v>sheffield-united-fc</v>
       </c>
       <c r="B233" s="5" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C233" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8158,10 +8172,10 @@
     <row r="234" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A234" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>swansea-city-afc</v>
+        <v>southampton-fc</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C234" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8178,10 +8192,10 @@
     <row r="235" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A235" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>watford-fc</v>
+        <v>stoke-city-fc</v>
       </c>
       <c r="B235" s="5" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C235" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8198,10 +8212,10 @@
     <row r="236" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A236" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>west-bromwich-albion-fc</v>
+        <v>swansea-city-afc</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C236" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8218,10 +8232,10 @@
     <row r="237" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A237" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>west-ham-united-fc</v>
+        <v>watford-fc</v>
       </c>
       <c r="B237" s="5" t="s">
-        <v>38</v>
+        <v>224</v>
       </c>
       <c r="C237" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8238,10 +8252,10 @@
     <row r="238" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A238" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>wolverhampton-wanderers-fc</v>
+        <v>west-bromwich-albion-fc</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>39</v>
+        <v>225</v>
       </c>
       <c r="C238" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8258,10 +8272,10 @@
     <row r="239" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A239" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>wrexham-afc</v>
+        <v>west-ham-united-fc</v>
       </c>
       <c r="B239" s="5" t="s">
-        <v>226</v>
+        <v>38</v>
       </c>
       <c r="C239" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8278,18 +8292,17 @@
     <row r="240" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A240" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>if-gnistan</v>
-      </c>
-      <c r="B240" s="5" t="s">
-        <v>514</v>
+        <v>wolverhampton-wanderers-fc</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="C240" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>finland</v>
-      </c>
-      <c r="D240" t="str">
-        <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>finland</v>
+        <v>england</v>
+      </c>
+      <c r="D240" t="s">
+        <v>578</v>
       </c>
       <c r="E240" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -8299,18 +8312,17 @@
     <row r="241" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A241" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>hjk-helsinki</v>
+        <v>wrexham-afc</v>
       </c>
       <c r="B241" s="5" t="s">
-        <v>515</v>
+        <v>226</v>
       </c>
       <c r="C241" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>finland</v>
-      </c>
-      <c r="D241" t="str">
-        <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>finland</v>
+        <v>england</v>
+      </c>
+      <c r="D241" t="s">
+        <v>578</v>
       </c>
       <c r="E241" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -8320,10 +8332,10 @@
     <row r="242" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A242" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-ilves</v>
+        <v>if-gnistan</v>
       </c>
       <c r="B242" s="5" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C242" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8341,10 +8353,10 @@
     <row r="243" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A243" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-inter-turku</v>
+        <v>hjk-helsinki</v>
       </c>
       <c r="B243" s="5" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C243" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8362,10 +8374,10 @@
     <row r="244" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A244" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ff-jaro</v>
+        <v>fc-ilves</v>
       </c>
       <c r="B244" s="5" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C244" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8383,10 +8395,10 @@
     <row r="245" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A245" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>kuopion-palloseura</v>
+        <v>fc-inter-turku</v>
       </c>
       <c r="B245" s="5" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C245" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8404,10 +8416,10 @@
     <row r="246" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A246" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-lahti</v>
+        <v>ff-jaro</v>
       </c>
       <c r="B246" s="5" t="s">
-        <v>575</v>
+        <v>518</v>
       </c>
       <c r="C246" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8425,10 +8437,10 @@
     <row r="247" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A247" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ifk-mariehamn</v>
+        <v>kuopion-palloseura</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C247" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8446,10 +8458,10 @@
     <row r="248" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A248" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ac-oulu</v>
+        <v>fc-lahti</v>
       </c>
       <c r="B248" s="5" t="s">
-        <v>521</v>
+        <v>575</v>
       </c>
       <c r="C248" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8467,10 +8479,10 @@
     <row r="249" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A249" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>sjk</v>
+        <v>ifk-mariehamn</v>
       </c>
       <c r="B249" s="5" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C249" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8488,10 +8500,10 @@
     <row r="250" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A250" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>tps-turku</v>
+        <v>ac-oulu</v>
       </c>
       <c r="B250" s="5" t="s">
-        <v>576</v>
+        <v>521</v>
       </c>
       <c r="C250" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8509,10 +8521,10 @@
     <row r="251" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A251" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>vaasan-palloseura</v>
+        <v>sjk</v>
       </c>
       <c r="B251" s="5" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C251" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8530,18 +8542,18 @@
     <row r="252" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A252" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>angers-sco</v>
-      </c>
-      <c r="B252" s="2" t="s">
-        <v>227</v>
+        <v>tps-turku</v>
+      </c>
+      <c r="B252" s="5" t="s">
+        <v>576</v>
       </c>
       <c r="C252" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>france</v>
+        <v>finland</v>
       </c>
       <c r="D252" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>france</v>
+        <v>finland</v>
       </c>
       <c r="E252" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -8551,18 +8563,18 @@
     <row r="253" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A253" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>aj-auxerre</v>
+        <v>vaasan-palloseura</v>
       </c>
       <c r="B253" s="5" t="s">
-        <v>228</v>
+        <v>523</v>
       </c>
       <c r="C253" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>france</v>
+        <v>finland</v>
       </c>
       <c r="D253" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>france</v>
+        <v>finland</v>
       </c>
       <c r="E253" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -8572,10 +8584,10 @@
     <row r="254" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A254" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>stade-brestois-29</v>
+        <v>angers-sco</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C254" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8593,10 +8605,10 @@
     <row r="255" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A255" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>le-havre-ac</v>
+        <v>aj-auxerre</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C255" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8614,10 +8626,10 @@
     <row r="256" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A256" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>le-mans-fc</v>
+        <v>stade-brestois-29</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>619</v>
+        <v>229</v>
       </c>
       <c r="C256" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8635,10 +8647,10 @@
     <row r="257" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A257" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>rc-lens</v>
+        <v>le-havre-ac</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C257" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8656,10 +8668,10 @@
     <row r="258" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A258" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>lille-osc</v>
+        <v>le-mans-fc</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>232</v>
+        <v>619</v>
       </c>
       <c r="C258" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8677,10 +8689,10 @@
     <row r="259" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A259" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-lorient</v>
+        <v>rc-lens</v>
       </c>
       <c r="B259" s="5" t="s">
-        <v>469</v>
+        <v>231</v>
       </c>
       <c r="C259" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8698,10 +8710,10 @@
     <row r="260" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A260" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>olympique-lyonnais</v>
+        <v>lille-osc</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C260" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8719,10 +8731,10 @@
     <row r="261" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A261" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>olympique-de-marseille</v>
+        <v>fc-lorient</v>
       </c>
       <c r="B261" s="5" t="s">
-        <v>234</v>
+        <v>469</v>
       </c>
       <c r="C261" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8740,10 +8752,10 @@
     <row r="262" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A262" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>as-monaco-fc</v>
+        <v>olympique-lyonnais</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C262" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8761,10 +8773,10 @@
     <row r="263" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A263" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ogc-nice</v>
+        <v>olympique-de-marseille</v>
       </c>
       <c r="B263" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C263" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8782,10 +8794,10 @@
     <row r="264" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A264" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>paris-fc</v>
+        <v>as-monaco-fc</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>470</v>
+        <v>235</v>
       </c>
       <c r="C264" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8803,10 +8815,10 @@
     <row r="265" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A265" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>paris-saint-germain-fc</v>
+        <v>ogc-nice</v>
       </c>
       <c r="B265" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C265" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8824,10 +8836,10 @@
     <row r="266" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A266" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>stade-rennais-fc</v>
+        <v>paris-fc</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>238</v>
+        <v>470</v>
       </c>
       <c r="C266" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8845,10 +8857,10 @@
     <row r="267" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A267" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>rc-strasbourg-alsace</v>
+        <v>paris-saint-germain-fc</v>
       </c>
       <c r="B267" s="5" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C267" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8866,10 +8878,10 @@
     <row r="268" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A268" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>toulouse-fc</v>
+        <v>stade-rennais-fc</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C268" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8887,10 +8899,10 @@
     <row r="269" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A269" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>troyes-ac</v>
+        <v>rc-strasbourg-alsace</v>
       </c>
       <c r="B269" s="5" t="s">
-        <v>620</v>
+        <v>239</v>
       </c>
       <c r="C269" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8908,18 +8920,18 @@
     <row r="270" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A270" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-augsburg</v>
+        <v>toulouse-fc</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="C270" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>germany</v>
+        <v>france</v>
       </c>
       <c r="D270" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>germany</v>
+        <v>france</v>
       </c>
       <c r="E270" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -8929,18 +8941,18 @@
     <row r="271" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A271" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>bayern-munich</v>
+        <v>troyes-ac</v>
       </c>
       <c r="B271" s="5" t="s">
-        <v>61</v>
+        <v>620</v>
       </c>
       <c r="C271" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>germany</v>
+        <v>france</v>
       </c>
       <c r="D271" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>germany</v>
+        <v>france</v>
       </c>
       <c r="E271" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -8950,10 +8962,10 @@
     <row r="272" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A272" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>werder-bremen</v>
+        <v>fc-augsburg</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C272" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8971,10 +8983,10 @@
     <row r="273" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A273" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>borussia-dortmund</v>
+        <v>bayern-munich</v>
       </c>
       <c r="B273" s="5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C273" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8992,10 +9004,10 @@
     <row r="274" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A274" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>sv-elversberg</v>
+        <v>werder-bremen</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>621</v>
+        <v>63</v>
       </c>
       <c r="C274" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9013,10 +9025,10 @@
     <row r="275" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A275" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-koln</v>
+        <v>borussia-dortmund</v>
       </c>
       <c r="B275" s="5" t="s">
-        <v>466</v>
+        <v>64</v>
       </c>
       <c r="C275" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9034,10 +9046,10 @@
     <row r="276" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A276" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>eintracht-frankfurt</v>
+        <v>sv-elversberg</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>65</v>
+        <v>621</v>
       </c>
       <c r="C276" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9055,10 +9067,10 @@
     <row r="277" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A277" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>sc-freiburg</v>
+        <v>fc-koln</v>
       </c>
       <c r="B277" s="5" t="s">
-        <v>66</v>
+        <v>466</v>
       </c>
       <c r="C277" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9076,10 +9088,10 @@
     <row r="278" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A278" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>hamburger-sv</v>
+        <v>eintracht-frankfurt</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>467</v>
+        <v>65</v>
       </c>
       <c r="C278" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9097,10 +9109,10 @@
     <row r="279" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A279" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>hoffenheim</v>
+        <v>sc-freiburg</v>
       </c>
       <c r="B279" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C279" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9118,10 +9130,10 @@
     <row r="280" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A280" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>bayer-leverkusen</v>
+        <v>hamburger-sv</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>70</v>
+        <v>467</v>
       </c>
       <c r="C280" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9139,10 +9151,10 @@
     <row r="281" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A281" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>mainz-05</v>
+        <v>hoffenheim</v>
       </c>
       <c r="B281" s="5" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C281" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9160,10 +9172,10 @@
     <row r="282" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A282" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>borussia-monchengladbach</v>
+        <v>bayer-leverkusen</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C282" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9181,10 +9193,10 @@
     <row r="283" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A283" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>sc-paderborn</v>
+        <v>mainz-05</v>
       </c>
       <c r="B283" s="5" t="s">
-        <v>622</v>
+        <v>71</v>
       </c>
       <c r="C283" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9202,10 +9214,10 @@
     <row r="284" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A284" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>rb-leipzig</v>
+        <v>borussia-monchengladbach</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C284" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9223,10 +9235,10 @@
     <row r="285" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A285" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>schalke-04</v>
+        <v>sc-paderborn</v>
       </c>
       <c r="B285" s="5" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C285" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9244,10 +9256,10 @@
     <row r="286" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A286" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>vfb-stuttgart</v>
+        <v>rb-leipzig</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C286" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9265,10 +9277,10 @@
     <row r="287" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A287" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>union-berlin</v>
+        <v>schalke-04</v>
       </c>
       <c r="B287" s="5" t="s">
-        <v>76</v>
+        <v>623</v>
       </c>
       <c r="C287" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9286,17 +9298,18 @@
     <row r="288" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A288" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>arminia-bielefeld</v>
+        <v>vfb-stuttgart</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>241</v>
+        <v>75</v>
       </c>
       <c r="C288" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>germany</v>
       </c>
-      <c r="D288" t="s">
-        <v>735</v>
+      <c r="D288" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>germany</v>
       </c>
       <c r="E288" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -9306,17 +9319,18 @@
     <row r="289" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A289" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>vfl-bochum</v>
+        <v>union-berlin</v>
       </c>
       <c r="B289" s="5" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="C289" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>germany</v>
       </c>
-      <c r="D289" t="s">
-        <v>735</v>
+      <c r="D289" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>germany</v>
       </c>
       <c r="E289" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -9326,10 +9340,10 @@
     <row r="290" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A290" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>eintracht-braunschweig</v>
+        <v>arminia-bielefeld</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C290" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9346,10 +9360,10 @@
     <row r="291" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A291" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-energie-cottbus</v>
+        <v>vfl-bochum</v>
       </c>
       <c r="B291" s="5" t="s">
-        <v>595</v>
+        <v>62</v>
       </c>
       <c r="C291" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9366,10 +9380,10 @@
     <row r="292" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A292" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>darmstadt-98</v>
+        <v>eintracht-braunschweig</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C292" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9386,10 +9400,10 @@
     <row r="293" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A293" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>dynamo-dresden</v>
+        <v>fc-energie-cottbus</v>
       </c>
       <c r="B293" s="5" t="s">
-        <v>244</v>
+        <v>595</v>
       </c>
       <c r="C293" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9406,10 +9420,10 @@
     <row r="294" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A294" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>greuther-furth</v>
+        <v>darmstadt-98</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C294" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9426,10 +9440,10 @@
     <row r="295" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A295" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>hannover-96</v>
+        <v>dynamo-dresden</v>
       </c>
       <c r="B295" s="5" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C295" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9446,10 +9460,10 @@
     <row r="296" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A296" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-heidenheim</v>
+        <v>greuther-furth</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>67</v>
+        <v>245</v>
       </c>
       <c r="C296" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9466,10 +9480,10 @@
     <row r="297" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A297" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>hertha-berlin</v>
+        <v>hannover-96</v>
       </c>
       <c r="B297" s="5" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C297" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9486,10 +9500,10 @@
     <row r="298" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A298" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-kaiserslautern</v>
+        <v>fc-heidenheim</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>248</v>
+        <v>67</v>
       </c>
       <c r="C298" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9506,10 +9520,10 @@
     <row r="299" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A299" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>karlsruher-sc</v>
+        <v>hertha-berlin</v>
       </c>
       <c r="B299" s="5" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C299" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9526,10 +9540,10 @@
     <row r="300" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A300" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>holstein-kiel</v>
+        <v>fc-kaiserslautern</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>69</v>
+        <v>248</v>
       </c>
       <c r="C300" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9546,10 +9560,10 @@
     <row r="301" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A301" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-magdeburg</v>
+        <v>karlsruher-sc</v>
       </c>
       <c r="B301" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C301" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9566,10 +9580,10 @@
     <row r="302" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A302" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-nurnberg</v>
+        <v>holstein-kiel</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>251</v>
+        <v>69</v>
       </c>
       <c r="C302" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9586,10 +9600,10 @@
     <row r="303" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A303" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>vfl-osnabruck</v>
+        <v>fc-magdeburg</v>
       </c>
       <c r="B303" s="5" t="s">
-        <v>596</v>
+        <v>250</v>
       </c>
       <c r="C303" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9606,10 +9620,10 @@
     <row r="304" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A304" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-st-pauli</v>
+        <v>fc-nurnberg</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>74</v>
+        <v>251</v>
       </c>
       <c r="C304" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9626,10 +9640,10 @@
     <row r="305" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A305" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>vfl-wolfsburg</v>
+        <v>vfl-osnabruck</v>
       </c>
       <c r="B305" s="5" t="s">
-        <v>77</v>
+        <v>596</v>
       </c>
       <c r="C305" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9646,18 +9660,17 @@
     <row r="306" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A306" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>aek-athens-fc</v>
-      </c>
-      <c r="B306" s="5" t="s">
-        <v>474</v>
+        <v>fc-st-pauli</v>
+      </c>
+      <c r="B306" s="2" t="s">
+        <v>74</v>
       </c>
       <c r="C306" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>greece</v>
-      </c>
-      <c r="D306" t="str">
-        <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>greece</v>
+        <v>germany</v>
+      </c>
+      <c r="D306" t="s">
+        <v>735</v>
       </c>
       <c r="E306" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -9667,18 +9680,17 @@
     <row r="307" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A307" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>aris-thessaloniki-fc</v>
+        <v>vfl-wolfsburg</v>
       </c>
       <c r="B307" s="5" t="s">
-        <v>475</v>
+        <v>77</v>
       </c>
       <c r="C307" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>greece</v>
-      </c>
-      <c r="D307" t="str">
-        <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>greece</v>
+        <v>germany</v>
+      </c>
+      <c r="D307" t="s">
+        <v>735</v>
       </c>
       <c r="E307" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -9688,10 +9700,10 @@
     <row r="308" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A308" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>asteras-tripolis-fc</v>
+        <v>aek-athens-fc</v>
       </c>
       <c r="B308" s="5" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C308" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9709,10 +9721,10 @@
     <row r="309" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A309" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>atromitos-fc</v>
+        <v>aris-thessaloniki-fc</v>
       </c>
       <c r="B309" s="5" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C309" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9730,10 +9742,10 @@
     <row r="310" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A310" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>iraklis-fc</v>
+        <v>asteras-tripolis-fc</v>
       </c>
       <c r="B310" s="5" t="s">
-        <v>624</v>
+        <v>476</v>
       </c>
       <c r="C310" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9751,10 +9763,10 @@
     <row r="311" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A311" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>kalamata-fc</v>
+        <v>atromitos-fc</v>
       </c>
       <c r="B311" s="5" t="s">
-        <v>625</v>
+        <v>477</v>
       </c>
       <c r="C311" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9772,10 +9784,10 @@
     <row r="312" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A312" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ae-kifisia-fc</v>
+        <v>iraklis-fc</v>
       </c>
       <c r="B312" s="5" t="s">
-        <v>478</v>
+        <v>624</v>
       </c>
       <c r="C312" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9793,10 +9805,10 @@
     <row r="313" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A313" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>levadiakos-fc</v>
+        <v>kalamata-fc</v>
       </c>
       <c r="B313" s="5" t="s">
-        <v>479</v>
+        <v>625</v>
       </c>
       <c r="C313" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9814,10 +9826,10 @@
     <row r="314" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A314" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ofi-crete-fc</v>
+        <v>ae-kifisia-fc</v>
       </c>
       <c r="B314" s="5" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C314" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9835,10 +9847,10 @@
     <row r="315" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A315" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>olympiacos-fc</v>
+        <v>levadiakos-fc</v>
       </c>
       <c r="B315" s="5" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C315" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9856,10 +9868,10 @@
     <row r="316" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A316" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>panathinaikos-fc</v>
+        <v>ofi-crete-fc</v>
       </c>
       <c r="B316" s="5" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C316" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9877,10 +9889,10 @@
     <row r="317" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A317" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>panetolikos-fc</v>
+        <v>olympiacos-fc</v>
       </c>
       <c r="B317" s="5" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C317" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9898,10 +9910,10 @@
     <row r="318" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A318" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>paok-fc</v>
+        <v>panathinaikos-fc</v>
       </c>
       <c r="B318" s="5" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C318" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9919,10 +9931,10 @@
     <row r="319" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A319" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>volos-fc</v>
+        <v>panetolikos-fc</v>
       </c>
       <c r="B319" s="5" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C319" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9940,18 +9952,18 @@
     <row r="320" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A320" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ac-milan</v>
-      </c>
-      <c r="B320" s="2" t="s">
-        <v>252</v>
+        <v>paok-fc</v>
+      </c>
+      <c r="B320" s="5" t="s">
+        <v>484</v>
       </c>
       <c r="C320" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>italy</v>
+        <v>greece</v>
       </c>
       <c r="D320" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>italy</v>
+        <v>greece</v>
       </c>
       <c r="E320" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -9961,18 +9973,18 @@
     <row r="321" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A321" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>as-roma</v>
+        <v>volos-fc</v>
       </c>
       <c r="B321" s="5" t="s">
-        <v>253</v>
+        <v>485</v>
       </c>
       <c r="C321" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>italy</v>
+        <v>greece</v>
       </c>
       <c r="D321" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>italy</v>
+        <v>greece</v>
       </c>
       <c r="E321" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -9982,10 +9994,10 @@
     <row r="322" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A322" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>atalanta-bc</v>
+        <v>ac-milan</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C322" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10003,10 +10015,10 @@
     <row r="323" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A323" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>bologna-fc-1909</v>
+        <v>as-roma</v>
       </c>
       <c r="B323" s="5" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C323" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10024,10 +10036,10 @@
     <row r="324" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A324" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>cagliari-calcio</v>
+        <v>atalanta-bc</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C324" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10045,10 +10057,10 @@
     <row r="325" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A325" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>como-1907</v>
+        <v>bologna-fc-1909</v>
       </c>
       <c r="B325" s="5" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C325" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10066,10 +10078,10 @@
     <row r="326" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A326" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>acf-fiorentina</v>
+        <v>cagliari-calcio</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C326" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10087,10 +10099,10 @@
     <row r="327" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A327" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>frosinone-calcio</v>
+        <v>como-1907</v>
       </c>
       <c r="B327" s="5" t="s">
-        <v>626</v>
+        <v>257</v>
       </c>
       <c r="C327" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10108,10 +10120,10 @@
     <row r="328" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A328" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>genoa-cfc</v>
+        <v>acf-fiorentina</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C328" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10129,10 +10141,10 @@
     <row r="329" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A329" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>inter-milan</v>
+        <v>frosinone-calcio</v>
       </c>
       <c r="B329" s="5" t="s">
-        <v>260</v>
+        <v>626</v>
       </c>
       <c r="C329" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10150,10 +10162,10 @@
     <row r="330" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A330" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>juventus-fc</v>
+        <v>genoa-cfc</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C330" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10171,10 +10183,10 @@
     <row r="331" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A331" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ss-lazio</v>
+        <v>inter-milan</v>
       </c>
       <c r="B331" s="5" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C331" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10192,10 +10204,10 @@
     <row r="332" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A332" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>us-lecce</v>
+        <v>juventus-fc</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C332" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10213,10 +10225,10 @@
     <row r="333" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A333" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ac-monza</v>
+        <v>ss-lazio</v>
       </c>
       <c r="B333" s="5" t="s">
-        <v>627</v>
+        <v>262</v>
       </c>
       <c r="C333" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10234,10 +10246,10 @@
     <row r="334" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A334" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ssc-napoli</v>
+        <v>us-lecce</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C334" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10255,10 +10267,10 @@
     <row r="335" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A335" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>parma-calcio-1913</v>
+        <v>ac-monza</v>
       </c>
       <c r="B335" s="5" t="s">
-        <v>265</v>
+        <v>627</v>
       </c>
       <c r="C335" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10276,10 +10288,10 @@
     <row r="336" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A336" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>us-sassuolo-calcio</v>
+        <v>ssc-napoli</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>468</v>
+        <v>264</v>
       </c>
       <c r="C336" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10297,10 +10309,10 @@
     <row r="337" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A337" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>torino-fc</v>
+        <v>parma-calcio-1913</v>
       </c>
       <c r="B337" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C337" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10318,10 +10330,10 @@
     <row r="338" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A338" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>udinese-calcio</v>
+        <v>us-sassuolo-calcio</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>267</v>
+        <v>468</v>
       </c>
       <c r="C338" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10339,10 +10351,10 @@
     <row r="339" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A339" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>venezia-fc</v>
+        <v>torino-fc</v>
       </c>
       <c r="B339" s="5" t="s">
-        <v>628</v>
+        <v>266</v>
       </c>
       <c r="C339" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10360,18 +10372,18 @@
     <row r="340" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A340" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>atletico-san-luis</v>
+        <v>udinese-calcio</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C340" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>mexico</v>
+        <v>italy</v>
       </c>
       <c r="D340" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>mexico</v>
+        <v>italy</v>
       </c>
       <c r="E340" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -10381,18 +10393,18 @@
     <row r="341" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A341" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>atlas-fc</v>
+        <v>venezia-fc</v>
       </c>
       <c r="B341" s="5" t="s">
-        <v>269</v>
+        <v>628</v>
       </c>
       <c r="C341" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>mexico</v>
+        <v>italy</v>
       </c>
       <c r="D341" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>mexico</v>
+        <v>italy</v>
       </c>
       <c r="E341" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -10402,10 +10414,10 @@
     <row r="342" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A342" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>club-america</v>
+        <v>atletico-san-luis</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C342" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10423,10 +10435,10 @@
     <row r="343" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A343" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>cruz-azul</v>
+        <v>atlas-fc</v>
       </c>
       <c r="B343" s="5" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C343" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10444,10 +10456,10 @@
     <row r="344" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A344" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>cd-guadalajara</v>
+        <v>club-america</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C344" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10465,10 +10477,10 @@
     <row r="345" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A345" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-juarez</v>
+        <v>cruz-azul</v>
       </c>
       <c r="B345" s="5" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C345" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10486,10 +10498,10 @@
     <row r="346" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A346" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>club-leon</v>
+        <v>cd-guadalajara</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C346" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10507,10 +10519,10 @@
     <row r="347" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A347" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>mazatlan-fc</v>
+        <v>fc-juarez</v>
       </c>
       <c r="B347" s="5" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C347" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10528,10 +10540,10 @@
     <row r="348" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A348" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>cf-monterrey</v>
+        <v>club-leon</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C348" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10549,10 +10561,10 @@
     <row r="349" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A349" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>club-necaxa</v>
+        <v>mazatlan-fc</v>
       </c>
       <c r="B349" s="5" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C349" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10570,10 +10582,10 @@
     <row r="350" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A350" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>cf-pachuca</v>
+        <v>cf-monterrey</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C350" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10591,10 +10603,10 @@
     <row r="351" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A351" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>club-puebla</v>
+        <v>club-necaxa</v>
       </c>
       <c r="B351" s="5" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C351" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10612,10 +10624,10 @@
     <row r="352" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A352" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>queretaro-fc</v>
+        <v>cf-pachuca</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C352" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10633,10 +10645,10 @@
     <row r="353" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A353" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>santos-laguna</v>
+        <v>club-puebla</v>
       </c>
       <c r="B353" s="5" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C353" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10654,10 +10666,10 @@
     <row r="354" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A354" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>tigres-uanl</v>
+        <v>queretaro-fc</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C354" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10675,10 +10687,10 @@
     <row r="355" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A355" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>club-tijuana</v>
+        <v>santos-laguna</v>
       </c>
       <c r="B355" s="5" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C355" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10696,10 +10708,10 @@
     <row r="356" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A356" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>deportivo-toluca-fc</v>
+        <v>tigres-uanl</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C356" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10717,10 +10729,10 @@
     <row r="357" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A357" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>unam</v>
+        <v>club-tijuana</v>
       </c>
       <c r="B357" s="5" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C357" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10738,18 +10750,18 @@
     <row r="358" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A358" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>afc-ajax</v>
+        <v>deportivo-toluca-fc</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C358" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>netherlands</v>
+        <v>mexico</v>
       </c>
       <c r="D358" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>netherlands</v>
+        <v>mexico</v>
       </c>
       <c r="E358" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -10759,18 +10771,18 @@
     <row r="359" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A359" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>az-alkmaar</v>
+        <v>unam</v>
       </c>
       <c r="B359" s="5" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C359" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>netherlands</v>
+        <v>mexico</v>
       </c>
       <c r="D359" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>netherlands</v>
+        <v>mexico</v>
       </c>
       <c r="E359" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -10780,10 +10792,10 @@
     <row r="360" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A360" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>sc-cambuur</v>
+        <v>afc-ajax</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>597</v>
+        <v>286</v>
       </c>
       <c r="C360" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10801,10 +10813,10 @@
     <row r="361" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A361" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ado-den-haag</v>
+        <v>az-alkmaar</v>
       </c>
       <c r="B361" s="5" t="s">
-        <v>598</v>
+        <v>287</v>
       </c>
       <c r="C361" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10822,10 +10834,10 @@
     <row r="362" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A362" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>sbv-excelsior</v>
+        <v>sc-cambuur</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>288</v>
+        <v>597</v>
       </c>
       <c r="C362" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10843,10 +10855,10 @@
     <row r="363" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A363" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>feyenoord-rotterdam</v>
+        <v>ado-den-haag</v>
       </c>
       <c r="B363" s="5" t="s">
-        <v>289</v>
+        <v>598</v>
       </c>
       <c r="C363" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10864,10 +10876,10 @@
     <row r="364" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A364" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>go-ahead-eagles</v>
+        <v>sbv-excelsior</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C364" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10885,10 +10897,10 @@
     <row r="365" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A365" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-groningen</v>
+        <v>feyenoord-rotterdam</v>
       </c>
       <c r="B365" s="5" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C365" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10906,10 +10918,10 @@
     <row r="366" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A366" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>sc-heerenveen</v>
+        <v>go-ahead-eagles</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C366" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10927,10 +10939,10 @@
     <row r="367" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A367" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>nec-nijmegen</v>
+        <v>fc-groningen</v>
       </c>
       <c r="B367" s="5" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C367" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10948,10 +10960,10 @@
     <row r="368" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A368" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>psv-eindhoven</v>
+        <v>sc-heerenveen</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C368" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10969,10 +10981,10 @@
     <row r="369" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A369" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fortuna-sittard</v>
+        <v>nec-nijmegen</v>
       </c>
       <c r="B369" s="5" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C369" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10990,10 +11002,10 @@
     <row r="370" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A370" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>sparta-rotterdam</v>
+        <v>psv-eindhoven</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C370" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11011,10 +11023,10 @@
     <row r="371" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A371" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>sc-telstar</v>
+        <v>fortuna-sittard</v>
       </c>
       <c r="B371" s="5" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C371" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11032,10 +11044,10 @@
     <row r="372" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A372" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-twente</v>
+        <v>sparta-rotterdam</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C372" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11053,10 +11065,10 @@
     <row r="373" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A373" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-utrecht</v>
+        <v>sc-telstar</v>
       </c>
       <c r="B373" s="5" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C373" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11074,10 +11086,10 @@
     <row r="374" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A374" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>willem-ii</v>
+        <v>fc-twente</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>599</v>
+        <v>298</v>
       </c>
       <c r="C374" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11095,10 +11107,10 @@
     <row r="375" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A375" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>pec-zwolle</v>
+        <v>fc-utrecht</v>
       </c>
       <c r="B375" s="5" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C375" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11116,18 +11128,18 @@
     <row r="376" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A376" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>aalesunds-fk</v>
+        <v>willem-ii</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>609</v>
+        <v>599</v>
       </c>
       <c r="C376" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>norway</v>
+        <v>netherlands</v>
       </c>
       <c r="D376" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>norway</v>
+        <v>netherlands</v>
       </c>
       <c r="E376" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -11137,18 +11149,18 @@
     <row r="377" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A377" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fk-bodo-glimt</v>
+        <v>pec-zwolle</v>
       </c>
       <c r="B377" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C377" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>norway</v>
+        <v>netherlands</v>
       </c>
       <c r="D377" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>norway</v>
+        <v>netherlands</v>
       </c>
       <c r="E377" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -11158,10 +11170,10 @@
     <row r="378" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A378" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>sk-brann</v>
+        <v>aalesunds-fk</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>302</v>
+        <v>609</v>
       </c>
       <c r="C378" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11179,10 +11191,10 @@
     <row r="379" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A379" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fredrikstad-fk</v>
+        <v>fk-bodo-glimt</v>
       </c>
       <c r="B379" s="5" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C379" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11200,10 +11212,10 @@
     <row r="380" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A380" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ham-kam</v>
+        <v>sk-brann</v>
       </c>
       <c r="B380" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C380" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11221,10 +11233,10 @@
     <row r="381" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A381" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>kfum-kameratene-oslo</v>
+        <v>fredrikstad-fk</v>
       </c>
       <c r="B381" s="5" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C381" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11242,10 +11254,10 @@
     <row r="382" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A382" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>kristiansund-bk</v>
+        <v>ham-kam</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C382" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11263,10 +11275,10 @@
     <row r="383" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A383" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>lillestrom-sk</v>
+        <v>kfum-kameratene-oslo</v>
       </c>
       <c r="B383" s="5" t="s">
-        <v>610</v>
+        <v>305</v>
       </c>
       <c r="C383" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11284,10 +11296,10 @@
     <row r="384" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A384" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>molde-fk</v>
+        <v>kristiansund-bk</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C384" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11305,10 +11317,10 @@
     <row r="385" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A385" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>rosenborg-bk</v>
+        <v>lillestrom-sk</v>
       </c>
       <c r="B385" s="5" t="s">
-        <v>308</v>
+        <v>610</v>
       </c>
       <c r="C385" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11326,10 +11338,10 @@
     <row r="386" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A386" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>sandefjord-fotball</v>
+        <v>molde-fk</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C386" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11347,10 +11359,10 @@
     <row r="387" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A387" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>sarpsborg-08-ff</v>
+        <v>rosenborg-bk</v>
       </c>
       <c r="B387" s="5" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C387" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11368,10 +11380,10 @@
     <row r="388" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A388" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ik-start</v>
+        <v>sandefjord-fotball</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>611</v>
+        <v>309</v>
       </c>
       <c r="C388" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11389,10 +11401,10 @@
     <row r="389" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A389" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>tromso-il</v>
+        <v>sarpsborg-08-ff</v>
       </c>
       <c r="B389" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C389" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11410,10 +11422,10 @@
     <row r="390" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A390" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>valerenga-fotball</v>
+        <v>ik-start</v>
       </c>
       <c r="B390" s="2" t="s">
-        <v>312</v>
+        <v>611</v>
       </c>
       <c r="C390" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11431,10 +11443,10 @@
     <row r="391" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A391" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>viking-fk</v>
+        <v>tromso-il</v>
       </c>
       <c r="B391" s="5" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C391" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11452,18 +11464,18 @@
     <row r="392" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A392" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>alianza-lima</v>
-      </c>
-      <c r="B392" t="s">
-        <v>314</v>
+        <v>valerenga-fotball</v>
+      </c>
+      <c r="B392" s="2" t="s">
+        <v>312</v>
       </c>
       <c r="C392" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>peru</v>
+        <v>norway</v>
       </c>
       <c r="D392" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>peru</v>
+        <v>norway</v>
       </c>
       <c r="E392" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -11473,18 +11485,18 @@
     <row r="393" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A393" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>asociacion-deportiva-tarma</v>
-      </c>
-      <c r="B393" t="s">
-        <v>315</v>
+        <v>viking-fk</v>
+      </c>
+      <c r="B393" s="5" t="s">
+        <v>313</v>
       </c>
       <c r="C393" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>peru</v>
+        <v>norway</v>
       </c>
       <c r="D393" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>peru</v>
+        <v>norway</v>
       </c>
       <c r="E393" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -11494,10 +11506,10 @@
     <row r="394" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A394" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>alianza-atletico</v>
+        <v>alianza-lima</v>
       </c>
       <c r="B394" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C394" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11515,10 +11527,10 @@
     <row r="395" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A395" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>universidad-tecnica-de-cajamarca</v>
+        <v>asociacion-deportiva-tarma</v>
       </c>
       <c r="B395" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C395" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11536,10 +11548,10 @@
     <row r="396" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A396" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>club-sportivo-cienciano</v>
+        <v>alianza-atletico</v>
       </c>
       <c r="B396" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C396" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11557,10 +11569,10 @@
     <row r="397" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A397" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>comerciantes-unidos</v>
+        <v>universidad-tecnica-de-cajamarca</v>
       </c>
       <c r="B397" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C397" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11578,10 +11590,10 @@
     <row r="398" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A398" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>cusco-fc</v>
+        <v>club-sportivo-cienciano</v>
       </c>
       <c r="B398" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C398" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11599,10 +11611,10 @@
     <row r="399" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A399" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>deportivo-garcilaso</v>
+        <v>comerciantes-unidos</v>
       </c>
       <c r="B399" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C399" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11620,10 +11632,10 @@
     <row r="400" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A400" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-cajamarca</v>
+        <v>cusco-fc</v>
       </c>
       <c r="B400" t="s">
-        <v>535</v>
+        <v>320</v>
       </c>
       <c r="C400" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11641,10 +11653,10 @@
     <row r="401" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A401" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>atletico-grau</v>
+        <v>deportivo-garcilaso</v>
       </c>
       <c r="B401" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C401" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11662,10 +11674,10 @@
     <row r="402" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A402" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>sport-huancayo</v>
+        <v>fc-cajamarca</v>
       </c>
       <c r="B402" t="s">
-        <v>323</v>
+        <v>535</v>
       </c>
       <c r="C402" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11683,10 +11695,10 @@
     <row r="403" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A403" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>adc-juan-pablo-ii-college</v>
+        <v>atletico-grau</v>
       </c>
       <c r="B403" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C403" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11704,10 +11716,10 @@
     <row r="404" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A404" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>los-chankas-cyc</v>
+        <v>sport-huancayo</v>
       </c>
       <c r="B404" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C404" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11725,10 +11737,10 @@
     <row r="405" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A405" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fbc-melgar</v>
+        <v>adc-juan-pablo-ii-college</v>
       </c>
       <c r="B405" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C405" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11746,10 +11758,10 @@
     <row r="406" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A406" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>club-deportivo-moquegua</v>
+        <v>los-chankas-cyc</v>
       </c>
       <c r="B406" t="s">
-        <v>536</v>
+        <v>325</v>
       </c>
       <c r="C406" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11767,10 +11779,10 @@
     <row r="407" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A407" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>sport-boys</v>
+        <v>fbc-melgar</v>
       </c>
       <c r="B407" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C407" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11788,10 +11800,10 @@
     <row r="408" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A408" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>sporting-cristal</v>
+        <v>club-deportivo-moquegua</v>
       </c>
       <c r="B408" t="s">
-        <v>328</v>
+        <v>536</v>
       </c>
       <c r="C408" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11809,10 +11821,10 @@
     <row r="409" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A409" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>club-universitario-de-deportes</v>
+        <v>sport-boys</v>
       </c>
       <c r="B409" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C409" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11830,18 +11842,18 @@
     <row r="410" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A410" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>cracovia</v>
-      </c>
-      <c r="B410" s="5" t="s">
-        <v>330</v>
+        <v>sporting-cristal</v>
+      </c>
+      <c r="B410" t="s">
+        <v>328</v>
       </c>
       <c r="C410" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>poland</v>
+        <v>peru</v>
       </c>
       <c r="D410" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>poland</v>
+        <v>peru</v>
       </c>
       <c r="E410" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -11851,18 +11863,18 @@
     <row r="411" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A411" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>gornik-zabrze</v>
-      </c>
-      <c r="B411" s="2" t="s">
-        <v>331</v>
+        <v>club-universitario-de-deportes</v>
+      </c>
+      <c r="B411" t="s">
+        <v>329</v>
       </c>
       <c r="C411" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>poland</v>
+        <v>peru</v>
       </c>
       <c r="D411" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>poland</v>
+        <v>peru</v>
       </c>
       <c r="E411" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -11872,10 +11884,10 @@
     <row r="412" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A412" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>jagiellona-bialystok</v>
+        <v>cracovia</v>
       </c>
       <c r="B412" s="5" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C412" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11893,10 +11905,10 @@
     <row r="413" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A413" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>gks-katowice</v>
+        <v>gornik-zabrze</v>
       </c>
       <c r="B413" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C413" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11914,10 +11926,10 @@
     <row r="414" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A414" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>korona-kielce</v>
+        <v>jagiellona-bialystok</v>
       </c>
       <c r="B414" s="5" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C414" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11935,10 +11947,10 @@
     <row r="415" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A415" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>lech-poznan</v>
+        <v>gks-katowice</v>
       </c>
       <c r="B415" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C415" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11956,10 +11968,10 @@
     <row r="416" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A416" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>legia-warsaw</v>
+        <v>korona-kielce</v>
       </c>
       <c r="B416" s="5" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C416" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11977,10 +11989,10 @@
     <row r="417" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A417" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>motor-lublin</v>
+        <v>lech-poznan</v>
       </c>
       <c r="B417" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C417" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11998,10 +12010,10 @@
     <row r="418" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A418" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>piast-gliwice</v>
+        <v>legia-warsaw</v>
       </c>
       <c r="B418" s="5" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C418" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12019,10 +12031,10 @@
     <row r="419" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A419" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>mks-pogon-szczecin</v>
+        <v>motor-lublin</v>
       </c>
       <c r="B419" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C419" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12040,10 +12052,10 @@
     <row r="420" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A420" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>radomiak-radom</v>
+        <v>piast-gliwice</v>
       </c>
       <c r="B420" s="5" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C420" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12061,10 +12073,10 @@
     <row r="421" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A421" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>rakow-czestochowa</v>
+        <v>mks-pogon-szczecin</v>
       </c>
       <c r="B421" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C421" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12082,10 +12094,10 @@
     <row r="422" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A422" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>slask-wroclaw</v>
+        <v>radomiak-radom</v>
       </c>
       <c r="B422" s="5" t="s">
-        <v>587</v>
+        <v>340</v>
       </c>
       <c r="C422" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12103,10 +12115,10 @@
     <row r="423" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A423" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>rts-widzew-lodz</v>
+        <v>rakow-czestochowa</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C423" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12124,10 +12136,10 @@
     <row r="424" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A424" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ks-wieczysta-krokow</v>
+        <v>slask-wroclaw</v>
       </c>
       <c r="B424" s="5" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C424" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12145,10 +12157,10 @@
     <row r="425" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A425" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>wisla-krakow</v>
+        <v>rts-widzew-lodz</v>
       </c>
       <c r="B425" s="2" t="s">
-        <v>589</v>
+        <v>342</v>
       </c>
       <c r="C425" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12166,10 +12178,10 @@
     <row r="426" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A426" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>wisla-plock</v>
+        <v>ks-wieczysta-krokow</v>
       </c>
       <c r="B426" s="5" t="s">
-        <v>343</v>
+        <v>588</v>
       </c>
       <c r="C426" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12187,10 +12199,10 @@
     <row r="427" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A427" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>zaglebie-lubin</v>
+        <v>wisla-krakow</v>
       </c>
       <c r="B427" s="2" t="s">
-        <v>344</v>
+        <v>589</v>
       </c>
       <c r="C427" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12208,18 +12220,18 @@
     <row r="428" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A428" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>academico-de-viseu-fc</v>
+        <v>wisla-plock</v>
       </c>
       <c r="B428" s="5" t="s">
-        <v>612</v>
+        <v>343</v>
       </c>
       <c r="C428" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>portugal</v>
+        <v>poland</v>
       </c>
       <c r="D428" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>portugal</v>
+        <v>poland</v>
       </c>
       <c r="E428" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -12229,18 +12241,18 @@
     <row r="429" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A429" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-alverca</v>
+        <v>zaglebie-lubin</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C429" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>portugal</v>
+        <v>poland</v>
       </c>
       <c r="D429" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>portugal</v>
+        <v>poland</v>
       </c>
       <c r="E429" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -12250,10 +12262,10 @@
     <row r="430" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A430" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-arouca</v>
+        <v>academico-de-viseu-fc</v>
       </c>
       <c r="B430" s="5" t="s">
-        <v>346</v>
+        <v>612</v>
       </c>
       <c r="C430" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12271,10 +12283,10 @@
     <row r="431" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A431" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>benfica</v>
+        <v>fc-alverca</v>
       </c>
       <c r="B431" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C431" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12292,10 +12304,10 @@
     <row r="432" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A432" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>braga</v>
+        <v>fc-arouca</v>
       </c>
       <c r="B432" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C432" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12313,10 +12325,10 @@
     <row r="433" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A433" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>casa-pia-ac</v>
+        <v>benfica</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C433" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12334,10 +12346,10 @@
     <row r="434" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A434" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>gd-estoril-praia</v>
+        <v>braga</v>
       </c>
       <c r="B434" s="5" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C434" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12355,10 +12367,10 @@
     <row r="435" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A435" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>cf-estrela-da-amadora</v>
+        <v>casa-pia-ac</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C435" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12376,10 +12388,10 @@
     <row r="436" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A436" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>famalicao</v>
+        <v>gd-estoril-praia</v>
       </c>
       <c r="B436" s="5" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C436" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12397,10 +12409,10 @@
     <row r="437" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A437" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-porto</v>
+        <v>cf-estrela-da-amadora</v>
       </c>
       <c r="B437" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C437" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12418,10 +12430,10 @@
     <row r="438" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A438" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>gil-vicente</v>
+        <v>famalicao</v>
       </c>
       <c r="B438" s="5" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C438" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12439,10 +12451,10 @@
     <row r="439" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A439" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>vitoria-de-guimaraes</v>
+        <v>fc-porto</v>
       </c>
       <c r="B439" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C439" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12460,10 +12472,10 @@
     <row r="440" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A440" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>maritimo</v>
+        <v>gil-vicente</v>
       </c>
       <c r="B440" s="5" t="s">
-        <v>613</v>
+        <v>354</v>
       </c>
       <c r="C440" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12481,10 +12493,10 @@
     <row r="441" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A441" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>moreirense-fc</v>
+        <v>vitoria-de-guimaraes</v>
       </c>
       <c r="B441" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C441" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12502,10 +12514,10 @@
     <row r="442" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A442" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>cd-nacional</v>
+        <v>maritimo</v>
       </c>
       <c r="B442" s="5" t="s">
-        <v>357</v>
+        <v>613</v>
       </c>
       <c r="C442" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12523,10 +12535,10 @@
     <row r="443" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A443" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>rio-ave-fc</v>
+        <v>moreirense-fc</v>
       </c>
       <c r="B443" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C443" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12544,10 +12556,10 @@
     <row r="444" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A444" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>santa-clara</v>
+        <v>cd-nacional</v>
       </c>
       <c r="B444" s="5" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C444" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12565,10 +12577,10 @@
     <row r="445" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A445" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>sporting-cp</v>
+        <v>rio-ave-fc</v>
       </c>
       <c r="B445" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C445" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12586,18 +12598,18 @@
     <row r="446" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A446" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-botosani</v>
+        <v>santa-clara</v>
       </c>
       <c r="B446" s="5" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C446" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>romania</v>
+        <v>portugal</v>
       </c>
       <c r="D446" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>romania</v>
+        <v>portugal</v>
       </c>
       <c r="E446" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -12607,18 +12619,18 @@
     <row r="447" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A447" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>cfr-cluj</v>
+        <v>sporting-cp</v>
       </c>
       <c r="B447" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C447" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>romania</v>
+        <v>portugal</v>
       </c>
       <c r="D447" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>romania</v>
+        <v>portugal</v>
       </c>
       <c r="E447" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -12628,10 +12640,10 @@
     <row r="448" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A448" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>corvinul-hunedoara</v>
+        <v>fc-botosani</v>
       </c>
       <c r="B448" s="5" t="s">
-        <v>590</v>
+        <v>361</v>
       </c>
       <c r="C448" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12649,10 +12661,10 @@
     <row r="449" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A449" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fk-miercurea-ciuc</v>
+        <v>cfr-cluj</v>
       </c>
       <c r="B449" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C449" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12670,10 +12682,10 @@
     <row r="450" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A450" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-dinamo-bucuresti</v>
+        <v>corvinul-hunedoara</v>
       </c>
       <c r="B450" s="5" t="s">
-        <v>364</v>
+        <v>590</v>
       </c>
       <c r="C450" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12691,10 +12703,10 @@
     <row r="451" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A451" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-farul-constanta</v>
+        <v>fk-miercurea-ciuc</v>
       </c>
       <c r="B451" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C451" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12712,10 +12724,10 @@
     <row r="452" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A452" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-arges-pitesti</v>
+        <v>fc-dinamo-bucuresti</v>
       </c>
       <c r="B452" s="5" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C452" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12733,10 +12745,10 @@
     <row r="453" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A453" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-rapid-bucuresti</v>
+        <v>fc-farul-constanta</v>
       </c>
       <c r="B453" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C453" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12754,10 +12766,10 @@
     <row r="454" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A454" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-voluntari</v>
+        <v>fc-arges-pitesti</v>
       </c>
       <c r="B454" s="5" t="s">
-        <v>591</v>
+        <v>366</v>
       </c>
       <c r="C454" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12775,10 +12787,10 @@
     <row r="455" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A455" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fcsb</v>
+        <v>fc-rapid-bucuresti</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C455" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12796,10 +12808,10 @@
     <row r="456" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A456" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>asc-otelul-galati</v>
+        <v>fc-voluntari</v>
       </c>
       <c r="B456" s="5" t="s">
-        <v>369</v>
+        <v>591</v>
       </c>
       <c r="C456" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12817,10 +12829,10 @@
     <row r="457" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A457" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-petrolul-ploiesti</v>
+        <v>fcsb</v>
       </c>
       <c r="B457" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C457" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12838,10 +12850,10 @@
     <row r="458" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A458" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>sepsi-osk-sftantu-gheorghe</v>
+        <v>asc-otelul-galati</v>
       </c>
       <c r="B458" s="5" t="s">
-        <v>592</v>
+        <v>369</v>
       </c>
       <c r="C458" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12859,10 +12871,10 @@
     <row r="459" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A459" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-universitatea-cluj</v>
+        <v>fc-petrolul-ploiesti</v>
       </c>
       <c r="B459" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C459" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12880,10 +12892,10 @@
     <row r="460" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A460" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>cs-universitatea-craiova</v>
+        <v>sepsi-osk-sftantu-gheorghe</v>
       </c>
       <c r="B460" s="5" t="s">
-        <v>372</v>
+        <v>592</v>
       </c>
       <c r="C460" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12901,10 +12913,10 @@
     <row r="461" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A461" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-uta-arad</v>
+        <v>fc-universitatea-cluj</v>
       </c>
       <c r="B461" s="2" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C461" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12922,18 +12934,18 @@
     <row r="462" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A462" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>abha-club</v>
+        <v>cs-universitatea-craiova</v>
       </c>
       <c r="B462" s="5" t="s">
-        <v>600</v>
+        <v>372</v>
       </c>
       <c r="C462" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>saudi-arabia</v>
+        <v>romania</v>
       </c>
       <c r="D462" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>saudi-arabia</v>
+        <v>romania</v>
       </c>
       <c r="E462" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -12943,18 +12955,18 @@
     <row r="463" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A463" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>diriyah-club</v>
+        <v>fc-uta-arad</v>
       </c>
       <c r="B463" s="2" t="s">
-        <v>601</v>
+        <v>373</v>
       </c>
       <c r="C463" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>saudi-arabia</v>
+        <v>romania</v>
       </c>
       <c r="D463" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>saudi-arabia</v>
+        <v>romania</v>
       </c>
       <c r="E463" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -12964,10 +12976,10 @@
     <row r="464" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A464" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>al-fateh-sc</v>
+        <v>abha-club</v>
       </c>
       <c r="B464" s="5" t="s">
-        <v>374</v>
+        <v>600</v>
       </c>
       <c r="C464" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12985,10 +12997,10 @@
     <row r="465" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A465" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>al-fayha-fc</v>
+        <v>diriyah-club</v>
       </c>
       <c r="B465" s="2" t="s">
-        <v>375</v>
+        <v>601</v>
       </c>
       <c r="C465" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13006,10 +13018,10 @@
     <row r="466" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A466" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>al-hazem-fc</v>
+        <v>al-fateh-sc</v>
       </c>
       <c r="B466" s="5" t="s">
-        <v>500</v>
+        <v>374</v>
       </c>
       <c r="C466" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13027,10 +13039,10 @@
     <row r="467" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A467" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>khaleej-fc</v>
+        <v>al-fayha-fc</v>
       </c>
       <c r="B467" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C467" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13048,10 +13060,10 @@
     <row r="468" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A468" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>al-kholood-club</v>
+        <v>al-hazem-fc</v>
       </c>
       <c r="B468" s="5" t="s">
-        <v>377</v>
+        <v>500</v>
       </c>
       <c r="C468" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13069,10 +13081,10 @@
     <row r="469" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A469" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>al-qadsiah-fc</v>
+        <v>khaleej-fc</v>
       </c>
       <c r="B469" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C469" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13090,10 +13102,10 @@
     <row r="470" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A470" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>al-riyadh-sc</v>
+        <v>al-kholood-club</v>
       </c>
       <c r="B470" s="5" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C470" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13111,10 +13123,10 @@
     <row r="471" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A471" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>al-ahli-saudi-fc</v>
+        <v>al-qadsiah-fc</v>
       </c>
       <c r="B471" s="2" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C471" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13132,10 +13144,10 @@
     <row r="472" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A472" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>al-ettifaq-fc</v>
+        <v>al-riyadh-sc</v>
       </c>
       <c r="B472" s="5" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C472" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13153,10 +13165,10 @@
     <row r="473" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A473" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>al-faisaly-fc</v>
+        <v>al-ahli-saudi-fc</v>
       </c>
       <c r="B473" s="2" t="s">
-        <v>602</v>
+        <v>380</v>
       </c>
       <c r="C473" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13174,10 +13186,10 @@
     <row r="474" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A474" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>al-hilal-fc</v>
+        <v>al-ettifaq-fc</v>
       </c>
       <c r="B474" s="5" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C474" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13195,10 +13207,10 @@
     <row r="475" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A475" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>al-ittihad-fc</v>
+        <v>al-faisaly-fc</v>
       </c>
       <c r="B475" s="2" t="s">
-        <v>383</v>
+        <v>602</v>
       </c>
       <c r="C475" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13216,10 +13228,10 @@
     <row r="476" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A476" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>al-nassr-fc</v>
+        <v>al-hilal-fc</v>
       </c>
       <c r="B476" s="5" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C476" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13237,10 +13249,10 @@
     <row r="477" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A477" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>al-shabab-fc</v>
+        <v>al-ittihad-fc</v>
       </c>
       <c r="B477" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C477" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13258,10 +13270,10 @@
     <row r="478" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A478" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>al-taawoun-fc</v>
+        <v>al-nassr-fc</v>
       </c>
       <c r="B478" s="5" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C478" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13279,10 +13291,10 @@
     <row r="479" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A479" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>neom-sc</v>
+        <v>al-shabab-fc</v>
       </c>
       <c r="B479" s="2" t="s">
-        <v>501</v>
+        <v>385</v>
       </c>
       <c r="C479" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13300,18 +13312,18 @@
     <row r="480" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A480" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>aberdeen-fc</v>
+        <v>al-taawoun-fc</v>
       </c>
       <c r="B480" s="5" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C480" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>scotland</v>
+        <v>saudi-arabia</v>
       </c>
       <c r="D480" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>scotland</v>
+        <v>saudi-arabia</v>
       </c>
       <c r="E480" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -13321,18 +13333,18 @@
     <row r="481" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A481" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>celtic-fc</v>
+        <v>neom-sc</v>
       </c>
       <c r="B481" s="2" t="s">
-        <v>388</v>
+        <v>501</v>
       </c>
       <c r="C481" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>scotland</v>
+        <v>saudi-arabia</v>
       </c>
       <c r="D481" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>scotland</v>
+        <v>saudi-arabia</v>
       </c>
       <c r="E481" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -13342,10 +13354,10 @@
     <row r="482" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A482" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>dundee-fc</v>
+        <v>aberdeen-fc</v>
       </c>
       <c r="B482" s="5" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C482" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13363,10 +13375,10 @@
     <row r="483" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A483" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>dundee-united-fc</v>
+        <v>celtic-fc</v>
       </c>
       <c r="B483" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C483" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13384,10 +13396,10 @@
     <row r="484" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A484" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>falkirk-fc</v>
+        <v>dundee-fc</v>
       </c>
       <c r="B484" s="5" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C484" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13405,10 +13417,10 @@
     <row r="485" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A485" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>heart-of-midlothian-fc</v>
+        <v>dundee-united-fc</v>
       </c>
       <c r="B485" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C485" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13426,10 +13438,10 @@
     <row r="486" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A486" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>hibernian-fc</v>
+        <v>falkirk-fc</v>
       </c>
       <c r="B486" s="5" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C486" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13447,10 +13459,10 @@
     <row r="487" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A487" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>kilmarnock-fc</v>
+        <v>heart-of-midlothian-fc</v>
       </c>
       <c r="B487" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C487" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13468,10 +13480,10 @@
     <row r="488" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A488" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>motherwell-fc</v>
+        <v>hibernian-fc</v>
       </c>
       <c r="B488" s="5" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C488" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13489,10 +13501,10 @@
     <row r="489" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A489" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>rangers-fc</v>
+        <v>kilmarnock-fc</v>
       </c>
       <c r="B489" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C489" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13510,10 +13522,10 @@
     <row r="490" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A490" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>st-johnstone-fc</v>
+        <v>motherwell-fc</v>
       </c>
       <c r="B490" s="5" t="s">
-        <v>593</v>
+        <v>395</v>
       </c>
       <c r="C490" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13531,10 +13543,10 @@
     <row r="491" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A491" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>st-mirren-fc</v>
+        <v>rangers-fc</v>
       </c>
       <c r="B491" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C491" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13552,18 +13564,18 @@
     <row r="492" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A492" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>deportivo-de-a-coruna</v>
+        <v>st-johnstone-fc</v>
       </c>
       <c r="B492" s="5" t="s">
-        <v>614</v>
+        <v>593</v>
       </c>
       <c r="C492" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>spain</v>
+        <v>scotland</v>
       </c>
       <c r="D492" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>spain</v>
+        <v>scotland</v>
       </c>
       <c r="E492" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -13573,18 +13585,18 @@
     <row r="493" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A493" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>deportivo-alaves</v>
+        <v>st-mirren-fc</v>
       </c>
       <c r="B493" s="2" t="s">
-        <v>40</v>
+        <v>397</v>
       </c>
       <c r="C493" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>spain</v>
+        <v>scotland</v>
       </c>
       <c r="D493" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>spain</v>
+        <v>scotland</v>
       </c>
       <c r="E493" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -13594,10 +13606,10 @@
     <row r="494" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A494" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>athletic-bilbao</v>
+        <v>deportivo-de-a-coruna</v>
       </c>
       <c r="B494" s="5" t="s">
-        <v>41</v>
+        <v>614</v>
       </c>
       <c r="C494" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13615,10 +13627,10 @@
     <row r="495" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A495" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>atletico-madrid</v>
+        <v>deportivo-alaves</v>
       </c>
       <c r="B495" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C495" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13636,10 +13648,10 @@
     <row r="496" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A496" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-barcelona</v>
+        <v>athletic-bilbao</v>
       </c>
       <c r="B496" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C496" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13657,10 +13669,10 @@
     <row r="497" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A497" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>real-betis-balompie</v>
+        <v>atletico-madrid</v>
       </c>
       <c r="B497" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C497" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13678,10 +13690,10 @@
     <row r="498" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A498" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>celta-vigo</v>
+        <v>fc-barcelona</v>
       </c>
       <c r="B498" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C498" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13699,10 +13711,10 @@
     <row r="499" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A499" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>elche-cf</v>
+        <v>real-betis-balompie</v>
       </c>
       <c r="B499" s="2" t="s">
-        <v>471</v>
+        <v>44</v>
       </c>
       <c r="C499" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13720,10 +13732,10 @@
     <row r="500" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A500" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>rcd-espanyol</v>
+        <v>celta-vigo</v>
       </c>
       <c r="B500" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C500" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13741,10 +13753,10 @@
     <row r="501" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A501" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>getafe-cf</v>
+        <v>elche-cf</v>
       </c>
       <c r="B501" s="2" t="s">
-        <v>47</v>
+        <v>471</v>
       </c>
       <c r="C501" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13762,10 +13774,10 @@
     <row r="502" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A502" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>levante-ud</v>
+        <v>rcd-espanyol</v>
       </c>
       <c r="B502" s="5" t="s">
-        <v>472</v>
+        <v>46</v>
       </c>
       <c r="C502" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13783,10 +13795,10 @@
     <row r="503" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A503" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>malaga-cf</v>
+        <v>getafe-cf</v>
       </c>
       <c r="B503" s="2" t="s">
-        <v>407</v>
+        <v>47</v>
       </c>
       <c r="C503" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13804,10 +13816,10 @@
     <row r="504" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A504" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ca-osasuna</v>
+        <v>levante-ud</v>
       </c>
       <c r="B504" s="5" t="s">
-        <v>52</v>
+        <v>472</v>
       </c>
       <c r="C504" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13825,10 +13837,10 @@
     <row r="505" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A505" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>racing-de-santander</v>
+        <v>malaga-cf</v>
       </c>
       <c r="B505" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C505" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13846,10 +13858,10 @@
     <row r="506" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A506" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>rayo-vallecano</v>
+        <v>ca-osasuna</v>
       </c>
       <c r="B506" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C506" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13867,10 +13879,10 @@
     <row r="507" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A507" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>real-madrid-cf</v>
+        <v>racing-de-santander</v>
       </c>
       <c r="B507" s="2" t="s">
-        <v>54</v>
+        <v>408</v>
       </c>
       <c r="C507" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13888,10 +13900,10 @@
     <row r="508" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A508" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>real-sociedad</v>
+        <v>rayo-vallecano</v>
       </c>
       <c r="B508" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C508" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13909,10 +13921,10 @@
     <row r="509" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A509" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>sevilla-fc</v>
+        <v>real-madrid-cf</v>
       </c>
       <c r="B509" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C509" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13930,10 +13942,10 @@
     <row r="510" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A510" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>valencia-cf</v>
+        <v>real-sociedad</v>
       </c>
       <c r="B510" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C510" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13951,10 +13963,10 @@
     <row r="511" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A511" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>villarreal-cf</v>
+        <v>sevilla-fc</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C511" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13972,17 +13984,18 @@
     <row r="512" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A512" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>albacete-balompie</v>
+        <v>valencia-cf</v>
       </c>
       <c r="B512" s="5" t="s">
-        <v>398</v>
+        <v>57</v>
       </c>
       <c r="C512" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
-      <c r="D512" t="s">
-        <v>579</v>
+      <c r="D512" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>spain</v>
       </c>
       <c r="E512" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -13992,17 +14005,18 @@
     <row r="513" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A513" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ud-almeria</v>
+        <v>villarreal-cf</v>
       </c>
       <c r="B513" s="2" t="s">
-        <v>399</v>
+        <v>59</v>
       </c>
       <c r="C513" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
-      <c r="D513" t="s">
-        <v>579</v>
+      <c r="D513" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>spain</v>
       </c>
       <c r="E513" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -14012,10 +14026,10 @@
     <row r="514" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A514" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-andorra</v>
+        <v>albacete-balompie</v>
       </c>
       <c r="B514" s="5" t="s">
-        <v>463</v>
+        <v>398</v>
       </c>
       <c r="C514" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14032,10 +14046,10 @@
     <row r="515" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A515" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>burgos-cf</v>
+        <v>ud-almeria</v>
       </c>
       <c r="B515" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C515" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14052,10 +14066,10 @@
     <row r="516" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A516" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>cadiz-cf</v>
+        <v>fc-andorra</v>
       </c>
       <c r="B516" s="5" t="s">
-        <v>401</v>
+        <v>463</v>
       </c>
       <c r="C516" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14072,10 +14086,10 @@
     <row r="517" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A517" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>cd-castellon</v>
+        <v>burgos-cf</v>
       </c>
       <c r="B517" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C517" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14092,10 +14106,10 @@
     <row r="518" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A518" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>celta-de-vigo-b</v>
+        <v>cadiz-cf</v>
       </c>
       <c r="B518" s="5" t="s">
-        <v>615</v>
+        <v>401</v>
       </c>
       <c r="C518" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14112,10 +14126,10 @@
     <row r="519" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A519" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ad-ceuta-fc</v>
+        <v>cd-castellon</v>
       </c>
       <c r="B519" s="2" t="s">
-        <v>464</v>
+        <v>402</v>
       </c>
       <c r="C519" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14132,10 +14146,10 @@
     <row r="520" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A520" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>cordoba-cf</v>
+        <v>celta-de-vigo-b</v>
       </c>
       <c r="B520" s="5" t="s">
-        <v>403</v>
+        <v>615</v>
       </c>
       <c r="C520" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14152,10 +14166,10 @@
     <row r="521" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A521" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>sd-eibar</v>
+        <v>ad-ceuta-fc</v>
       </c>
       <c r="B521" s="2" t="s">
-        <v>404</v>
+        <v>464</v>
       </c>
       <c r="C521" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14172,10 +14186,10 @@
     <row r="522" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A522" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>cd-eldense</v>
+        <v>cordoba-cf</v>
       </c>
       <c r="B522" s="5" t="s">
-        <v>616</v>
+        <v>403</v>
       </c>
       <c r="C522" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14192,10 +14206,10 @@
     <row r="523" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A523" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>sporting-de-gijon</v>
+        <v>sd-eibar</v>
       </c>
       <c r="B523" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C523" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14212,10 +14226,10 @@
     <row r="524" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A524" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>girona-fc</v>
+        <v>cd-eldense</v>
       </c>
       <c r="B524" s="5" t="s">
-        <v>48</v>
+        <v>616</v>
       </c>
       <c r="C524" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14232,10 +14246,10 @@
     <row r="525" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A525" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>granada-cf</v>
+        <v>sporting-de-gijon</v>
       </c>
       <c r="B525" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C525" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14252,10 +14266,10 @@
     <row r="526" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A526" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ud-las-palmas</v>
+        <v>girona-fc</v>
       </c>
       <c r="B526" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C526" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14272,10 +14286,10 @@
     <row r="527" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A527" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>cd-leganes</v>
+        <v>granada-cf</v>
       </c>
       <c r="B527" s="2" t="s">
-        <v>50</v>
+        <v>406</v>
       </c>
       <c r="C527" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14292,10 +14306,10 @@
     <row r="528" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A528" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>rcd-mallorca</v>
+        <v>ud-las-palmas</v>
       </c>
       <c r="B528" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C528" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14312,10 +14326,10 @@
     <row r="529" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A529" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>real-oviedo</v>
+        <v>cd-leganes</v>
       </c>
       <c r="B529" s="2" t="s">
-        <v>473</v>
+        <v>50</v>
       </c>
       <c r="C529" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14332,10 +14346,10 @@
     <row r="530" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A530" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>real-sociedad-b</v>
+        <v>rcd-mallorca</v>
       </c>
       <c r="B530" s="5" t="s">
-        <v>465</v>
+        <v>51</v>
       </c>
       <c r="C530" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14352,10 +14366,10 @@
     <row r="531" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A531" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ce-sabadell-fc</v>
+        <v>real-oviedo</v>
       </c>
       <c r="B531" s="2" t="s">
-        <v>617</v>
+        <v>473</v>
       </c>
       <c r="C531" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14372,10 +14386,10 @@
     <row r="532" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A532" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>cd-tenerife</v>
+        <v>real-sociedad-b</v>
       </c>
       <c r="B532" s="5" t="s">
-        <v>618</v>
+        <v>465</v>
       </c>
       <c r="C532" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14392,10 +14406,10 @@
     <row r="533" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A533" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>real-valladolid</v>
+        <v>ce-sabadell-fc</v>
       </c>
       <c r="B533" s="2" t="s">
-        <v>58</v>
+        <v>617</v>
       </c>
       <c r="C533" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14412,18 +14426,17 @@
     <row r="534" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A534" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>aik</v>
+        <v>cd-tenerife</v>
       </c>
       <c r="B534" s="5" t="s">
-        <v>409</v>
+        <v>618</v>
       </c>
       <c r="C534" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>sweden</v>
-      </c>
-      <c r="D534" t="str">
-        <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>sweden</v>
+        <v>spain</v>
+      </c>
+      <c r="D534" t="s">
+        <v>579</v>
       </c>
       <c r="E534" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -14433,18 +14446,17 @@
     <row r="535" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A535" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>if-brommapojkarna</v>
+        <v>real-valladolid</v>
       </c>
       <c r="B535" s="2" t="s">
-        <v>410</v>
+        <v>58</v>
       </c>
       <c r="C535" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>sweden</v>
-      </c>
-      <c r="D535" t="str">
-        <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>sweden</v>
+        <v>spain</v>
+      </c>
+      <c r="D535" t="s">
+        <v>579</v>
       </c>
       <c r="E535" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -14454,10 +14466,10 @@
     <row r="536" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A536" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>degerfors-if</v>
+        <v>aik</v>
       </c>
       <c r="B536" s="5" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C536" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14475,10 +14487,10 @@
     <row r="537" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A537" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>djurgardens-if</v>
+        <v>if-brommapojkarna</v>
       </c>
       <c r="B537" s="2" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C537" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14496,10 +14508,10 @@
     <row r="538" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A538" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>if-elfsborg</v>
+        <v>degerfors-if</v>
       </c>
       <c r="B538" s="5" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C538" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14517,10 +14529,10 @@
     <row r="539" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A539" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>gais</v>
+        <v>djurgardens-if</v>
       </c>
       <c r="B539" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C539" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14538,10 +14550,10 @@
     <row r="540" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A540" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ifk-goteborg</v>
+        <v>if-elfsborg</v>
       </c>
       <c r="B540" s="5" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C540" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14559,10 +14571,10 @@
     <row r="541" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A541" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>bk-hacken</v>
+        <v>gais</v>
       </c>
       <c r="B541" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C541" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14580,10 +14592,10 @@
     <row r="542" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A542" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>halmstads-bk</v>
+        <v>ifk-goteborg</v>
       </c>
       <c r="B542" s="5" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C542" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14601,10 +14613,10 @@
     <row r="543" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A543" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>hammarby-if</v>
+        <v>bk-hacken</v>
       </c>
       <c r="B543" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C543" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14622,10 +14634,10 @@
     <row r="544" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A544" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>kalmar-ff</v>
+        <v>halmstads-bk</v>
       </c>
       <c r="B544" s="5" t="s">
-        <v>541</v>
+        <v>417</v>
       </c>
       <c r="C544" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14643,10 +14655,10 @@
     <row r="545" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A545" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>malmo-ff</v>
+        <v>hammarby-if</v>
       </c>
       <c r="B545" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C545" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14664,10 +14676,10 @@
     <row r="546" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A546" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>mjallby-aif</v>
+        <v>kalmar-ff</v>
       </c>
       <c r="B546" s="5" t="s">
-        <v>420</v>
+        <v>541</v>
       </c>
       <c r="C546" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14685,10 +14697,10 @@
     <row r="547" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A547" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>orgryte-is</v>
+        <v>malmo-ff</v>
       </c>
       <c r="B547" s="2" t="s">
-        <v>542</v>
+        <v>419</v>
       </c>
       <c r="C547" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14706,10 +14718,10 @@
     <row r="548" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A548" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ik-sirius</v>
+        <v>mjallby-aif</v>
       </c>
       <c r="B548" s="5" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C548" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14727,10 +14739,10 @@
     <row r="549" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A549" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>vasteras-sk</v>
+        <v>orgryte-is</v>
       </c>
       <c r="B549" s="2" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C549" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14748,18 +14760,18 @@
     <row r="550" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A550" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-basel</v>
+        <v>ik-sirius</v>
       </c>
       <c r="B550" s="5" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C550" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>switzerland</v>
+        <v>sweden</v>
       </c>
       <c r="D550" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>switzerland</v>
+        <v>sweden</v>
       </c>
       <c r="E550" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -14769,18 +14781,18 @@
     <row r="551" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A551" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>grasshopper-club-zurich</v>
+        <v>vasteras-sk</v>
       </c>
       <c r="B551" s="2" t="s">
-        <v>423</v>
+        <v>543</v>
       </c>
       <c r="C551" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>switzerland</v>
+        <v>sweden</v>
       </c>
       <c r="D551" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>switzerland</v>
+        <v>sweden</v>
       </c>
       <c r="E551" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -14790,10 +14802,10 @@
     <row r="552" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A552" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-lausanne-sport</v>
+        <v>fc-basel</v>
       </c>
       <c r="B552" s="5" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C552" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14811,10 +14823,10 @@
     <row r="553" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A553" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-lugano</v>
+        <v>grasshopper-club-zurich</v>
       </c>
       <c r="B553" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C553" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14832,10 +14844,10 @@
     <row r="554" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A554" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-luzern</v>
+        <v>fc-lausanne-sport</v>
       </c>
       <c r="B554" s="5" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C554" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14853,10 +14865,10 @@
     <row r="555" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A555" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>servette-fc</v>
-      </c>
-      <c r="B555" s="6" t="s">
-        <v>427</v>
+        <v>fc-lugano</v>
+      </c>
+      <c r="B555" s="2" t="s">
+        <v>425</v>
       </c>
       <c r="C555" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14874,10 +14886,10 @@
     <row r="556" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A556" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-sion</v>
-      </c>
-      <c r="B556" t="s">
-        <v>428</v>
+        <v>fc-luzern</v>
+      </c>
+      <c r="B556" s="5" t="s">
+        <v>426</v>
       </c>
       <c r="C556" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14895,10 +14907,10 @@
     <row r="557" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A557" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-st-gallen</v>
-      </c>
-      <c r="B557" s="7" t="s">
-        <v>429</v>
+        <v>servette-fc</v>
+      </c>
+      <c r="B557" s="6" t="s">
+        <v>427</v>
       </c>
       <c r="C557" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14916,10 +14928,10 @@
     <row r="558" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A558" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-thun</v>
+        <v>fc-sion</v>
       </c>
       <c r="B558" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C558" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14937,10 +14949,10 @@
     <row r="559" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A559" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-vaduz</v>
+        <v>fc-st-gallen</v>
       </c>
       <c r="B559" s="7" t="s">
-        <v>594</v>
+        <v>429</v>
       </c>
       <c r="C559" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14958,10 +14970,10 @@
     <row r="560" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A560" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>bsc-young-boys</v>
+        <v>fc-thun</v>
       </c>
       <c r="B560" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C560" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14979,10 +14991,10 @@
     <row r="561" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A561" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-zurich</v>
+        <v>fc-vaduz</v>
       </c>
       <c r="B561" s="7" t="s">
-        <v>432</v>
+        <v>594</v>
       </c>
       <c r="C561" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15000,18 +15012,18 @@
     <row r="562" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A562" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>atlanta-united-fc</v>
+        <v>bsc-young-boys</v>
       </c>
       <c r="B562" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C562" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>usa</v>
+        <v>switzerland</v>
       </c>
       <c r="D562" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>usa</v>
+        <v>switzerland</v>
       </c>
       <c r="E562" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -15021,18 +15033,18 @@
     <row r="563" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A563" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>austin-fc</v>
+        <v>fc-zurich</v>
       </c>
       <c r="B563" s="7" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C563" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>usa</v>
+        <v>switzerland</v>
       </c>
       <c r="D563" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>usa</v>
+        <v>switzerland</v>
       </c>
       <c r="E563" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -15042,10 +15054,10 @@
     <row r="564" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A564" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>club-de-foot-montreal</v>
+        <v>atlanta-united-fc</v>
       </c>
       <c r="B564" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C564" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15063,10 +15075,10 @@
     <row r="565" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A565" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>charlotte-fc</v>
+        <v>austin-fc</v>
       </c>
       <c r="B565" s="7" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C565" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15084,10 +15096,10 @@
     <row r="566" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A566" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>chicago-fire-fc</v>
+        <v>club-de-foot-montreal</v>
       </c>
       <c r="B566" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C566" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15105,10 +15117,10 @@
     <row r="567" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A567" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-cincinnati</v>
+        <v>charlotte-fc</v>
       </c>
       <c r="B567" s="7" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C567" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15126,10 +15138,10 @@
     <row r="568" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A568" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>colorado-rapids</v>
+        <v>chicago-fire-fc</v>
       </c>
       <c r="B568" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C568" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15147,10 +15159,10 @@
     <row r="569" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A569" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>columbus-crew-sc</v>
+        <v>fc-cincinnati</v>
       </c>
       <c r="B569" s="7" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C569" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15168,10 +15180,10 @@
     <row r="570" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A570" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>dc-united</v>
+        <v>colorado-rapids</v>
       </c>
       <c r="B570" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C570" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15189,10 +15201,10 @@
     <row r="571" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A571" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-dallas</v>
+        <v>columbus-crew-sc</v>
       </c>
       <c r="B571" s="7" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C571" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15210,10 +15222,10 @@
     <row r="572" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A572" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>houston-dynamo</v>
+        <v>dc-united</v>
       </c>
       <c r="B572" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C572" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15231,10 +15243,10 @@
     <row r="573" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A573" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>inter-miami-cf</v>
+        <v>fc-dallas</v>
       </c>
       <c r="B573" s="7" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C573" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15252,10 +15264,10 @@
     <row r="574" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A574" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>los-angeles-fc</v>
+        <v>houston-dynamo</v>
       </c>
       <c r="B574" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C574" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15273,10 +15285,10 @@
     <row r="575" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A575" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>los-angeles-galaxy</v>
+        <v>inter-miami-cf</v>
       </c>
       <c r="B575" s="7" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C575" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15294,10 +15306,10 @@
     <row r="576" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A576" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>minnesota-united-fc</v>
+        <v>los-angeles-fc</v>
       </c>
       <c r="B576" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C576" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15315,10 +15327,10 @@
     <row r="577" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A577" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>nashville-sc</v>
+        <v>los-angeles-galaxy</v>
       </c>
       <c r="B577" s="7" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C577" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15336,10 +15348,10 @@
     <row r="578" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A578" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>new-england-revolution</v>
+        <v>minnesota-united-fc</v>
       </c>
       <c r="B578" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C578" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15357,10 +15369,10 @@
     <row r="579" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A579" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>new-york-city-fc</v>
+        <v>nashville-sc</v>
       </c>
       <c r="B579" s="7" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C579" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15378,10 +15390,10 @@
     <row r="580" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A580" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>new-york-red-bulls</v>
+        <v>new-england-revolution</v>
       </c>
       <c r="B580" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C580" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15399,10 +15411,10 @@
     <row r="581" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A581" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>orlando-city-sc</v>
+        <v>new-york-city-fc</v>
       </c>
       <c r="B581" s="7" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C581" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15420,10 +15432,10 @@
     <row r="582" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A582" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>philadelphia-union</v>
+        <v>new-york-red-bulls</v>
       </c>
       <c r="B582" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C582" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15441,10 +15453,10 @@
     <row r="583" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A583" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>portland-timbers</v>
+        <v>orlando-city-sc</v>
       </c>
       <c r="B583" s="7" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C583" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15462,10 +15474,10 @@
     <row r="584" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A584" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>real-salt-lake</v>
+        <v>philadelphia-union</v>
       </c>
       <c r="B584" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C584" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15483,10 +15495,10 @@
     <row r="585" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A585" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>san-diego-fc</v>
+        <v>portland-timbers</v>
       </c>
       <c r="B585" s="7" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C585" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15504,10 +15516,10 @@
     <row r="586" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A586" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>san-jose-earthquakes</v>
+        <v>real-salt-lake</v>
       </c>
       <c r="B586" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C586" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15525,10 +15537,10 @@
     <row r="587" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A587" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>seattle-sounders-fc</v>
+        <v>san-diego-fc</v>
       </c>
       <c r="B587" s="7" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C587" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15546,10 +15558,10 @@
     <row r="588" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A588" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>sporting-kansas-city</v>
+        <v>san-jose-earthquakes</v>
       </c>
       <c r="B588" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C588" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15567,10 +15579,10 @@
     <row r="589" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A589" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>st-louis-city-sc</v>
+        <v>seattle-sounders-fc</v>
       </c>
       <c r="B589" s="7" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C589" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15588,10 +15600,10 @@
     <row r="590" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A590" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>toronto-fc</v>
+        <v>sporting-kansas-city</v>
       </c>
       <c r="B590" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C590" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15609,10 +15621,10 @@
     <row r="591" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A591" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>vancouver-whitecaps-fc</v>
+        <v>st-louis-city-sc</v>
       </c>
       <c r="B591" s="7" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C591" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15630,18 +15642,18 @@
     <row r="592" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A592" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>bohemians-fc</v>
+        <v>toronto-fc</v>
       </c>
       <c r="B592" t="s">
-        <v>544</v>
+        <v>461</v>
       </c>
       <c r="C592" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>ireland</v>
+        <v>usa</v>
       </c>
       <c r="D592" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>ireland</v>
+        <v>usa</v>
       </c>
       <c r="E592" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -15651,18 +15663,18 @@
     <row r="593" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A593" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>derry-city-fc</v>
-      </c>
-      <c r="B593" t="s">
-        <v>545</v>
+        <v>vancouver-whitecaps-fc</v>
+      </c>
+      <c r="B593" s="7" t="s">
+        <v>462</v>
       </c>
       <c r="C593" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>ireland</v>
+        <v>usa</v>
       </c>
       <c r="D593" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>ireland</v>
+        <v>usa</v>
       </c>
       <c r="E593" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -15672,10 +15684,10 @@
     <row r="594" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A594" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>drogheda-united-fc</v>
+        <v>bohemians-fc</v>
       </c>
       <c r="B594" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C594" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15693,10 +15705,10 @@
     <row r="595" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A595" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>dundalk-fc</v>
+        <v>derry-city-fc</v>
       </c>
       <c r="B595" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C595" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15714,10 +15726,10 @@
     <row r="596" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A596" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>galway-united-fc</v>
+        <v>drogheda-united-fc</v>
       </c>
       <c r="B596" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C596" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15735,10 +15747,10 @@
     <row r="597" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A597" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>shamrock-rovers-fc</v>
+        <v>dundalk-fc</v>
       </c>
       <c r="B597" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C597" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15756,10 +15768,10 @@
     <row r="598" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A598" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>shelbourne-fc</v>
+        <v>galway-united-fc</v>
       </c>
       <c r="B598" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C598" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15777,10 +15789,10 @@
     <row r="599" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A599" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>sligo-rovers-fc</v>
+        <v>shamrock-rovers-fc</v>
       </c>
       <c r="B599" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C599" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15798,10 +15810,10 @@
     <row r="600" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A600" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>st-patricks-athletic-fc</v>
+        <v>shelbourne-fc</v>
       </c>
       <c r="B600" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C600" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15819,10 +15831,10 @@
     <row r="601" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A601" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>waterford-fc</v>
+        <v>sligo-rovers-fc</v>
       </c>
       <c r="B601" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="C601" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15840,18 +15852,18 @@
     <row r="602" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A602" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>al-ahly-sc</v>
+        <v>st-patricks-athletic-fc</v>
       </c>
       <c r="B602" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="C602" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>egypt</v>
+        <v>ireland</v>
       </c>
       <c r="D602" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>egypt</v>
+        <v>ireland</v>
       </c>
       <c r="E602" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -15861,18 +15873,18 @@
     <row r="603" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A603" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>al-ittihad-ac</v>
+        <v>waterford-fc</v>
       </c>
       <c r="B603" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C603" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>egypt</v>
+        <v>ireland</v>
       </c>
       <c r="D603" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>egypt</v>
+        <v>ireland</v>
       </c>
       <c r="E603" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -15882,10 +15894,10 @@
     <row r="604" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A604" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>al-masry-sc</v>
+        <v>al-ahly-sc</v>
       </c>
       <c r="B604" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C604" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15903,10 +15915,10 @@
     <row r="605" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A605" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>arab-contractors-sc</v>
+        <v>al-ittihad-ac</v>
       </c>
       <c r="B605" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C605" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15924,10 +15936,10 @@
     <row r="606" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A606" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ceramica-cleopatra-fc</v>
+        <v>al-masry-sc</v>
       </c>
       <c r="B606" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C606" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15945,10 +15957,10 @@
     <row r="607" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A607" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>talaea-el-gaish-sc</v>
+        <v>arab-contractors-sc</v>
       </c>
       <c r="B607" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C607" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15966,10 +15978,10 @@
     <row r="608" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A608" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>el-gouna-fc</v>
+        <v>ceramica-cleopatra-fc</v>
       </c>
       <c r="B608" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C608" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15987,10 +15999,10 @@
     <row r="609" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A609" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>enppi-sc</v>
+        <v>talaea-el-gaish-sc</v>
       </c>
       <c r="B609" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C609" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16008,10 +16020,10 @@
     <row r="610" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A610" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ghazi-el-mahalla-sc</v>
+        <v>el-gouna-fc</v>
       </c>
       <c r="B610" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C610" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16029,10 +16041,10 @@
     <row r="611" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A611" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>haras-el-hodoud-sc</v>
+        <v>enppi-sc</v>
       </c>
       <c r="B611" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C611" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16050,10 +16062,10 @@
     <row r="612" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A612" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ismaily-sc</v>
+        <v>ghazi-el-mahalla-sc</v>
       </c>
       <c r="B612" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C612" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16071,10 +16083,10 @@
     <row r="613" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A613" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>kahrabaa-ismailia-sc</v>
+        <v>haras-el-hodoud-sc</v>
       </c>
       <c r="B613" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C613" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16092,10 +16104,10 @@
     <row r="614" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A614" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>modern-sport-fc</v>
+        <v>ismaily-sc</v>
       </c>
       <c r="B614" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C614" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16113,10 +16125,10 @@
     <row r="615" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A615" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>national-bank-of-egypt-sc</v>
+        <v>kahrabaa-ismailia-sc</v>
       </c>
       <c r="B615" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C615" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16134,10 +16146,10 @@
     <row r="616" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A616" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>petrojet-sc</v>
+        <v>modern-sport-fc</v>
       </c>
       <c r="B616" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="C616" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16155,10 +16167,10 @@
     <row r="617" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A617" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>pharco-fc</v>
+        <v>national-bank-of-egypt-sc</v>
       </c>
       <c r="B617" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C617" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16176,10 +16188,10 @@
     <row r="618" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A618" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>pyramids-fc</v>
+        <v>petrojet-sc</v>
       </c>
       <c r="B618" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="C618" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16197,10 +16209,10 @@
     <row r="619" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A619" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>smouha-sc</v>
+        <v>pharco-fc</v>
       </c>
       <c r="B619" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C619" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16218,10 +16230,10 @@
     <row r="620" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A620" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>wadi-degla-sc</v>
+        <v>pyramids-fc</v>
       </c>
       <c r="B620" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C620" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16239,10 +16251,10 @@
     <row r="621" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A621" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>zamalek-sc</v>
+        <v>smouha-sc</v>
       </c>
       <c r="B621" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C621" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16260,10 +16272,10 @@
     <row r="622" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A622" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>zed-fc</v>
+        <v>wadi-degla-sc</v>
       </c>
       <c r="B622" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C622" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16281,18 +16293,18 @@
     <row r="623" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A623" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>aek-larnaca-fc</v>
+        <v>zamalek-sc</v>
       </c>
       <c r="B623" t="s">
-        <v>629</v>
+        <v>573</v>
       </c>
       <c r="C623" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>cyprus</v>
+        <v>egypt</v>
       </c>
       <c r="D623" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>cyprus</v>
+        <v>egypt</v>
       </c>
       <c r="E623" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -16302,18 +16314,18 @@
     <row r="624" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A624" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ael-limassol</v>
+        <v>zed-fc</v>
       </c>
       <c r="B624" t="s">
-        <v>630</v>
+        <v>574</v>
       </c>
       <c r="C624" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>cyprus</v>
+        <v>egypt</v>
       </c>
       <c r="D624" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>cyprus</v>
+        <v>egypt</v>
       </c>
       <c r="E624" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -16323,10 +16335,10 @@
     <row r="625" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A625" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>anorthosis-famagusta-fc</v>
+        <v>aek-larnaca-fc</v>
       </c>
       <c r="B625" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="C625" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16344,10 +16356,10 @@
     <row r="626" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A626" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>apoel-fc</v>
+        <v>ael-limassol</v>
       </c>
       <c r="B626" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C626" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16365,10 +16377,10 @@
     <row r="627" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A627" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>apollon-limassol</v>
+        <v>anorthosis-famagusta-fc</v>
       </c>
       <c r="B627" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C627" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16386,10 +16398,10 @@
     <row r="628" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A628" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>aris-limassol-fc</v>
+        <v>apoel-fc</v>
       </c>
       <c r="B628" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C628" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16407,10 +16419,10 @@
     <row r="629" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A629" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>karmiotissa-fc</v>
+        <v>apollon-limassol</v>
       </c>
       <c r="B629" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C629" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16428,10 +16440,10 @@
     <row r="630" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A630" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>krasava-eny-ypsonas-fc</v>
+        <v>aris-limassol-fc</v>
       </c>
       <c r="B630" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="C630" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16449,10 +16461,10 @@
     <row r="631" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A631" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>nea-salamis-famagusta-fc</v>
+        <v>karmiotissa-fc</v>
       </c>
       <c r="B631" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C631" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16470,10 +16482,10 @@
     <row r="632" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A632" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>olympiakos-nicosia</v>
+        <v>krasava-eny-ypsonas-fc</v>
       </c>
       <c r="B632" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="C632" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16491,10 +16503,10 @@
     <row r="633" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A633" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ac-omonia</v>
+        <v>nea-salamis-famagusta-fc</v>
       </c>
       <c r="B633" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C633" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16512,10 +16524,10 @@
     <row r="634" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A634" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>pac-omonia-29m</v>
+        <v>olympiakos-nicosia</v>
       </c>
       <c r="B634" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="C634" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16533,10 +16545,10 @@
     <row r="635" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A635" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>omonia-aradippou</v>
+        <v>ac-omonia</v>
       </c>
       <c r="B635" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C635" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16554,10 +16566,10 @@
     <row r="636" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A636" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>pafos-fc</v>
+        <v>pac-omonia-29m</v>
       </c>
       <c r="B636" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="C636" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16575,18 +16587,18 @@
     <row r="637" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A637" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>debrecen</v>
+        <v>omonia-aradippou</v>
       </c>
       <c r="B637" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C637" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>hungary</v>
+        <v>cyprus</v>
       </c>
       <c r="D637" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>hungary</v>
+        <v>cyprus</v>
       </c>
       <c r="E637" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -16596,18 +16608,18 @@
     <row r="638" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A638" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ferencvaros</v>
+        <v>pafos-fc</v>
       </c>
       <c r="B638" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="C638" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>hungary</v>
+        <v>cyprus</v>
       </c>
       <c r="D638" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>hungary</v>
+        <v>cyprus</v>
       </c>
       <c r="E638" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -16617,10 +16629,10 @@
     <row r="639" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A639" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>gyori-eto-fc</v>
+        <v>debrecen</v>
       </c>
       <c r="B639" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C639" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16638,10 +16650,10 @@
     <row r="640" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A640" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>budapest-honved-fc</v>
+        <v>ferencvaros</v>
       </c>
       <c r="B640" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="C640" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16659,10 +16671,10 @@
     <row r="641" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A641" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>kisvarda-fc</v>
+        <v>gyori-eto-fc</v>
       </c>
       <c r="B641" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="C641" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16680,10 +16692,10 @@
     <row r="642" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A642" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>mtk-budapest-fc</v>
+        <v>budapest-honved-fc</v>
       </c>
       <c r="B642" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C642" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16701,10 +16713,10 @@
     <row r="643" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A643" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>nyiregyhaza-spartacus-fc</v>
+        <v>kisvarda-fc</v>
       </c>
       <c r="B643" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C643" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16722,10 +16734,10 @@
     <row r="644" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A644" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>paksi-fc</v>
+        <v>mtk-budapest-fc</v>
       </c>
       <c r="B644" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C644" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16743,10 +16755,10 @@
     <row r="645" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A645" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>puskas-akademia-fc</v>
+        <v>nyiregyhaza-spartacus-fc</v>
       </c>
       <c r="B645" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C645" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16764,10 +16776,10 @@
     <row r="646" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A646" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ujpest-fc</v>
+        <v>paksi-fc</v>
       </c>
       <c r="B646" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C646" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16785,10 +16797,10 @@
     <row r="647" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A647" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>vasas-sc</v>
+        <v>puskas-akademia-fc</v>
       </c>
       <c r="B647" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="C647" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16806,10 +16818,10 @@
     <row r="648" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A648" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>zalaegerszeg-te</v>
+        <v>ujpest-fc</v>
       </c>
       <c r="B648" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C648" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16827,18 +16839,18 @@
     <row r="649" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A649" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>albion-fc</v>
+        <v>vasas-sc</v>
       </c>
       <c r="B649" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C649" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>uruguay</v>
+        <v>hungary</v>
       </c>
       <c r="D649" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>uruguay</v>
+        <v>hungary</v>
       </c>
       <c r="E649" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -16848,18 +16860,18 @@
     <row r="650" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A650" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>boston-river</v>
+        <v>zalaegerszeg-te</v>
       </c>
       <c r="B650" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="C650" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>uruguay</v>
+        <v>hungary</v>
       </c>
       <c r="D650" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>uruguay</v>
+        <v>hungary</v>
       </c>
       <c r="E650" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -16869,10 +16881,10 @@
     <row r="651" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A651" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>central-espanol</v>
+        <v>albion-fc</v>
       </c>
       <c r="B651" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C651" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16890,10 +16902,10 @@
     <row r="652" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A652" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>club-atletico-cerro</v>
+        <v>boston-river</v>
       </c>
       <c r="B652" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C652" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16911,10 +16923,10 @@
     <row r="653" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A653" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>cerro-largo-fc</v>
+        <v>central-espanol</v>
       </c>
       <c r="B653" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="C653" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16932,10 +16944,10 @@
     <row r="654" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A654" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>danubio-fc</v>
+        <v>club-atletico-cerro</v>
       </c>
       <c r="B654" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C654" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16953,10 +16965,10 @@
     <row r="655" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A655" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>defensor-sporting</v>
+        <v>cerro-largo-fc</v>
       </c>
       <c r="B655" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C655" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16974,10 +16986,10 @@
     <row r="656" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A656" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>juventud-de-las-piedras</v>
+        <v>danubio-fc</v>
       </c>
       <c r="B656" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C656" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16995,10 +17007,10 @@
     <row r="657" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A657" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>liverpool-fc-montevideo</v>
+        <v>defensor-sporting</v>
       </c>
       <c r="B657" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="C657" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17016,10 +17028,10 @@
     <row r="658" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A658" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>deportivo-maldonado</v>
+        <v>juventud-de-las-piedras</v>
       </c>
       <c r="B658" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="C658" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17037,10 +17049,10 @@
     <row r="659" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A659" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>montevideo-city-torque</v>
+        <v>liverpool-fc-montevideo</v>
       </c>
       <c r="B659" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="C659" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17058,10 +17070,10 @@
     <row r="660" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A660" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>club-nacional-de-football</v>
+        <v>deportivo-maldonado</v>
       </c>
       <c r="B660" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C660" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17079,10 +17091,10 @@
     <row r="661" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A661" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>penarol</v>
+        <v>montevideo-city-torque</v>
       </c>
       <c r="B661" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="C661" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17100,10 +17112,10 @@
     <row r="662" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A662" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>club-atletico-progreso</v>
+        <v>club-nacional-de-football</v>
       </c>
       <c r="B662" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C662" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17121,10 +17133,10 @@
     <row r="663" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A663" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>racing-club-de-montevideo</v>
+        <v>penarol</v>
       </c>
       <c r="B663" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="C663" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17142,10 +17154,10 @@
     <row r="664" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A664" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>montevideo-wanderers-fc</v>
+        <v>club-atletico-progreso</v>
       </c>
       <c r="B664" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C664" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17163,18 +17175,18 @@
     <row r="665" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A665" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fsc-bukovyna-chernivtsi</v>
+        <v>racing-club-de-montevideo</v>
       </c>
       <c r="B665" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C665" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>ukraine</v>
+        <v>uruguay</v>
       </c>
       <c r="D665" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>ukraine</v>
+        <v>uruguay</v>
       </c>
       <c r="E665" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -17184,18 +17196,18 @@
     <row r="666" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A666" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-chornomorets-odessa</v>
+        <v>montevideo-wanderers-fc</v>
       </c>
       <c r="B666" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C666" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>ukraine</v>
+        <v>uruguay</v>
       </c>
       <c r="D666" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>ukraine</v>
+        <v>uruguay</v>
       </c>
       <c r="E666" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -17205,10 +17217,10 @@
     <row r="667" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A667" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-dynamo-kyiv</v>
+        <v>fsc-bukovyna-chernivtsi</v>
       </c>
       <c r="B667" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="C667" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17226,10 +17238,10 @@
     <row r="668" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A668" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-epitsentr-kamianets-podilskyi</v>
+        <v>fc-chornomorets-odessa</v>
       </c>
       <c r="B668" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="C668" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17247,10 +17259,10 @@
     <row r="669" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A669" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-kharkiv</v>
+        <v>fc-dynamo-kyiv</v>
       </c>
       <c r="B669" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="C669" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17268,10 +17280,10 @@
     <row r="670" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A670" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-karpaty-lviv</v>
+        <v>fc-epitsentr-kamianets-podilskyi</v>
       </c>
       <c r="B670" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="C670" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17289,10 +17301,10 @@
     <row r="671" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A671" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-kolos-kovalivka</v>
+        <v>fc-kharkiv</v>
       </c>
       <c r="B671" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C671" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17310,10 +17322,10 @@
     <row r="672" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A672" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-kryvbas-kryvyi-rih</v>
+        <v>fc-karpaty-lviv</v>
       </c>
       <c r="B672" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C672" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17331,10 +17343,10 @@
     <row r="673" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A673" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-kudrivka</v>
+        <v>fc-kolos-kovalivka</v>
       </c>
       <c r="B673" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C673" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17352,10 +17364,10 @@
     <row r="674" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A674" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-livyi-bereh-kyiv</v>
+        <v>fc-kryvbas-kryvyi-rih</v>
       </c>
       <c r="B674" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="C674" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17373,10 +17385,10 @@
     <row r="675" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A675" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-lnz-cherkasy</v>
+        <v>fc-kudrivka</v>
       </c>
       <c r="B675" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C675" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17394,10 +17406,10 @@
     <row r="676" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A676" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-obolon-kyiv</v>
+        <v>fc-livyi-bereh-kyiv</v>
       </c>
       <c r="B676" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C676" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17415,10 +17427,10 @@
     <row r="677" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A677" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-polissya-zhytomyr</v>
+        <v>fc-lnz-cherkasy</v>
       </c>
       <c r="B677" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="C677" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17436,10 +17448,10 @@
     <row r="678" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A678" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-shakhtar-donetsk</v>
+        <v>fc-obolon-kyiv</v>
       </c>
       <c r="B678" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="C678" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17457,10 +17469,10 @@
     <row r="679" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A679" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>nk-veres-rivne</v>
+        <v>fc-polissya-zhytomyr</v>
       </c>
       <c r="B679" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="C679" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17478,10 +17490,10 @@
     <row r="680" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A680" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-zorya-luhansk</v>
+        <v>fc-shakhtar-donetsk</v>
       </c>
       <c r="B680" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="C680" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17499,18 +17511,18 @@
     <row r="681" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A681" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>avispa-fukuoka</v>
+        <v>nk-veres-rivne</v>
       </c>
       <c r="B681" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="C681" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>japan</v>
+        <v>ukraine</v>
       </c>
       <c r="D681" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>japan</v>
+        <v>ukraine</v>
       </c>
       <c r="E681" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -17520,18 +17532,18 @@
     <row r="682" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A682" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>cerezo-osaka</v>
+        <v>fc-zorya-luhansk</v>
       </c>
       <c r="B682" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="C682" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>japan</v>
+        <v>ukraine</v>
       </c>
       <c r="D682" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>japan</v>
+        <v>ukraine</v>
       </c>
       <c r="E682" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -17541,10 +17553,10 @@
     <row r="683" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A683" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fagiano-okayama</v>
+        <v>avispa-fukuoka</v>
       </c>
       <c r="B683" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C683" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17562,10 +17574,10 @@
     <row r="684" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A684" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>gamba-osaka</v>
+        <v>cerezo-osaka</v>
       </c>
       <c r="B684" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="C684" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17583,10 +17595,10 @@
     <row r="685" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A685" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>sanfreece-hiroshima</v>
+        <v>fagiano-okayama</v>
       </c>
       <c r="B685" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="C685" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17604,10 +17616,10 @@
     <row r="686" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A686" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>jef-united-chiba</v>
+        <v>gamba-osaka</v>
       </c>
       <c r="B686" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="C686" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17625,10 +17637,10 @@
     <row r="687" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A687" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>kashima-antlers</v>
+        <v>sanfreece-hiroshima</v>
       </c>
       <c r="B687" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="C687" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17646,10 +17658,10 @@
     <row r="688" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A688" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>kashiwa-reysol</v>
+        <v>jef-united-chiba</v>
       </c>
       <c r="B688" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="C688" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17667,10 +17679,10 @@
     <row r="689" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A689" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>kawasaki-frontale</v>
+        <v>kashima-antlers</v>
       </c>
       <c r="B689" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C689" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17688,10 +17700,10 @@
     <row r="690" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A690" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>vissel-kobe</v>
+        <v>kashiwa-reysol</v>
       </c>
       <c r="B690" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="C690" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17709,10 +17721,10 @@
     <row r="691" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A691" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>kyoto-sanga-fc</v>
+        <v>kawasaki-frontale</v>
       </c>
       <c r="B691" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="C691" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17730,10 +17742,10 @@
     <row r="692" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A692" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-machida-zelvia</v>
+        <v>vissel-kobe</v>
       </c>
       <c r="B692" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="C692" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17751,10 +17763,10 @@
     <row r="693" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A693" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>mito-hollyhock</v>
+        <v>kyoto-sanga-fc</v>
       </c>
       <c r="B693" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C693" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17772,10 +17784,10 @@
     <row r="694" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A694" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>nagoya-grampus</v>
+        <v>fc-machida-zelvia</v>
       </c>
       <c r="B694" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="C694" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17793,10 +17805,10 @@
     <row r="695" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A695" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>shimizu-s-pulse</v>
+        <v>mito-hollyhock</v>
       </c>
       <c r="B695" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C695" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17814,10 +17826,10 @@
     <row r="696" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A696" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-tokyo</v>
+        <v>nagoya-grampus</v>
       </c>
       <c r="B696" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="C696" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17835,10 +17847,10 @@
     <row r="697" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A697" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>tokyo-verdy</v>
+        <v>shimizu-s-pulse</v>
       </c>
       <c r="B697" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="C697" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17856,10 +17868,10 @@
     <row r="698" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A698" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>urawa-red-diamonds</v>
+        <v>fc-tokyo</v>
       </c>
       <c r="B698" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="C698" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17877,10 +17889,10 @@
     <row r="699" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A699" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>v-varen-nagasaki</v>
+        <v>tokyo-verdy</v>
       </c>
       <c r="B699" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="C699" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17898,10 +17910,10 @@
     <row r="700" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A700" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>yokohama-f-marinos</v>
+        <v>urawa-red-diamonds</v>
       </c>
       <c r="B700" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="C700" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17919,18 +17931,18 @@
     <row r="701" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A701" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-anyang</v>
+        <v>v-varen-nagasaki</v>
       </c>
       <c r="B701" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="C701" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>south-korea</v>
+        <v>japan</v>
       </c>
       <c r="D701" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>south-korea</v>
+        <v>japan</v>
       </c>
       <c r="E701" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -17940,18 +17952,18 @@
     <row r="702" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A702" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>bucheon-fc-1995</v>
+        <v>yokohama-f-marinos</v>
       </c>
       <c r="B702" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="C702" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>south-korea</v>
+        <v>japan</v>
       </c>
       <c r="D702" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>south-korea</v>
+        <v>japan</v>
       </c>
       <c r="E702" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -17961,10 +17973,10 @@
     <row r="703" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A703" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>daejeon-hana-citizen</v>
+        <v>fc-anyang</v>
       </c>
       <c r="B703" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C703" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17982,10 +17994,10 @@
     <row r="704" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A704" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>gangwon-fc</v>
+        <v>bucheon-fc-1995</v>
       </c>
       <c r="B704" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="C704" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -18003,10 +18015,10 @@
     <row r="705" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A705" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>gimcheon-sangmu-fc</v>
+        <v>daejeon-hana-citizen</v>
       </c>
       <c r="B705" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="C705" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -18024,10 +18036,10 @@
     <row r="706" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A706" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>gwangju-fc</v>
+        <v>gangwon-fc</v>
       </c>
       <c r="B706" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="C706" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -18045,10 +18057,10 @@
     <row r="707" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A707" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>incheon-united</v>
+        <v>gimcheon-sangmu-fc</v>
       </c>
       <c r="B707" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="C707" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -18066,10 +18078,10 @@
     <row r="708" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A708" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>jeju-sk-fc</v>
+        <v>gwangju-fc</v>
       </c>
       <c r="B708" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="C708" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -18087,10 +18099,10 @@
     <row r="709" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A709" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>jeonbuk-hyundai-motors</v>
+        <v>incheon-united</v>
       </c>
       <c r="B709" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C709" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -18108,10 +18120,10 @@
     <row r="710" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A710" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>pohang-steelers</v>
+        <v>jeju-sk-fc</v>
       </c>
       <c r="B710" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="C710" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -18129,10 +18141,10 @@
     <row r="711" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A711" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-seoul</v>
+        <v>jeonbuk-hyundai-motors</v>
       </c>
       <c r="B711" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="C711" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -18150,10 +18162,10 @@
     <row r="712" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A712" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ulsan-hd-fc</v>
+        <v>pohang-steelers</v>
       </c>
       <c r="B712" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C712" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -18171,18 +18183,18 @@
     <row r="713" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A713" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>beijing-guoan-fc</v>
+        <v>fc-seoul</v>
       </c>
       <c r="B713" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="C713" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>china</v>
+        <v>south-korea</v>
       </c>
       <c r="D713" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>china</v>
+        <v>south-korea</v>
       </c>
       <c r="E713" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -18192,18 +18204,18 @@
     <row r="714" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A714" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>chengdu-rongcheng-fc</v>
+        <v>ulsan-hd-fc</v>
       </c>
       <c r="B714" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="C714" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>china</v>
+        <v>south-korea</v>
       </c>
       <c r="D714" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>china</v>
+        <v>south-korea</v>
       </c>
       <c r="E714" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -18213,10 +18225,10 @@
     <row r="715" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A715" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>chongqing-tonglianglong-fc</v>
+        <v>beijing-guoan-fc</v>
       </c>
       <c r="B715" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="C715" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -18234,10 +18246,10 @@
     <row r="716" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A716" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>dalian-yingbo-fc</v>
+        <v>chengdu-rongcheng-fc</v>
       </c>
       <c r="B716" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C716" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -18255,10 +18267,10 @@
     <row r="717" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A717" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>henan-fc</v>
+        <v>chongqing-tonglianglong-fc</v>
       </c>
       <c r="B717" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="C717" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -18276,10 +18288,10 @@
     <row r="718" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A718" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>liaoning-tieren-fc</v>
+        <v>dalian-yingbo-fc</v>
       </c>
       <c r="B718" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="C718" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -18297,10 +18309,10 @@
     <row r="719" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A719" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>qingdao-hainiu-fc</v>
+        <v>henan-fc</v>
       </c>
       <c r="B719" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="C719" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -18318,10 +18330,10 @@
     <row r="720" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A720" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>qingdao-west-coast-fc</v>
+        <v>liaoning-tieren-fc</v>
       </c>
       <c r="B720" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="C720" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -18339,10 +18351,10 @@
     <row r="721" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A721" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>shandong-taishan-fc</v>
+        <v>qingdao-hainiu-fc</v>
       </c>
       <c r="B721" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C721" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -18360,10 +18372,10 @@
     <row r="722" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A722" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>shanghai-port-fc</v>
+        <v>qingdao-west-coast-fc</v>
       </c>
       <c r="B722" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="C722" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -18381,10 +18393,10 @@
     <row r="723" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A723" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>shanghai-shenhua-fc</v>
+        <v>shandong-taishan-fc</v>
       </c>
       <c r="B723" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="C723" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -18402,10 +18414,10 @@
     <row r="724" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A724" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>shenzhen-peng-city-fc</v>
+        <v>shanghai-port-fc</v>
       </c>
       <c r="B724" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C724" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -18423,10 +18435,10 @@
     <row r="725" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A725" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>tianjin-jinmen-tiger-fc</v>
+        <v>shanghai-shenhua-fc</v>
       </c>
       <c r="B725" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="C725" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -18444,10 +18456,10 @@
     <row r="726" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A726" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>wuhan-three-towns-fc</v>
+        <v>shenzhen-peng-city-fc</v>
       </c>
       <c r="B726" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="C726" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -18465,10 +18477,10 @@
     <row r="727" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A727" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>yunnan-yukun-fc</v>
+        <v>tianjin-jinmen-tiger-fc</v>
       </c>
       <c r="B727" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="C727" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -18486,20 +18498,62 @@
     <row r="728" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A728" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>wuhan-three-towns-fc</v>
+      </c>
+      <c r="B728" t="s">
+        <v>732</v>
+      </c>
+      <c r="C728" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>china</v>
+      </c>
+      <c r="D728" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>china</v>
+      </c>
+      <c r="E728" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="729" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A729" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
+        <v>yunnan-yukun-fc</v>
+      </c>
+      <c r="B729" t="s">
+        <v>733</v>
+      </c>
+      <c r="C729" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
+        <v>china</v>
+      </c>
+      <c r="D729" t="str">
+        <f>Tabla1[[#This Row],[PAIS]]</f>
+        <v>china</v>
+      </c>
+      <c r="E729" s="8" t="str">
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <v>SI</v>
+      </c>
+    </row>
+    <row r="730" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A730" t="str">
+        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
         <v>zhejiang-professional-fc</v>
       </c>
-      <c r="B728" t="s">
+      <c r="B730" t="s">
         <v>734</v>
       </c>
-      <c r="C728" t="str">
+      <c r="C730" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>china</v>
       </c>
-      <c r="D728" t="str">
+      <c r="D730" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
         <v>china</v>
       </c>
-      <c r="E728" s="8" t="str">
+      <c r="E730" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
@@ -18513,7 +18567,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="D216:D239 D512:D533 D288:D305" calculatedColumn="1"/>
+    <ignoredError sqref="D218:D241 D514:D535 D290:D307" calculatedColumn="1"/>
   </ignoredErrors>
   <tableParts count="1">
     <tablePart r:id="rId2"/>

--- a/enlaces_equipos.xlsx
+++ b/enlaces_equipos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose-\Trabajo\statsFutbol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE335276-0F42-4080-9B9E-E7075569CE42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA91C5A1-A3DF-42ED-A218-6C96A8959BAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{474EBA83-D6A0-4565-BEB0-BC6B2AA992C1}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="738">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="737">
   <si>
     <t>EQUIPO</t>
   </si>
@@ -885,9 +885,6 @@
     <t>n-s-america/mexico/club-leon</t>
   </si>
   <si>
-    <t>n-s-america/mexico/mazatlan-fc</t>
-  </si>
-  <si>
     <t>n-s-america/mexico/cf-monterrey</t>
   </si>
   <si>
@@ -1749,15 +1746,6 @@
     <t>rest-of-the-world/egypt/ghazi-el-mahalla-sc</t>
   </si>
   <si>
-    <t>rest-of-the-world/egypt/haras-el-hodoud-sc</t>
-  </si>
-  <si>
-    <t>rest-of-the-world/egypt/ismaily-sc</t>
-  </si>
-  <si>
-    <t>rest-of-the-world/egypt/kahrabaa-ismailia-sc</t>
-  </si>
-  <si>
     <t>rest-of-the-world/egypt/modern-sport-fc</t>
   </si>
   <si>
@@ -1767,9 +1755,6 @@
     <t>rest-of-the-world/egypt/petrojet-sc</t>
   </si>
   <si>
-    <t>rest-of-the-world/egypt/pharco-fc</t>
-  </si>
-  <si>
     <t>rest-of-the-world/egypt/pyramids-fc</t>
   </si>
   <si>
@@ -2272,6 +2257,18 @@
   </si>
   <si>
     <t>europe/belgium/kvc-westerlo</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/egypt/el-qanah-fc</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/egypt/asyut-petroleum-sc</t>
+  </si>
+  <si>
+    <t>rest-of-the-world/egypt/abou-qir-fertilizers-sc</t>
+  </si>
+  <si>
+    <t>n-s-america/mexico/atlante-fc</t>
   </si>
 </sst>
 </file>
@@ -2367,7 +2364,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2389,10 +2386,6 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2442,8 +2435,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1329FF03-B366-468C-915B-7B9006981626}" name="Tabla1" displayName="Tabla1" ref="A1:E730" totalsRowShown="0" headerRowDxfId="5">
-  <autoFilter ref="A1:E730" xr:uid="{1329FF03-B366-468C-915B-7B9006981626}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1329FF03-B366-468C-915B-7B9006981626}" name="Tabla1" displayName="Tabla1" ref="A1:E729" totalsRowShown="0" headerRowDxfId="5">
+  <autoFilter ref="A1:E729" xr:uid="{1329FF03-B366-468C-915B-7B9006981626}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C593">
     <sortCondition ref="C1:C593"/>
   </sortState>
@@ -2763,7 +2756,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EC3E121-4DD2-4C5A-A60B-ED62DD98B116}">
-  <dimension ref="A1:K730"/>
+  <dimension ref="A1:K729"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.33203125" bestFit="1" customWidth="1"/>
@@ -2786,10 +2779,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -2824,7 +2817,7 @@
         <v>46227</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -2852,13 +2845,13 @@
       </c>
       <c r="I3" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>X</v>
       </c>
       <c r="J3" s="10">
         <v>46313</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
@@ -2892,7 +2885,7 @@
         <v>46237</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
@@ -2926,7 +2919,7 @@
         <v>46241</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
@@ -2960,7 +2953,7 @@
         <v>46050</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -2994,7 +2987,7 @@
         <v>46224</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
@@ -3028,7 +3021,7 @@
         <v>46052</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
@@ -3062,7 +3055,7 @@
         <v>46230</v>
       </c>
       <c r="K9" s="9" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
@@ -3096,7 +3089,7 @@
         <v>46235</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
@@ -3130,7 +3123,7 @@
         <v>46231</v>
       </c>
       <c r="K11" s="9" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
@@ -3164,7 +3157,7 @@
         <v>46230</v>
       </c>
       <c r="K12" s="9" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -3173,7 +3166,7 @@
         <v>estudiantes-de-rio-cuarto</v>
       </c>
       <c r="B13" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C13" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3198,7 +3191,7 @@
         <v>46220</v>
       </c>
       <c r="K13" s="9" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -3232,7 +3225,7 @@
         <v>46252</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
@@ -3241,7 +3234,7 @@
         <v>club-gimnasia-de-mendoza</v>
       </c>
       <c r="B15" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C15" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3266,7 +3259,7 @@
         <v>46116</v>
       </c>
       <c r="K15" s="9" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
@@ -3300,7 +3293,7 @@
         <v>46258</v>
       </c>
       <c r="K16" s="9" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
@@ -3334,7 +3327,7 @@
         <v>46244</v>
       </c>
       <c r="K17" s="9" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
@@ -3368,7 +3361,7 @@
         <v>46257</v>
       </c>
       <c r="K18" s="9" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
@@ -3402,7 +3395,7 @@
         <v>46259</v>
       </c>
       <c r="K19" s="9" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
@@ -3436,7 +3429,7 @@
         <v>46220</v>
       </c>
       <c r="K20" s="9" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
@@ -3470,7 +3463,7 @@
         <v>46244</v>
       </c>
       <c r="K21" s="9" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
@@ -3504,7 +3497,7 @@
         <v>46095</v>
       </c>
       <c r="K22" s="9" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
@@ -3538,7 +3531,7 @@
         <v>46223</v>
       </c>
       <c r="K23" s="9" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
@@ -3572,7 +3565,7 @@
         <v>46231</v>
       </c>
       <c r="K24" s="9" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
@@ -3606,7 +3599,7 @@
         <v>46243</v>
       </c>
       <c r="K25" s="9" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
@@ -3640,7 +3633,7 @@
         <v>46224</v>
       </c>
       <c r="K26" s="9" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
@@ -3674,7 +3667,7 @@
         <v>46242</v>
       </c>
       <c r="K27" s="9" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
@@ -3708,7 +3701,7 @@
         <v>46238</v>
       </c>
       <c r="K28" s="9" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
@@ -3742,7 +3735,7 @@
         <v>46252</v>
       </c>
       <c r="K29" s="9" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
@@ -3776,7 +3769,7 @@
         <v>46229</v>
       </c>
       <c r="K30" s="9" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
@@ -3810,7 +3803,7 @@
         <v>46230</v>
       </c>
       <c r="K31" s="9" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
@@ -3819,7 +3812,7 @@
         <v>adelaide-united-fc</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C32" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3831,7 +3824,7 @@
       </c>
       <c r="E32" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="H32" s="9" t="str">
         <v>usa</v>
@@ -3844,7 +3837,7 @@
         <v>46074</v>
       </c>
       <c r="K32" s="9" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
@@ -3853,7 +3846,7 @@
         <v>auckland-fc</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C33" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3865,7 +3858,7 @@
       </c>
       <c r="E33" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="H33" s="9" t="str">
         <v>ireland</v>
@@ -3878,7 +3871,7 @@
         <v>46121</v>
       </c>
       <c r="K33" s="9" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
@@ -3887,7 +3880,7 @@
         <v>brisbane-roar-fc</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C34" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3899,7 +3892,7 @@
       </c>
       <c r="E34" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="H34" s="9" t="str">
         <v>egypt</v>
@@ -3912,7 +3905,7 @@
         <v>46121</v>
       </c>
       <c r="K34" s="9" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
@@ -3921,7 +3914,7 @@
         <v>central-coast-mariners-fc</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C35" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3933,7 +3926,7 @@
       </c>
       <c r="E35" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="H35" s="9" t="str">
         <v>cyprus</v>
@@ -3946,7 +3939,7 @@
         <v>46284</v>
       </c>
       <c r="K35" s="9" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
@@ -3955,7 +3948,7 @@
         <v>macarthur-fc</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C36" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -3967,7 +3960,7 @@
       </c>
       <c r="E36" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="H36" s="9" t="str">
         <v>hungary</v>
@@ -3980,7 +3973,7 @@
         <v>46284</v>
       </c>
       <c r="K36" s="9" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
@@ -3989,7 +3982,7 @@
         <v>melbourne-city-fc</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C37" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4001,7 +3994,7 @@
       </c>
       <c r="E37" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="H37" s="9" t="str">
         <v>uruguay</v>
@@ -4014,7 +4007,7 @@
         <v>46284</v>
       </c>
       <c r="K37" s="9" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
@@ -4023,7 +4016,7 @@
         <v>melbourne-victory-fc</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C38" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4035,7 +4028,7 @@
       </c>
       <c r="E38" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="H38" s="9" t="str">
         <v>ukraine</v>
@@ -4048,7 +4041,7 @@
         <v>46299</v>
       </c>
       <c r="K38" s="9" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
@@ -4057,7 +4050,7 @@
         <v>newcastle-jets-fc</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C39" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4069,7 +4062,7 @@
       </c>
       <c r="E39" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="H39" s="9" t="str">
         <v>japan</v>
@@ -4082,7 +4075,7 @@
         <v>46299</v>
       </c>
       <c r="K39" s="9" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
@@ -4091,7 +4084,7 @@
         <v>perth-glory-fc</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C40" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4103,7 +4096,7 @@
       </c>
       <c r="E40" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="H40" s="9" t="str">
         <v>south-korea</v>
@@ -4116,7 +4109,7 @@
         <v>46299</v>
       </c>
       <c r="K40" s="9" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
@@ -4125,7 +4118,7 @@
         <v>sydney-fc</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C41" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4137,7 +4130,7 @@
       </c>
       <c r="E41" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="H41" s="9" t="str">
         <v>china</v>
@@ -4150,7 +4143,7 @@
         <v>46299</v>
       </c>
       <c r="K41" s="9" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
@@ -4159,7 +4152,7 @@
         <v>wellington-phoenix-fc</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C42" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4171,7 +4164,7 @@
       </c>
       <c r="E42" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
@@ -4180,7 +4173,7 @@
         <v>western-sydney-wanderers-fc</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C43" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4192,7 +4185,7 @@
       </c>
       <c r="E43" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>NO</v>
+        <v>SI</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
@@ -4201,7 +4194,7 @@
         <v>sc-austria-lustenau</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="C44" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4495,7 +4488,7 @@
         <v>sk-beveren</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="C58" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4621,7 +4614,7 @@
         <v>kv-kortrijk</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="C64" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4684,7 +4677,7 @@
         <v>lommel-sk</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="C67" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4784,43 +4777,43 @@
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A72" s="12" t="str">
+      <c r="A72" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
         <v>sv-zulte-waregem</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>736</v>
-      </c>
-      <c r="C72" s="12" t="str">
+        <v>731</v>
+      </c>
+      <c r="C72" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>belgium</v>
       </c>
-      <c r="D72" s="12" t="str">
+      <c r="D72" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
         <v>belgium</v>
       </c>
-      <c r="E72" s="13" t="str">
+      <c r="E72" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A73" s="12" t="str">
+      <c r="A73" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
         <v>kvc-westerlo</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>737</v>
-      </c>
-      <c r="C73" s="12" t="str">
+        <v>732</v>
+      </c>
+      <c r="C73" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>belgium</v>
       </c>
-      <c r="D73" s="12" t="str">
+      <c r="D73" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
         <v>belgium</v>
       </c>
-      <c r="E73" s="13" t="str">
+      <c r="E73" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>
@@ -4831,7 +4824,7 @@
         <v>club-athletico-paranaense</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C74" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4936,7 +4929,7 @@
         <v>associacao-chapecoense-de-futebol</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C79" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -4978,7 +4971,7 @@
         <v>coritiba-football-club</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C81" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5146,7 +5139,7 @@
         <v>clube-do-remo</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C89" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5377,7 +5370,7 @@
         <v>fc-dunav-ruse</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="C100" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5629,7 +5622,7 @@
         <v>deportes-concepcion</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C112" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -5860,7 +5853,7 @@
         <v>cd-universidad-de-concepcion</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C123" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6007,7 +6000,7 @@
         <v>cucuta-deportivo-fc</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C130" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6091,7 +6084,7 @@
         <v>internacional-de-bogota</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C134" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6112,7 +6105,7 @@
         <v>jaguares-de-cordoba</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C135" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6448,7 +6441,7 @@
         <v>nk-rudes</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="C151" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6511,7 +6504,7 @@
         <v>sk-artis-brno</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="C154" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6553,7 +6546,7 @@
         <v>fc-zbrojovka-brno</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="C156" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6910,7 +6903,7 @@
         <v>ac-horsens</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="C173" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -6931,7 +6924,7 @@
         <v>lyngby-bk</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C174" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7099,7 +7092,7 @@
         <v>sd-aucas</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C182" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7120,7 +7113,7 @@
         <v>barcelona-sc</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C183" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7141,7 +7134,7 @@
         <v>delfin-sc</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C184" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7162,7 +7155,7 @@
         <v>cd-cuenca</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C185" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7183,7 +7176,7 @@
         <v>cs-emelec</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C186" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7204,7 +7197,7 @@
         <v>guayaquil-city-fc</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C187" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7225,7 +7218,7 @@
         <v>csd-independiente-del-valle</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C188" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7246,7 +7239,7 @@
         <v>ldu-quito</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C189" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7267,7 +7260,7 @@
         <v>leones-fc</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C190" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7288,7 +7281,7 @@
         <v>libertad-fc</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C191" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7309,7 +7302,7 @@
         <v>csd-macara</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C192" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7330,7 +7323,7 @@
         <v>manta-fc</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C193" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7351,7 +7344,7 @@
         <v>mushuc-runa-sc</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C194" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7372,7 +7365,7 @@
         <v>orense-sc</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C195" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7393,7 +7386,7 @@
         <v>tecnico-universitario</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C196" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7414,7 +7407,7 @@
         <v>cd-universidad-catolica</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C197" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -7862,7 +7855,7 @@
         <v>england</v>
       </c>
       <c r="D218" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E218" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -7882,7 +7875,7 @@
         <v>england</v>
       </c>
       <c r="D219" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E219" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -7895,14 +7888,14 @@
         <v>bolton-wanderers-fc</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="C220" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>england</v>
       </c>
       <c r="D220" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E220" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -7922,7 +7915,7 @@
         <v>england</v>
       </c>
       <c r="D221" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E221" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -7942,7 +7935,7 @@
         <v>england</v>
       </c>
       <c r="D222" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E222" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -7955,14 +7948,14 @@
         <v>cardiff-city-fc</v>
       </c>
       <c r="B223" s="5" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="C223" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>england</v>
       </c>
       <c r="D223" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E223" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -7982,7 +7975,7 @@
         <v>england</v>
       </c>
       <c r="D224" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E224" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -8002,7 +7995,7 @@
         <v>england</v>
       </c>
       <c r="D225" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E225" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -8015,14 +8008,14 @@
         <v>lincoln-city-fc</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="C226" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>england</v>
       </c>
       <c r="D226" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E226" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -8042,7 +8035,7 @@
         <v>england</v>
       </c>
       <c r="D227" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E227" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -8062,7 +8055,7 @@
         <v>england</v>
       </c>
       <c r="D228" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E228" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -8082,7 +8075,7 @@
         <v>england</v>
       </c>
       <c r="D229" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E229" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -8102,7 +8095,7 @@
         <v>england</v>
       </c>
       <c r="D230" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E230" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -8122,7 +8115,7 @@
         <v>england</v>
       </c>
       <c r="D231" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E231" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -8142,7 +8135,7 @@
         <v>england</v>
       </c>
       <c r="D232" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E232" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -8162,7 +8155,7 @@
         <v>england</v>
       </c>
       <c r="D233" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E233" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -8182,7 +8175,7 @@
         <v>england</v>
       </c>
       <c r="D234" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E234" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -8202,7 +8195,7 @@
         <v>england</v>
       </c>
       <c r="D235" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E235" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -8222,7 +8215,7 @@
         <v>england</v>
       </c>
       <c r="D236" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E236" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -8242,7 +8235,7 @@
         <v>england</v>
       </c>
       <c r="D237" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E237" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -8262,7 +8255,7 @@
         <v>england</v>
       </c>
       <c r="D238" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E238" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -8282,7 +8275,7 @@
         <v>england</v>
       </c>
       <c r="D239" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E239" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -8302,7 +8295,7 @@
         <v>england</v>
       </c>
       <c r="D240" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E240" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -8322,7 +8315,7 @@
         <v>england</v>
       </c>
       <c r="D241" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E241" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -8335,7 +8328,7 @@
         <v>if-gnistan</v>
       </c>
       <c r="B242" s="5" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C242" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8356,7 +8349,7 @@
         <v>hjk-helsinki</v>
       </c>
       <c r="B243" s="5" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C243" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8377,7 +8370,7 @@
         <v>fc-ilves</v>
       </c>
       <c r="B244" s="5" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C244" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8398,7 +8391,7 @@
         <v>fc-inter-turku</v>
       </c>
       <c r="B245" s="5" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C245" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8419,7 +8412,7 @@
         <v>ff-jaro</v>
       </c>
       <c r="B246" s="5" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C246" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8440,7 +8433,7 @@
         <v>kuopion-palloseura</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C247" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8461,7 +8454,7 @@
         <v>fc-lahti</v>
       </c>
       <c r="B248" s="5" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="C248" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8482,7 +8475,7 @@
         <v>ifk-mariehamn</v>
       </c>
       <c r="B249" s="5" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C249" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8503,7 +8496,7 @@
         <v>ac-oulu</v>
       </c>
       <c r="B250" s="5" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C250" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8524,7 +8517,7 @@
         <v>sjk</v>
       </c>
       <c r="B251" s="5" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C251" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8545,7 +8538,7 @@
         <v>tps-turku</v>
       </c>
       <c r="B252" s="5" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="C252" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8566,7 +8559,7 @@
         <v>vaasan-palloseura</v>
       </c>
       <c r="B253" s="5" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C253" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8671,7 +8664,7 @@
         <v>le-mans-fc</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="C258" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8734,7 +8727,7 @@
         <v>fc-lorient</v>
       </c>
       <c r="B261" s="5" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C261" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8839,7 +8832,7 @@
         <v>paris-fc</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C266" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -8944,7 +8937,7 @@
         <v>troyes-ac</v>
       </c>
       <c r="B271" s="5" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="C271" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9049,7 +9042,7 @@
         <v>sv-elversberg</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="C276" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9070,7 +9063,7 @@
         <v>fc-koln</v>
       </c>
       <c r="B277" s="5" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C277" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9133,7 +9126,7 @@
         <v>hamburger-sv</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C280" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9238,7 +9231,7 @@
         <v>sc-paderborn</v>
       </c>
       <c r="B285" s="5" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="C285" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9280,7 +9273,7 @@
         <v>schalke-04</v>
       </c>
       <c r="B287" s="5" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="C287" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9350,7 +9343,7 @@
         <v>germany</v>
       </c>
       <c r="D290" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="E290" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -9370,7 +9363,7 @@
         <v>germany</v>
       </c>
       <c r="D291" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="E291" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -9390,7 +9383,7 @@
         <v>germany</v>
       </c>
       <c r="D292" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="E292" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -9403,14 +9396,14 @@
         <v>fc-energie-cottbus</v>
       </c>
       <c r="B293" s="5" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="C293" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>germany</v>
       </c>
       <c r="D293" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="E293" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -9430,7 +9423,7 @@
         <v>germany</v>
       </c>
       <c r="D294" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="E294" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -9450,7 +9443,7 @@
         <v>germany</v>
       </c>
       <c r="D295" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="E295" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -9470,7 +9463,7 @@
         <v>germany</v>
       </c>
       <c r="D296" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="E296" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -9490,7 +9483,7 @@
         <v>germany</v>
       </c>
       <c r="D297" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="E297" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -9510,7 +9503,7 @@
         <v>germany</v>
       </c>
       <c r="D298" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="E298" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -9530,7 +9523,7 @@
         <v>germany</v>
       </c>
       <c r="D299" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="E299" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -9550,7 +9543,7 @@
         <v>germany</v>
       </c>
       <c r="D300" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="E300" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -9570,7 +9563,7 @@
         <v>germany</v>
       </c>
       <c r="D301" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="E301" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -9590,7 +9583,7 @@
         <v>germany</v>
       </c>
       <c r="D302" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="E302" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -9610,7 +9603,7 @@
         <v>germany</v>
       </c>
       <c r="D303" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="E303" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -9630,7 +9623,7 @@
         <v>germany</v>
       </c>
       <c r="D304" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="E304" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -9643,14 +9636,14 @@
         <v>vfl-osnabruck</v>
       </c>
       <c r="B305" s="5" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="C305" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>germany</v>
       </c>
       <c r="D305" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="E305" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -9670,7 +9663,7 @@
         <v>germany</v>
       </c>
       <c r="D306" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="E306" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -9690,7 +9683,7 @@
         <v>germany</v>
       </c>
       <c r="D307" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="E307" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -9703,7 +9696,7 @@
         <v>aek-athens-fc</v>
       </c>
       <c r="B308" s="5" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C308" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9724,7 +9717,7 @@
         <v>aris-thessaloniki-fc</v>
       </c>
       <c r="B309" s="5" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C309" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9745,7 +9738,7 @@
         <v>asteras-tripolis-fc</v>
       </c>
       <c r="B310" s="5" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C310" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9766,7 +9759,7 @@
         <v>atromitos-fc</v>
       </c>
       <c r="B311" s="5" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C311" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9787,7 +9780,7 @@
         <v>iraklis-fc</v>
       </c>
       <c r="B312" s="5" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="C312" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9808,7 +9801,7 @@
         <v>kalamata-fc</v>
       </c>
       <c r="B313" s="5" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="C313" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9829,7 +9822,7 @@
         <v>ae-kifisia-fc</v>
       </c>
       <c r="B314" s="5" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C314" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9850,7 +9843,7 @@
         <v>levadiakos-fc</v>
       </c>
       <c r="B315" s="5" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C315" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9871,7 +9864,7 @@
         <v>ofi-crete-fc</v>
       </c>
       <c r="B316" s="5" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C316" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9892,7 +9885,7 @@
         <v>olympiacos-fc</v>
       </c>
       <c r="B317" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C317" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9913,7 +9906,7 @@
         <v>panathinaikos-fc</v>
       </c>
       <c r="B318" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C318" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9934,7 +9927,7 @@
         <v>panetolikos-fc</v>
       </c>
       <c r="B319" s="5" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C319" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9955,7 +9948,7 @@
         <v>paok-fc</v>
       </c>
       <c r="B320" s="5" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C320" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -9976,7 +9969,7 @@
         <v>volos-fc</v>
       </c>
       <c r="B321" s="5" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C321" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10144,7 +10137,7 @@
         <v>frosinone-calcio</v>
       </c>
       <c r="B329" s="5" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="C329" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10270,7 +10263,7 @@
         <v>ac-monza</v>
       </c>
       <c r="B335" s="5" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="C335" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10333,7 +10326,7 @@
         <v>us-sassuolo-calcio</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C338" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10396,7 +10389,7 @@
         <v>venezia-fc</v>
       </c>
       <c r="B341" s="5" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="C341" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10435,10 +10428,10 @@
     <row r="343" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A343" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>atlas-fc</v>
+        <v>atlante-fc</v>
       </c>
       <c r="B343" s="5" t="s">
-        <v>269</v>
+        <v>736</v>
       </c>
       <c r="C343" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10456,10 +10449,10 @@
     <row r="344" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A344" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>club-america</v>
+        <v>atlas-fc</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C344" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10477,10 +10470,10 @@
     <row r="345" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A345" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>cruz-azul</v>
+        <v>club-america</v>
       </c>
       <c r="B345" s="5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C345" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10498,10 +10491,10 @@
     <row r="346" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A346" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>cd-guadalajara</v>
+        <v>cruz-azul</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C346" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10519,10 +10512,10 @@
     <row r="347" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A347" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-juarez</v>
+        <v>cd-guadalajara</v>
       </c>
       <c r="B347" s="5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C347" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10540,10 +10533,10 @@
     <row r="348" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A348" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>club-leon</v>
+        <v>fc-juarez</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C348" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10561,10 +10554,10 @@
     <row r="349" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A349" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>mazatlan-fc</v>
+        <v>club-leon</v>
       </c>
       <c r="B349" s="5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C349" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10585,7 +10578,7 @@
         <v>cf-monterrey</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C350" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10606,7 +10599,7 @@
         <v>club-necaxa</v>
       </c>
       <c r="B351" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C351" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10627,7 +10620,7 @@
         <v>cf-pachuca</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C352" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10648,7 +10641,7 @@
         <v>club-puebla</v>
       </c>
       <c r="B353" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C353" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10669,7 +10662,7 @@
         <v>queretaro-fc</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C354" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10690,7 +10683,7 @@
         <v>santos-laguna</v>
       </c>
       <c r="B355" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C355" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10711,7 +10704,7 @@
         <v>tigres-uanl</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C356" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10732,7 +10725,7 @@
         <v>club-tijuana</v>
       </c>
       <c r="B357" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C357" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10753,7 +10746,7 @@
         <v>deportivo-toluca-fc</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C358" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10774,7 +10767,7 @@
         <v>unam</v>
       </c>
       <c r="B359" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C359" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10795,7 +10788,7 @@
         <v>afc-ajax</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C360" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10816,7 +10809,7 @@
         <v>az-alkmaar</v>
       </c>
       <c r="B361" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C361" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10837,7 +10830,7 @@
         <v>sc-cambuur</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="C362" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10858,7 +10851,7 @@
         <v>ado-den-haag</v>
       </c>
       <c r="B363" s="5" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="C363" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10879,7 +10872,7 @@
         <v>sbv-excelsior</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C364" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10900,7 +10893,7 @@
         <v>feyenoord-rotterdam</v>
       </c>
       <c r="B365" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C365" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10921,7 +10914,7 @@
         <v>go-ahead-eagles</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C366" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10942,7 +10935,7 @@
         <v>fc-groningen</v>
       </c>
       <c r="B367" s="5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C367" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10963,7 +10956,7 @@
         <v>sc-heerenveen</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C368" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -10984,7 +10977,7 @@
         <v>nec-nijmegen</v>
       </c>
       <c r="B369" s="5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C369" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11005,7 +10998,7 @@
         <v>psv-eindhoven</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C370" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11026,7 +11019,7 @@
         <v>fortuna-sittard</v>
       </c>
       <c r="B371" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C371" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11047,7 +11040,7 @@
         <v>sparta-rotterdam</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C372" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11068,7 +11061,7 @@
         <v>sc-telstar</v>
       </c>
       <c r="B373" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C373" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11089,7 +11082,7 @@
         <v>fc-twente</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C374" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11110,7 +11103,7 @@
         <v>fc-utrecht</v>
       </c>
       <c r="B375" s="5" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C375" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11131,7 +11124,7 @@
         <v>willem-ii</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="C376" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11152,7 +11145,7 @@
         <v>pec-zwolle</v>
       </c>
       <c r="B377" s="5" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C377" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11173,7 +11166,7 @@
         <v>aalesunds-fk</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="C378" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11194,7 +11187,7 @@
         <v>fk-bodo-glimt</v>
       </c>
       <c r="B379" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C379" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11215,7 +11208,7 @@
         <v>sk-brann</v>
       </c>
       <c r="B380" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C380" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11236,7 +11229,7 @@
         <v>fredrikstad-fk</v>
       </c>
       <c r="B381" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C381" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11257,7 +11250,7 @@
         <v>ham-kam</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C382" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11278,7 +11271,7 @@
         <v>kfum-kameratene-oslo</v>
       </c>
       <c r="B383" s="5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C383" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11299,7 +11292,7 @@
         <v>kristiansund-bk</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C384" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11320,7 +11313,7 @@
         <v>lillestrom-sk</v>
       </c>
       <c r="B385" s="5" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="C385" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11341,7 +11334,7 @@
         <v>molde-fk</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C386" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11362,7 +11355,7 @@
         <v>rosenborg-bk</v>
       </c>
       <c r="B387" s="5" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C387" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11383,7 +11376,7 @@
         <v>sandefjord-fotball</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C388" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11404,7 +11397,7 @@
         <v>sarpsborg-08-ff</v>
       </c>
       <c r="B389" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C389" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11425,7 +11418,7 @@
         <v>ik-start</v>
       </c>
       <c r="B390" s="2" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="C390" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11446,7 +11439,7 @@
         <v>tromso-il</v>
       </c>
       <c r="B391" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C391" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11467,7 +11460,7 @@
         <v>valerenga-fotball</v>
       </c>
       <c r="B392" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C392" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11488,7 +11481,7 @@
         <v>viking-fk</v>
       </c>
       <c r="B393" s="5" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C393" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11509,7 +11502,7 @@
         <v>alianza-lima</v>
       </c>
       <c r="B394" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C394" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11530,7 +11523,7 @@
         <v>asociacion-deportiva-tarma</v>
       </c>
       <c r="B395" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C395" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11551,7 +11544,7 @@
         <v>alianza-atletico</v>
       </c>
       <c r="B396" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C396" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11572,7 +11565,7 @@
         <v>universidad-tecnica-de-cajamarca</v>
       </c>
       <c r="B397" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C397" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11593,7 +11586,7 @@
         <v>club-sportivo-cienciano</v>
       </c>
       <c r="B398" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C398" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11614,7 +11607,7 @@
         <v>comerciantes-unidos</v>
       </c>
       <c r="B399" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C399" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11635,7 +11628,7 @@
         <v>cusco-fc</v>
       </c>
       <c r="B400" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C400" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11656,7 +11649,7 @@
         <v>deportivo-garcilaso</v>
       </c>
       <c r="B401" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C401" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11677,7 +11670,7 @@
         <v>fc-cajamarca</v>
       </c>
       <c r="B402" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C402" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11698,7 +11691,7 @@
         <v>atletico-grau</v>
       </c>
       <c r="B403" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C403" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11719,7 +11712,7 @@
         <v>sport-huancayo</v>
       </c>
       <c r="B404" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C404" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11740,7 +11733,7 @@
         <v>adc-juan-pablo-ii-college</v>
       </c>
       <c r="B405" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C405" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11761,7 +11754,7 @@
         <v>los-chankas-cyc</v>
       </c>
       <c r="B406" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C406" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11782,7 +11775,7 @@
         <v>fbc-melgar</v>
       </c>
       <c r="B407" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C407" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11803,7 +11796,7 @@
         <v>club-deportivo-moquegua</v>
       </c>
       <c r="B408" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C408" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11824,7 +11817,7 @@
         <v>sport-boys</v>
       </c>
       <c r="B409" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C409" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11845,7 +11838,7 @@
         <v>sporting-cristal</v>
       </c>
       <c r="B410" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C410" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11866,7 +11859,7 @@
         <v>club-universitario-de-deportes</v>
       </c>
       <c r="B411" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C411" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11887,7 +11880,7 @@
         <v>cracovia</v>
       </c>
       <c r="B412" s="5" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C412" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11908,7 +11901,7 @@
         <v>gornik-zabrze</v>
       </c>
       <c r="B413" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C413" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11929,7 +11922,7 @@
         <v>jagiellona-bialystok</v>
       </c>
       <c r="B414" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C414" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11950,7 +11943,7 @@
         <v>gks-katowice</v>
       </c>
       <c r="B415" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C415" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11971,7 +11964,7 @@
         <v>korona-kielce</v>
       </c>
       <c r="B416" s="5" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C416" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -11992,7 +11985,7 @@
         <v>lech-poznan</v>
       </c>
       <c r="B417" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C417" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12013,7 +12006,7 @@
         <v>legia-warsaw</v>
       </c>
       <c r="B418" s="5" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C418" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12034,7 +12027,7 @@
         <v>motor-lublin</v>
       </c>
       <c r="B419" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C419" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12055,7 +12048,7 @@
         <v>piast-gliwice</v>
       </c>
       <c r="B420" s="5" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C420" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12076,7 +12069,7 @@
         <v>mks-pogon-szczecin</v>
       </c>
       <c r="B421" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C421" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12097,7 +12090,7 @@
         <v>radomiak-radom</v>
       </c>
       <c r="B422" s="5" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C422" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12118,7 +12111,7 @@
         <v>rakow-czestochowa</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C423" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12139,7 +12132,7 @@
         <v>slask-wroclaw</v>
       </c>
       <c r="B424" s="5" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="C424" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12160,7 +12153,7 @@
         <v>rts-widzew-lodz</v>
       </c>
       <c r="B425" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C425" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12181,7 +12174,7 @@
         <v>ks-wieczysta-krokow</v>
       </c>
       <c r="B426" s="5" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="C426" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12202,7 +12195,7 @@
         <v>wisla-krakow</v>
       </c>
       <c r="B427" s="2" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="C427" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12223,7 +12216,7 @@
         <v>wisla-plock</v>
       </c>
       <c r="B428" s="5" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C428" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12244,7 +12237,7 @@
         <v>zaglebie-lubin</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C429" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12265,7 +12258,7 @@
         <v>academico-de-viseu-fc</v>
       </c>
       <c r="B430" s="5" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="C430" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12286,7 +12279,7 @@
         <v>fc-alverca</v>
       </c>
       <c r="B431" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C431" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12307,7 +12300,7 @@
         <v>fc-arouca</v>
       </c>
       <c r="B432" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C432" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12328,7 +12321,7 @@
         <v>benfica</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C433" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12349,7 +12342,7 @@
         <v>braga</v>
       </c>
       <c r="B434" s="5" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C434" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12370,7 +12363,7 @@
         <v>casa-pia-ac</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C435" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12391,7 +12384,7 @@
         <v>gd-estoril-praia</v>
       </c>
       <c r="B436" s="5" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C436" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12412,7 +12405,7 @@
         <v>cf-estrela-da-amadora</v>
       </c>
       <c r="B437" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C437" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12433,7 +12426,7 @@
         <v>famalicao</v>
       </c>
       <c r="B438" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C438" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12454,7 +12447,7 @@
         <v>fc-porto</v>
       </c>
       <c r="B439" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C439" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12475,7 +12468,7 @@
         <v>gil-vicente</v>
       </c>
       <c r="B440" s="5" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C440" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12496,7 +12489,7 @@
         <v>vitoria-de-guimaraes</v>
       </c>
       <c r="B441" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C441" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12517,7 +12510,7 @@
         <v>maritimo</v>
       </c>
       <c r="B442" s="5" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="C442" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12538,7 +12531,7 @@
         <v>moreirense-fc</v>
       </c>
       <c r="B443" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C443" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12559,7 +12552,7 @@
         <v>cd-nacional</v>
       </c>
       <c r="B444" s="5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C444" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12580,7 +12573,7 @@
         <v>rio-ave-fc</v>
       </c>
       <c r="B445" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C445" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12601,7 +12594,7 @@
         <v>santa-clara</v>
       </c>
       <c r="B446" s="5" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C446" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12622,7 +12615,7 @@
         <v>sporting-cp</v>
       </c>
       <c r="B447" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C447" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12643,7 +12636,7 @@
         <v>fc-botosani</v>
       </c>
       <c r="B448" s="5" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C448" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12664,7 +12657,7 @@
         <v>cfr-cluj</v>
       </c>
       <c r="B449" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C449" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12685,7 +12678,7 @@
         <v>corvinul-hunedoara</v>
       </c>
       <c r="B450" s="5" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="C450" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12706,7 +12699,7 @@
         <v>fk-miercurea-ciuc</v>
       </c>
       <c r="B451" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C451" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12727,7 +12720,7 @@
         <v>fc-dinamo-bucuresti</v>
       </c>
       <c r="B452" s="5" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C452" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12748,7 +12741,7 @@
         <v>fc-farul-constanta</v>
       </c>
       <c r="B453" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C453" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12769,7 +12762,7 @@
         <v>fc-arges-pitesti</v>
       </c>
       <c r="B454" s="5" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C454" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12790,7 +12783,7 @@
         <v>fc-rapid-bucuresti</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C455" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12811,7 +12804,7 @@
         <v>fc-voluntari</v>
       </c>
       <c r="B456" s="5" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="C456" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12832,7 +12825,7 @@
         <v>fcsb</v>
       </c>
       <c r="B457" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C457" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12853,7 +12846,7 @@
         <v>asc-otelul-galati</v>
       </c>
       <c r="B458" s="5" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C458" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12874,7 +12867,7 @@
         <v>fc-petrolul-ploiesti</v>
       </c>
       <c r="B459" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C459" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12895,7 +12888,7 @@
         <v>sepsi-osk-sftantu-gheorghe</v>
       </c>
       <c r="B460" s="5" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="C460" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12916,7 +12909,7 @@
         <v>fc-universitatea-cluj</v>
       </c>
       <c r="B461" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C461" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12937,7 +12930,7 @@
         <v>cs-universitatea-craiova</v>
       </c>
       <c r="B462" s="5" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C462" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12958,7 +12951,7 @@
         <v>fc-uta-arad</v>
       </c>
       <c r="B463" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C463" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -12979,7 +12972,7 @@
         <v>abha-club</v>
       </c>
       <c r="B464" s="5" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="C464" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13000,7 +12993,7 @@
         <v>diriyah-club</v>
       </c>
       <c r="B465" s="2" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="C465" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13021,7 +13014,7 @@
         <v>al-fateh-sc</v>
       </c>
       <c r="B466" s="5" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C466" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13042,7 +13035,7 @@
         <v>al-fayha-fc</v>
       </c>
       <c r="B467" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C467" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13063,7 +13056,7 @@
         <v>al-hazem-fc</v>
       </c>
       <c r="B468" s="5" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C468" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13084,7 +13077,7 @@
         <v>khaleej-fc</v>
       </c>
       <c r="B469" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C469" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13105,7 +13098,7 @@
         <v>al-kholood-club</v>
       </c>
       <c r="B470" s="5" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C470" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13126,7 +13119,7 @@
         <v>al-qadsiah-fc</v>
       </c>
       <c r="B471" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C471" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13147,7 +13140,7 @@
         <v>al-riyadh-sc</v>
       </c>
       <c r="B472" s="5" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C472" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13168,7 +13161,7 @@
         <v>al-ahli-saudi-fc</v>
       </c>
       <c r="B473" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C473" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13189,7 +13182,7 @@
         <v>al-ettifaq-fc</v>
       </c>
       <c r="B474" s="5" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C474" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13210,7 +13203,7 @@
         <v>al-faisaly-fc</v>
       </c>
       <c r="B475" s="2" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="C475" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13231,7 +13224,7 @@
         <v>al-hilal-fc</v>
       </c>
       <c r="B476" s="5" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C476" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13252,7 +13245,7 @@
         <v>al-ittihad-fc</v>
       </c>
       <c r="B477" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C477" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13273,7 +13266,7 @@
         <v>al-nassr-fc</v>
       </c>
       <c r="B478" s="5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C478" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13294,7 +13287,7 @@
         <v>al-shabab-fc</v>
       </c>
       <c r="B479" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C479" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13315,7 +13308,7 @@
         <v>al-taawoun-fc</v>
       </c>
       <c r="B480" s="5" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C480" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13336,7 +13329,7 @@
         <v>neom-sc</v>
       </c>
       <c r="B481" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C481" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13357,7 +13350,7 @@
         <v>aberdeen-fc</v>
       </c>
       <c r="B482" s="5" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C482" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13378,7 +13371,7 @@
         <v>celtic-fc</v>
       </c>
       <c r="B483" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C483" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13399,7 +13392,7 @@
         <v>dundee-fc</v>
       </c>
       <c r="B484" s="5" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C484" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13420,7 +13413,7 @@
         <v>dundee-united-fc</v>
       </c>
       <c r="B485" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C485" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13441,7 +13434,7 @@
         <v>falkirk-fc</v>
       </c>
       <c r="B486" s="5" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C486" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13462,7 +13455,7 @@
         <v>heart-of-midlothian-fc</v>
       </c>
       <c r="B487" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C487" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13483,7 +13476,7 @@
         <v>hibernian-fc</v>
       </c>
       <c r="B488" s="5" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C488" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13504,7 +13497,7 @@
         <v>kilmarnock-fc</v>
       </c>
       <c r="B489" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C489" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13525,7 +13518,7 @@
         <v>motherwell-fc</v>
       </c>
       <c r="B490" s="5" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C490" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13546,7 +13539,7 @@
         <v>rangers-fc</v>
       </c>
       <c r="B491" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C491" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13567,7 +13560,7 @@
         <v>st-johnstone-fc</v>
       </c>
       <c r="B492" s="5" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="C492" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13588,7 +13581,7 @@
         <v>st-mirren-fc</v>
       </c>
       <c r="B493" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C493" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13609,7 +13602,7 @@
         <v>deportivo-de-a-coruna</v>
       </c>
       <c r="B494" s="5" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="C494" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13756,7 +13749,7 @@
         <v>elche-cf</v>
       </c>
       <c r="B501" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C501" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13819,7 +13812,7 @@
         <v>levante-ud</v>
       </c>
       <c r="B504" s="5" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C504" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13840,7 +13833,7 @@
         <v>malaga-cf</v>
       </c>
       <c r="B505" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C505" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -13882,7 +13875,7 @@
         <v>racing-de-santander</v>
       </c>
       <c r="B507" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C507" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14029,14 +14022,14 @@
         <v>albacete-balompie</v>
       </c>
       <c r="B514" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C514" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D514" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="E514" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -14049,14 +14042,14 @@
         <v>ud-almeria</v>
       </c>
       <c r="B515" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C515" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D515" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="E515" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -14069,14 +14062,14 @@
         <v>fc-andorra</v>
       </c>
       <c r="B516" s="5" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C516" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D516" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="E516" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -14089,14 +14082,14 @@
         <v>burgos-cf</v>
       </c>
       <c r="B517" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C517" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D517" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="E517" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -14109,14 +14102,14 @@
         <v>cadiz-cf</v>
       </c>
       <c r="B518" s="5" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C518" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D518" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="E518" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -14129,14 +14122,14 @@
         <v>cd-castellon</v>
       </c>
       <c r="B519" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C519" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D519" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="E519" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -14149,14 +14142,14 @@
         <v>celta-de-vigo-b</v>
       </c>
       <c r="B520" s="5" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="C520" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D520" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="E520" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -14169,14 +14162,14 @@
         <v>ad-ceuta-fc</v>
       </c>
       <c r="B521" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C521" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D521" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="E521" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -14189,14 +14182,14 @@
         <v>cordoba-cf</v>
       </c>
       <c r="B522" s="5" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C522" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D522" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="E522" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -14209,14 +14202,14 @@
         <v>sd-eibar</v>
       </c>
       <c r="B523" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C523" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D523" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="E523" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -14229,14 +14222,14 @@
         <v>cd-eldense</v>
       </c>
       <c r="B524" s="5" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="C524" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D524" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="E524" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -14249,14 +14242,14 @@
         <v>sporting-de-gijon</v>
       </c>
       <c r="B525" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C525" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D525" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="E525" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -14276,7 +14269,7 @@
         <v>spain</v>
       </c>
       <c r="D526" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="E526" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -14289,14 +14282,14 @@
         <v>granada-cf</v>
       </c>
       <c r="B527" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C527" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D527" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="E527" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -14316,7 +14309,7 @@
         <v>spain</v>
       </c>
       <c r="D528" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="E528" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -14336,7 +14329,7 @@
         <v>spain</v>
       </c>
       <c r="D529" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="E529" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -14356,7 +14349,7 @@
         <v>spain</v>
       </c>
       <c r="D530" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="E530" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -14369,14 +14362,14 @@
         <v>real-oviedo</v>
       </c>
       <c r="B531" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C531" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D531" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="E531" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -14389,14 +14382,14 @@
         <v>real-sociedad-b</v>
       </c>
       <c r="B532" s="5" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C532" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D532" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="E532" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -14409,14 +14402,14 @@
         <v>ce-sabadell-fc</v>
       </c>
       <c r="B533" s="2" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="C533" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D533" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="E533" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -14429,14 +14422,14 @@
         <v>cd-tenerife</v>
       </c>
       <c r="B534" s="5" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="C534" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
         <v>spain</v>
       </c>
       <c r="D534" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="E534" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -14456,7 +14449,7 @@
         <v>spain</v>
       </c>
       <c r="D535" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="E535" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -14469,7 +14462,7 @@
         <v>aik</v>
       </c>
       <c r="B536" s="5" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C536" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14490,7 +14483,7 @@
         <v>if-brommapojkarna</v>
       </c>
       <c r="B537" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C537" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14511,7 +14504,7 @@
         <v>degerfors-if</v>
       </c>
       <c r="B538" s="5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C538" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14532,7 +14525,7 @@
         <v>djurgardens-if</v>
       </c>
       <c r="B539" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C539" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14553,7 +14546,7 @@
         <v>if-elfsborg</v>
       </c>
       <c r="B540" s="5" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C540" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14574,7 +14567,7 @@
         <v>gais</v>
       </c>
       <c r="B541" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C541" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14595,7 +14588,7 @@
         <v>ifk-goteborg</v>
       </c>
       <c r="B542" s="5" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C542" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14616,7 +14609,7 @@
         <v>bk-hacken</v>
       </c>
       <c r="B543" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C543" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14637,7 +14630,7 @@
         <v>halmstads-bk</v>
       </c>
       <c r="B544" s="5" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C544" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14658,7 +14651,7 @@
         <v>hammarby-if</v>
       </c>
       <c r="B545" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C545" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14679,7 +14672,7 @@
         <v>kalmar-ff</v>
       </c>
       <c r="B546" s="5" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C546" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14700,7 +14693,7 @@
         <v>malmo-ff</v>
       </c>
       <c r="B547" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C547" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14721,7 +14714,7 @@
         <v>mjallby-aif</v>
       </c>
       <c r="B548" s="5" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C548" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14742,7 +14735,7 @@
         <v>orgryte-is</v>
       </c>
       <c r="B549" s="2" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C549" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14763,7 +14756,7 @@
         <v>ik-sirius</v>
       </c>
       <c r="B550" s="5" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C550" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14784,7 +14777,7 @@
         <v>vasteras-sk</v>
       </c>
       <c r="B551" s="2" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C551" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14805,7 +14798,7 @@
         <v>fc-basel</v>
       </c>
       <c r="B552" s="5" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C552" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14826,7 +14819,7 @@
         <v>grasshopper-club-zurich</v>
       </c>
       <c r="B553" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C553" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14847,7 +14840,7 @@
         <v>fc-lausanne-sport</v>
       </c>
       <c r="B554" s="5" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C554" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14868,7 +14861,7 @@
         <v>fc-lugano</v>
       </c>
       <c r="B555" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C555" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14889,7 +14882,7 @@
         <v>fc-luzern</v>
       </c>
       <c r="B556" s="5" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C556" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14910,7 +14903,7 @@
         <v>servette-fc</v>
       </c>
       <c r="B557" s="6" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C557" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14931,7 +14924,7 @@
         <v>fc-sion</v>
       </c>
       <c r="B558" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C558" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14952,7 +14945,7 @@
         <v>fc-st-gallen</v>
       </c>
       <c r="B559" s="7" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C559" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14973,7 +14966,7 @@
         <v>fc-thun</v>
       </c>
       <c r="B560" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C560" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -14994,7 +14987,7 @@
         <v>fc-vaduz</v>
       </c>
       <c r="B561" s="7" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="C561" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15015,7 +15008,7 @@
         <v>bsc-young-boys</v>
       </c>
       <c r="B562" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C562" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15036,7 +15029,7 @@
         <v>fc-zurich</v>
       </c>
       <c r="B563" s="7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C563" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15057,7 +15050,7 @@
         <v>atlanta-united-fc</v>
       </c>
       <c r="B564" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C564" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15078,7 +15071,7 @@
         <v>austin-fc</v>
       </c>
       <c r="B565" s="7" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C565" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15099,7 +15092,7 @@
         <v>club-de-foot-montreal</v>
       </c>
       <c r="B566" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C566" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15120,7 +15113,7 @@
         <v>charlotte-fc</v>
       </c>
       <c r="B567" s="7" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C567" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15141,7 +15134,7 @@
         <v>chicago-fire-fc</v>
       </c>
       <c r="B568" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C568" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15162,7 +15155,7 @@
         <v>fc-cincinnati</v>
       </c>
       <c r="B569" s="7" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C569" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15183,7 +15176,7 @@
         <v>colorado-rapids</v>
       </c>
       <c r="B570" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C570" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15204,7 +15197,7 @@
         <v>columbus-crew-sc</v>
       </c>
       <c r="B571" s="7" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C571" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15225,7 +15218,7 @@
         <v>dc-united</v>
       </c>
       <c r="B572" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C572" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15246,7 +15239,7 @@
         <v>fc-dallas</v>
       </c>
       <c r="B573" s="7" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C573" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15267,7 +15260,7 @@
         <v>houston-dynamo</v>
       </c>
       <c r="B574" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C574" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15288,7 +15281,7 @@
         <v>inter-miami-cf</v>
       </c>
       <c r="B575" s="7" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C575" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15309,7 +15302,7 @@
         <v>los-angeles-fc</v>
       </c>
       <c r="B576" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C576" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15330,7 +15323,7 @@
         <v>los-angeles-galaxy</v>
       </c>
       <c r="B577" s="7" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C577" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15351,7 +15344,7 @@
         <v>minnesota-united-fc</v>
       </c>
       <c r="B578" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C578" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15372,7 +15365,7 @@
         <v>nashville-sc</v>
       </c>
       <c r="B579" s="7" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C579" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15393,7 +15386,7 @@
         <v>new-england-revolution</v>
       </c>
       <c r="B580" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C580" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15414,7 +15407,7 @@
         <v>new-york-city-fc</v>
       </c>
       <c r="B581" s="7" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C581" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15435,7 +15428,7 @@
         <v>new-york-red-bulls</v>
       </c>
       <c r="B582" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C582" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15456,7 +15449,7 @@
         <v>orlando-city-sc</v>
       </c>
       <c r="B583" s="7" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C583" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15477,7 +15470,7 @@
         <v>philadelphia-union</v>
       </c>
       <c r="B584" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C584" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15498,7 +15491,7 @@
         <v>portland-timbers</v>
       </c>
       <c r="B585" s="7" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C585" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15519,7 +15512,7 @@
         <v>real-salt-lake</v>
       </c>
       <c r="B586" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C586" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15540,7 +15533,7 @@
         <v>san-diego-fc</v>
       </c>
       <c r="B587" s="7" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C587" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15561,7 +15554,7 @@
         <v>san-jose-earthquakes</v>
       </c>
       <c r="B588" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C588" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15582,7 +15575,7 @@
         <v>seattle-sounders-fc</v>
       </c>
       <c r="B589" s="7" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C589" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15603,7 +15596,7 @@
         <v>sporting-kansas-city</v>
       </c>
       <c r="B590" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C590" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15624,7 +15617,7 @@
         <v>st-louis-city-sc</v>
       </c>
       <c r="B591" s="7" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C591" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15645,7 +15638,7 @@
         <v>toronto-fc</v>
       </c>
       <c r="B592" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C592" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15666,7 +15659,7 @@
         <v>vancouver-whitecaps-fc</v>
       </c>
       <c r="B593" s="7" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C593" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15687,7 +15680,7 @@
         <v>bohemians-fc</v>
       </c>
       <c r="B594" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C594" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15708,7 +15701,7 @@
         <v>derry-city-fc</v>
       </c>
       <c r="B595" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C595" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15729,7 +15722,7 @@
         <v>drogheda-united-fc</v>
       </c>
       <c r="B596" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C596" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15750,7 +15743,7 @@
         <v>dundalk-fc</v>
       </c>
       <c r="B597" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C597" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15771,7 +15764,7 @@
         <v>galway-united-fc</v>
       </c>
       <c r="B598" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C598" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15792,7 +15785,7 @@
         <v>shamrock-rovers-fc</v>
       </c>
       <c r="B599" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C599" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15813,7 +15806,7 @@
         <v>shelbourne-fc</v>
       </c>
       <c r="B600" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C600" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15834,7 +15827,7 @@
         <v>sligo-rovers-fc</v>
       </c>
       <c r="B601" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C601" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15855,7 +15848,7 @@
         <v>st-patricks-athletic-fc</v>
       </c>
       <c r="B602" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C602" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15876,7 +15869,7 @@
         <v>waterford-fc</v>
       </c>
       <c r="B603" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C603" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15894,10 +15887,10 @@
     <row r="604" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A604" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>al-ahly-sc</v>
+        <v>abou-qir-fertilizers-sc</v>
       </c>
       <c r="B604" t="s">
-        <v>554</v>
+        <v>735</v>
       </c>
       <c r="C604" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15915,10 +15908,10 @@
     <row r="605" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A605" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>al-ittihad-ac</v>
+        <v>al-ahly-sc</v>
       </c>
       <c r="B605" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C605" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15936,10 +15929,10 @@
     <row r="606" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A606" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>al-masry-sc</v>
+        <v>al-ittihad-ac</v>
       </c>
       <c r="B606" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C606" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15957,10 +15950,10 @@
     <row r="607" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A607" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>arab-contractors-sc</v>
+        <v>al-masry-sc</v>
       </c>
       <c r="B607" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C607" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15978,10 +15971,10 @@
     <row r="608" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A608" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ceramica-cleopatra-fc</v>
+        <v>el-qanah-fc</v>
       </c>
       <c r="B608" t="s">
-        <v>558</v>
+        <v>733</v>
       </c>
       <c r="C608" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -15999,10 +15992,10 @@
     <row r="609" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A609" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>talaea-el-gaish-sc</v>
+        <v>arab-contractors-sc</v>
       </c>
       <c r="B609" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="C609" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16020,10 +16013,10 @@
     <row r="610" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A610" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>el-gouna-fc</v>
+        <v>asyut-petroleum-sc</v>
       </c>
       <c r="B610" t="s">
-        <v>560</v>
+        <v>734</v>
       </c>
       <c r="C610" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16041,10 +16034,10 @@
     <row r="611" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A611" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>enppi-sc</v>
+        <v>ceramica-cleopatra-fc</v>
       </c>
       <c r="B611" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="C611" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16062,10 +16055,10 @@
     <row r="612" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A612" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ghazi-el-mahalla-sc</v>
+        <v>talaea-el-gaish-sc</v>
       </c>
       <c r="B612" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="C612" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16083,10 +16076,10 @@
     <row r="613" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A613" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>haras-el-hodoud-sc</v>
+        <v>el-gouna-fc</v>
       </c>
       <c r="B613" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="C613" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16104,10 +16097,10 @@
     <row r="614" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A614" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ismaily-sc</v>
+        <v>enppi-sc</v>
       </c>
       <c r="B614" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="C614" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16125,10 +16118,10 @@
     <row r="615" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A615" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>kahrabaa-ismailia-sc</v>
+        <v>ghazi-el-mahalla-sc</v>
       </c>
       <c r="B615" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="C615" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16149,7 +16142,7 @@
         <v>modern-sport-fc</v>
       </c>
       <c r="B616" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="C616" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16170,7 +16163,7 @@
         <v>national-bank-of-egypt-sc</v>
       </c>
       <c r="B617" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="C617" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16191,7 +16184,7 @@
         <v>petrojet-sc</v>
       </c>
       <c r="B618" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="C618" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16209,10 +16202,10 @@
     <row r="619" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A619" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>pharco-fc</v>
+        <v>pyramids-fc</v>
       </c>
       <c r="B619" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="C619" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16230,10 +16223,10 @@
     <row r="620" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A620" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>pyramids-fc</v>
+        <v>smouha-sc</v>
       </c>
       <c r="B620" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="C620" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16251,10 +16244,10 @@
     <row r="621" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A621" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>smouha-sc</v>
+        <v>wadi-degla-sc</v>
       </c>
       <c r="B621" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="C621" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16272,10 +16265,10 @@
     <row r="622" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A622" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>wadi-degla-sc</v>
+        <v>zamalek-sc</v>
       </c>
       <c r="B622" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="C622" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16293,10 +16286,10 @@
     <row r="623" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A623" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>zamalek-sc</v>
+        <v>zed-fc</v>
       </c>
       <c r="B623" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="C623" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16314,18 +16307,18 @@
     <row r="624" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A624" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>zed-fc</v>
+        <v>aek-larnaca-fc</v>
       </c>
       <c r="B624" t="s">
-        <v>574</v>
+        <v>624</v>
       </c>
       <c r="C624" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>egypt</v>
+        <v>cyprus</v>
       </c>
       <c r="D624" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>egypt</v>
+        <v>cyprus</v>
       </c>
       <c r="E624" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -16335,10 +16328,10 @@
     <row r="625" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A625" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>aek-larnaca-fc</v>
+        <v>ael-limassol</v>
       </c>
       <c r="B625" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="C625" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16356,10 +16349,10 @@
     <row r="626" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A626" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ael-limassol</v>
+        <v>anorthosis-famagusta-fc</v>
       </c>
       <c r="B626" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="C626" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16377,10 +16370,10 @@
     <row r="627" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A627" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>anorthosis-famagusta-fc</v>
+        <v>apoel-fc</v>
       </c>
       <c r="B627" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="C627" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16398,10 +16391,10 @@
     <row r="628" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A628" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>apoel-fc</v>
+        <v>apollon-limassol</v>
       </c>
       <c r="B628" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="C628" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16419,10 +16412,10 @@
     <row r="629" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A629" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>apollon-limassol</v>
+        <v>aris-limassol-fc</v>
       </c>
       <c r="B629" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="C629" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16440,10 +16433,10 @@
     <row r="630" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A630" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>aris-limassol-fc</v>
+        <v>karmiotissa-fc</v>
       </c>
       <c r="B630" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="C630" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16461,10 +16454,10 @@
     <row r="631" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A631" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>karmiotissa-fc</v>
+        <v>krasava-eny-ypsonas-fc</v>
       </c>
       <c r="B631" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="C631" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16482,10 +16475,10 @@
     <row r="632" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A632" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>krasava-eny-ypsonas-fc</v>
+        <v>nea-salamis-famagusta-fc</v>
       </c>
       <c r="B632" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="C632" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16503,10 +16496,10 @@
     <row r="633" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A633" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>nea-salamis-famagusta-fc</v>
+        <v>olympiakos-nicosia</v>
       </c>
       <c r="B633" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="C633" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16524,10 +16517,10 @@
     <row r="634" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A634" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>olympiakos-nicosia</v>
+        <v>ac-omonia</v>
       </c>
       <c r="B634" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="C634" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16545,10 +16538,10 @@
     <row r="635" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A635" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ac-omonia</v>
+        <v>pac-omonia-29m</v>
       </c>
       <c r="B635" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="C635" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16566,10 +16559,10 @@
     <row r="636" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A636" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>pac-omonia-29m</v>
+        <v>omonia-aradippou</v>
       </c>
       <c r="B636" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="C636" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16587,10 +16580,10 @@
     <row r="637" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A637" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>omonia-aradippou</v>
+        <v>pafos-fc</v>
       </c>
       <c r="B637" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="C637" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16608,18 +16601,18 @@
     <row r="638" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A638" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>pafos-fc</v>
+        <v>debrecen</v>
       </c>
       <c r="B638" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="C638" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>cyprus</v>
+        <v>hungary</v>
       </c>
       <c r="D638" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>cyprus</v>
+        <v>hungary</v>
       </c>
       <c r="E638" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -16629,10 +16622,10 @@
     <row r="639" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A639" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>debrecen</v>
+        <v>ferencvaros</v>
       </c>
       <c r="B639" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="C639" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16650,10 +16643,10 @@
     <row r="640" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A640" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ferencvaros</v>
+        <v>gyori-eto-fc</v>
       </c>
       <c r="B640" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="C640" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16671,10 +16664,10 @@
     <row r="641" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A641" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>gyori-eto-fc</v>
+        <v>budapest-honved-fc</v>
       </c>
       <c r="B641" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="C641" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16692,10 +16685,10 @@
     <row r="642" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A642" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>budapest-honved-fc</v>
+        <v>kisvarda-fc</v>
       </c>
       <c r="B642" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="C642" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16713,10 +16706,10 @@
     <row r="643" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A643" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>kisvarda-fc</v>
+        <v>mtk-budapest-fc</v>
       </c>
       <c r="B643" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="C643" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16734,10 +16727,10 @@
     <row r="644" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A644" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>mtk-budapest-fc</v>
+        <v>nyiregyhaza-spartacus-fc</v>
       </c>
       <c r="B644" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="C644" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16755,10 +16748,10 @@
     <row r="645" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A645" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>nyiregyhaza-spartacus-fc</v>
+        <v>paksi-fc</v>
       </c>
       <c r="B645" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="C645" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16776,10 +16769,10 @@
     <row r="646" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A646" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>paksi-fc</v>
+        <v>puskas-akademia-fc</v>
       </c>
       <c r="B646" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="C646" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16797,10 +16790,10 @@
     <row r="647" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A647" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>puskas-akademia-fc</v>
+        <v>ujpest-fc</v>
       </c>
       <c r="B647" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="C647" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16818,10 +16811,10 @@
     <row r="648" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A648" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ujpest-fc</v>
+        <v>vasas-sc</v>
       </c>
       <c r="B648" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="C648" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16839,10 +16832,10 @@
     <row r="649" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A649" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>vasas-sc</v>
+        <v>zalaegerszeg-te</v>
       </c>
       <c r="B649" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="C649" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16860,18 +16853,18 @@
     <row r="650" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A650" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>zalaegerszeg-te</v>
+        <v>albion-fc</v>
       </c>
       <c r="B650" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="C650" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>hungary</v>
+        <v>uruguay</v>
       </c>
       <c r="D650" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>hungary</v>
+        <v>uruguay</v>
       </c>
       <c r="E650" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -16881,10 +16874,10 @@
     <row r="651" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A651" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>albion-fc</v>
+        <v>boston-river</v>
       </c>
       <c r="B651" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="C651" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16902,10 +16895,10 @@
     <row r="652" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A652" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>boston-river</v>
+        <v>central-espanol</v>
       </c>
       <c r="B652" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="C652" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16923,10 +16916,10 @@
     <row r="653" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A653" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>central-espanol</v>
+        <v>club-atletico-cerro</v>
       </c>
       <c r="B653" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C653" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16944,10 +16937,10 @@
     <row r="654" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A654" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>club-atletico-cerro</v>
+        <v>cerro-largo-fc</v>
       </c>
       <c r="B654" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="C654" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16965,10 +16958,10 @@
     <row r="655" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A655" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>cerro-largo-fc</v>
+        <v>danubio-fc</v>
       </c>
       <c r="B655" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="C655" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -16986,10 +16979,10 @@
     <row r="656" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A656" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>danubio-fc</v>
+        <v>defensor-sporting</v>
       </c>
       <c r="B656" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="C656" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17007,10 +17000,10 @@
     <row r="657" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A657" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>defensor-sporting</v>
+        <v>juventud-de-las-piedras</v>
       </c>
       <c r="B657" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="C657" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17028,10 +17021,10 @@
     <row r="658" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A658" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>juventud-de-las-piedras</v>
+        <v>liverpool-fc-montevideo</v>
       </c>
       <c r="B658" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="C658" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17049,10 +17042,10 @@
     <row r="659" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A659" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>liverpool-fc-montevideo</v>
+        <v>deportivo-maldonado</v>
       </c>
       <c r="B659" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="C659" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17070,10 +17063,10 @@
     <row r="660" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A660" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>deportivo-maldonado</v>
+        <v>montevideo-city-torque</v>
       </c>
       <c r="B660" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="C660" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17091,10 +17084,10 @@
     <row r="661" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A661" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>montevideo-city-torque</v>
+        <v>club-nacional-de-football</v>
       </c>
       <c r="B661" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="C661" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17112,10 +17105,10 @@
     <row r="662" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A662" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>club-nacional-de-football</v>
+        <v>penarol</v>
       </c>
       <c r="B662" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="C662" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17133,10 +17126,10 @@
     <row r="663" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A663" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>penarol</v>
+        <v>club-atletico-progreso</v>
       </c>
       <c r="B663" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="C663" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17154,10 +17147,10 @@
     <row r="664" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A664" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>club-atletico-progreso</v>
+        <v>racing-club-de-montevideo</v>
       </c>
       <c r="B664" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="C664" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17175,10 +17168,10 @@
     <row r="665" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A665" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>racing-club-de-montevideo</v>
+        <v>montevideo-wanderers-fc</v>
       </c>
       <c r="B665" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="C665" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17196,18 +17189,18 @@
     <row r="666" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A666" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>montevideo-wanderers-fc</v>
+        <v>fsc-bukovyna-chernivtsi</v>
       </c>
       <c r="B666" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="C666" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>uruguay</v>
+        <v>ukraine</v>
       </c>
       <c r="D666" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>uruguay</v>
+        <v>ukraine</v>
       </c>
       <c r="E666" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -17217,10 +17210,10 @@
     <row r="667" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A667" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fsc-bukovyna-chernivtsi</v>
+        <v>fc-chornomorets-odessa</v>
       </c>
       <c r="B667" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="C667" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17238,10 +17231,10 @@
     <row r="668" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A668" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-chornomorets-odessa</v>
+        <v>fc-dynamo-kyiv</v>
       </c>
       <c r="B668" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="C668" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17259,10 +17252,10 @@
     <row r="669" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A669" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-dynamo-kyiv</v>
+        <v>fc-epitsentr-kamianets-podilskyi</v>
       </c>
       <c r="B669" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="C669" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17280,10 +17273,10 @@
     <row r="670" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A670" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-epitsentr-kamianets-podilskyi</v>
+        <v>fc-kharkiv</v>
       </c>
       <c r="B670" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="C670" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17301,10 +17294,10 @@
     <row r="671" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A671" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-kharkiv</v>
+        <v>fc-karpaty-lviv</v>
       </c>
       <c r="B671" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="C671" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17322,10 +17315,10 @@
     <row r="672" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A672" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-karpaty-lviv</v>
+        <v>fc-kolos-kovalivka</v>
       </c>
       <c r="B672" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="C672" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17343,10 +17336,10 @@
     <row r="673" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A673" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-kolos-kovalivka</v>
+        <v>fc-kryvbas-kryvyi-rih</v>
       </c>
       <c r="B673" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="C673" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17364,10 +17357,10 @@
     <row r="674" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A674" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-kryvbas-kryvyi-rih</v>
+        <v>fc-kudrivka</v>
       </c>
       <c r="B674" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="C674" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17385,10 +17378,10 @@
     <row r="675" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A675" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-kudrivka</v>
+        <v>fc-livyi-bereh-kyiv</v>
       </c>
       <c r="B675" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="C675" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17406,10 +17399,10 @@
     <row r="676" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A676" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-livyi-bereh-kyiv</v>
+        <v>fc-lnz-cherkasy</v>
       </c>
       <c r="B676" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="C676" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17427,10 +17420,10 @@
     <row r="677" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A677" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-lnz-cherkasy</v>
+        <v>fc-obolon-kyiv</v>
       </c>
       <c r="B677" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="C677" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17448,10 +17441,10 @@
     <row r="678" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A678" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-obolon-kyiv</v>
+        <v>fc-polissya-zhytomyr</v>
       </c>
       <c r="B678" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="C678" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17469,10 +17462,10 @@
     <row r="679" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A679" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-polissya-zhytomyr</v>
+        <v>fc-shakhtar-donetsk</v>
       </c>
       <c r="B679" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="C679" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17490,10 +17483,10 @@
     <row r="680" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A680" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-shakhtar-donetsk</v>
+        <v>nk-veres-rivne</v>
       </c>
       <c r="B680" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="C680" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17511,10 +17504,10 @@
     <row r="681" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A681" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>nk-veres-rivne</v>
+        <v>fc-zorya-luhansk</v>
       </c>
       <c r="B681" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="C681" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17532,18 +17525,18 @@
     <row r="682" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A682" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-zorya-luhansk</v>
+        <v>avispa-fukuoka</v>
       </c>
       <c r="B682" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="C682" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>ukraine</v>
+        <v>japan</v>
       </c>
       <c r="D682" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>ukraine</v>
+        <v>japan</v>
       </c>
       <c r="E682" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -17553,10 +17546,10 @@
     <row r="683" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A683" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>avispa-fukuoka</v>
+        <v>cerezo-osaka</v>
       </c>
       <c r="B683" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="C683" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17574,10 +17567,10 @@
     <row r="684" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A684" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>cerezo-osaka</v>
+        <v>fagiano-okayama</v>
       </c>
       <c r="B684" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="C684" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17595,10 +17588,10 @@
     <row r="685" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A685" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fagiano-okayama</v>
+        <v>gamba-osaka</v>
       </c>
       <c r="B685" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="C685" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17616,10 +17609,10 @@
     <row r="686" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A686" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>gamba-osaka</v>
+        <v>sanfreece-hiroshima</v>
       </c>
       <c r="B686" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="C686" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17637,10 +17630,10 @@
     <row r="687" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A687" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>sanfreece-hiroshima</v>
+        <v>jef-united-chiba</v>
       </c>
       <c r="B687" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="C687" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17658,10 +17651,10 @@
     <row r="688" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A688" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>jef-united-chiba</v>
+        <v>kashima-antlers</v>
       </c>
       <c r="B688" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="C688" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17679,10 +17672,10 @@
     <row r="689" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A689" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>kashima-antlers</v>
+        <v>kashiwa-reysol</v>
       </c>
       <c r="B689" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="C689" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17700,10 +17693,10 @@
     <row r="690" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A690" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>kashiwa-reysol</v>
+        <v>kawasaki-frontale</v>
       </c>
       <c r="B690" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="C690" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17721,10 +17714,10 @@
     <row r="691" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A691" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>kawasaki-frontale</v>
+        <v>vissel-kobe</v>
       </c>
       <c r="B691" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="C691" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17742,10 +17735,10 @@
     <row r="692" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A692" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>vissel-kobe</v>
+        <v>kyoto-sanga-fc</v>
       </c>
       <c r="B692" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="C692" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17763,10 +17756,10 @@
     <row r="693" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A693" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>kyoto-sanga-fc</v>
+        <v>fc-machida-zelvia</v>
       </c>
       <c r="B693" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="C693" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17784,10 +17777,10 @@
     <row r="694" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A694" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-machida-zelvia</v>
+        <v>mito-hollyhock</v>
       </c>
       <c r="B694" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="C694" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17805,10 +17798,10 @@
     <row r="695" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A695" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>mito-hollyhock</v>
+        <v>nagoya-grampus</v>
       </c>
       <c r="B695" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="C695" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17826,10 +17819,10 @@
     <row r="696" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A696" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>nagoya-grampus</v>
+        <v>shimizu-s-pulse</v>
       </c>
       <c r="B696" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="C696" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17847,10 +17840,10 @@
     <row r="697" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A697" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>shimizu-s-pulse</v>
+        <v>fc-tokyo</v>
       </c>
       <c r="B697" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="C697" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17868,10 +17861,10 @@
     <row r="698" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A698" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-tokyo</v>
+        <v>tokyo-verdy</v>
       </c>
       <c r="B698" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="C698" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17889,10 +17882,10 @@
     <row r="699" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A699" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>tokyo-verdy</v>
+        <v>urawa-red-diamonds</v>
       </c>
       <c r="B699" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="C699" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17910,10 +17903,10 @@
     <row r="700" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A700" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>urawa-red-diamonds</v>
+        <v>v-varen-nagasaki</v>
       </c>
       <c r="B700" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="C700" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17931,10 +17924,10 @@
     <row r="701" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A701" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>v-varen-nagasaki</v>
+        <v>yokohama-f-marinos</v>
       </c>
       <c r="B701" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="C701" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17952,18 +17945,18 @@
     <row r="702" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A702" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>yokohama-f-marinos</v>
+        <v>fc-anyang</v>
       </c>
       <c r="B702" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="C702" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>japan</v>
+        <v>south-korea</v>
       </c>
       <c r="D702" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>japan</v>
+        <v>south-korea</v>
       </c>
       <c r="E702" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -17973,10 +17966,10 @@
     <row r="703" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A703" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-anyang</v>
+        <v>bucheon-fc-1995</v>
       </c>
       <c r="B703" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="C703" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -17994,10 +17987,10 @@
     <row r="704" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A704" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>bucheon-fc-1995</v>
+        <v>daejeon-hana-citizen</v>
       </c>
       <c r="B704" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="C704" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -18015,10 +18008,10 @@
     <row r="705" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A705" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>daejeon-hana-citizen</v>
+        <v>gangwon-fc</v>
       </c>
       <c r="B705" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="C705" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -18036,10 +18029,10 @@
     <row r="706" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A706" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>gangwon-fc</v>
+        <v>gimcheon-sangmu-fc</v>
       </c>
       <c r="B706" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="C706" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -18057,10 +18050,10 @@
     <row r="707" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A707" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>gimcheon-sangmu-fc</v>
+        <v>gwangju-fc</v>
       </c>
       <c r="B707" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="C707" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -18078,10 +18071,10 @@
     <row r="708" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A708" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>gwangju-fc</v>
+        <v>incheon-united</v>
       </c>
       <c r="B708" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="C708" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -18099,10 +18092,10 @@
     <row r="709" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A709" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>incheon-united</v>
+        <v>jeju-sk-fc</v>
       </c>
       <c r="B709" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="C709" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -18120,10 +18113,10 @@
     <row r="710" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A710" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>jeju-sk-fc</v>
+        <v>jeonbuk-hyundai-motors</v>
       </c>
       <c r="B710" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="C710" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -18141,10 +18134,10 @@
     <row r="711" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A711" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>jeonbuk-hyundai-motors</v>
+        <v>pohang-steelers</v>
       </c>
       <c r="B711" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="C711" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -18162,10 +18155,10 @@
     <row r="712" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A712" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>pohang-steelers</v>
+        <v>fc-seoul</v>
       </c>
       <c r="B712" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="C712" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -18183,10 +18176,10 @@
     <row r="713" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A713" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>fc-seoul</v>
+        <v>ulsan-hd-fc</v>
       </c>
       <c r="B713" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="C713" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -18204,18 +18197,18 @@
     <row r="714" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A714" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>ulsan-hd-fc</v>
+        <v>beijing-guoan-fc</v>
       </c>
       <c r="B714" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="C714" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>south-korea</v>
+        <v>china</v>
       </c>
       <c r="D714" t="str">
         <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>south-korea</v>
+        <v>china</v>
       </c>
       <c r="E714" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
@@ -18225,10 +18218,10 @@
     <row r="715" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A715" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>beijing-guoan-fc</v>
+        <v>chengdu-rongcheng-fc</v>
       </c>
       <c r="B715" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="C715" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -18246,10 +18239,10 @@
     <row r="716" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A716" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>chengdu-rongcheng-fc</v>
+        <v>chongqing-tonglianglong-fc</v>
       </c>
       <c r="B716" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="C716" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -18267,10 +18260,10 @@
     <row r="717" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A717" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>chongqing-tonglianglong-fc</v>
+        <v>dalian-yingbo-fc</v>
       </c>
       <c r="B717" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="C717" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -18288,10 +18281,10 @@
     <row r="718" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A718" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>dalian-yingbo-fc</v>
+        <v>henan-fc</v>
       </c>
       <c r="B718" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="C718" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -18309,10 +18302,10 @@
     <row r="719" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A719" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>henan-fc</v>
+        <v>liaoning-tieren-fc</v>
       </c>
       <c r="B719" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="C719" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -18330,10 +18323,10 @@
     <row r="720" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A720" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>liaoning-tieren-fc</v>
+        <v>qingdao-hainiu-fc</v>
       </c>
       <c r="B720" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="C720" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -18351,10 +18344,10 @@
     <row r="721" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A721" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>qingdao-hainiu-fc</v>
+        <v>qingdao-west-coast-fc</v>
       </c>
       <c r="B721" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="C721" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -18372,10 +18365,10 @@
     <row r="722" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A722" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>qingdao-west-coast-fc</v>
+        <v>shandong-taishan-fc</v>
       </c>
       <c r="B722" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="C722" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -18393,10 +18386,10 @@
     <row r="723" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A723" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>shandong-taishan-fc</v>
+        <v>shanghai-port-fc</v>
       </c>
       <c r="B723" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="C723" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -18414,10 +18407,10 @@
     <row r="724" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A724" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>shanghai-port-fc</v>
+        <v>shanghai-shenhua-fc</v>
       </c>
       <c r="B724" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="C724" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -18435,10 +18428,10 @@
     <row r="725" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A725" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>shanghai-shenhua-fc</v>
+        <v>shenzhen-peng-city-fc</v>
       </c>
       <c r="B725" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="C725" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -18456,10 +18449,10 @@
     <row r="726" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A726" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>shenzhen-peng-city-fc</v>
+        <v>tianjin-jinmen-tiger-fc</v>
       </c>
       <c r="B726" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="C726" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -18477,10 +18470,10 @@
     <row r="727" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A727" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>tianjin-jinmen-tiger-fc</v>
+        <v>wuhan-three-towns-fc</v>
       </c>
       <c r="B727" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="C727" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -18498,10 +18491,10 @@
     <row r="728" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A728" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>wuhan-three-towns-fc</v>
+        <v>yunnan-yukun-fc</v>
       </c>
       <c r="B728" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="C728" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -18519,10 +18512,10 @@
     <row r="729" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A729" t="str">
         <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>yunnan-yukun-fc</v>
+        <v>zhejiang-professional-fc</v>
       </c>
       <c r="B729" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="C729" t="str">
         <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
@@ -18533,27 +18526,6 @@
         <v>china</v>
       </c>
       <c r="E729" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>SI</v>
-      </c>
-    </row>
-    <row r="730" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A730" t="str">
-        <f>MID(Tabla1[[#This Row],[ENLACE]],FIND("~",SUBSTITUTE(Tabla1[[#This Row],[ENLACE]],"/","~",2))+1,LEN(Tabla1[[#This Row],[ENLACE]]))</f>
-        <v>zhejiang-professional-fc</v>
-      </c>
-      <c r="B730" t="s">
-        <v>734</v>
-      </c>
-      <c r="C730" t="str">
-        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(Tabla1[[#This Row],[ENLACE]],"/",1),"/")</f>
-        <v>china</v>
-      </c>
-      <c r="D730" t="str">
-        <f>Tabla1[[#This Row],[PAIS]]</f>
-        <v>china</v>
-      </c>
-      <c r="E730" s="8" t="str">
         <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
         <v>SI</v>
       </c>

--- a/enlaces_equipos.xlsx
+++ b/enlaces_equipos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose-\Trabajo\statsFutbol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA91C5A1-A3DF-42ED-A218-6C96A8959BAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADCBF9DA-E272-4F49-8C47-19A78A8B5D91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{474EBA83-D6A0-4565-BEB0-BC6B2AA992C1}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="737">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="737">
   <si>
     <t>EQUIPO</t>
   </si>
@@ -2393,15 +2393,15 @@
   </cellStyles>
   <dxfs count="6">
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -2451,8 +2451,8 @@
     <tableColumn id="5" xr3:uid="{F2E44DAA-70E6-4294-A083-84669D9B9C01}" name="DIVISION" dataDxfId="2">
       <calculatedColumnFormula>Tabla1[[#This Row],[PAIS]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{864CABB9-1E94-4601-B818-3F8256A83250}" name="ANALIZAR" dataDxfId="1">
-      <calculatedColumnFormula>IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</calculatedColumnFormula>
+    <tableColumn id="4" xr3:uid="{864CABB9-1E94-4601-B818-3F8256A83250}" name="ANALIZAR" dataDxfId="0">
+      <calculatedColumnFormula>IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2802,15 +2802,15 @@
         <v>argentina</v>
       </c>
       <c r="E2" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
       <c r="H2" s="9" t="str" cm="1">
-        <f t="array" ref="H2:H41">_xlfn.UNIQUE(Tabla1[PAIS])</f>
+        <f t="array" ref="H2:H44">_xlfn.UNIQUE(Tabla1[DIVISION])</f>
         <v>argentina</v>
       </c>
       <c r="I2" s="9" t="str">
-        <f t="shared" ref="I2:I37" ca="1" si="0">IF(J2&gt;TODAY(),"","X")</f>
+        <f t="shared" ref="I2:I38" ca="1" si="0">IF(J2&gt;TODAY(),"","X")</f>
         <v>X</v>
       </c>
       <c r="J2" s="10">
@@ -2837,7 +2837,7 @@
         <v>argentina</v>
       </c>
       <c r="E3" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
       <c r="H3" s="9" t="str">
@@ -2871,7 +2871,7 @@
         <v>argentina</v>
       </c>
       <c r="E4" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
       <c r="H4" s="9" t="str">
@@ -2905,7 +2905,7 @@
         <v>argentina</v>
       </c>
       <c r="E5" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
       <c r="H5" s="9" t="str">
@@ -2939,7 +2939,7 @@
         <v>argentina</v>
       </c>
       <c r="E6" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
       <c r="H6" s="9" t="str">
@@ -2973,7 +2973,7 @@
         <v>argentina</v>
       </c>
       <c r="E7" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
       <c r="H7" s="9" t="str">
@@ -3007,7 +3007,7 @@
         <v>argentina</v>
       </c>
       <c r="E8" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
       <c r="H8" s="9" t="str">
@@ -3041,7 +3041,7 @@
         <v>argentina</v>
       </c>
       <c r="E9" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
       <c r="H9" s="9" t="str">
@@ -3075,7 +3075,7 @@
         <v>argentina</v>
       </c>
       <c r="E10" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
       <c r="H10" s="9" t="str">
@@ -3109,7 +3109,7 @@
         <v>argentina</v>
       </c>
       <c r="E11" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
       <c r="H11" s="9" t="str">
@@ -3143,7 +3143,7 @@
         <v>argentina</v>
       </c>
       <c r="E12" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
       <c r="H12" s="9" t="str">
@@ -3177,7 +3177,7 @@
         <v>argentina</v>
       </c>
       <c r="E13" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
       <c r="H13" s="9" t="str">
@@ -3211,7 +3211,7 @@
         <v>argentina</v>
       </c>
       <c r="E14" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
       <c r="H14" s="9" t="str">
@@ -3245,11 +3245,11 @@
         <v>argentina</v>
       </c>
       <c r="E15" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
       <c r="H15" s="9" t="str">
-        <v>finland</v>
+        <v>england_b</v>
       </c>
       <c r="I15" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -3279,11 +3279,11 @@
         <v>argentina</v>
       </c>
       <c r="E16" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
       <c r="H16" s="9" t="str">
-        <v>france</v>
+        <v>finland</v>
       </c>
       <c r="I16" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -3313,11 +3313,11 @@
         <v>argentina</v>
       </c>
       <c r="E17" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
       <c r="H17" s="9" t="str">
-        <v>germany</v>
+        <v>france</v>
       </c>
       <c r="I17" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -3347,11 +3347,11 @@
         <v>argentina</v>
       </c>
       <c r="E18" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
       <c r="H18" s="9" t="str">
-        <v>greece</v>
+        <v>germany</v>
       </c>
       <c r="I18" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -3381,11 +3381,11 @@
         <v>argentina</v>
       </c>
       <c r="E19" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
       <c r="H19" s="9" t="str">
-        <v>italy</v>
+        <v>germany_b</v>
       </c>
       <c r="I19" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -3415,11 +3415,11 @@
         <v>argentina</v>
       </c>
       <c r="E20" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
       <c r="H20" s="9" t="str">
-        <v>mexico</v>
+        <v>greece</v>
       </c>
       <c r="I20" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -3449,11 +3449,11 @@
         <v>argentina</v>
       </c>
       <c r="E21" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
       <c r="H21" s="9" t="str">
-        <v>netherlands</v>
+        <v>italy</v>
       </c>
       <c r="I21" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -3483,11 +3483,11 @@
         <v>argentina</v>
       </c>
       <c r="E22" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
       <c r="H22" s="9" t="str">
-        <v>norway</v>
+        <v>mexico</v>
       </c>
       <c r="I22" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -3517,11 +3517,11 @@
         <v>argentina</v>
       </c>
       <c r="E23" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
       <c r="H23" s="9" t="str">
-        <v>peru</v>
+        <v>netherlands</v>
       </c>
       <c r="I23" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -3551,11 +3551,11 @@
         <v>argentina</v>
       </c>
       <c r="E24" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
       <c r="H24" s="9" t="str">
-        <v>poland</v>
+        <v>norway</v>
       </c>
       <c r="I24" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -3585,11 +3585,11 @@
         <v>argentina</v>
       </c>
       <c r="E25" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
       <c r="H25" s="9" t="str">
-        <v>portugal</v>
+        <v>peru</v>
       </c>
       <c r="I25" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -3619,11 +3619,11 @@
         <v>argentina</v>
       </c>
       <c r="E26" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
       <c r="H26" s="9" t="str">
-        <v>romania</v>
+        <v>poland</v>
       </c>
       <c r="I26" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -3653,11 +3653,11 @@
         <v>argentina</v>
       </c>
       <c r="E27" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
       <c r="H27" s="9" t="str">
-        <v>saudi-arabia</v>
+        <v>portugal</v>
       </c>
       <c r="I27" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -3687,11 +3687,11 @@
         <v>argentina</v>
       </c>
       <c r="E28" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
       <c r="H28" s="9" t="str">
-        <v>scotland</v>
+        <v>romania</v>
       </c>
       <c r="I28" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -3721,11 +3721,11 @@
         <v>argentina</v>
       </c>
       <c r="E29" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
       <c r="H29" s="9" t="str">
-        <v>spain</v>
+        <v>saudi-arabia</v>
       </c>
       <c r="I29" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -3755,11 +3755,11 @@
         <v>argentina</v>
       </c>
       <c r="E30" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
       <c r="H30" s="9" t="str">
-        <v>sweden</v>
+        <v>scotland</v>
       </c>
       <c r="I30" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -3789,11 +3789,11 @@
         <v>argentina</v>
       </c>
       <c r="E31" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
       <c r="H31" s="9" t="str">
-        <v>switzerland</v>
+        <v>spain</v>
       </c>
       <c r="I31" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -3823,11 +3823,11 @@
         <v>australia</v>
       </c>
       <c r="E32" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
       <c r="H32" s="9" t="str">
-        <v>usa</v>
+        <v>spain_b</v>
       </c>
       <c r="I32" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -3857,11 +3857,11 @@
         <v>australia</v>
       </c>
       <c r="E33" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
       <c r="H33" s="9" t="str">
-        <v>ireland</v>
+        <v>sweden</v>
       </c>
       <c r="I33" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -3891,11 +3891,11 @@
         <v>australia</v>
       </c>
       <c r="E34" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
       <c r="H34" s="9" t="str">
-        <v>egypt</v>
+        <v>switzerland</v>
       </c>
       <c r="I34" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -3925,11 +3925,11 @@
         <v>australia</v>
       </c>
       <c r="E35" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
       <c r="H35" s="9" t="str">
-        <v>cyprus</v>
+        <v>usa</v>
       </c>
       <c r="I35" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -3959,11 +3959,11 @@
         <v>australia</v>
       </c>
       <c r="E36" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
       <c r="H36" s="9" t="str">
-        <v>hungary</v>
+        <v>ireland</v>
       </c>
       <c r="I36" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -3993,11 +3993,11 @@
         <v>australia</v>
       </c>
       <c r="E37" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
       <c r="H37" s="9" t="str">
-        <v>uruguay</v>
+        <v>egypt</v>
       </c>
       <c r="I37" s="9" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -4027,14 +4027,14 @@
         <v>australia</v>
       </c>
       <c r="E38" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
       <c r="H38" s="9" t="str">
-        <v>ukraine</v>
+        <v>cyprus</v>
       </c>
       <c r="I38" s="9" t="str">
-        <f t="shared" ref="I38:I41" ca="1" si="1">IF(J38&gt;TODAY(),"","X")</f>
+        <f t="shared" ca="1" si="0"/>
         <v>X</v>
       </c>
       <c r="J38" s="11">
@@ -4061,14 +4061,14 @@
         <v>australia</v>
       </c>
       <c r="E39" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
       <c r="H39" s="9" t="str">
-        <v>japan</v>
+        <v>hungary</v>
       </c>
       <c r="I39" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ref="I33:I39" ca="1" si="1">IF(J39&gt;TODAY(),"","X")</f>
         <v>X</v>
       </c>
       <c r="J39" s="11">
@@ -4095,14 +4095,14 @@
         <v>australia</v>
       </c>
       <c r="E40" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
       <c r="H40" s="9" t="str">
-        <v>south-korea</v>
+        <v>uruguay</v>
       </c>
       <c r="I40" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ref="I36:I44" ca="1" si="2">IF(J40&gt;TODAY(),"","X")</f>
         <v>X</v>
       </c>
       <c r="J40" s="11">
@@ -4129,14 +4129,14 @@
         <v>australia</v>
       </c>
       <c r="E41" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
       <c r="H41" s="9" t="str">
-        <v>china</v>
+        <v>ukraine</v>
       </c>
       <c r="I41" s="9" t="str">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" ca="1" si="2"/>
         <v>X</v>
       </c>
       <c r="J41" s="11">
@@ -4163,8 +4163,21 @@
         <v>australia</v>
       </c>
       <c r="E42" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>SI</v>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="H42" s="9" t="str">
+        <v>japan</v>
+      </c>
+      <c r="I42" s="9" t="str">
+        <f ca="1">IF(J42&gt;TODAY(),"","X")</f>
+        <v>X</v>
+      </c>
+      <c r="J42" s="11">
+        <v>46300</v>
+      </c>
+      <c r="K42" s="9" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
@@ -4184,8 +4197,21 @@
         <v>australia</v>
       </c>
       <c r="E43" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>SI</v>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="H43" s="9" t="str">
+        <v>south-korea</v>
+      </c>
+      <c r="I43" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>X</v>
+      </c>
+      <c r="J43" s="11">
+        <v>46301</v>
+      </c>
+      <c r="K43" s="9" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
@@ -4205,8 +4231,21 @@
         <v>austria</v>
       </c>
       <c r="E44" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
-        <v>SI</v>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
+        <v>SI</v>
+      </c>
+      <c r="H44" s="9" t="str">
+        <v>china</v>
+      </c>
+      <c r="I44" s="9" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>X</v>
+      </c>
+      <c r="J44" s="11">
+        <v>46302</v>
+      </c>
+      <c r="K44" s="9" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
@@ -4226,7 +4265,7 @@
         <v>austria</v>
       </c>
       <c r="E45" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -4247,7 +4286,7 @@
         <v>austria</v>
       </c>
       <c r="E46" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -4268,7 +4307,7 @@
         <v>austria</v>
       </c>
       <c r="E47" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -4289,7 +4328,7 @@
         <v>austria</v>
       </c>
       <c r="E48" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -4310,7 +4349,7 @@
         <v>austria</v>
       </c>
       <c r="E49" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -4331,7 +4370,7 @@
         <v>austria</v>
       </c>
       <c r="E50" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -4352,7 +4391,7 @@
         <v>austria</v>
       </c>
       <c r="E51" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -4373,7 +4412,7 @@
         <v>austria</v>
       </c>
       <c r="E52" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -4394,7 +4433,7 @@
         <v>austria</v>
       </c>
       <c r="E53" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -4415,7 +4454,7 @@
         <v>austria</v>
       </c>
       <c r="E54" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -4436,7 +4475,7 @@
         <v>austria</v>
       </c>
       <c r="E55" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -4457,7 +4496,7 @@
         <v>belgium</v>
       </c>
       <c r="E56" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -4478,7 +4517,7 @@
         <v>belgium</v>
       </c>
       <c r="E57" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -4499,7 +4538,7 @@
         <v>belgium</v>
       </c>
       <c r="E58" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -4520,7 +4559,7 @@
         <v>belgium</v>
       </c>
       <c r="E59" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -4541,7 +4580,7 @@
         <v>belgium</v>
       </c>
       <c r="E60" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -4562,7 +4601,7 @@
         <v>belgium</v>
       </c>
       <c r="E61" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -4583,7 +4622,7 @@
         <v>belgium</v>
       </c>
       <c r="E62" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -4604,7 +4643,7 @@
         <v>belgium</v>
       </c>
       <c r="E63" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -4625,7 +4664,7 @@
         <v>belgium</v>
       </c>
       <c r="E64" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -4646,7 +4685,7 @@
         <v>belgium</v>
       </c>
       <c r="E65" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -4667,7 +4706,7 @@
         <v>belgium</v>
       </c>
       <c r="E66" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -4688,7 +4727,7 @@
         <v>belgium</v>
       </c>
       <c r="E67" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -4709,7 +4748,7 @@
         <v>belgium</v>
       </c>
       <c r="E68" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -4730,7 +4769,7 @@
         <v>belgium</v>
       </c>
       <c r="E69" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -4751,7 +4790,7 @@
         <v>belgium</v>
       </c>
       <c r="E70" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -4772,7 +4811,7 @@
         <v>belgium</v>
       </c>
       <c r="E71" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -4793,7 +4832,7 @@
         <v>belgium</v>
       </c>
       <c r="E72" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -4814,7 +4853,7 @@
         <v>belgium</v>
       </c>
       <c r="E73" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -4835,7 +4874,7 @@
         <v>brazil</v>
       </c>
       <c r="E74" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -4856,7 +4895,7 @@
         <v>brazil</v>
       </c>
       <c r="E75" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -4877,7 +4916,7 @@
         <v>brazil</v>
       </c>
       <c r="E76" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -4898,7 +4937,7 @@
         <v>brazil</v>
       </c>
       <c r="E77" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -4919,7 +4958,7 @@
         <v>brazil</v>
       </c>
       <c r="E78" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -4940,7 +4979,7 @@
         <v>brazil</v>
       </c>
       <c r="E79" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -4961,7 +5000,7 @@
         <v>brazil</v>
       </c>
       <c r="E80" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -4982,7 +5021,7 @@
         <v>brazil</v>
       </c>
       <c r="E81" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -5003,7 +5042,7 @@
         <v>brazil</v>
       </c>
       <c r="E82" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -5024,7 +5063,7 @@
         <v>brazil</v>
       </c>
       <c r="E83" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -5045,7 +5084,7 @@
         <v>brazil</v>
       </c>
       <c r="E84" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -5066,7 +5105,7 @@
         <v>brazil</v>
       </c>
       <c r="E85" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -5087,7 +5126,7 @@
         <v>brazil</v>
       </c>
       <c r="E86" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -5108,7 +5147,7 @@
         <v>brazil</v>
       </c>
       <c r="E87" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -5129,7 +5168,7 @@
         <v>brazil</v>
       </c>
       <c r="E88" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -5150,7 +5189,7 @@
         <v>brazil</v>
       </c>
       <c r="E89" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -5171,7 +5210,7 @@
         <v>brazil</v>
       </c>
       <c r="E90" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -5192,7 +5231,7 @@
         <v>brazil</v>
       </c>
       <c r="E91" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -5213,7 +5252,7 @@
         <v>brazil</v>
       </c>
       <c r="E92" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -5234,7 +5273,7 @@
         <v>brazil</v>
       </c>
       <c r="E93" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -5255,7 +5294,7 @@
         <v>bulgaria</v>
       </c>
       <c r="E94" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -5276,7 +5315,7 @@
         <v>bulgaria</v>
       </c>
       <c r="E95" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -5297,7 +5336,7 @@
         <v>bulgaria</v>
       </c>
       <c r="E96" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -5318,7 +5357,7 @@
         <v>bulgaria</v>
       </c>
       <c r="E97" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -5339,7 +5378,7 @@
         <v>bulgaria</v>
       </c>
       <c r="E98" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -5360,7 +5399,7 @@
         <v>bulgaria</v>
       </c>
       <c r="E99" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -5381,7 +5420,7 @@
         <v>bulgaria</v>
       </c>
       <c r="E100" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -5402,7 +5441,7 @@
         <v>bulgaria</v>
       </c>
       <c r="E101" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -5423,7 +5462,7 @@
         <v>bulgaria</v>
       </c>
       <c r="E102" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -5444,7 +5483,7 @@
         <v>bulgaria</v>
       </c>
       <c r="E103" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -5465,7 +5504,7 @@
         <v>bulgaria</v>
       </c>
       <c r="E104" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -5486,7 +5525,7 @@
         <v>bulgaria</v>
       </c>
       <c r="E105" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -5507,7 +5546,7 @@
         <v>bulgaria</v>
       </c>
       <c r="E106" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -5528,7 +5567,7 @@
         <v>bulgaria</v>
       </c>
       <c r="E107" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -5549,7 +5588,7 @@
         <v>chile</v>
       </c>
       <c r="E108" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -5570,7 +5609,7 @@
         <v>chile</v>
       </c>
       <c r="E109" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -5591,7 +5630,7 @@
         <v>chile</v>
       </c>
       <c r="E110" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -5612,7 +5651,7 @@
         <v>chile</v>
       </c>
       <c r="E111" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -5633,7 +5672,7 @@
         <v>chile</v>
       </c>
       <c r="E112" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -5654,7 +5693,7 @@
         <v>chile</v>
       </c>
       <c r="E113" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -5675,7 +5714,7 @@
         <v>chile</v>
       </c>
       <c r="E114" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -5696,7 +5735,7 @@
         <v>chile</v>
       </c>
       <c r="E115" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -5717,7 +5756,7 @@
         <v>chile</v>
       </c>
       <c r="E116" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -5738,7 +5777,7 @@
         <v>chile</v>
       </c>
       <c r="E117" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -5759,7 +5798,7 @@
         <v>chile</v>
       </c>
       <c r="E118" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -5780,7 +5819,7 @@
         <v>chile</v>
       </c>
       <c r="E119" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -5801,7 +5840,7 @@
         <v>chile</v>
       </c>
       <c r="E120" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -5822,7 +5861,7 @@
         <v>chile</v>
       </c>
       <c r="E121" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -5843,7 +5882,7 @@
         <v>chile</v>
       </c>
       <c r="E122" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -5864,7 +5903,7 @@
         <v>chile</v>
       </c>
       <c r="E123" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -5885,7 +5924,7 @@
         <v>colombia</v>
       </c>
       <c r="E124" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -5906,7 +5945,7 @@
         <v>colombia</v>
       </c>
       <c r="E125" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -5927,7 +5966,7 @@
         <v>colombia</v>
       </c>
       <c r="E126" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -5948,7 +5987,7 @@
         <v>colombia</v>
       </c>
       <c r="E127" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -5969,7 +6008,7 @@
         <v>colombia</v>
       </c>
       <c r="E128" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -5990,7 +6029,7 @@
         <v>colombia</v>
       </c>
       <c r="E129" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -6011,7 +6050,7 @@
         <v>colombia</v>
       </c>
       <c r="E130" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -6032,7 +6071,7 @@
         <v>colombia</v>
       </c>
       <c r="E131" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -6053,7 +6092,7 @@
         <v>colombia</v>
       </c>
       <c r="E132" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -6074,7 +6113,7 @@
         <v>colombia</v>
       </c>
       <c r="E133" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -6095,7 +6134,7 @@
         <v>colombia</v>
       </c>
       <c r="E134" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -6116,7 +6155,7 @@
         <v>colombia</v>
       </c>
       <c r="E135" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -6137,7 +6176,7 @@
         <v>colombia</v>
       </c>
       <c r="E136" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -6158,7 +6197,7 @@
         <v>colombia</v>
       </c>
       <c r="E137" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -6179,7 +6218,7 @@
         <v>colombia</v>
       </c>
       <c r="E138" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -6200,7 +6239,7 @@
         <v>colombia</v>
       </c>
       <c r="E139" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -6221,7 +6260,7 @@
         <v>colombia</v>
       </c>
       <c r="E140" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -6242,7 +6281,7 @@
         <v>colombia</v>
       </c>
       <c r="E141" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -6263,7 +6302,7 @@
         <v>colombia</v>
       </c>
       <c r="E142" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -6284,7 +6323,7 @@
         <v>colombia</v>
       </c>
       <c r="E143" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -6305,7 +6344,7 @@
         <v>croatia</v>
       </c>
       <c r="E144" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -6326,7 +6365,7 @@
         <v>croatia</v>
       </c>
       <c r="E145" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -6347,7 +6386,7 @@
         <v>croatia</v>
       </c>
       <c r="E146" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -6368,7 +6407,7 @@
         <v>croatia</v>
       </c>
       <c r="E147" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -6389,7 +6428,7 @@
         <v>croatia</v>
       </c>
       <c r="E148" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -6410,7 +6449,7 @@
         <v>croatia</v>
       </c>
       <c r="E149" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -6431,7 +6470,7 @@
         <v>croatia</v>
       </c>
       <c r="E150" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -6452,7 +6491,7 @@
         <v>croatia</v>
       </c>
       <c r="E151" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -6473,7 +6512,7 @@
         <v>croatia</v>
       </c>
       <c r="E152" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -6494,7 +6533,7 @@
         <v>croatia</v>
       </c>
       <c r="E153" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -6515,7 +6554,7 @@
         <v>czech-republic</v>
       </c>
       <c r="E154" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -6536,7 +6575,7 @@
         <v>czech-republic</v>
       </c>
       <c r="E155" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -6557,7 +6596,7 @@
         <v>czech-republic</v>
       </c>
       <c r="E156" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -6578,7 +6617,7 @@
         <v>czech-republic</v>
       </c>
       <c r="E157" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -6599,7 +6638,7 @@
         <v>czech-republic</v>
       </c>
       <c r="E158" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -6620,7 +6659,7 @@
         <v>czech-republic</v>
       </c>
       <c r="E159" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -6641,7 +6680,7 @@
         <v>czech-republic</v>
       </c>
       <c r="E160" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -6662,7 +6701,7 @@
         <v>czech-republic</v>
       </c>
       <c r="E161" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -6683,7 +6722,7 @@
         <v>czech-republic</v>
       </c>
       <c r="E162" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -6704,7 +6743,7 @@
         <v>czech-republic</v>
       </c>
       <c r="E163" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -6725,7 +6764,7 @@
         <v>czech-republic</v>
       </c>
       <c r="E164" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -6746,7 +6785,7 @@
         <v>czech-republic</v>
       </c>
       <c r="E165" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -6767,7 +6806,7 @@
         <v>czech-republic</v>
       </c>
       <c r="E166" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -6788,7 +6827,7 @@
         <v>czech-republic</v>
       </c>
       <c r="E167" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -6809,7 +6848,7 @@
         <v>czech-republic</v>
       </c>
       <c r="E168" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -6830,7 +6869,7 @@
         <v>czech-republic</v>
       </c>
       <c r="E169" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -6851,7 +6890,7 @@
         <v>denmark</v>
       </c>
       <c r="E170" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -6872,7 +6911,7 @@
         <v>denmark</v>
       </c>
       <c r="E171" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -6893,7 +6932,7 @@
         <v>denmark</v>
       </c>
       <c r="E172" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -6914,7 +6953,7 @@
         <v>denmark</v>
       </c>
       <c r="E173" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -6935,7 +6974,7 @@
         <v>denmark</v>
       </c>
       <c r="E174" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -6956,7 +6995,7 @@
         <v>denmark</v>
       </c>
       <c r="E175" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -6977,7 +7016,7 @@
         <v>denmark</v>
       </c>
       <c r="E176" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -6998,7 +7037,7 @@
         <v>denmark</v>
       </c>
       <c r="E177" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -7019,7 +7058,7 @@
         <v>denmark</v>
       </c>
       <c r="E178" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -7040,7 +7079,7 @@
         <v>denmark</v>
       </c>
       <c r="E179" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -7061,7 +7100,7 @@
         <v>denmark</v>
       </c>
       <c r="E180" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -7082,7 +7121,7 @@
         <v>denmark</v>
       </c>
       <c r="E181" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -7103,7 +7142,7 @@
         <v>ecuador</v>
       </c>
       <c r="E182" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -7124,7 +7163,7 @@
         <v>ecuador</v>
       </c>
       <c r="E183" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -7145,7 +7184,7 @@
         <v>ecuador</v>
       </c>
       <c r="E184" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -7166,7 +7205,7 @@
         <v>ecuador</v>
       </c>
       <c r="E185" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -7187,7 +7226,7 @@
         <v>ecuador</v>
       </c>
       <c r="E186" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -7208,7 +7247,7 @@
         <v>ecuador</v>
       </c>
       <c r="E187" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -7229,7 +7268,7 @@
         <v>ecuador</v>
       </c>
       <c r="E188" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -7250,7 +7289,7 @@
         <v>ecuador</v>
       </c>
       <c r="E189" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -7271,7 +7310,7 @@
         <v>ecuador</v>
       </c>
       <c r="E190" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -7292,7 +7331,7 @@
         <v>ecuador</v>
       </c>
       <c r="E191" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -7313,7 +7352,7 @@
         <v>ecuador</v>
       </c>
       <c r="E192" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -7334,7 +7373,7 @@
         <v>ecuador</v>
       </c>
       <c r="E193" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -7355,7 +7394,7 @@
         <v>ecuador</v>
       </c>
       <c r="E194" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -7376,7 +7415,7 @@
         <v>ecuador</v>
       </c>
       <c r="E195" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -7397,7 +7436,7 @@
         <v>ecuador</v>
       </c>
       <c r="E196" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -7418,7 +7457,7 @@
         <v>ecuador</v>
       </c>
       <c r="E197" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -7439,7 +7478,7 @@
         <v>england</v>
       </c>
       <c r="E198" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -7460,7 +7499,7 @@
         <v>england</v>
       </c>
       <c r="E199" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -7481,7 +7520,7 @@
         <v>england</v>
       </c>
       <c r="E200" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -7502,7 +7541,7 @@
         <v>england</v>
       </c>
       <c r="E201" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -7523,7 +7562,7 @@
         <v>england</v>
       </c>
       <c r="E202" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -7544,7 +7583,7 @@
         <v>england</v>
       </c>
       <c r="E203" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -7565,7 +7604,7 @@
         <v>england</v>
       </c>
       <c r="E204" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -7586,7 +7625,7 @@
         <v>england</v>
       </c>
       <c r="E205" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -7607,7 +7646,7 @@
         <v>england</v>
       </c>
       <c r="E206" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -7628,7 +7667,7 @@
         <v>england</v>
       </c>
       <c r="E207" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -7649,7 +7688,7 @@
         <v>england</v>
       </c>
       <c r="E208" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -7670,7 +7709,7 @@
         <v>england</v>
       </c>
       <c r="E209" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -7691,7 +7730,7 @@
         <v>england</v>
       </c>
       <c r="E210" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -7712,7 +7751,7 @@
         <v>england</v>
       </c>
       <c r="E211" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -7733,7 +7772,7 @@
         <v>england</v>
       </c>
       <c r="E212" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -7754,7 +7793,7 @@
         <v>england</v>
       </c>
       <c r="E213" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -7775,7 +7814,7 @@
         <v>england</v>
       </c>
       <c r="E214" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -7796,7 +7835,7 @@
         <v>england</v>
       </c>
       <c r="E215" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -7817,7 +7856,7 @@
         <v>england</v>
       </c>
       <c r="E216" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -7838,7 +7877,7 @@
         <v>england</v>
       </c>
       <c r="E217" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -7858,7 +7897,7 @@
         <v>573</v>
       </c>
       <c r="E218" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -7878,7 +7917,7 @@
         <v>573</v>
       </c>
       <c r="E219" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -7898,7 +7937,7 @@
         <v>573</v>
       </c>
       <c r="E220" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -7918,7 +7957,7 @@
         <v>573</v>
       </c>
       <c r="E221" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -7938,7 +7977,7 @@
         <v>573</v>
       </c>
       <c r="E222" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -7958,7 +7997,7 @@
         <v>573</v>
       </c>
       <c r="E223" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -7978,7 +8017,7 @@
         <v>573</v>
       </c>
       <c r="E224" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -7998,7 +8037,7 @@
         <v>573</v>
       </c>
       <c r="E225" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -8018,7 +8057,7 @@
         <v>573</v>
       </c>
       <c r="E226" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -8038,7 +8077,7 @@
         <v>573</v>
       </c>
       <c r="E227" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -8058,7 +8097,7 @@
         <v>573</v>
       </c>
       <c r="E228" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -8078,7 +8117,7 @@
         <v>573</v>
       </c>
       <c r="E229" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -8098,7 +8137,7 @@
         <v>573</v>
       </c>
       <c r="E230" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -8118,7 +8157,7 @@
         <v>573</v>
       </c>
       <c r="E231" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -8138,7 +8177,7 @@
         <v>573</v>
       </c>
       <c r="E232" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -8158,7 +8197,7 @@
         <v>573</v>
       </c>
       <c r="E233" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -8178,7 +8217,7 @@
         <v>573</v>
       </c>
       <c r="E234" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -8198,7 +8237,7 @@
         <v>573</v>
       </c>
       <c r="E235" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -8218,7 +8257,7 @@
         <v>573</v>
       </c>
       <c r="E236" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -8238,7 +8277,7 @@
         <v>573</v>
       </c>
       <c r="E237" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -8258,7 +8297,7 @@
         <v>573</v>
       </c>
       <c r="E238" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -8278,7 +8317,7 @@
         <v>573</v>
       </c>
       <c r="E239" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -8298,7 +8337,7 @@
         <v>573</v>
       </c>
       <c r="E240" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -8318,7 +8357,7 @@
         <v>573</v>
       </c>
       <c r="E241" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -8339,7 +8378,7 @@
         <v>finland</v>
       </c>
       <c r="E242" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -8360,7 +8399,7 @@
         <v>finland</v>
       </c>
       <c r="E243" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -8381,7 +8420,7 @@
         <v>finland</v>
       </c>
       <c r="E244" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -8402,7 +8441,7 @@
         <v>finland</v>
       </c>
       <c r="E245" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -8423,7 +8462,7 @@
         <v>finland</v>
       </c>
       <c r="E246" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -8444,7 +8483,7 @@
         <v>finland</v>
       </c>
       <c r="E247" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -8465,7 +8504,7 @@
         <v>finland</v>
       </c>
       <c r="E248" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -8486,7 +8525,7 @@
         <v>finland</v>
       </c>
       <c r="E249" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -8507,7 +8546,7 @@
         <v>finland</v>
       </c>
       <c r="E250" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -8528,7 +8567,7 @@
         <v>finland</v>
       </c>
       <c r="E251" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -8549,7 +8588,7 @@
         <v>finland</v>
       </c>
       <c r="E252" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -8570,7 +8609,7 @@
         <v>finland</v>
       </c>
       <c r="E253" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -8591,7 +8630,7 @@
         <v>france</v>
       </c>
       <c r="E254" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -8612,7 +8651,7 @@
         <v>france</v>
       </c>
       <c r="E255" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -8633,7 +8672,7 @@
         <v>france</v>
       </c>
       <c r="E256" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -8654,7 +8693,7 @@
         <v>france</v>
       </c>
       <c r="E257" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -8675,7 +8714,7 @@
         <v>france</v>
       </c>
       <c r="E258" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -8696,7 +8735,7 @@
         <v>france</v>
       </c>
       <c r="E259" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -8717,7 +8756,7 @@
         <v>france</v>
       </c>
       <c r="E260" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -8738,7 +8777,7 @@
         <v>france</v>
       </c>
       <c r="E261" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -8759,7 +8798,7 @@
         <v>france</v>
       </c>
       <c r="E262" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -8780,7 +8819,7 @@
         <v>france</v>
       </c>
       <c r="E263" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -8801,7 +8840,7 @@
         <v>france</v>
       </c>
       <c r="E264" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -8822,7 +8861,7 @@
         <v>france</v>
       </c>
       <c r="E265" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -8843,7 +8882,7 @@
         <v>france</v>
       </c>
       <c r="E266" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -8864,7 +8903,7 @@
         <v>france</v>
       </c>
       <c r="E267" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -8885,7 +8924,7 @@
         <v>france</v>
       </c>
       <c r="E268" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -8906,7 +8945,7 @@
         <v>france</v>
       </c>
       <c r="E269" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -8927,7 +8966,7 @@
         <v>france</v>
       </c>
       <c r="E270" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -8948,7 +8987,7 @@
         <v>france</v>
       </c>
       <c r="E271" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -8969,7 +9008,7 @@
         <v>germany</v>
       </c>
       <c r="E272" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -8990,7 +9029,7 @@
         <v>germany</v>
       </c>
       <c r="E273" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -9011,7 +9050,7 @@
         <v>germany</v>
       </c>
       <c r="E274" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -9032,7 +9071,7 @@
         <v>germany</v>
       </c>
       <c r="E275" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -9053,7 +9092,7 @@
         <v>germany</v>
       </c>
       <c r="E276" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -9074,7 +9113,7 @@
         <v>germany</v>
       </c>
       <c r="E277" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -9095,7 +9134,7 @@
         <v>germany</v>
       </c>
       <c r="E278" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -9116,7 +9155,7 @@
         <v>germany</v>
       </c>
       <c r="E279" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -9137,7 +9176,7 @@
         <v>germany</v>
       </c>
       <c r="E280" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -9158,7 +9197,7 @@
         <v>germany</v>
       </c>
       <c r="E281" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -9179,7 +9218,7 @@
         <v>germany</v>
       </c>
       <c r="E282" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -9200,7 +9239,7 @@
         <v>germany</v>
       </c>
       <c r="E283" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -9221,7 +9260,7 @@
         <v>germany</v>
       </c>
       <c r="E284" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -9242,7 +9281,7 @@
         <v>germany</v>
       </c>
       <c r="E285" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -9263,7 +9302,7 @@
         <v>germany</v>
       </c>
       <c r="E286" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -9284,7 +9323,7 @@
         <v>germany</v>
       </c>
       <c r="E287" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -9305,7 +9344,7 @@
         <v>germany</v>
       </c>
       <c r="E288" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -9326,7 +9365,7 @@
         <v>germany</v>
       </c>
       <c r="E289" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -9346,7 +9385,7 @@
         <v>730</v>
       </c>
       <c r="E290" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -9366,7 +9405,7 @@
         <v>730</v>
       </c>
       <c r="E291" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -9386,7 +9425,7 @@
         <v>730</v>
       </c>
       <c r="E292" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -9406,7 +9445,7 @@
         <v>730</v>
       </c>
       <c r="E293" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -9426,7 +9465,7 @@
         <v>730</v>
       </c>
       <c r="E294" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -9446,7 +9485,7 @@
         <v>730</v>
       </c>
       <c r="E295" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -9466,7 +9505,7 @@
         <v>730</v>
       </c>
       <c r="E296" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -9486,7 +9525,7 @@
         <v>730</v>
       </c>
       <c r="E297" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -9506,7 +9545,7 @@
         <v>730</v>
       </c>
       <c r="E298" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -9526,7 +9565,7 @@
         <v>730</v>
       </c>
       <c r="E299" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -9546,7 +9585,7 @@
         <v>730</v>
       </c>
       <c r="E300" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -9566,7 +9605,7 @@
         <v>730</v>
       </c>
       <c r="E301" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -9586,7 +9625,7 @@
         <v>730</v>
       </c>
       <c r="E302" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -9606,7 +9645,7 @@
         <v>730</v>
       </c>
       <c r="E303" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -9626,7 +9665,7 @@
         <v>730</v>
       </c>
       <c r="E304" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -9646,7 +9685,7 @@
         <v>730</v>
       </c>
       <c r="E305" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -9666,7 +9705,7 @@
         <v>730</v>
       </c>
       <c r="E306" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -9686,7 +9725,7 @@
         <v>730</v>
       </c>
       <c r="E307" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -9707,7 +9746,7 @@
         <v>greece</v>
       </c>
       <c r="E308" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -9728,7 +9767,7 @@
         <v>greece</v>
       </c>
       <c r="E309" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -9749,7 +9788,7 @@
         <v>greece</v>
       </c>
       <c r="E310" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -9770,7 +9809,7 @@
         <v>greece</v>
       </c>
       <c r="E311" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -9791,7 +9830,7 @@
         <v>greece</v>
       </c>
       <c r="E312" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -9812,7 +9851,7 @@
         <v>greece</v>
       </c>
       <c r="E313" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -9833,7 +9872,7 @@
         <v>greece</v>
       </c>
       <c r="E314" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -9854,7 +9893,7 @@
         <v>greece</v>
       </c>
       <c r="E315" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -9875,7 +9914,7 @@
         <v>greece</v>
       </c>
       <c r="E316" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -9896,7 +9935,7 @@
         <v>greece</v>
       </c>
       <c r="E317" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -9917,7 +9956,7 @@
         <v>greece</v>
       </c>
       <c r="E318" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -9938,7 +9977,7 @@
         <v>greece</v>
       </c>
       <c r="E319" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -9959,7 +9998,7 @@
         <v>greece</v>
       </c>
       <c r="E320" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -9980,7 +10019,7 @@
         <v>greece</v>
       </c>
       <c r="E321" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -10001,7 +10040,7 @@
         <v>italy</v>
       </c>
       <c r="E322" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -10022,7 +10061,7 @@
         <v>italy</v>
       </c>
       <c r="E323" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -10043,7 +10082,7 @@
         <v>italy</v>
       </c>
       <c r="E324" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -10064,7 +10103,7 @@
         <v>italy</v>
       </c>
       <c r="E325" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -10085,7 +10124,7 @@
         <v>italy</v>
       </c>
       <c r="E326" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -10106,7 +10145,7 @@
         <v>italy</v>
       </c>
       <c r="E327" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -10127,7 +10166,7 @@
         <v>italy</v>
       </c>
       <c r="E328" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -10148,7 +10187,7 @@
         <v>italy</v>
       </c>
       <c r="E329" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -10169,7 +10208,7 @@
         <v>italy</v>
       </c>
       <c r="E330" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -10190,7 +10229,7 @@
         <v>italy</v>
       </c>
       <c r="E331" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -10211,7 +10250,7 @@
         <v>italy</v>
       </c>
       <c r="E332" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -10232,7 +10271,7 @@
         <v>italy</v>
       </c>
       <c r="E333" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -10253,7 +10292,7 @@
         <v>italy</v>
       </c>
       <c r="E334" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -10274,7 +10313,7 @@
         <v>italy</v>
       </c>
       <c r="E335" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -10295,7 +10334,7 @@
         <v>italy</v>
       </c>
       <c r="E336" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -10316,7 +10355,7 @@
         <v>italy</v>
       </c>
       <c r="E337" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -10337,7 +10376,7 @@
         <v>italy</v>
       </c>
       <c r="E338" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -10358,7 +10397,7 @@
         <v>italy</v>
       </c>
       <c r="E339" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -10379,7 +10418,7 @@
         <v>italy</v>
       </c>
       <c r="E340" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -10400,7 +10439,7 @@
         <v>italy</v>
       </c>
       <c r="E341" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -10421,7 +10460,7 @@
         <v>mexico</v>
       </c>
       <c r="E342" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -10442,7 +10481,7 @@
         <v>mexico</v>
       </c>
       <c r="E343" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -10463,7 +10502,7 @@
         <v>mexico</v>
       </c>
       <c r="E344" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -10484,7 +10523,7 @@
         <v>mexico</v>
       </c>
       <c r="E345" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -10505,7 +10544,7 @@
         <v>mexico</v>
       </c>
       <c r="E346" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -10526,7 +10565,7 @@
         <v>mexico</v>
       </c>
       <c r="E347" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -10547,7 +10586,7 @@
         <v>mexico</v>
       </c>
       <c r="E348" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -10568,7 +10607,7 @@
         <v>mexico</v>
       </c>
       <c r="E349" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -10589,7 +10628,7 @@
         <v>mexico</v>
       </c>
       <c r="E350" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -10610,7 +10649,7 @@
         <v>mexico</v>
       </c>
       <c r="E351" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -10631,7 +10670,7 @@
         <v>mexico</v>
       </c>
       <c r="E352" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -10652,7 +10691,7 @@
         <v>mexico</v>
       </c>
       <c r="E353" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -10673,7 +10712,7 @@
         <v>mexico</v>
       </c>
       <c r="E354" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -10694,7 +10733,7 @@
         <v>mexico</v>
       </c>
       <c r="E355" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -10715,7 +10754,7 @@
         <v>mexico</v>
       </c>
       <c r="E356" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -10736,7 +10775,7 @@
         <v>mexico</v>
       </c>
       <c r="E357" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -10757,7 +10796,7 @@
         <v>mexico</v>
       </c>
       <c r="E358" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -10778,7 +10817,7 @@
         <v>mexico</v>
       </c>
       <c r="E359" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -10799,7 +10838,7 @@
         <v>netherlands</v>
       </c>
       <c r="E360" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -10820,7 +10859,7 @@
         <v>netherlands</v>
       </c>
       <c r="E361" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -10841,7 +10880,7 @@
         <v>netherlands</v>
       </c>
       <c r="E362" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -10862,7 +10901,7 @@
         <v>netherlands</v>
       </c>
       <c r="E363" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -10883,7 +10922,7 @@
         <v>netherlands</v>
       </c>
       <c r="E364" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -10904,7 +10943,7 @@
         <v>netherlands</v>
       </c>
       <c r="E365" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -10925,7 +10964,7 @@
         <v>netherlands</v>
       </c>
       <c r="E366" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -10946,7 +10985,7 @@
         <v>netherlands</v>
       </c>
       <c r="E367" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -10967,7 +11006,7 @@
         <v>netherlands</v>
       </c>
       <c r="E368" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -10988,7 +11027,7 @@
         <v>netherlands</v>
       </c>
       <c r="E369" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -11009,7 +11048,7 @@
         <v>netherlands</v>
       </c>
       <c r="E370" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -11030,7 +11069,7 @@
         <v>netherlands</v>
       </c>
       <c r="E371" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -11051,7 +11090,7 @@
         <v>netherlands</v>
       </c>
       <c r="E372" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -11072,7 +11111,7 @@
         <v>netherlands</v>
       </c>
       <c r="E373" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -11093,7 +11132,7 @@
         <v>netherlands</v>
       </c>
       <c r="E374" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -11114,7 +11153,7 @@
         <v>netherlands</v>
       </c>
       <c r="E375" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -11135,7 +11174,7 @@
         <v>netherlands</v>
       </c>
       <c r="E376" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -11156,7 +11195,7 @@
         <v>netherlands</v>
       </c>
       <c r="E377" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -11177,7 +11216,7 @@
         <v>norway</v>
       </c>
       <c r="E378" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -11198,7 +11237,7 @@
         <v>norway</v>
       </c>
       <c r="E379" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -11219,7 +11258,7 @@
         <v>norway</v>
       </c>
       <c r="E380" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -11240,7 +11279,7 @@
         <v>norway</v>
       </c>
       <c r="E381" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -11261,7 +11300,7 @@
         <v>norway</v>
       </c>
       <c r="E382" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -11282,7 +11321,7 @@
         <v>norway</v>
       </c>
       <c r="E383" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -11303,7 +11342,7 @@
         <v>norway</v>
       </c>
       <c r="E384" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -11324,7 +11363,7 @@
         <v>norway</v>
       </c>
       <c r="E385" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -11345,7 +11384,7 @@
         <v>norway</v>
       </c>
       <c r="E386" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -11366,7 +11405,7 @@
         <v>norway</v>
       </c>
       <c r="E387" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -11387,7 +11426,7 @@
         <v>norway</v>
       </c>
       <c r="E388" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -11408,7 +11447,7 @@
         <v>norway</v>
       </c>
       <c r="E389" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -11429,7 +11468,7 @@
         <v>norway</v>
       </c>
       <c r="E390" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -11450,7 +11489,7 @@
         <v>norway</v>
       </c>
       <c r="E391" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -11471,7 +11510,7 @@
         <v>norway</v>
       </c>
       <c r="E392" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -11492,7 +11531,7 @@
         <v>norway</v>
       </c>
       <c r="E393" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -11513,7 +11552,7 @@
         <v>peru</v>
       </c>
       <c r="E394" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -11534,7 +11573,7 @@
         <v>peru</v>
       </c>
       <c r="E395" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -11555,7 +11594,7 @@
         <v>peru</v>
       </c>
       <c r="E396" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -11576,7 +11615,7 @@
         <v>peru</v>
       </c>
       <c r="E397" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -11597,7 +11636,7 @@
         <v>peru</v>
       </c>
       <c r="E398" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -11618,7 +11657,7 @@
         <v>peru</v>
       </c>
       <c r="E399" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -11639,7 +11678,7 @@
         <v>peru</v>
       </c>
       <c r="E400" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -11660,7 +11699,7 @@
         <v>peru</v>
       </c>
       <c r="E401" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -11681,7 +11720,7 @@
         <v>peru</v>
       </c>
       <c r="E402" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -11702,7 +11741,7 @@
         <v>peru</v>
       </c>
       <c r="E403" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -11723,7 +11762,7 @@
         <v>peru</v>
       </c>
       <c r="E404" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -11744,7 +11783,7 @@
         <v>peru</v>
       </c>
       <c r="E405" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -11765,7 +11804,7 @@
         <v>peru</v>
       </c>
       <c r="E406" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -11786,7 +11825,7 @@
         <v>peru</v>
       </c>
       <c r="E407" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -11807,7 +11846,7 @@
         <v>peru</v>
       </c>
       <c r="E408" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -11828,7 +11867,7 @@
         <v>peru</v>
       </c>
       <c r="E409" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -11849,7 +11888,7 @@
         <v>peru</v>
       </c>
       <c r="E410" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -11870,7 +11909,7 @@
         <v>peru</v>
       </c>
       <c r="E411" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -11891,7 +11930,7 @@
         <v>poland</v>
       </c>
       <c r="E412" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -11912,7 +11951,7 @@
         <v>poland</v>
       </c>
       <c r="E413" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -11933,7 +11972,7 @@
         <v>poland</v>
       </c>
       <c r="E414" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -11954,7 +11993,7 @@
         <v>poland</v>
       </c>
       <c r="E415" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -11975,7 +12014,7 @@
         <v>poland</v>
       </c>
       <c r="E416" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -11996,7 +12035,7 @@
         <v>poland</v>
       </c>
       <c r="E417" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -12017,7 +12056,7 @@
         <v>poland</v>
       </c>
       <c r="E418" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -12038,7 +12077,7 @@
         <v>poland</v>
       </c>
       <c r="E419" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -12059,7 +12098,7 @@
         <v>poland</v>
       </c>
       <c r="E420" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -12080,7 +12119,7 @@
         <v>poland</v>
       </c>
       <c r="E421" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -12101,7 +12140,7 @@
         <v>poland</v>
       </c>
       <c r="E422" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -12122,7 +12161,7 @@
         <v>poland</v>
       </c>
       <c r="E423" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -12143,7 +12182,7 @@
         <v>poland</v>
       </c>
       <c r="E424" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -12164,7 +12203,7 @@
         <v>poland</v>
       </c>
       <c r="E425" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -12185,7 +12224,7 @@
         <v>poland</v>
       </c>
       <c r="E426" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -12206,7 +12245,7 @@
         <v>poland</v>
       </c>
       <c r="E427" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -12227,7 +12266,7 @@
         <v>poland</v>
       </c>
       <c r="E428" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -12248,7 +12287,7 @@
         <v>poland</v>
       </c>
       <c r="E429" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -12269,7 +12308,7 @@
         <v>portugal</v>
       </c>
       <c r="E430" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -12290,7 +12329,7 @@
         <v>portugal</v>
       </c>
       <c r="E431" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -12311,7 +12350,7 @@
         <v>portugal</v>
       </c>
       <c r="E432" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -12332,7 +12371,7 @@
         <v>portugal</v>
       </c>
       <c r="E433" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -12353,7 +12392,7 @@
         <v>portugal</v>
       </c>
       <c r="E434" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -12374,7 +12413,7 @@
         <v>portugal</v>
       </c>
       <c r="E435" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -12395,7 +12434,7 @@
         <v>portugal</v>
       </c>
       <c r="E436" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -12416,7 +12455,7 @@
         <v>portugal</v>
       </c>
       <c r="E437" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -12437,7 +12476,7 @@
         <v>portugal</v>
       </c>
       <c r="E438" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -12458,7 +12497,7 @@
         <v>portugal</v>
       </c>
       <c r="E439" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -12479,7 +12518,7 @@
         <v>portugal</v>
       </c>
       <c r="E440" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -12500,7 +12539,7 @@
         <v>portugal</v>
       </c>
       <c r="E441" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -12521,7 +12560,7 @@
         <v>portugal</v>
       </c>
       <c r="E442" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -12542,7 +12581,7 @@
         <v>portugal</v>
       </c>
       <c r="E443" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -12563,7 +12602,7 @@
         <v>portugal</v>
       </c>
       <c r="E444" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -12584,7 +12623,7 @@
         <v>portugal</v>
       </c>
       <c r="E445" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -12605,7 +12644,7 @@
         <v>portugal</v>
       </c>
       <c r="E446" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -12626,7 +12665,7 @@
         <v>portugal</v>
       </c>
       <c r="E447" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -12647,7 +12686,7 @@
         <v>romania</v>
       </c>
       <c r="E448" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -12668,7 +12707,7 @@
         <v>romania</v>
       </c>
       <c r="E449" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -12689,7 +12728,7 @@
         <v>romania</v>
       </c>
       <c r="E450" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -12710,7 +12749,7 @@
         <v>romania</v>
       </c>
       <c r="E451" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -12731,7 +12770,7 @@
         <v>romania</v>
       </c>
       <c r="E452" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -12752,7 +12791,7 @@
         <v>romania</v>
       </c>
       <c r="E453" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -12773,7 +12812,7 @@
         <v>romania</v>
       </c>
       <c r="E454" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -12794,7 +12833,7 @@
         <v>romania</v>
       </c>
       <c r="E455" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -12815,7 +12854,7 @@
         <v>romania</v>
       </c>
       <c r="E456" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -12836,7 +12875,7 @@
         <v>romania</v>
       </c>
       <c r="E457" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -12857,7 +12896,7 @@
         <v>romania</v>
       </c>
       <c r="E458" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -12878,7 +12917,7 @@
         <v>romania</v>
       </c>
       <c r="E459" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -12899,7 +12938,7 @@
         <v>romania</v>
       </c>
       <c r="E460" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -12920,7 +12959,7 @@
         <v>romania</v>
       </c>
       <c r="E461" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -12941,7 +12980,7 @@
         <v>romania</v>
       </c>
       <c r="E462" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -12962,7 +13001,7 @@
         <v>romania</v>
       </c>
       <c r="E463" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -12983,7 +13022,7 @@
         <v>saudi-arabia</v>
       </c>
       <c r="E464" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -13004,7 +13043,7 @@
         <v>saudi-arabia</v>
       </c>
       <c r="E465" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -13025,7 +13064,7 @@
         <v>saudi-arabia</v>
       </c>
       <c r="E466" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -13046,7 +13085,7 @@
         <v>saudi-arabia</v>
       </c>
       <c r="E467" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -13067,7 +13106,7 @@
         <v>saudi-arabia</v>
       </c>
       <c r="E468" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -13088,7 +13127,7 @@
         <v>saudi-arabia</v>
       </c>
       <c r="E469" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -13109,7 +13148,7 @@
         <v>saudi-arabia</v>
       </c>
       <c r="E470" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -13130,7 +13169,7 @@
         <v>saudi-arabia</v>
       </c>
       <c r="E471" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -13151,7 +13190,7 @@
         <v>saudi-arabia</v>
       </c>
       <c r="E472" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -13172,7 +13211,7 @@
         <v>saudi-arabia</v>
       </c>
       <c r="E473" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -13193,7 +13232,7 @@
         <v>saudi-arabia</v>
       </c>
       <c r="E474" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -13214,7 +13253,7 @@
         <v>saudi-arabia</v>
       </c>
       <c r="E475" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -13235,7 +13274,7 @@
         <v>saudi-arabia</v>
       </c>
       <c r="E476" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -13256,7 +13295,7 @@
         <v>saudi-arabia</v>
       </c>
       <c r="E477" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -13277,7 +13316,7 @@
         <v>saudi-arabia</v>
       </c>
       <c r="E478" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -13298,7 +13337,7 @@
         <v>saudi-arabia</v>
       </c>
       <c r="E479" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -13319,7 +13358,7 @@
         <v>saudi-arabia</v>
       </c>
       <c r="E480" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -13340,7 +13379,7 @@
         <v>saudi-arabia</v>
       </c>
       <c r="E481" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -13361,7 +13400,7 @@
         <v>scotland</v>
       </c>
       <c r="E482" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -13382,7 +13421,7 @@
         <v>scotland</v>
       </c>
       <c r="E483" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -13403,7 +13442,7 @@
         <v>scotland</v>
       </c>
       <c r="E484" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -13424,7 +13463,7 @@
         <v>scotland</v>
       </c>
       <c r="E485" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -13445,7 +13484,7 @@
         <v>scotland</v>
       </c>
       <c r="E486" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -13466,7 +13505,7 @@
         <v>scotland</v>
       </c>
       <c r="E487" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -13487,7 +13526,7 @@
         <v>scotland</v>
       </c>
       <c r="E488" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -13508,7 +13547,7 @@
         <v>scotland</v>
       </c>
       <c r="E489" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -13529,7 +13568,7 @@
         <v>scotland</v>
       </c>
       <c r="E490" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -13550,7 +13589,7 @@
         <v>scotland</v>
       </c>
       <c r="E491" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -13571,7 +13610,7 @@
         <v>scotland</v>
       </c>
       <c r="E492" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -13592,7 +13631,7 @@
         <v>scotland</v>
       </c>
       <c r="E493" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -13613,7 +13652,7 @@
         <v>spain</v>
       </c>
       <c r="E494" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -13634,7 +13673,7 @@
         <v>spain</v>
       </c>
       <c r="E495" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -13655,7 +13694,7 @@
         <v>spain</v>
       </c>
       <c r="E496" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -13676,7 +13715,7 @@
         <v>spain</v>
       </c>
       <c r="E497" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -13697,7 +13736,7 @@
         <v>spain</v>
       </c>
       <c r="E498" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -13718,7 +13757,7 @@
         <v>spain</v>
       </c>
       <c r="E499" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -13739,7 +13778,7 @@
         <v>spain</v>
       </c>
       <c r="E500" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -13760,7 +13799,7 @@
         <v>spain</v>
       </c>
       <c r="E501" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -13781,7 +13820,7 @@
         <v>spain</v>
       </c>
       <c r="E502" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -13802,7 +13841,7 @@
         <v>spain</v>
       </c>
       <c r="E503" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -13823,7 +13862,7 @@
         <v>spain</v>
       </c>
       <c r="E504" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -13844,7 +13883,7 @@
         <v>spain</v>
       </c>
       <c r="E505" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -13865,7 +13904,7 @@
         <v>spain</v>
       </c>
       <c r="E506" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -13886,7 +13925,7 @@
         <v>spain</v>
       </c>
       <c r="E507" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -13907,7 +13946,7 @@
         <v>spain</v>
       </c>
       <c r="E508" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -13928,7 +13967,7 @@
         <v>spain</v>
       </c>
       <c r="E509" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -13949,7 +13988,7 @@
         <v>spain</v>
       </c>
       <c r="E510" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -13970,7 +14009,7 @@
         <v>spain</v>
       </c>
       <c r="E511" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -13991,7 +14030,7 @@
         <v>spain</v>
       </c>
       <c r="E512" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -14012,7 +14051,7 @@
         <v>spain</v>
       </c>
       <c r="E513" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -14032,7 +14071,7 @@
         <v>574</v>
       </c>
       <c r="E514" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -14052,7 +14091,7 @@
         <v>574</v>
       </c>
       <c r="E515" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -14072,7 +14111,7 @@
         <v>574</v>
       </c>
       <c r="E516" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -14092,7 +14131,7 @@
         <v>574</v>
       </c>
       <c r="E517" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -14112,7 +14151,7 @@
         <v>574</v>
       </c>
       <c r="E518" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -14132,7 +14171,7 @@
         <v>574</v>
       </c>
       <c r="E519" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -14152,7 +14191,7 @@
         <v>574</v>
       </c>
       <c r="E520" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -14172,7 +14211,7 @@
         <v>574</v>
       </c>
       <c r="E521" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -14192,7 +14231,7 @@
         <v>574</v>
       </c>
       <c r="E522" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -14212,7 +14251,7 @@
         <v>574</v>
       </c>
       <c r="E523" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -14232,7 +14271,7 @@
         <v>574</v>
       </c>
       <c r="E524" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -14252,7 +14291,7 @@
         <v>574</v>
       </c>
       <c r="E525" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -14272,7 +14311,7 @@
         <v>574</v>
       </c>
       <c r="E526" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -14292,7 +14331,7 @@
         <v>574</v>
       </c>
       <c r="E527" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -14312,7 +14351,7 @@
         <v>574</v>
       </c>
       <c r="E528" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -14332,7 +14371,7 @@
         <v>574</v>
       </c>
       <c r="E529" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -14352,7 +14391,7 @@
         <v>574</v>
       </c>
       <c r="E530" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -14372,7 +14411,7 @@
         <v>574</v>
       </c>
       <c r="E531" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -14392,7 +14431,7 @@
         <v>574</v>
       </c>
       <c r="E532" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -14412,7 +14451,7 @@
         <v>574</v>
       </c>
       <c r="E533" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -14432,7 +14471,7 @@
         <v>574</v>
       </c>
       <c r="E534" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -14452,7 +14491,7 @@
         <v>574</v>
       </c>
       <c r="E535" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -14473,7 +14512,7 @@
         <v>sweden</v>
       </c>
       <c r="E536" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -14494,7 +14533,7 @@
         <v>sweden</v>
       </c>
       <c r="E537" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -14515,7 +14554,7 @@
         <v>sweden</v>
       </c>
       <c r="E538" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -14536,7 +14575,7 @@
         <v>sweden</v>
       </c>
       <c r="E539" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -14557,7 +14596,7 @@
         <v>sweden</v>
       </c>
       <c r="E540" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -14578,7 +14617,7 @@
         <v>sweden</v>
       </c>
       <c r="E541" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -14599,7 +14638,7 @@
         <v>sweden</v>
       </c>
       <c r="E542" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -14620,7 +14659,7 @@
         <v>sweden</v>
       </c>
       <c r="E543" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -14641,7 +14680,7 @@
         <v>sweden</v>
       </c>
       <c r="E544" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -14662,7 +14701,7 @@
         <v>sweden</v>
       </c>
       <c r="E545" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -14683,7 +14722,7 @@
         <v>sweden</v>
       </c>
       <c r="E546" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -14704,7 +14743,7 @@
         <v>sweden</v>
       </c>
       <c r="E547" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -14725,7 +14764,7 @@
         <v>sweden</v>
       </c>
       <c r="E548" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -14746,7 +14785,7 @@
         <v>sweden</v>
       </c>
       <c r="E549" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -14767,7 +14806,7 @@
         <v>sweden</v>
       </c>
       <c r="E550" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -14788,7 +14827,7 @@
         <v>sweden</v>
       </c>
       <c r="E551" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -14809,7 +14848,7 @@
         <v>switzerland</v>
       </c>
       <c r="E552" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -14830,7 +14869,7 @@
         <v>switzerland</v>
       </c>
       <c r="E553" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -14851,7 +14890,7 @@
         <v>switzerland</v>
       </c>
       <c r="E554" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -14872,7 +14911,7 @@
         <v>switzerland</v>
       </c>
       <c r="E555" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -14893,7 +14932,7 @@
         <v>switzerland</v>
       </c>
       <c r="E556" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -14914,7 +14953,7 @@
         <v>switzerland</v>
       </c>
       <c r="E557" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -14935,7 +14974,7 @@
         <v>switzerland</v>
       </c>
       <c r="E558" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -14956,7 +14995,7 @@
         <v>switzerland</v>
       </c>
       <c r="E559" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -14977,7 +15016,7 @@
         <v>switzerland</v>
       </c>
       <c r="E560" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -14998,7 +15037,7 @@
         <v>switzerland</v>
       </c>
       <c r="E561" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -15019,7 +15058,7 @@
         <v>switzerland</v>
       </c>
       <c r="E562" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -15040,7 +15079,7 @@
         <v>switzerland</v>
       </c>
       <c r="E563" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -15061,7 +15100,7 @@
         <v>usa</v>
       </c>
       <c r="E564" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -15082,7 +15121,7 @@
         <v>usa</v>
       </c>
       <c r="E565" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -15103,7 +15142,7 @@
         <v>usa</v>
       </c>
       <c r="E566" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -15124,7 +15163,7 @@
         <v>usa</v>
       </c>
       <c r="E567" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -15145,7 +15184,7 @@
         <v>usa</v>
       </c>
       <c r="E568" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -15166,7 +15205,7 @@
         <v>usa</v>
       </c>
       <c r="E569" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -15187,7 +15226,7 @@
         <v>usa</v>
       </c>
       <c r="E570" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -15208,7 +15247,7 @@
         <v>usa</v>
       </c>
       <c r="E571" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -15229,7 +15268,7 @@
         <v>usa</v>
       </c>
       <c r="E572" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -15250,7 +15289,7 @@
         <v>usa</v>
       </c>
       <c r="E573" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -15271,7 +15310,7 @@
         <v>usa</v>
       </c>
       <c r="E574" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -15292,7 +15331,7 @@
         <v>usa</v>
       </c>
       <c r="E575" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -15313,7 +15352,7 @@
         <v>usa</v>
       </c>
       <c r="E576" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -15334,7 +15373,7 @@
         <v>usa</v>
       </c>
       <c r="E577" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -15355,7 +15394,7 @@
         <v>usa</v>
       </c>
       <c r="E578" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -15376,7 +15415,7 @@
         <v>usa</v>
       </c>
       <c r="E579" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -15397,7 +15436,7 @@
         <v>usa</v>
       </c>
       <c r="E580" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -15418,7 +15457,7 @@
         <v>usa</v>
       </c>
       <c r="E581" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -15439,7 +15478,7 @@
         <v>usa</v>
       </c>
       <c r="E582" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -15460,7 +15499,7 @@
         <v>usa</v>
       </c>
       <c r="E583" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -15481,7 +15520,7 @@
         <v>usa</v>
       </c>
       <c r="E584" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -15502,7 +15541,7 @@
         <v>usa</v>
       </c>
       <c r="E585" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -15523,7 +15562,7 @@
         <v>usa</v>
       </c>
       <c r="E586" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -15544,7 +15583,7 @@
         <v>usa</v>
       </c>
       <c r="E587" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -15565,7 +15604,7 @@
         <v>usa</v>
       </c>
       <c r="E588" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -15586,7 +15625,7 @@
         <v>usa</v>
       </c>
       <c r="E589" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -15607,7 +15646,7 @@
         <v>usa</v>
       </c>
       <c r="E590" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -15628,7 +15667,7 @@
         <v>usa</v>
       </c>
       <c r="E591" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -15649,7 +15688,7 @@
         <v>usa</v>
       </c>
       <c r="E592" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -15670,7 +15709,7 @@
         <v>usa</v>
       </c>
       <c r="E593" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -15691,7 +15730,7 @@
         <v>ireland</v>
       </c>
       <c r="E594" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -15712,7 +15751,7 @@
         <v>ireland</v>
       </c>
       <c r="E595" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -15733,7 +15772,7 @@
         <v>ireland</v>
       </c>
       <c r="E596" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -15754,7 +15793,7 @@
         <v>ireland</v>
       </c>
       <c r="E597" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -15775,7 +15814,7 @@
         <v>ireland</v>
       </c>
       <c r="E598" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -15796,7 +15835,7 @@
         <v>ireland</v>
       </c>
       <c r="E599" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -15817,7 +15856,7 @@
         <v>ireland</v>
       </c>
       <c r="E600" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -15838,7 +15877,7 @@
         <v>ireland</v>
       </c>
       <c r="E601" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -15859,7 +15898,7 @@
         <v>ireland</v>
       </c>
       <c r="E602" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -15880,7 +15919,7 @@
         <v>ireland</v>
       </c>
       <c r="E603" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -15901,7 +15940,7 @@
         <v>egypt</v>
       </c>
       <c r="E604" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -15922,7 +15961,7 @@
         <v>egypt</v>
       </c>
       <c r="E605" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -15943,7 +15982,7 @@
         <v>egypt</v>
       </c>
       <c r="E606" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -15964,7 +16003,7 @@
         <v>egypt</v>
       </c>
       <c r="E607" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -15985,7 +16024,7 @@
         <v>egypt</v>
       </c>
       <c r="E608" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -16006,7 +16045,7 @@
         <v>egypt</v>
       </c>
       <c r="E609" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -16027,7 +16066,7 @@
         <v>egypt</v>
       </c>
       <c r="E610" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -16048,7 +16087,7 @@
         <v>egypt</v>
       </c>
       <c r="E611" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -16069,7 +16108,7 @@
         <v>egypt</v>
       </c>
       <c r="E612" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -16090,7 +16129,7 @@
         <v>egypt</v>
       </c>
       <c r="E613" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -16111,7 +16150,7 @@
         <v>egypt</v>
       </c>
       <c r="E614" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -16132,7 +16171,7 @@
         <v>egypt</v>
       </c>
       <c r="E615" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -16153,7 +16192,7 @@
         <v>egypt</v>
       </c>
       <c r="E616" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -16174,7 +16213,7 @@
         <v>egypt</v>
       </c>
       <c r="E617" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -16195,7 +16234,7 @@
         <v>egypt</v>
       </c>
       <c r="E618" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -16216,7 +16255,7 @@
         <v>egypt</v>
       </c>
       <c r="E619" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -16237,7 +16276,7 @@
         <v>egypt</v>
       </c>
       <c r="E620" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -16258,7 +16297,7 @@
         <v>egypt</v>
       </c>
       <c r="E621" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -16279,7 +16318,7 @@
         <v>egypt</v>
       </c>
       <c r="E622" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -16300,7 +16339,7 @@
         <v>egypt</v>
       </c>
       <c r="E623" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -16321,7 +16360,7 @@
         <v>cyprus</v>
       </c>
       <c r="E624" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -16342,7 +16381,7 @@
         <v>cyprus</v>
       </c>
       <c r="E625" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -16363,7 +16402,7 @@
         <v>cyprus</v>
       </c>
       <c r="E626" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -16384,7 +16423,7 @@
         <v>cyprus</v>
       </c>
       <c r="E627" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -16405,7 +16444,7 @@
         <v>cyprus</v>
       </c>
       <c r="E628" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -16426,7 +16465,7 @@
         <v>cyprus</v>
       </c>
       <c r="E629" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -16447,7 +16486,7 @@
         <v>cyprus</v>
       </c>
       <c r="E630" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -16468,7 +16507,7 @@
         <v>cyprus</v>
       </c>
       <c r="E631" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -16489,7 +16528,7 @@
         <v>cyprus</v>
       </c>
       <c r="E632" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -16510,7 +16549,7 @@
         <v>cyprus</v>
       </c>
       <c r="E633" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -16531,7 +16570,7 @@
         <v>cyprus</v>
       </c>
       <c r="E634" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -16552,7 +16591,7 @@
         <v>cyprus</v>
       </c>
       <c r="E635" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -16573,7 +16612,7 @@
         <v>cyprus</v>
       </c>
       <c r="E636" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -16594,7 +16633,7 @@
         <v>cyprus</v>
       </c>
       <c r="E637" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -16615,7 +16654,7 @@
         <v>hungary</v>
       </c>
       <c r="E638" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -16636,7 +16675,7 @@
         <v>hungary</v>
       </c>
       <c r="E639" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -16657,7 +16696,7 @@
         <v>hungary</v>
       </c>
       <c r="E640" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -16678,7 +16717,7 @@
         <v>hungary</v>
       </c>
       <c r="E641" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -16699,7 +16738,7 @@
         <v>hungary</v>
       </c>
       <c r="E642" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -16720,7 +16759,7 @@
         <v>hungary</v>
       </c>
       <c r="E643" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -16741,7 +16780,7 @@
         <v>hungary</v>
       </c>
       <c r="E644" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -16762,7 +16801,7 @@
         <v>hungary</v>
       </c>
       <c r="E645" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -16783,7 +16822,7 @@
         <v>hungary</v>
       </c>
       <c r="E646" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -16804,7 +16843,7 @@
         <v>hungary</v>
       </c>
       <c r="E647" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -16825,7 +16864,7 @@
         <v>hungary</v>
       </c>
       <c r="E648" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -16846,7 +16885,7 @@
         <v>hungary</v>
       </c>
       <c r="E649" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -16867,7 +16906,7 @@
         <v>uruguay</v>
       </c>
       <c r="E650" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -16888,7 +16927,7 @@
         <v>uruguay</v>
       </c>
       <c r="E651" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -16909,7 +16948,7 @@
         <v>uruguay</v>
       </c>
       <c r="E652" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -16930,7 +16969,7 @@
         <v>uruguay</v>
       </c>
       <c r="E653" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -16951,7 +16990,7 @@
         <v>uruguay</v>
       </c>
       <c r="E654" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -16972,7 +17011,7 @@
         <v>uruguay</v>
       </c>
       <c r="E655" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -16993,7 +17032,7 @@
         <v>uruguay</v>
       </c>
       <c r="E656" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -17014,7 +17053,7 @@
         <v>uruguay</v>
       </c>
       <c r="E657" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -17035,7 +17074,7 @@
         <v>uruguay</v>
       </c>
       <c r="E658" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -17056,7 +17095,7 @@
         <v>uruguay</v>
       </c>
       <c r="E659" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -17077,7 +17116,7 @@
         <v>uruguay</v>
       </c>
       <c r="E660" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -17098,7 +17137,7 @@
         <v>uruguay</v>
       </c>
       <c r="E661" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -17119,7 +17158,7 @@
         <v>uruguay</v>
       </c>
       <c r="E662" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -17140,7 +17179,7 @@
         <v>uruguay</v>
       </c>
       <c r="E663" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -17161,7 +17200,7 @@
         <v>uruguay</v>
       </c>
       <c r="E664" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -17182,7 +17221,7 @@
         <v>uruguay</v>
       </c>
       <c r="E665" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -17203,7 +17242,7 @@
         <v>ukraine</v>
       </c>
       <c r="E666" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -17224,7 +17263,7 @@
         <v>ukraine</v>
       </c>
       <c r="E667" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -17245,7 +17284,7 @@
         <v>ukraine</v>
       </c>
       <c r="E668" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -17266,7 +17305,7 @@
         <v>ukraine</v>
       </c>
       <c r="E669" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -17287,7 +17326,7 @@
         <v>ukraine</v>
       </c>
       <c r="E670" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -17308,7 +17347,7 @@
         <v>ukraine</v>
       </c>
       <c r="E671" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -17329,7 +17368,7 @@
         <v>ukraine</v>
       </c>
       <c r="E672" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -17350,7 +17389,7 @@
         <v>ukraine</v>
       </c>
       <c r="E673" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -17371,7 +17410,7 @@
         <v>ukraine</v>
       </c>
       <c r="E674" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -17392,7 +17431,7 @@
         <v>ukraine</v>
       </c>
       <c r="E675" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -17413,7 +17452,7 @@
         <v>ukraine</v>
       </c>
       <c r="E676" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -17434,7 +17473,7 @@
         <v>ukraine</v>
       </c>
       <c r="E677" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -17455,7 +17494,7 @@
         <v>ukraine</v>
       </c>
       <c r="E678" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -17476,7 +17515,7 @@
         <v>ukraine</v>
       </c>
       <c r="E679" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -17497,7 +17536,7 @@
         <v>ukraine</v>
       </c>
       <c r="E680" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -17518,7 +17557,7 @@
         <v>ukraine</v>
       </c>
       <c r="E681" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -17539,7 +17578,7 @@
         <v>japan</v>
       </c>
       <c r="E682" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -17560,7 +17599,7 @@
         <v>japan</v>
       </c>
       <c r="E683" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -17581,7 +17620,7 @@
         <v>japan</v>
       </c>
       <c r="E684" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -17602,7 +17641,7 @@
         <v>japan</v>
       </c>
       <c r="E685" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -17623,7 +17662,7 @@
         <v>japan</v>
       </c>
       <c r="E686" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -17644,7 +17683,7 @@
         <v>japan</v>
       </c>
       <c r="E687" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -17665,7 +17704,7 @@
         <v>japan</v>
       </c>
       <c r="E688" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -17686,7 +17725,7 @@
         <v>japan</v>
       </c>
       <c r="E689" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -17707,7 +17746,7 @@
         <v>japan</v>
       </c>
       <c r="E690" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -17728,7 +17767,7 @@
         <v>japan</v>
       </c>
       <c r="E691" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -17749,7 +17788,7 @@
         <v>japan</v>
       </c>
       <c r="E692" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -17770,7 +17809,7 @@
         <v>japan</v>
       </c>
       <c r="E693" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -17791,7 +17830,7 @@
         <v>japan</v>
       </c>
       <c r="E694" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -17812,7 +17851,7 @@
         <v>japan</v>
       </c>
       <c r="E695" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -17833,7 +17872,7 @@
         <v>japan</v>
       </c>
       <c r="E696" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -17854,7 +17893,7 @@
         <v>japan</v>
       </c>
       <c r="E697" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -17875,7 +17914,7 @@
         <v>japan</v>
       </c>
       <c r="E698" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -17896,7 +17935,7 @@
         <v>japan</v>
       </c>
       <c r="E699" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -17917,7 +17956,7 @@
         <v>japan</v>
       </c>
       <c r="E700" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -17938,7 +17977,7 @@
         <v>japan</v>
       </c>
       <c r="E701" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -17959,7 +17998,7 @@
         <v>south-korea</v>
       </c>
       <c r="E702" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -17980,7 +18019,7 @@
         <v>south-korea</v>
       </c>
       <c r="E703" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -18001,7 +18040,7 @@
         <v>south-korea</v>
       </c>
       <c r="E704" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -18022,7 +18061,7 @@
         <v>south-korea</v>
       </c>
       <c r="E705" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -18043,7 +18082,7 @@
         <v>south-korea</v>
       </c>
       <c r="E706" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -18064,7 +18103,7 @@
         <v>south-korea</v>
       </c>
       <c r="E707" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -18085,7 +18124,7 @@
         <v>south-korea</v>
       </c>
       <c r="E708" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -18106,7 +18145,7 @@
         <v>south-korea</v>
       </c>
       <c r="E709" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -18127,7 +18166,7 @@
         <v>south-korea</v>
       </c>
       <c r="E710" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -18148,7 +18187,7 @@
         <v>south-korea</v>
       </c>
       <c r="E711" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -18169,7 +18208,7 @@
         <v>south-korea</v>
       </c>
       <c r="E712" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -18190,7 +18229,7 @@
         <v>south-korea</v>
       </c>
       <c r="E713" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -18211,7 +18250,7 @@
         <v>china</v>
       </c>
       <c r="E714" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -18232,7 +18271,7 @@
         <v>china</v>
       </c>
       <c r="E715" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -18253,7 +18292,7 @@
         <v>china</v>
       </c>
       <c r="E716" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -18274,7 +18313,7 @@
         <v>china</v>
       </c>
       <c r="E717" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -18295,7 +18334,7 @@
         <v>china</v>
       </c>
       <c r="E718" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -18316,7 +18355,7 @@
         <v>china</v>
       </c>
       <c r="E719" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -18337,7 +18376,7 @@
         <v>china</v>
       </c>
       <c r="E720" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -18358,7 +18397,7 @@
         <v>china</v>
       </c>
       <c r="E721" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -18379,7 +18418,7 @@
         <v>china</v>
       </c>
       <c r="E722" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -18400,7 +18439,7 @@
         <v>china</v>
       </c>
       <c r="E723" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -18421,7 +18460,7 @@
         <v>china</v>
       </c>
       <c r="E724" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -18442,7 +18481,7 @@
         <v>china</v>
       </c>
       <c r="E725" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -18463,7 +18502,7 @@
         <v>china</v>
       </c>
       <c r="E726" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -18484,7 +18523,7 @@
         <v>china</v>
       </c>
       <c r="E727" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -18505,7 +18544,7 @@
         <v>china</v>
       </c>
       <c r="E728" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
@@ -18526,13 +18565,13 @@
         <v>china</v>
       </c>
       <c r="E729" s="8" t="str">
-        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[PAIS]],$H$2:$I$34,2)="x","SI","NO")</f>
+        <f ca="1">IF(VLOOKUP(Tabla1[[#This Row],[DIVISION]],$H$2:$I$44,2)="X","SI","NO")</f>
         <v>SI</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="K2:K41">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="act">
+  <conditionalFormatting sqref="K2:K44">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="act">
       <formula>NOT(ISERROR(SEARCH("act",K2)))</formula>
     </cfRule>
   </conditionalFormatting>
